--- a/reports/latest_one_month_follow_up.xlsx
+++ b/reports/latest_one_month_follow_up.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="TAKIP_OZETI" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="POZISYONLAR" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="GUNLUK_TAKIP" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="NOTLAR" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TAKIP_OZETI" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="POZISYONLAR" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GUNLUK_TAKIP" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NOTLAR" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'TAKIP_OZETI'!$A$1:$B$16</definedName>
@@ -27,16 +27,13 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="YYYY-MM-DD HH:MM:SS"/>
   </numFmts>
-  <fonts count="3">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
     <font>
       <b val="1"/>
@@ -56,7 +53,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -64,23 +61,14 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -464,186 +452,186 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="29" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="3" t="inlineStr">
+      <c r="A1" s="2" t="inlineStr">
         <is>
           <t>Alan</t>
         </is>
       </c>
-      <c r="B1" s="3" t="inlineStr">
+      <c r="B1" s="2" t="inlineStr">
         <is>
           <t>Değer</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="4" t="inlineStr">
+      <c r="A2" s="3" t="inlineStr">
         <is>
           <t>Rapor Tarihi</t>
         </is>
       </c>
-      <c r="B2" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="inlineStr">
+      <c r="A3" s="3" t="inlineStr">
         <is>
           <t>Strateji</t>
         </is>
       </c>
-      <c r="B3" s="4" t="inlineStr">
+      <c r="B3" s="3" t="inlineStr">
         <is>
           <t>Top3 Ranking Only</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="3" t="inlineStr">
         <is>
           <t>Rejim Durumu</t>
         </is>
       </c>
-      <c r="B4" s="4" t="inlineStr">
+      <c r="B4" s="3" t="inlineStr">
         <is>
           <t>ABOVE_MA200_RISK_ON</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="3" t="inlineStr">
         <is>
           <t>BIST100 Kapanış</t>
         </is>
       </c>
-      <c r="B5" s="4" t="n">
-        <v>13704</v>
+      <c r="B5" s="3" t="n">
+        <v>14729.7001953125</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="inlineStr">
+      <c r="A6" s="3" t="inlineStr">
         <is>
           <t>Portföy Başlangıç Değeri</t>
         </is>
       </c>
-      <c r="B6" s="4" t="n">
+      <c r="B6" s="3" t="n">
         <v>100000</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="inlineStr">
+      <c r="A7" s="3" t="inlineStr">
         <is>
           <t>Seçilen 3 Hisse</t>
         </is>
       </c>
-      <c r="B7" s="4" t="inlineStr">
-        <is>
-          <t>EREGL.IS, SISE.IS, BIMAS.IS</t>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>AKBNK.IS, YKBNK.IS, BIMAS.IS</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="4" t="inlineStr">
+      <c r="A8" s="3" t="inlineStr">
         <is>
           <t>Eşit Ağırlık</t>
         </is>
       </c>
-      <c r="B8" s="4" t="inlineStr">
+      <c r="B8" s="3" t="inlineStr">
         <is>
           <t>33.33% / 33.33% / 33.33%</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="inlineStr">
+      <c r="A9" s="3" t="inlineStr">
         <is>
           <t>Başlangıç Tarihi</t>
         </is>
       </c>
-      <c r="B9" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="4" t="inlineStr">
+      <c r="A10" s="3" t="inlineStr">
         <is>
           <t>Güncel Fiyat Tarihi</t>
         </is>
       </c>
-      <c r="B10" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="4" t="inlineStr">
+      <c r="A11" s="3" t="inlineStr">
         <is>
           <t>BIST100 Başlangıç Tarihi</t>
         </is>
       </c>
-      <c r="B11" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="4" t="inlineStr">
+      <c r="A12" s="3" t="inlineStr">
         <is>
           <t>BIST100 Güncel Tarihi</t>
         </is>
       </c>
-      <c r="B12" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="4" t="inlineStr">
+      <c r="A13" s="3" t="inlineStr">
         <is>
           <t>Portföy Toplam Getiri</t>
         </is>
       </c>
-      <c r="B13" s="4" t="n">
+      <c r="B13" s="3" t="n">
         <v>-1.110223024625157e-16</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="4" t="inlineStr">
+      <c r="A14" s="3" t="inlineStr">
         <is>
           <t>BIST100 Getiri</t>
         </is>
       </c>
-      <c r="B14" s="4" t="n">
+      <c r="B14" s="3" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="4" t="inlineStr">
+      <c r="A15" s="3" t="inlineStr">
         <is>
           <t>BIST100'e Göre Fark</t>
         </is>
       </c>
-      <c r="B15" s="4" t="n">
+      <c r="B15" s="3" t="n">
         <v>-1.110223024625157e-16</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="4" t="inlineStr">
+      <c r="A16" s="3" t="inlineStr">
         <is>
           <t>Durum</t>
         </is>
       </c>
-      <c r="B16" s="4" t="inlineStr">
+      <c r="B16" s="3" t="inlineStr">
         <is>
           <t>Zararda / BIST Altı</t>
         </is>
@@ -666,8 +654,8 @@
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
     <col width="19" customWidth="1" min="6" max="6"/>
     <col width="19" customWidth="1" min="7" max="7"/>
@@ -675,128 +663,128 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="3" t="inlineStr">
+      <c r="A1" s="2" t="inlineStr">
         <is>
           <t>Hisse</t>
         </is>
       </c>
-      <c r="B1" s="3" t="inlineStr">
+      <c r="B1" s="2" t="inlineStr">
         <is>
           <t>Ağırlık %</t>
         </is>
       </c>
-      <c r="C1" s="3" t="inlineStr">
+      <c r="C1" s="2" t="inlineStr">
         <is>
           <t>Başlangıç Fiyatı</t>
         </is>
       </c>
-      <c r="D1" s="3" t="inlineStr">
+      <c r="D1" s="2" t="inlineStr">
         <is>
           <t>Güncel Fiyat</t>
         </is>
       </c>
-      <c r="E1" s="3" t="inlineStr">
+      <c r="E1" s="2" t="inlineStr">
         <is>
           <t>Getiri %</t>
         </is>
       </c>
-      <c r="F1" s="3" t="inlineStr">
+      <c r="F1" s="2" t="inlineStr">
         <is>
           <t>Başlangıç Tutarı</t>
         </is>
       </c>
-      <c r="G1" s="3" t="inlineStr">
+      <c r="G1" s="2" t="inlineStr">
         <is>
           <t>Güncel Tutar</t>
         </is>
       </c>
-      <c r="H1" s="3" t="inlineStr">
+      <c r="H1" s="2" t="inlineStr">
         <is>
           <t>Kar/Zarar TL</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="4" t="inlineStr">
-        <is>
-          <t>EREGL.IS</t>
-        </is>
-      </c>
-      <c r="B2" s="5" t="n">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>AKBNK.IS</t>
+        </is>
+      </c>
+      <c r="B2" s="4" t="n">
         <v>0.3333333333333333</v>
       </c>
-      <c r="C2" s="6" t="n">
-        <v>40</v>
-      </c>
-      <c r="D2" s="6" t="n">
-        <v>40</v>
-      </c>
-      <c r="E2" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F2" s="6" t="n">
+      <c r="C2" s="5" t="n">
+        <v>82</v>
+      </c>
+      <c r="D2" s="5" t="n">
+        <v>82</v>
+      </c>
+      <c r="E2" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" s="5" t="n">
         <v>33333.33333333333</v>
       </c>
-      <c r="G2" s="6" t="n">
+      <c r="G2" s="5" t="n">
         <v>33333.33333333333</v>
       </c>
-      <c r="H2" s="6" t="n">
+      <c r="H2" s="5" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>SISE.IS</t>
-        </is>
-      </c>
-      <c r="B3" s="5" t="n">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>YKBNK.IS</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="n">
         <v>0.3333333333333333</v>
       </c>
-      <c r="C3" s="6" t="n">
-        <v>45.5</v>
-      </c>
-      <c r="D3" s="6" t="n">
-        <v>45.5</v>
-      </c>
-      <c r="E3" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F3" s="6" t="n">
+      <c r="C3" s="5" t="n">
+        <v>43.84000015258789</v>
+      </c>
+      <c r="D3" s="5" t="n">
+        <v>43.84000015258789</v>
+      </c>
+      <c r="E3" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" s="5" t="n">
         <v>33333.33333333333</v>
       </c>
-      <c r="G3" s="6" t="n">
+      <c r="G3" s="5" t="n">
         <v>33333.33333333333</v>
       </c>
-      <c r="H3" s="6" t="n">
+      <c r="H3" s="5" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="3" t="inlineStr">
         <is>
           <t>BIMAS.IS</t>
         </is>
       </c>
-      <c r="B4" s="5" t="n">
+      <c r="B4" s="4" t="n">
         <v>0.3333333333333333</v>
       </c>
-      <c r="C4" s="6" t="n">
-        <v>371.25</v>
-      </c>
-      <c r="D4" s="6" t="n">
-        <v>371.25</v>
-      </c>
-      <c r="E4" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F4" s="6" t="n">
+      <c r="C4" s="5" t="n">
+        <v>379</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>379</v>
+      </c>
+      <c r="E4" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" s="5" t="n">
         <v>33333.33333333333</v>
       </c>
-      <c r="G4" s="6" t="n">
+      <c r="G4" s="5" t="n">
         <v>33333.33333333333</v>
       </c>
-      <c r="H4" s="6" t="n">
+      <c r="H4" s="5" t="n">
         <v>0</v>
       </c>
     </row>
@@ -819,68 +807,68 @@
     <col width="16" customWidth="1" min="2" max="2"/>
     <col width="17" customWidth="1" min="3" max="3"/>
     <col width="17" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
     <col width="18" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="3" t="inlineStr">
+      <c r="A1" s="2" t="inlineStr">
         <is>
           <t>Tarih</t>
         </is>
       </c>
-      <c r="B1" s="3" t="inlineStr">
+      <c r="B1" s="2" t="inlineStr">
         <is>
           <t>Portföy Değeri</t>
         </is>
       </c>
-      <c r="C1" s="3" t="inlineStr">
+      <c r="C1" s="2" t="inlineStr">
         <is>
           <t>Günlük Getiri %</t>
         </is>
       </c>
-      <c r="D1" s="3" t="inlineStr">
+      <c r="D1" s="2" t="inlineStr">
         <is>
           <t>Toplam Getiri %</t>
         </is>
       </c>
-      <c r="E1" s="3" t="inlineStr">
+      <c r="E1" s="2" t="inlineStr">
         <is>
           <t>BIST100 Değeri</t>
         </is>
       </c>
-      <c r="F1" s="3" t="inlineStr">
+      <c r="F1" s="2" t="inlineStr">
         <is>
           <t>BIST100 Getiri %</t>
         </is>
       </c>
-      <c r="G1" s="3" t="inlineStr">
+      <c r="G1" s="2" t="inlineStr">
         <is>
           <t>Fark %</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="7" t="n">
-        <v>46174</v>
-      </c>
-      <c r="B2" s="6" t="n">
+      <c r="A2" s="6" t="n">
+        <v>46195</v>
+      </c>
+      <c r="B2" s="5" t="n">
         <v>100000</v>
       </c>
-      <c r="C2" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2" s="6" t="n">
-        <v>13704</v>
-      </c>
-      <c r="F2" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G2" s="5" t="n">
+      <c r="C2" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2" s="5" t="n">
+        <v>14729.7001953125</v>
+      </c>
+      <c r="F2" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -903,42 +891,42 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="3" t="inlineStr">
+      <c r="A1" s="2" t="inlineStr">
         <is>
           <t>Notlar</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="4" t="inlineStr">
+      <c r="A2" s="3" t="inlineStr">
         <is>
           <t>Bu dosya araştırma dosyası değildir.</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="inlineStr">
+      <c r="A3" s="3" t="inlineStr">
         <is>
           <t>Bir aylık takip dosyasıdır.</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="3" t="inlineStr">
         <is>
           <t>Alım/satım önerisi değildir.</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="3" t="inlineStr">
         <is>
           <t>Amaç stratejinin BIST100’e göre performansını takip etmektir.</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="inlineStr">
+      <c r="A6" s="3" t="inlineStr">
         <is>
           <t>Bir ay boyunca aynı 3 hisse takip edilir.</t>
         </is>

--- a/reports/latest_one_month_follow_up.xlsx
+++ b/reports/latest_one_month_follow_up.xlsx
@@ -13,10 +13,10 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NOTLAR" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'TAKIP_OZETI'!$A$1:$B$16</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'TAKIP_OZETI'!$A$1:$B$19</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'POZISYONLAR'!$A$1:$H$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'GUNLUK_TAKIP'!$A$1:$G$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'NOTLAR'!$A$1:$A$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'GUNLUK_TAKIP'!$A$1:$G$17</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'NOTLAR'!$A$1:$A$7</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -448,11 +448,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B16"/>
+  <dimension ref="A1:B19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="29" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -482,163 +482,199 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Strateji</t>
+          <t>Takip Modu</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>Top3 Ranking Only</t>
+          <t>Sabit portföy</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>Rejim Durumu</t>
+          <t>Strateji</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>ABOVE_MA200_RISK_ON</t>
+          <t>Top3 Ranking Only</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>BIST100 Kapanış</t>
-        </is>
-      </c>
-      <c r="B5" s="3" t="n">
-        <v>14729.7001953125</v>
+          <t>Başlangıç Modeli</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>volume_heavy</t>
+        </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>Portföy Başlangıç Değeri</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="n">
-        <v>100000</v>
+          <t>Başlangıç Rejim Durumu</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>ABOVE_MA200_RISK_ON</t>
+        </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>Seçilen 3 Hisse</t>
+          <t>Güncel Rejim Durumu</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>AKBNK.IS, YKBNK.IS, BIMAS.IS</t>
+          <t>ABOVE_MA200_RISK_ON</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>Eşit Ağırlık</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>33.33% / 33.33% / 33.33%</t>
-        </is>
+          <t>BIST100 Kapanış</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="n">
+        <v>14729.7001953125</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>Başlangıç Tarihi</t>
-        </is>
-      </c>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>2026-06-22</t>
-        </is>
+          <t>Portföy Başlangıç Değeri</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="n">
+        <v>100000</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>Güncel Fiyat Tarihi</t>
+          <t>Seçilen 3 Hisse</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>EREGL.IS, SISE.IS, BIMAS.IS</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>BIST100 Başlangıç Tarihi</t>
+          <t>Eşit Ağırlık</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>33.33% / 33.33% / 33.33%</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>BIST100 Güncel Tarihi</t>
+          <t>Başlangıç Tarihi</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-01</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>Portföy Toplam Getiri</t>
-        </is>
-      </c>
-      <c r="B13" s="3" t="n">
-        <v>-1.110223024625157e-16</v>
+          <t>Güncel Fiyat Tarihi</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>BIST100 Getiri</t>
-        </is>
-      </c>
-      <c r="B14" s="3" t="n">
-        <v>0</v>
+          <t>BIST100 Başlangıç Tarihi</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>BIST100'e Göre Fark</t>
-        </is>
-      </c>
-      <c r="B15" s="3" t="n">
-        <v>-1.110223024625157e-16</v>
+          <t>BIST100 Güncel Tarihi</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
+          <t>Portföy Toplam Getiri</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="n">
+        <v>0.01579913200164529</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>BIST100 Getiri</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="n">
+        <v>0.07484677432227826</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>BIST100'e Göre Fark</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="n">
+        <v>-0.05904764232063298</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
           <t>Durum</t>
         </is>
       </c>
-      <c r="B16" s="3" t="inlineStr">
-        <is>
-          <t>Zararda / BIST Altı</t>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>Karda / BIST Altı</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:B16"/>
+  <autoFilter ref="A1:B19"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -654,12 +690,12 @@
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="19" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
     <col width="19" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
     <col width="19" customWidth="1" min="6" max="6"/>
     <col width="19" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="19" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -707,57 +743,57 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>AKBNK.IS</t>
+          <t>EREGL.IS</t>
         </is>
       </c>
       <c r="B2" s="4" t="n">
         <v>0.3333333333333333</v>
       </c>
       <c r="C2" s="5" t="n">
-        <v>82</v>
+        <v>40</v>
       </c>
       <c r="D2" s="5" t="n">
-        <v>82</v>
+        <v>40.34000015258789</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>0</v>
+        <v>0.008500003814697177</v>
       </c>
       <c r="F2" s="5" t="n">
         <v>33333.33333333333</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>33333.33333333333</v>
+        <v>33616.66679382323</v>
       </c>
       <c r="H2" s="5" t="n">
-        <v>0</v>
+        <v>283.3334604899064</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>YKBNK.IS</t>
+          <t>SISE.IS</t>
         </is>
       </c>
       <c r="B3" s="4" t="n">
         <v>0.3333333333333333</v>
       </c>
       <c r="C3" s="5" t="n">
-        <v>43.84000015258789</v>
+        <v>45.5</v>
       </c>
       <c r="D3" s="5" t="n">
-        <v>43.84000015258789</v>
+        <v>46.31999969482422</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>0</v>
+        <v>0.01802197131481797</v>
       </c>
       <c r="F3" s="5" t="n">
         <v>33333.33333333333</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>33333.33333333333</v>
+        <v>33934.06571049393</v>
       </c>
       <c r="H3" s="5" t="n">
-        <v>0</v>
+        <v>600.7323771606025</v>
       </c>
     </row>
     <row r="4">
@@ -770,22 +806,22 @@
         <v>0.3333333333333333</v>
       </c>
       <c r="C4" s="5" t="n">
-        <v>379</v>
+        <v>371.25</v>
       </c>
       <c r="D4" s="5" t="n">
         <v>379</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>0</v>
+        <v>0.02087542087542094</v>
       </c>
       <c r="F4" s="5" t="n">
         <v>33333.33333333333</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>33333.33333333333</v>
+        <v>34029.18069584736</v>
       </c>
       <c r="H4" s="5" t="n">
-        <v>0</v>
+        <v>695.8473625140323</v>
       </c>
     </row>
   </sheetData>
@@ -800,16 +836,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:G17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="17" customWidth="1" min="3" max="3"/>
-    <col width="17" customWidth="1" min="4" max="4"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
+    <col width="23" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="24" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -851,7 +887,7 @@
     </row>
     <row r="2">
       <c r="A2" s="6" t="n">
-        <v>46195</v>
+        <v>46174</v>
       </c>
       <c r="B2" s="5" t="n">
         <v>100000</v>
@@ -863,7 +899,7 @@
         <v>0</v>
       </c>
       <c r="E2" s="5" t="n">
-        <v>14729.7001953125</v>
+        <v>13704</v>
       </c>
       <c r="F2" s="4" t="n">
         <v>0</v>
@@ -872,8 +908,353 @@
         <v>0</v>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" s="6" t="n">
+        <v>46175</v>
+      </c>
+      <c r="B3" s="5" t="n">
+        <v>102223.0027697347</v>
+      </c>
+      <c r="C3" s="4" t="n">
+        <v>0.02223002769734705</v>
+      </c>
+      <c r="D3" s="4" t="n">
+        <v>0.02223002769734705</v>
+      </c>
+      <c r="E3" s="5" t="n">
+        <v>14200.2001953125</v>
+      </c>
+      <c r="F3" s="4" t="n">
+        <v>0.03620842055695417</v>
+      </c>
+      <c r="G3" s="4" t="n">
+        <v>-0.01397839285960711</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="6" t="n">
+        <v>46176</v>
+      </c>
+      <c r="B4" s="5" t="n">
+        <v>101548.9054270188</v>
+      </c>
+      <c r="C4" s="4" t="n">
+        <v>-0.006594380173260195</v>
+      </c>
+      <c r="D4" s="4" t="n">
+        <v>0.01548905427018843</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>13965.7001953125</v>
+      </c>
+      <c r="F4" s="4" t="n">
+        <v>0.01909662837948778</v>
+      </c>
+      <c r="G4" s="4" t="n">
+        <v>-0.00360757410929935</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="6" t="n">
+        <v>46177</v>
+      </c>
+      <c r="B5" s="5" t="n">
+        <v>100052.2803667449</v>
+      </c>
+      <c r="C5" s="4" t="n">
+        <v>-0.01473797333393734</v>
+      </c>
+      <c r="D5" s="4" t="n">
+        <v>0.0005228036674491676</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>13872.2998046875</v>
+      </c>
+      <c r="F5" s="4" t="n">
+        <v>0.01228107156213509</v>
+      </c>
+      <c r="G5" s="4" t="n">
+        <v>-0.01175826789468593</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="6" t="n">
+        <v>46178</v>
+      </c>
+      <c r="B6" s="5" t="n">
+        <v>99150.39483732327</v>
+      </c>
+      <c r="C6" s="4" t="n">
+        <v>-0.009014142667371106</v>
+      </c>
+      <c r="D6" s="4" t="n">
+        <v>-0.008496051626767365</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>13694.2001953125</v>
+      </c>
+      <c r="F6" s="4" t="n">
+        <v>-0.0007151054208625052</v>
+      </c>
+      <c r="G6" s="4" t="n">
+        <v>-0.00778094620590486</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="n">
+        <v>46181</v>
+      </c>
+      <c r="B7" s="5" t="n">
+        <v>99194.90173474306</v>
+      </c>
+      <c r="C7" s="4" t="n">
+        <v>0.000448882704832565</v>
+      </c>
+      <c r="D7" s="4" t="n">
+        <v>-0.008050982652569316</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>13860.599609375</v>
+      </c>
+      <c r="F7" s="4" t="n">
+        <v>0.01142729198591641</v>
+      </c>
+      <c r="G7" s="4" t="n">
+        <v>-0.01947827463848573</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="6" t="n">
+        <v>46182</v>
+      </c>
+      <c r="B8" s="5" t="n">
+        <v>98960.65707117392</v>
+      </c>
+      <c r="C8" s="4" t="n">
+        <v>-0.002361458698709518</v>
+      </c>
+      <c r="D8" s="4" t="n">
+        <v>-0.01039342928826081</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>13741.900390625</v>
+      </c>
+      <c r="F8" s="4" t="n">
+        <v>0.002765644383026844</v>
+      </c>
+      <c r="G8" s="4" t="n">
+        <v>-0.01315907367128766</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="6" t="n">
+        <v>46183</v>
+      </c>
+      <c r="B9" s="5" t="n">
+        <v>98567.79623824963</v>
+      </c>
+      <c r="C9" s="4" t="n">
+        <v>-0.003969868880738581</v>
+      </c>
+      <c r="D9" s="4" t="n">
+        <v>-0.01432203761750372</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>13744.599609375</v>
+      </c>
+      <c r="F9" s="4" t="n">
+        <v>0.002962610141199695</v>
+      </c>
+      <c r="G9" s="4" t="n">
+        <v>-0.01728464775870342</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="6" t="n">
+        <v>46184</v>
+      </c>
+      <c r="B10" s="5" t="n">
+        <v>97972.1929521213</v>
+      </c>
+      <c r="C10" s="4" t="n">
+        <v>-0.006042574845527504</v>
+      </c>
+      <c r="D10" s="4" t="n">
+        <v>-0.02027807047878705</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>13743.5</v>
+      </c>
+      <c r="F10" s="4" t="n">
+        <v>0.00288237011091641</v>
+      </c>
+      <c r="G10" s="4" t="n">
+        <v>-0.02316044058970346</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="6" t="n">
+        <v>46185</v>
+      </c>
+      <c r="B11" s="5" t="n">
+        <v>99533.39140527607</v>
+      </c>
+      <c r="C11" s="4" t="n">
+        <v>0.01593511797697267</v>
+      </c>
+      <c r="D11" s="4" t="n">
+        <v>-0.004666085947239274</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>13938.5</v>
+      </c>
+      <c r="F11" s="4" t="n">
+        <v>0.01711179217746639</v>
+      </c>
+      <c r="G11" s="4" t="n">
+        <v>-0.02177787812470566</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="6" t="n">
+        <v>46188</v>
+      </c>
+      <c r="B12" s="5" t="n">
+        <v>102685.3605150107</v>
+      </c>
+      <c r="C12" s="4" t="n">
+        <v>0.03166745416018824</v>
+      </c>
+      <c r="D12" s="4" t="n">
+        <v>0.02685360515010737</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>14446.400390625</v>
+      </c>
+      <c r="F12" s="4" t="n">
+        <v>0.05417399231063924</v>
+      </c>
+      <c r="G12" s="4" t="n">
+        <v>-0.02732038716053187</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="6" t="n">
+        <v>46189</v>
+      </c>
+      <c r="B13" s="5" t="n">
+        <v>101717.1238252686</v>
+      </c>
+      <c r="C13" s="4" t="n">
+        <v>-0.009429159958985744</v>
+      </c>
+      <c r="D13" s="4" t="n">
+        <v>0.01717123825268585</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>14493.099609375</v>
+      </c>
+      <c r="F13" s="4" t="n">
+        <v>0.05758169945818747</v>
+      </c>
+      <c r="G13" s="4" t="n">
+        <v>-0.04041046120550162</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="6" t="n">
+        <v>46190</v>
+      </c>
+      <c r="B14" s="5" t="n">
+        <v>100070.5429599663</v>
+      </c>
+      <c r="C14" s="4" t="n">
+        <v>-0.01618784333826406</v>
+      </c>
+      <c r="D14" s="4" t="n">
+        <v>0.0007054295996633542</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>14421.2001953125</v>
+      </c>
+      <c r="F14" s="4" t="n">
+        <v>0.05233509889904409</v>
+      </c>
+      <c r="G14" s="4" t="n">
+        <v>-0.05162966929938073</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="6" t="n">
+        <v>46191</v>
+      </c>
+      <c r="B15" s="5" t="n">
+        <v>103232.5710170966</v>
+      </c>
+      <c r="C15" s="4" t="n">
+        <v>0.03159799041357481</v>
+      </c>
+      <c r="D15" s="4" t="n">
+        <v>0.03232571017096575</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>14827.400390625</v>
+      </c>
+      <c r="F15" s="4" t="n">
+        <v>0.08197609388682126</v>
+      </c>
+      <c r="G15" s="4" t="n">
+        <v>-0.04965038371585551</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="6" t="n">
+        <v>46192</v>
+      </c>
+      <c r="B16" s="5" t="n">
+        <v>101665.535802718</v>
+      </c>
+      <c r="C16" s="4" t="n">
+        <v>-0.0151796588900126</v>
+      </c>
+      <c r="D16" s="4" t="n">
+        <v>0.01665535802718043</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>14734.5</v>
+      </c>
+      <c r="F16" s="4" t="n">
+        <v>0.07519702276707529</v>
+      </c>
+      <c r="G16" s="4" t="n">
+        <v>-0.05854166473989486</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="6" t="n">
+        <v>46195</v>
+      </c>
+      <c r="B17" s="5" t="n">
+        <v>101579.9132001645</v>
+      </c>
+      <c r="C17" s="4" t="n">
+        <v>-0.0008421989013038811</v>
+      </c>
+      <c r="D17" s="4" t="n">
+        <v>0.01579913200164529</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>14729.7001953125</v>
+      </c>
+      <c r="F17" s="4" t="n">
+        <v>0.07484677432227826</v>
+      </c>
+      <c r="G17" s="4" t="n">
+        <v>-0.05904764232063298</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G2"/>
+  <autoFilter ref="A1:G17"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -884,7 +1265,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -921,19 +1302,26 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Amaç stratejinin BIST100’e göre performansını takip etmektir.</t>
+          <t>Amaç stratejinin BIST100'e göre performansını takip etmektir.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>Bir ay boyunca aynı 3 hisse takip edilir.</t>
+          <t>Portföy reports/tracking_state.json içinden okunur.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>Sonraki çalıştırmalarda yeni hisse seçilmez.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:A6"/>
+  <autoFilter ref="A1:A7"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/reports/latest_one_month_follow_up.xlsx
+++ b/reports/latest_one_month_follow_up.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TAKIP_OZETI" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="POZISYONLAR" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GUNLUK_TAKIP" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NOTLAR" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="TAKIP_OZETI" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="POZISYONLAR" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="GUNLUK_TAKIP" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="NOTLAR" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'TAKIP_OZETI'!$A$1:$B$19</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'POZISYONLAR'!$A$1:$H$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'GUNLUK_TAKIP'!$A$1:$G$17</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'GUNLUK_TAKIP'!$A$1:$G$18</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'NOTLAR'!$A$1:$A$7</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -546,7 +546,7 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>14729.7001953125</v>
+        <v>14539.599609375</v>
       </c>
     </row>
     <row r="9">
@@ -627,7 +627,7 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
     </row>
@@ -648,7 +648,7 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>0.07484677432227826</v>
+        <v>0.06097486933559537</v>
       </c>
     </row>
     <row r="18">
@@ -658,7 +658,7 @@
         </is>
       </c>
       <c r="B18" s="3" t="n">
-        <v>-0.05904764232063298</v>
+        <v>-0.04517573733395008</v>
       </c>
     </row>
     <row r="19">
@@ -836,7 +836,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G17"/>
+  <dimension ref="A1:G18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -1253,8 +1253,31 @@
         <v>-0.05904764232063298</v>
       </c>
     </row>
+    <row r="18">
+      <c r="A18" s="6" t="n">
+        <v>46196</v>
+      </c>
+      <c r="B18" s="5" t="n">
+        <v>101579.9132001645</v>
+      </c>
+      <c r="C18" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D18" s="4" t="n">
+        <v>0.01579913200164529</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>14539.599609375</v>
+      </c>
+      <c r="F18" s="4" t="n">
+        <v>0.06097486933559537</v>
+      </c>
+      <c r="G18" s="4" t="n">
+        <v>-0.04517573733395008</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G17"/>
+  <autoFilter ref="A1:G18"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/reports/latest_one_month_follow_up.xlsx
+++ b/reports/latest_one_month_follow_up.xlsx
@@ -15,7 +15,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'TAKIP_OZETI'!$A$1:$B$19</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'POZISYONLAR'!$A$1:$H$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'GUNLUK_TAKIP'!$A$1:$G$18</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'GUNLUK_TAKIP'!$A$1:$G$19</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'NOTLAR'!$A$1:$A$7</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -475,7 +475,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-24</t>
         </is>
       </c>
     </row>
@@ -546,7 +546,7 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>14539.599609375</v>
+        <v>14331.2001953125</v>
       </c>
     </row>
     <row r="9">
@@ -603,7 +603,7 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-24</t>
         </is>
       </c>
     </row>
@@ -627,7 +627,7 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>0.01579913200164529</v>
+        <v>-0.0009612897506259266</v>
       </c>
     </row>
     <row r="17">
@@ -648,7 +648,7 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>0.06097486933559537</v>
+        <v>0.04576767332986709</v>
       </c>
     </row>
     <row r="18">
@@ -658,7 +658,7 @@
         </is>
       </c>
       <c r="B18" s="3" t="n">
-        <v>-0.04517573733395008</v>
+        <v>-0.04672896308049301</v>
       </c>
     </row>
     <row r="19">
@@ -669,7 +669,7 @@
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>Karda / BIST Altı</t>
+          <t>Zararda / BIST Altı</t>
         </is>
       </c>
     </row>
@@ -692,10 +692,10 @@
     <col width="20" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
     <col width="19" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="23" customWidth="1" min="5" max="5"/>
     <col width="19" customWidth="1" min="6" max="6"/>
     <col width="19" customWidth="1" min="7" max="7"/>
-    <col width="19" customWidth="1" min="8" max="8"/>
+    <col width="20" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -753,19 +753,19 @@
         <v>40</v>
       </c>
       <c r="D2" s="5" t="n">
-        <v>40.34000015258789</v>
+        <v>39.93999862670898</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>0.008500003814697177</v>
+        <v>-0.001500034332275413</v>
       </c>
       <c r="F2" s="5" t="n">
         <v>33333.33333333333</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>33616.66679382323</v>
+        <v>33283.33218892415</v>
       </c>
       <c r="H2" s="5" t="n">
-        <v>283.3334604899064</v>
+        <v>-50.00114440917969</v>
       </c>
     </row>
     <row r="3">
@@ -781,19 +781,19 @@
         <v>45.5</v>
       </c>
       <c r="D3" s="5" t="n">
-        <v>46.31999969482422</v>
+        <v>45.09999847412109</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>0.01802197131481797</v>
+        <v>-0.008791242327008897</v>
       </c>
       <c r="F3" s="5" t="n">
         <v>33333.33333333333</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>33934.06571049393</v>
+        <v>33040.29192243303</v>
       </c>
       <c r="H3" s="5" t="n">
-        <v>600.7323771606025</v>
+        <v>-293.0414109002959</v>
       </c>
     </row>
     <row r="4">
@@ -809,19 +809,19 @@
         <v>371.25</v>
       </c>
       <c r="D4" s="5" t="n">
-        <v>379</v>
+        <v>374</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>0.02087542087542094</v>
+        <v>0.007407407407407307</v>
       </c>
       <c r="F4" s="5" t="n">
         <v>33333.33333333333</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>34029.18069584736</v>
+        <v>33580.24691358024</v>
       </c>
       <c r="H4" s="5" t="n">
-        <v>695.8473625140323</v>
+        <v>246.91358024691</v>
       </c>
     </row>
   </sheetData>
@@ -836,13 +836,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G18"/>
+  <dimension ref="A1:G19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
     <col width="19" customWidth="1" min="2" max="2"/>
-    <col width="24" customWidth="1" min="3" max="3"/>
-    <col width="23" customWidth="1" min="4" max="4"/>
+    <col width="23" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
     <col width="24" customWidth="1" min="6" max="6"/>
     <col width="22" customWidth="1" min="7" max="7"/>
@@ -1215,10 +1215,10 @@
         <v>101665.535802718</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>-0.0151796588900126</v>
+        <v>-0.01517965889001283</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>0.01665535802718043</v>
+        <v>0.01665535802718021</v>
       </c>
       <c r="E16" s="5" t="n">
         <v>14734.5</v>
@@ -1227,7 +1227,7 @@
         <v>0.07519702276707529</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>-0.05854166473989486</v>
+        <v>-0.05854166473989508</v>
       </c>
     </row>
     <row r="17">
@@ -1238,7 +1238,7 @@
         <v>101579.9132001645</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>-0.0008421989013038811</v>
+        <v>-0.000842198901303659</v>
       </c>
       <c r="D17" s="4" t="n">
         <v>0.01579913200164529</v>
@@ -1258,13 +1258,13 @@
         <v>46196</v>
       </c>
       <c r="B18" s="5" t="n">
-        <v>101579.9132001645</v>
+        <v>100618.810734021</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>0</v>
+        <v>-0.009461540533606483</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>0.01579913200164529</v>
+        <v>0.00618810734020947</v>
       </c>
       <c r="E18" s="5" t="n">
         <v>14539.599609375</v>
@@ -1273,11 +1273,34 @@
         <v>0.06097486933559537</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>-0.04517573733395008</v>
+        <v>-0.0547867619953859</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="6" t="n">
+        <v>46197</v>
+      </c>
+      <c r="B19" s="5" t="n">
+        <v>99903.87102493743</v>
+      </c>
+      <c r="C19" s="4" t="n">
+        <v>-0.007105427940044096</v>
+      </c>
+      <c r="D19" s="4" t="n">
+        <v>-0.0009612897506257045</v>
+      </c>
+      <c r="E19" s="5" t="n">
+        <v>14331.2001953125</v>
+      </c>
+      <c r="F19" s="4" t="n">
+        <v>0.04576767332986709</v>
+      </c>
+      <c r="G19" s="4" t="n">
+        <v>-0.04672896308049279</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G18"/>
+  <autoFilter ref="A1:G19"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/reports/latest_one_month_follow_up.xlsx
+++ b/reports/latest_one_month_follow_up.xlsx
@@ -15,7 +15,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'TAKIP_OZETI'!$A$1:$B$19</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'POZISYONLAR'!$A$1:$H$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'GUNLUK_TAKIP'!$A$1:$G$19</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'GUNLUK_TAKIP'!$A$1:$G$20</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'NOTLAR'!$A$1:$A$7</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -475,7 +475,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
     </row>
@@ -546,7 +546,7 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>14331.2001953125</v>
+        <v>14259.7998046875</v>
       </c>
     </row>
     <row r="9">
@@ -603,7 +603,7 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
     </row>
@@ -627,7 +627,7 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>-0.0009612897506259266</v>
+        <v>-0.00274815566150366</v>
       </c>
     </row>
     <row r="17">
@@ -648,7 +648,7 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>0.04576767332986709</v>
+        <v>0.04055748720720231</v>
       </c>
     </row>
     <row r="18">
@@ -658,7 +658,7 @@
         </is>
       </c>
       <c r="B18" s="3" t="n">
-        <v>-0.04672896308049301</v>
+        <v>-0.04330564286870597</v>
       </c>
     </row>
     <row r="19">
@@ -692,7 +692,7 @@
     <col width="20" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
     <col width="19" customWidth="1" min="4" max="4"/>
-    <col width="23" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
     <col width="19" customWidth="1" min="6" max="6"/>
     <col width="19" customWidth="1" min="7" max="7"/>
     <col width="20" customWidth="1" min="8" max="8"/>
@@ -753,19 +753,19 @@
         <v>40</v>
       </c>
       <c r="D2" s="5" t="n">
-        <v>39.93999862670898</v>
+        <v>40.31999969482422</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>-0.001500034332275413</v>
+        <v>0.007999992370605558</v>
       </c>
       <c r="F2" s="5" t="n">
         <v>33333.33333333333</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>33283.33218892415</v>
+        <v>33599.99974568684</v>
       </c>
       <c r="H2" s="5" t="n">
-        <v>-50.00114440917969</v>
+        <v>266.6664123535156</v>
       </c>
     </row>
     <row r="3">
@@ -781,19 +781,19 @@
         <v>45.5</v>
       </c>
       <c r="D3" s="5" t="n">
-        <v>45.09999847412109</v>
+        <v>44.2400016784668</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>-0.008791242327008897</v>
+        <v>-0.02769227080292758</v>
       </c>
       <c r="F3" s="5" t="n">
         <v>33333.33333333333</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>33040.29192243303</v>
+        <v>32410.25763990241</v>
       </c>
       <c r="H3" s="5" t="n">
-        <v>-293.0414109002959</v>
+        <v>-923.0756934309175</v>
       </c>
     </row>
     <row r="4">
@@ -809,19 +809,19 @@
         <v>371.25</v>
       </c>
       <c r="D4" s="5" t="n">
-        <v>374</v>
+        <v>375.5</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>0.007407407407407307</v>
+        <v>0.01144781144781137</v>
       </c>
       <c r="F4" s="5" t="n">
         <v>33333.33333333333</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>33580.24691358024</v>
+        <v>33714.92704826038</v>
       </c>
       <c r="H4" s="5" t="n">
-        <v>246.91358024691</v>
+        <v>381.5937149270467</v>
       </c>
     </row>
   </sheetData>
@@ -836,7 +836,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G19"/>
+  <dimension ref="A1:G20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -1299,8 +1299,31 @@
         <v>-0.04672896308049279</v>
       </c>
     </row>
+    <row r="20">
+      <c r="A20" s="6" t="n">
+        <v>46198</v>
+      </c>
+      <c r="B20" s="5" t="n">
+        <v>99725.18443384963</v>
+      </c>
+      <c r="C20" s="4" t="n">
+        <v>-0.001788585259556053</v>
+      </c>
+      <c r="D20" s="4" t="n">
+        <v>-0.00274815566150366</v>
+      </c>
+      <c r="E20" s="5" t="n">
+        <v>14259.7998046875</v>
+      </c>
+      <c r="F20" s="4" t="n">
+        <v>0.04055748720720231</v>
+      </c>
+      <c r="G20" s="4" t="n">
+        <v>-0.04330564286870597</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G19"/>
+  <autoFilter ref="A1:G20"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/reports/latest_one_month_follow_up.xlsx
+++ b/reports/latest_one_month_follow_up.xlsx
@@ -15,7 +15,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'TAKIP_OZETI'!$A$1:$B$19</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'POZISYONLAR'!$A$1:$H$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'GUNLUK_TAKIP'!$A$1:$G$20</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'GUNLUK_TAKIP'!$A$1:$G$21</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'NOTLAR'!$A$1:$A$7</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -475,7 +475,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
     </row>
@@ -603,7 +603,7 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>-0.00274815566150366</v>
+        <v>0.01926604379604102</v>
       </c>
     </row>
     <row r="17">
@@ -658,7 +658,7 @@
         </is>
       </c>
       <c r="B18" s="3" t="n">
-        <v>-0.04330564286870597</v>
+        <v>-0.02129144341116129</v>
       </c>
     </row>
     <row r="19">
@@ -669,7 +669,7 @@
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>Zararda / BIST Altı</t>
+          <t>Karda / BIST Altı</t>
         </is>
       </c>
     </row>
@@ -692,7 +692,7 @@
     <col width="20" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
     <col width="19" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="23" customWidth="1" min="5" max="5"/>
     <col width="19" customWidth="1" min="6" max="6"/>
     <col width="19" customWidth="1" min="7" max="7"/>
     <col width="20" customWidth="1" min="8" max="8"/>
@@ -753,19 +753,19 @@
         <v>40</v>
       </c>
       <c r="D2" s="5" t="n">
-        <v>40.31999969482422</v>
+        <v>42.11999893188477</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>0.007999992370605558</v>
+        <v>0.05299997329711914</v>
       </c>
       <c r="F2" s="5" t="n">
         <v>33333.33333333333</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>33599.99974568684</v>
+        <v>35099.99910990397</v>
       </c>
       <c r="H2" s="5" t="n">
-        <v>266.6664123535156</v>
+        <v>1766.66577657064</v>
       </c>
     </row>
     <row r="3">
@@ -781,19 +781,19 @@
         <v>45.5</v>
       </c>
       <c r="D3" s="5" t="n">
-        <v>44.2400016784668</v>
+        <v>45.31999969482422</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>-0.02769227080292758</v>
+        <v>-0.003956050663204036</v>
       </c>
       <c r="F3" s="5" t="n">
         <v>33333.33333333333</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>32410.25763990241</v>
+        <v>33201.46497789319</v>
       </c>
       <c r="H3" s="5" t="n">
-        <v>-923.0756934309175</v>
+        <v>-131.8683554401359</v>
       </c>
     </row>
     <row r="4">
@@ -809,19 +809,19 @@
         <v>371.25</v>
       </c>
       <c r="D4" s="5" t="n">
-        <v>375.5</v>
+        <v>374.5</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>0.01144781144781137</v>
+        <v>0.008754208754208737</v>
       </c>
       <c r="F4" s="5" t="n">
         <v>33333.33333333333</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>33714.92704826038</v>
+        <v>33625.14029180695</v>
       </c>
       <c r="H4" s="5" t="n">
-        <v>381.5937149270467</v>
+        <v>291.8069584736222</v>
       </c>
     </row>
   </sheetData>
@@ -836,7 +836,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G20"/>
+  <dimension ref="A1:G21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -1322,8 +1322,31 @@
         <v>-0.04330564286870597</v>
       </c>
     </row>
+    <row r="21">
+      <c r="A21" s="6" t="n">
+        <v>46199</v>
+      </c>
+      <c r="B21" s="5" t="n">
+        <v>101926.6043796041</v>
+      </c>
+      <c r="C21" s="4" t="n">
+        <v>0.02207486462173192</v>
+      </c>
+      <c r="D21" s="4" t="n">
+        <v>0.01926604379604102</v>
+      </c>
+      <c r="E21" s="5" t="n">
+        <v>14259.7998046875</v>
+      </c>
+      <c r="F21" s="4" t="n">
+        <v>0.04055748720720231</v>
+      </c>
+      <c r="G21" s="4" t="n">
+        <v>-0.02129144341116129</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G20"/>
+  <autoFilter ref="A1:G21"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/reports/latest_one_month_follow_up.xlsx
+++ b/reports/latest_one_month_follow_up.xlsx
@@ -841,7 +841,7 @@
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
     <col width="19" customWidth="1" min="2" max="2"/>
-    <col width="23" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
     <col width="24" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
     <col width="24" customWidth="1" min="6" max="6"/>
@@ -1215,10 +1215,10 @@
         <v>101665.535802718</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>-0.01517965889001283</v>
+        <v>-0.0151796588900126</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>0.01665535802718021</v>
+        <v>0.01665535802718043</v>
       </c>
       <c r="E16" s="5" t="n">
         <v>14734.5</v>
@@ -1227,7 +1227,7 @@
         <v>0.07519702276707529</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>-0.05854166473989508</v>
+        <v>-0.05854166473989486</v>
       </c>
     </row>
     <row r="17">
@@ -1238,7 +1238,7 @@
         <v>101579.9132001645</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>-0.000842198901303659</v>
+        <v>-0.0008421989013038811</v>
       </c>
       <c r="D17" s="4" t="n">
         <v>0.01579913200164529</v>
@@ -1281,13 +1281,13 @@
         <v>46197</v>
       </c>
       <c r="B19" s="5" t="n">
-        <v>99903.87102493743</v>
+        <v>99903.87102493741</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>-0.007105427940044096</v>
+        <v>-0.007105427940044318</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>-0.0009612897506257045</v>
+        <v>-0.0009612897506259266</v>
       </c>
       <c r="E19" s="5" t="n">
         <v>14331.2001953125</v>
@@ -1296,7 +1296,7 @@
         <v>0.04576767332986709</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>-0.04672896308049279</v>
+        <v>-0.04672896308049301</v>
       </c>
     </row>
     <row r="20">
@@ -1307,7 +1307,7 @@
         <v>99725.18443384963</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>-0.001788585259556053</v>
+        <v>-0.00178858525955583</v>
       </c>
       <c r="D20" s="4" t="n">
         <v>-0.00274815566150366</v>

--- a/reports/latest_one_month_follow_up.xlsx
+++ b/reports/latest_one_month_follow_up.xlsx
@@ -546,7 +546,7 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>14259.7998046875</v>
+        <v>14274</v>
       </c>
     </row>
     <row r="9">
@@ -627,7 +627,7 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
     </row>
@@ -648,7 +648,7 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>0.04055748720720231</v>
+        <v>0.04159369527145351</v>
       </c>
     </row>
     <row r="18">
@@ -658,7 +658,7 @@
         </is>
       </c>
       <c r="B18" s="3" t="n">
-        <v>-0.02129144341116129</v>
+        <v>-0.02232765147541249</v>
       </c>
     </row>
     <row r="19">
@@ -1336,13 +1336,13 @@
         <v>0.01926604379604102</v>
       </c>
       <c r="E21" s="5" t="n">
-        <v>14259.7998046875</v>
+        <v>14274</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>0.04055748720720231</v>
+        <v>0.04159369527145351</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>-0.02129144341116129</v>
+        <v>-0.02232765147541249</v>
       </c>
     </row>
   </sheetData>

--- a/reports/latest_one_month_follow_up.xlsx
+++ b/reports/latest_one_month_follow_up.xlsx
@@ -15,7 +15,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'TAKIP_OZETI'!$A$1:$B$19</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'POZISYONLAR'!$A$1:$H$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'GUNLUK_TAKIP'!$A$1:$G$21</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'GUNLUK_TAKIP'!$A$1:$G$22</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'NOTLAR'!$A$1:$A$7</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -475,7 +475,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-29</t>
         </is>
       </c>
     </row>
@@ -546,7 +546,7 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>14274</v>
+        <v>14183.2001953125</v>
       </c>
     </row>
     <row r="9">
@@ -603,7 +603,7 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-29</t>
         </is>
       </c>
     </row>
@@ -627,7 +627,7 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-29</t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>0.01926604379604102</v>
+        <v>0.00567296530339112</v>
       </c>
     </row>
     <row r="17">
@@ -648,7 +648,7 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>0.04159369527145351</v>
+        <v>0.03496790683833195</v>
       </c>
     </row>
     <row r="18">
@@ -658,7 +658,7 @@
         </is>
       </c>
       <c r="B18" s="3" t="n">
-        <v>-0.02232765147541249</v>
+        <v>-0.02929494153494083</v>
       </c>
     </row>
     <row r="19">
@@ -692,7 +692,7 @@
     <col width="20" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
     <col width="19" customWidth="1" min="4" max="4"/>
-    <col width="23" customWidth="1" min="5" max="5"/>
+    <col width="24" customWidth="1" min="5" max="5"/>
     <col width="19" customWidth="1" min="6" max="6"/>
     <col width="19" customWidth="1" min="7" max="7"/>
     <col width="20" customWidth="1" min="8" max="8"/>
@@ -753,19 +753,19 @@
         <v>40</v>
       </c>
       <c r="D2" s="5" t="n">
-        <v>42.11999893188477</v>
+        <v>41.20000076293945</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>0.05299997329711914</v>
+        <v>0.03000001907348637</v>
       </c>
       <c r="F2" s="5" t="n">
         <v>33333.33333333333</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>35099.99910990397</v>
+        <v>34333.33396911621</v>
       </c>
       <c r="H2" s="5" t="n">
-        <v>1766.66577657064</v>
+        <v>1000.000635782882</v>
       </c>
     </row>
     <row r="3">
@@ -781,19 +781,19 @@
         <v>45.5</v>
       </c>
       <c r="D3" s="5" t="n">
-        <v>45.31999969482422</v>
+        <v>44.93999862670898</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>-0.003956050663204036</v>
+        <v>-0.01230772248991241</v>
       </c>
       <c r="F3" s="5" t="n">
         <v>33333.33333333333</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>33201.46497789319</v>
+        <v>32923.07591700291</v>
       </c>
       <c r="H3" s="5" t="n">
-        <v>-131.8683554401359</v>
+        <v>-410.2574163304162</v>
       </c>
     </row>
     <row r="4">
@@ -809,19 +809,19 @@
         <v>371.25</v>
       </c>
       <c r="D4" s="5" t="n">
-        <v>374.5</v>
+        <v>371</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>0.008754208754208737</v>
+        <v>-0.0006734006734007147</v>
       </c>
       <c r="F4" s="5" t="n">
         <v>33333.33333333333</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>33625.14029180695</v>
+        <v>33310.88664421997</v>
       </c>
       <c r="H4" s="5" t="n">
-        <v>291.8069584736222</v>
+        <v>-22.44668911335611</v>
       </c>
     </row>
   </sheetData>
@@ -836,12 +836,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G21"/>
+  <dimension ref="A1:G22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
     <col width="19" customWidth="1" min="2" max="2"/>
-    <col width="24" customWidth="1" min="3" max="3"/>
+    <col width="23" customWidth="1" min="3" max="3"/>
     <col width="24" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
     <col width="24" customWidth="1" min="6" max="6"/>
@@ -1215,10 +1215,10 @@
         <v>101665.535802718</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>-0.0151796588900126</v>
+        <v>-0.01517965889001283</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>0.01665535802718043</v>
+        <v>0.01665535802718021</v>
       </c>
       <c r="E16" s="5" t="n">
         <v>14734.5</v>
@@ -1227,7 +1227,7 @@
         <v>0.07519702276707529</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>-0.05854166473989486</v>
+        <v>-0.05854166473989508</v>
       </c>
     </row>
     <row r="17">
@@ -1238,7 +1238,7 @@
         <v>101579.9132001645</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>-0.0008421989013038811</v>
+        <v>-0.000842198901303659</v>
       </c>
       <c r="D17" s="4" t="n">
         <v>0.01579913200164529</v>
@@ -1281,13 +1281,13 @@
         <v>46197</v>
       </c>
       <c r="B19" s="5" t="n">
-        <v>99903.87102493741</v>
+        <v>99903.87102493743</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>-0.007105427940044318</v>
+        <v>-0.007105427940044096</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>-0.0009612897506259266</v>
+        <v>-0.0009612897506257045</v>
       </c>
       <c r="E19" s="5" t="n">
         <v>14331.2001953125</v>
@@ -1296,7 +1296,7 @@
         <v>0.04576767332986709</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>-0.04672896308049301</v>
+        <v>-0.04672896308049279</v>
       </c>
     </row>
     <row r="20">
@@ -1307,7 +1307,7 @@
         <v>99725.18443384963</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>-0.00178858525955583</v>
+        <v>-0.001788585259556053</v>
       </c>
       <c r="D20" s="4" t="n">
         <v>-0.00274815566150366</v>
@@ -1345,8 +1345,31 @@
         <v>-0.02232765147541249</v>
       </c>
     </row>
+    <row r="22">
+      <c r="A22" s="6" t="n">
+        <v>46202</v>
+      </c>
+      <c r="B22" s="5" t="n">
+        <v>100567.2965303391</v>
+      </c>
+      <c r="C22" s="4" t="n">
+        <v>-0.01333614376284464</v>
+      </c>
+      <c r="D22" s="4" t="n">
+        <v>0.00567296530339112</v>
+      </c>
+      <c r="E22" s="5" t="n">
+        <v>14183.2001953125</v>
+      </c>
+      <c r="F22" s="4" t="n">
+        <v>0.03496790683833195</v>
+      </c>
+      <c r="G22" s="4" t="n">
+        <v>-0.02929494153494083</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G21"/>
+  <autoFilter ref="A1:G22"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/reports/latest_one_month_follow_up.xlsx
+++ b/reports/latest_one_month_follow_up.xlsx
@@ -15,7 +15,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'TAKIP_OZETI'!$A$1:$B$19</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'POZISYONLAR'!$A$1:$H$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'GUNLUK_TAKIP'!$A$1:$G$22</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'GUNLUK_TAKIP'!$A$1:$G$23</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'NOTLAR'!$A$1:$A$7</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -475,7 +475,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
     </row>
@@ -546,7 +546,7 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>14183.2001953125</v>
+        <v>14121.7998046875</v>
       </c>
     </row>
     <row r="9">
@@ -603,7 +603,7 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
     </row>
@@ -627,7 +627,7 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>0.00567296530339112</v>
+        <v>-0.0101784235824115</v>
       </c>
     </row>
     <row r="17">
@@ -648,7 +648,7 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>0.03496790683833195</v>
+        <v>0.03048743466779769</v>
       </c>
     </row>
     <row r="18">
@@ -658,7 +658,7 @@
         </is>
       </c>
       <c r="B18" s="3" t="n">
-        <v>-0.02929494153494083</v>
+        <v>-0.04066585825020919</v>
       </c>
     </row>
     <row r="19">
@@ -669,7 +669,7 @@
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>Karda / BIST Altı</t>
+          <t>Zararda / BIST Altı</t>
         </is>
       </c>
     </row>
@@ -692,7 +692,7 @@
     <col width="20" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
     <col width="19" customWidth="1" min="4" max="4"/>
-    <col width="24" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
     <col width="19" customWidth="1" min="6" max="6"/>
     <col width="19" customWidth="1" min="7" max="7"/>
     <col width="20" customWidth="1" min="8" max="8"/>
@@ -753,19 +753,19 @@
         <v>40</v>
       </c>
       <c r="D2" s="5" t="n">
-        <v>41.20000076293945</v>
+        <v>40.47999954223633</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>0.03000001907348637</v>
+        <v>0.01199998855590811</v>
       </c>
       <c r="F2" s="5" t="n">
         <v>33333.33333333333</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>34333.33396911621</v>
+        <v>33733.3329518636</v>
       </c>
       <c r="H2" s="5" t="n">
-        <v>1000.000635782882</v>
+        <v>399.9996185302734</v>
       </c>
     </row>
     <row r="3">
@@ -781,19 +781,19 @@
         <v>45.5</v>
       </c>
       <c r="D3" s="5" t="n">
-        <v>44.93999862670898</v>
+        <v>44.29999923706055</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>-0.01230772248991241</v>
+        <v>-0.02637364314152646</v>
       </c>
       <c r="F3" s="5" t="n">
         <v>33333.33333333333</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>32923.07591700291</v>
+        <v>32454.21189528245</v>
       </c>
       <c r="H3" s="5" t="n">
-        <v>-410.2574163304162</v>
+        <v>-879.1214380508827</v>
       </c>
     </row>
     <row r="4">
@@ -809,19 +809,19 @@
         <v>371.25</v>
       </c>
       <c r="D4" s="5" t="n">
-        <v>371</v>
+        <v>365.25</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>-0.0006734006734007147</v>
+        <v>-0.01616161616161615</v>
       </c>
       <c r="F4" s="5" t="n">
         <v>33333.33333333333</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>33310.88664421997</v>
+        <v>32794.61279461279</v>
       </c>
       <c r="H4" s="5" t="n">
-        <v>-22.44668911335611</v>
+        <v>-538.7205387205395</v>
       </c>
     </row>
   </sheetData>
@@ -836,7 +836,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G22"/>
+  <dimension ref="A1:G23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -1368,8 +1368,31 @@
         <v>-0.02929494153494083</v>
       </c>
     </row>
+    <row r="23">
+      <c r="A23" s="6" t="n">
+        <v>46203</v>
+      </c>
+      <c r="B23" s="5" t="n">
+        <v>98982.15764175884</v>
+      </c>
+      <c r="C23" s="4" t="n">
+        <v>-0.01576197176685634</v>
+      </c>
+      <c r="D23" s="4" t="n">
+        <v>-0.01017842358241161</v>
+      </c>
+      <c r="E23" s="5" t="n">
+        <v>14121.7998046875</v>
+      </c>
+      <c r="F23" s="4" t="n">
+        <v>0.03048743466779769</v>
+      </c>
+      <c r="G23" s="4" t="n">
+        <v>-0.0406658582502093</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G22"/>
+  <autoFilter ref="A1:G23"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/reports/latest_one_month_follow_up.xlsx
+++ b/reports/latest_one_month_follow_up.xlsx
@@ -15,7 +15,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'TAKIP_OZETI'!$A$1:$B$19</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'POZISYONLAR'!$A$1:$H$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'GUNLUK_TAKIP'!$A$1:$G$23</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'GUNLUK_TAKIP'!$A$1:$G$24</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'NOTLAR'!$A$1:$A$7</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -475,7 +475,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
     </row>
@@ -546,7 +546,7 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>14121.7998046875</v>
+        <v>14350.599609375</v>
       </c>
     </row>
     <row r="9">
@@ -603,7 +603,7 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
     </row>
@@ -627,7 +627,7 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>-0.0101784235824115</v>
+        <v>-0.007082591055236009</v>
       </c>
     </row>
     <row r="17">
@@ -648,7 +648,7 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>0.03048743466779769</v>
+        <v>0.0471832756403241</v>
       </c>
     </row>
     <row r="18">
@@ -658,7 +658,7 @@
         </is>
       </c>
       <c r="B18" s="3" t="n">
-        <v>-0.04066585825020919</v>
+        <v>-0.05426586669556011</v>
       </c>
     </row>
     <row r="19">
@@ -753,19 +753,19 @@
         <v>40</v>
       </c>
       <c r="D2" s="5" t="n">
-        <v>40.47999954223633</v>
+        <v>40.43999862670898</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>0.01199998855590811</v>
+        <v>0.01099996566772465</v>
       </c>
       <c r="F2" s="5" t="n">
         <v>33333.33333333333</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>33733.3329518636</v>
+        <v>33699.99885559082</v>
       </c>
       <c r="H2" s="5" t="n">
-        <v>399.9996185302734</v>
+        <v>366.6655222574918</v>
       </c>
     </row>
     <row r="3">
@@ -781,19 +781,19 @@
         <v>45.5</v>
       </c>
       <c r="D3" s="5" t="n">
-        <v>44.29999923706055</v>
+        <v>44.86000061035156</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>-0.02637364314152646</v>
+        <v>-0.01406592065161405</v>
       </c>
       <c r="F3" s="5" t="n">
         <v>33333.33333333333</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>32454.21189528245</v>
+        <v>32864.46931161286</v>
       </c>
       <c r="H3" s="5" t="n">
-        <v>-879.1214380508827</v>
+        <v>-468.8640217204666</v>
       </c>
     </row>
     <row r="4">
@@ -809,19 +809,19 @@
         <v>371.25</v>
       </c>
       <c r="D4" s="5" t="n">
-        <v>365.25</v>
+        <v>364.5</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>-0.01616161616161615</v>
+        <v>-0.01818181818181819</v>
       </c>
       <c r="F4" s="5" t="n">
         <v>33333.33333333333</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>32794.61279461279</v>
+        <v>32727.27272727272</v>
       </c>
       <c r="H4" s="5" t="n">
-        <v>-538.7205387205395</v>
+        <v>-606.0606060606078</v>
       </c>
     </row>
   </sheetData>
@@ -836,7 +836,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G23"/>
+  <dimension ref="A1:G24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -1391,8 +1391,31 @@
         <v>-0.0406658582502093</v>
       </c>
     </row>
+    <row r="24">
+      <c r="A24" s="6" t="n">
+        <v>46204</v>
+      </c>
+      <c r="B24" s="5" t="n">
+        <v>99291.7408944764</v>
+      </c>
+      <c r="C24" s="4" t="n">
+        <v>0.003127667249263499</v>
+      </c>
+      <c r="D24" s="4" t="n">
+        <v>-0.007082591055235898</v>
+      </c>
+      <c r="E24" s="5" t="n">
+        <v>14350.599609375</v>
+      </c>
+      <c r="F24" s="4" t="n">
+        <v>0.0471832756403241</v>
+      </c>
+      <c r="G24" s="4" t="n">
+        <v>-0.05426586669555999</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G23"/>
+  <autoFilter ref="A1:G24"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/reports/latest_one_month_follow_up.xlsx
+++ b/reports/latest_one_month_follow_up.xlsx
@@ -15,7 +15,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'TAKIP_OZETI'!$A$1:$B$19</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'POZISYONLAR'!$A$1:$H$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'GUNLUK_TAKIP'!$A$1:$G$24</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'GUNLUK_TAKIP'!$A$1:$G$25</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'NOTLAR'!$A$1:$A$7</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -475,7 +475,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
     </row>
@@ -546,7 +546,7 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>14350.599609375</v>
+        <v>14455</v>
       </c>
     </row>
     <row r="9">
@@ -603,7 +603,7 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
     </row>
@@ -627,7 +627,7 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>-0.007082591055236009</v>
+        <v>-0.01300502602951525</v>
       </c>
     </row>
     <row r="17">
@@ -648,7 +648,7 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>0.0471832756403241</v>
+        <v>0.05480151780502052</v>
       </c>
     </row>
     <row r="18">
@@ -658,7 +658,7 @@
         </is>
       </c>
       <c r="B18" s="3" t="n">
-        <v>-0.05426586669556011</v>
+        <v>-0.06780654383453577</v>
       </c>
     </row>
     <row r="19">
@@ -753,19 +753,19 @@
         <v>40</v>
       </c>
       <c r="D2" s="5" t="n">
-        <v>40.43999862670898</v>
+        <v>40.79999923706055</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>0.01099996566772465</v>
+        <v>0.01999998092651367</v>
       </c>
       <c r="F2" s="5" t="n">
         <v>33333.33333333333</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>33699.99885559082</v>
+        <v>33999.99936421712</v>
       </c>
       <c r="H2" s="5" t="n">
-        <v>366.6655222574918</v>
+        <v>666.6660308837891</v>
       </c>
     </row>
     <row r="3">
@@ -781,19 +781,19 @@
         <v>45.5</v>
       </c>
       <c r="D3" s="5" t="n">
-        <v>44.86000061035156</v>
+        <v>44.5</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>-0.01406592065161405</v>
+        <v>-0.02197802197802201</v>
       </c>
       <c r="F3" s="5" t="n">
         <v>33333.33333333333</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>32864.46931161286</v>
+        <v>32600.73260073259</v>
       </c>
       <c r="H3" s="5" t="n">
-        <v>-468.8640217204666</v>
+        <v>-732.6007326007348</v>
       </c>
     </row>
     <row r="4">
@@ -809,19 +809,19 @@
         <v>371.25</v>
       </c>
       <c r="D4" s="5" t="n">
-        <v>364.5</v>
+        <v>357.5</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>-0.01818181818181819</v>
+        <v>-0.03703703703703709</v>
       </c>
       <c r="F4" s="5" t="n">
         <v>33333.33333333333</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>32727.27272727272</v>
+        <v>32098.76543209876</v>
       </c>
       <c r="H4" s="5" t="n">
-        <v>-606.0606060606078</v>
+        <v>-1234.567901234568</v>
       </c>
     </row>
   </sheetData>
@@ -836,7 +836,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G24"/>
+  <dimension ref="A1:G25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -1414,8 +1414,31 @@
         <v>-0.05426586669555999</v>
       </c>
     </row>
+    <row r="25">
+      <c r="A25" s="6" t="n">
+        <v>46205</v>
+      </c>
+      <c r="B25" s="5" t="n">
+        <v>98699.49739704847</v>
+      </c>
+      <c r="C25" s="4" t="n">
+        <v>-0.005964680366087549</v>
+      </c>
+      <c r="D25" s="4" t="n">
+        <v>-0.01300502602951525</v>
+      </c>
+      <c r="E25" s="5" t="n">
+        <v>14455</v>
+      </c>
+      <c r="F25" s="4" t="n">
+        <v>0.05480151780502052</v>
+      </c>
+      <c r="G25" s="4" t="n">
+        <v>-0.06780654383453577</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G24"/>
+  <autoFilter ref="A1:G25"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/reports/latest_one_month_follow_up.xlsx
+++ b/reports/latest_one_month_follow_up.xlsx
@@ -15,7 +15,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'TAKIP_OZETI'!$A$1:$B$19</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'POZISYONLAR'!$A$1:$H$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'GUNLUK_TAKIP'!$A$1:$G$25</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'GUNLUK_TAKIP'!$A$1:$G$26</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'NOTLAR'!$A$1:$A$7</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -475,7 +475,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
     </row>
@@ -546,7 +546,7 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>14455</v>
+        <v>14417.900390625</v>
       </c>
     </row>
     <row r="9">
@@ -603,7 +603,7 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
     </row>
@@ -627,7 +627,7 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>-0.01300502602951525</v>
+        <v>-0.0204594595572456</v>
       </c>
     </row>
     <row r="17">
@@ -648,7 +648,7 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>0.05480151780502052</v>
+        <v>0.05209430754706657</v>
       </c>
     </row>
     <row r="18">
@@ -658,7 +658,7 @@
         </is>
       </c>
       <c r="B18" s="3" t="n">
-        <v>-0.06780654383453577</v>
+        <v>-0.07255376710431216</v>
       </c>
     </row>
     <row r="19">
@@ -753,19 +753,19 @@
         <v>40</v>
       </c>
       <c r="D2" s="5" t="n">
-        <v>40.79999923706055</v>
+        <v>40.09999847412109</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>0.01999998092651367</v>
+        <v>0.002499961853027255</v>
       </c>
       <c r="F2" s="5" t="n">
         <v>33333.33333333333</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>33999.99936421712</v>
+        <v>33416.66539510091</v>
       </c>
       <c r="H2" s="5" t="n">
-        <v>666.6660308837891</v>
+        <v>83.33206176757812</v>
       </c>
     </row>
     <row r="3">
@@ -781,19 +781,19 @@
         <v>45.5</v>
       </c>
       <c r="D3" s="5" t="n">
-        <v>44.5</v>
+        <v>44.34000015258789</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>-0.02197802197802201</v>
+        <v>-0.02549450214092552</v>
       </c>
       <c r="F3" s="5" t="n">
         <v>33333.33333333333</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>32600.73260073259</v>
+        <v>32483.51659530248</v>
       </c>
       <c r="H3" s="5" t="n">
-        <v>-732.6007326007348</v>
+        <v>-849.8167380308514</v>
       </c>
     </row>
     <row r="4">
@@ -809,19 +809,19 @@
         <v>371.25</v>
       </c>
       <c r="D4" s="5" t="n">
-        <v>357.5</v>
+        <v>357</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>-0.03703703703703709</v>
+        <v>-0.03838383838383841</v>
       </c>
       <c r="F4" s="5" t="n">
         <v>33333.33333333333</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>32098.76543209876</v>
+        <v>32053.87205387205</v>
       </c>
       <c r="H4" s="5" t="n">
-        <v>-1234.567901234568</v>
+        <v>-1279.46127946128</v>
       </c>
     </row>
   </sheetData>
@@ -836,7 +836,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G25"/>
+  <dimension ref="A1:G26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -1437,8 +1437,31 @@
         <v>-0.06780654383453577</v>
       </c>
     </row>
+    <row r="26">
+      <c r="A26" s="6" t="n">
+        <v>46206</v>
+      </c>
+      <c r="B26" s="5" t="n">
+        <v>97954.05404427544</v>
+      </c>
+      <c r="C26" s="4" t="n">
+        <v>-0.007552656015807901</v>
+      </c>
+      <c r="D26" s="4" t="n">
+        <v>-0.0204594595572456</v>
+      </c>
+      <c r="E26" s="5" t="n">
+        <v>14417.900390625</v>
+      </c>
+      <c r="F26" s="4" t="n">
+        <v>0.05209430754706657</v>
+      </c>
+      <c r="G26" s="4" t="n">
+        <v>-0.07255376710431216</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G25"/>
+  <autoFilter ref="A1:G26"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/reports/latest_one_month_follow_up.xlsx
+++ b/reports/latest_one_month_follow_up.xlsx
@@ -841,7 +841,7 @@
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
     <col width="19" customWidth="1" min="2" max="2"/>
-    <col width="23" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
     <col width="24" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
     <col width="24" customWidth="1" min="6" max="6"/>
@@ -1215,10 +1215,10 @@
         <v>101665.535802718</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>-0.01517965889001283</v>
+        <v>-0.0151796588900126</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>0.01665535802718021</v>
+        <v>0.01665535802718043</v>
       </c>
       <c r="E16" s="5" t="n">
         <v>14734.5</v>
@@ -1227,7 +1227,7 @@
         <v>0.07519702276707529</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>-0.05854166473989508</v>
+        <v>-0.05854166473989486</v>
       </c>
     </row>
     <row r="17">
@@ -1238,7 +1238,7 @@
         <v>101579.9132001645</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>-0.000842198901303659</v>
+        <v>-0.0008421989013038811</v>
       </c>
       <c r="D17" s="4" t="n">
         <v>0.01579913200164529</v>
@@ -1281,13 +1281,13 @@
         <v>46197</v>
       </c>
       <c r="B19" s="5" t="n">
-        <v>99903.87102493743</v>
+        <v>99903.87102493741</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>-0.007105427940044096</v>
+        <v>-0.007105427940044318</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>-0.0009612897506257045</v>
+        <v>-0.0009612897506259266</v>
       </c>
       <c r="E19" s="5" t="n">
         <v>14331.2001953125</v>
@@ -1296,7 +1296,7 @@
         <v>0.04576767332986709</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>-0.04672896308049279</v>
+        <v>-0.04672896308049301</v>
       </c>
     </row>
     <row r="20">
@@ -1307,7 +1307,7 @@
         <v>99725.18443384963</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>-0.001788585259556053</v>
+        <v>-0.00178858525955583</v>
       </c>
       <c r="D20" s="4" t="n">
         <v>-0.00274815566150366</v>
@@ -1353,10 +1353,10 @@
         <v>100567.2965303391</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>-0.01333614376284464</v>
+        <v>-0.01333614376284487</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>0.00567296530339112</v>
+        <v>0.005672965303390898</v>
       </c>
       <c r="E22" s="5" t="n">
         <v>14183.2001953125</v>
@@ -1365,7 +1365,7 @@
         <v>0.03496790683833195</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>-0.02929494153494083</v>
+        <v>-0.02929494153494105</v>
       </c>
     </row>
     <row r="23">
@@ -1376,7 +1376,7 @@
         <v>98982.15764175884</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>-0.01576197176685634</v>
+        <v>-0.01576197176685612</v>
       </c>
       <c r="D23" s="4" t="n">
         <v>-0.01017842358241161</v>
@@ -1402,7 +1402,7 @@
         <v>0.003127667249263499</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>-0.007082591055235898</v>
+        <v>-0.007082591055236009</v>
       </c>
       <c r="E24" s="5" t="n">
         <v>14350.599609375</v>
@@ -1411,7 +1411,7 @@
         <v>0.0471832756403241</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>-0.05426586669555999</v>
+        <v>-0.05426586669556011</v>
       </c>
     </row>
     <row r="25">
@@ -1422,7 +1422,7 @@
         <v>98699.49739704847</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>-0.005964680366087549</v>
+        <v>-0.005964680366087438</v>
       </c>
       <c r="D25" s="4" t="n">
         <v>-0.01300502602951525</v>

--- a/reports/latest_one_month_follow_up.xlsx
+++ b/reports/latest_one_month_follow_up.xlsx
@@ -15,7 +15,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'TAKIP_OZETI'!$A$1:$B$19</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'POZISYONLAR'!$A$1:$H$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'GUNLUK_TAKIP'!$A$1:$G$26</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'GUNLUK_TAKIP'!$A$1:$G$27</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'NOTLAR'!$A$1:$A$7</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -546,7 +546,7 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>14417.900390625</v>
+        <v>14424.5</v>
       </c>
     </row>
     <row r="9">
@@ -627,7 +627,7 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-06</t>
         </is>
       </c>
     </row>
@@ -648,7 +648,7 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>0.05209430754706657</v>
+        <v>0.05257589025102161</v>
       </c>
     </row>
     <row r="18">
@@ -658,7 +658,7 @@
         </is>
       </c>
       <c r="B18" s="3" t="n">
-        <v>-0.07255376710431216</v>
+        <v>-0.0730353498082672</v>
       </c>
     </row>
     <row r="19">
@@ -836,12 +836,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G26"/>
+  <dimension ref="A1:G27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
     <col width="19" customWidth="1" min="2" max="2"/>
-    <col width="24" customWidth="1" min="3" max="3"/>
+    <col width="23" customWidth="1" min="3" max="3"/>
     <col width="24" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
     <col width="24" customWidth="1" min="6" max="6"/>
@@ -1215,10 +1215,10 @@
         <v>101665.535802718</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>-0.0151796588900126</v>
+        <v>-0.01517965889001283</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>0.01665535802718043</v>
+        <v>0.01665535802718021</v>
       </c>
       <c r="E16" s="5" t="n">
         <v>14734.5</v>
@@ -1227,7 +1227,7 @@
         <v>0.07519702276707529</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>-0.05854166473989486</v>
+        <v>-0.05854166473989508</v>
       </c>
     </row>
     <row r="17">
@@ -1238,7 +1238,7 @@
         <v>101579.9132001645</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>-0.0008421989013038811</v>
+        <v>-0.000842198901303659</v>
       </c>
       <c r="D17" s="4" t="n">
         <v>0.01579913200164529</v>
@@ -1281,13 +1281,13 @@
         <v>46197</v>
       </c>
       <c r="B19" s="5" t="n">
-        <v>99903.87102493741</v>
+        <v>99903.87102493743</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>-0.007105427940044318</v>
+        <v>-0.007105427940044096</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>-0.0009612897506259266</v>
+        <v>-0.0009612897506257045</v>
       </c>
       <c r="E19" s="5" t="n">
         <v>14331.2001953125</v>
@@ -1296,7 +1296,7 @@
         <v>0.04576767332986709</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>-0.04672896308049301</v>
+        <v>-0.04672896308049279</v>
       </c>
     </row>
     <row r="20">
@@ -1307,7 +1307,7 @@
         <v>99725.18443384963</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>-0.00178858525955583</v>
+        <v>-0.001788585259556053</v>
       </c>
       <c r="D20" s="4" t="n">
         <v>-0.00274815566150366</v>
@@ -1353,10 +1353,10 @@
         <v>100567.2965303391</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>-0.01333614376284487</v>
+        <v>-0.01333614376284464</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>0.005672965303390898</v>
+        <v>0.00567296530339112</v>
       </c>
       <c r="E22" s="5" t="n">
         <v>14183.2001953125</v>
@@ -1365,7 +1365,7 @@
         <v>0.03496790683833195</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>-0.02929494153494105</v>
+        <v>-0.02929494153494083</v>
       </c>
     </row>
     <row r="23">
@@ -1376,7 +1376,7 @@
         <v>98982.15764175884</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>-0.01576197176685612</v>
+        <v>-0.01576197176685634</v>
       </c>
       <c r="D23" s="4" t="n">
         <v>-0.01017842358241161</v>
@@ -1402,7 +1402,7 @@
         <v>0.003127667249263499</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>-0.007082591055236009</v>
+        <v>-0.007082591055235898</v>
       </c>
       <c r="E24" s="5" t="n">
         <v>14350.599609375</v>
@@ -1411,7 +1411,7 @@
         <v>0.0471832756403241</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>-0.05426586669556011</v>
+        <v>-0.05426586669555999</v>
       </c>
     </row>
     <row r="25">
@@ -1422,7 +1422,7 @@
         <v>98699.49739704847</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>-0.005964680366087438</v>
+        <v>-0.005964680366087549</v>
       </c>
       <c r="D25" s="4" t="n">
         <v>-0.01300502602951525</v>
@@ -1460,8 +1460,31 @@
         <v>-0.07255376710431216</v>
       </c>
     </row>
+    <row r="27">
+      <c r="A27" s="6" t="n">
+        <v>46209</v>
+      </c>
+      <c r="B27" s="5" t="n">
+        <v>97954.05404427544</v>
+      </c>
+      <c r="C27" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D27" s="4" t="n">
+        <v>-0.0204594595572456</v>
+      </c>
+      <c r="E27" s="5" t="n">
+        <v>14424.5</v>
+      </c>
+      <c r="F27" s="4" t="n">
+        <v>0.05257589025102161</v>
+      </c>
+      <c r="G27" s="4" t="n">
+        <v>-0.0730353498082672</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G26"/>
+  <autoFilter ref="A1:G27"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/reports/latest_one_month_follow_up.xlsx
+++ b/reports/latest_one_month_follow_up.xlsx
@@ -15,7 +15,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'TAKIP_OZETI'!$A$1:$B$19</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'POZISYONLAR'!$A$1:$H$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'GUNLUK_TAKIP'!$A$1:$G$27</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'GUNLUK_TAKIP'!$A$1:$G$28</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'NOTLAR'!$A$1:$A$7</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -475,7 +475,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-06</t>
         </is>
       </c>
     </row>
@@ -546,7 +546,7 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>14424.5</v>
+        <v>14497.400390625</v>
       </c>
     </row>
     <row r="9">
@@ -603,7 +603,7 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-06</t>
         </is>
       </c>
     </row>
@@ -627,7 +627,7 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>-0.0204594595572456</v>
+        <v>-0.002356334561884554</v>
       </c>
     </row>
     <row r="17">
@@ -648,7 +648,7 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>0.05257589025102161</v>
+        <v>0.05789553346650611</v>
       </c>
     </row>
     <row r="18">
@@ -658,7 +658,7 @@
         </is>
       </c>
       <c r="B18" s="3" t="n">
-        <v>-0.0730353498082672</v>
+        <v>-0.06025186802839066</v>
       </c>
     </row>
     <row r="19">
@@ -692,7 +692,7 @@
     <col width="20" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
     <col width="19" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="24" customWidth="1" min="5" max="5"/>
     <col width="19" customWidth="1" min="6" max="6"/>
     <col width="19" customWidth="1" min="7" max="7"/>
     <col width="20" customWidth="1" min="8" max="8"/>
@@ -753,19 +753,19 @@
         <v>40</v>
       </c>
       <c r="D2" s="5" t="n">
-        <v>40.09999847412109</v>
+        <v>41.52000045776367</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>0.002499961853027255</v>
+        <v>0.03800001144409171</v>
       </c>
       <c r="F2" s="5" t="n">
         <v>33333.33333333333</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>33416.66539510091</v>
+        <v>34600.00038146972</v>
       </c>
       <c r="H2" s="5" t="n">
-        <v>83.33206176757812</v>
+        <v>1266.667048136391</v>
       </c>
     </row>
     <row r="3">
@@ -781,19 +781,19 @@
         <v>45.5</v>
       </c>
       <c r="D3" s="5" t="n">
-        <v>44.34000015258789</v>
+        <v>43.47999954223633</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>-0.02549450214092552</v>
+        <v>-0.04439561445634443</v>
       </c>
       <c r="F3" s="5" t="n">
         <v>33333.33333333333</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>32483.51659530248</v>
+        <v>31853.47951812185</v>
       </c>
       <c r="H3" s="5" t="n">
-        <v>-849.8167380308514</v>
+        <v>-1479.853815211482</v>
       </c>
     </row>
     <row r="4">
@@ -809,19 +809,19 @@
         <v>371.25</v>
       </c>
       <c r="D4" s="5" t="n">
-        <v>357</v>
+        <v>371</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>-0.03838383838383841</v>
+        <v>-0.0006734006734007147</v>
       </c>
       <c r="F4" s="5" t="n">
         <v>33333.33333333333</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>32053.87205387205</v>
+        <v>33310.88664421997</v>
       </c>
       <c r="H4" s="5" t="n">
-        <v>-1279.46127946128</v>
+        <v>-22.44668911335611</v>
       </c>
     </row>
   </sheetData>
@@ -836,7 +836,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G27"/>
+  <dimension ref="A1:G28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -1465,13 +1465,13 @@
         <v>46209</v>
       </c>
       <c r="B27" s="5" t="n">
-        <v>97954.05404427544</v>
+        <v>99764.36654381154</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>0</v>
+        <v>0.01848124120230743</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>-0.0204594595572456</v>
+        <v>-0.002356334561884554</v>
       </c>
       <c r="E27" s="5" t="n">
         <v>14424.5</v>
@@ -1480,11 +1480,34 @@
         <v>0.05257589025102161</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>-0.0730353498082672</v>
+        <v>-0.05493222481290616</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="6" t="n">
+        <v>46210</v>
+      </c>
+      <c r="B28" s="5" t="n">
+        <v>99764.36654381154</v>
+      </c>
+      <c r="C28" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D28" s="4" t="n">
+        <v>-0.002356334561884554</v>
+      </c>
+      <c r="E28" s="5" t="n">
+        <v>14497.400390625</v>
+      </c>
+      <c r="F28" s="4" t="n">
+        <v>0.05789553346650611</v>
+      </c>
+      <c r="G28" s="4" t="n">
+        <v>-0.06025186802839066</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G27"/>
+  <autoFilter ref="A1:G28"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/reports/latest_one_month_follow_up.xlsx
+++ b/reports/latest_one_month_follow_up.xlsx
@@ -15,7 +15,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'TAKIP_OZETI'!$A$1:$B$19</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'POZISYONLAR'!$A$1:$H$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'GUNLUK_TAKIP'!$A$1:$G$28</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'GUNLUK_TAKIP'!$A$1:$G$29</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'NOTLAR'!$A$1:$A$7</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -475,7 +475,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
     </row>
@@ -546,7 +546,7 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>14497.400390625</v>
+        <v>14190</v>
       </c>
     </row>
     <row r="9">
@@ -603,7 +603,7 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
     </row>
@@ -627,7 +627,7 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>-0.002356334561884554</v>
+        <v>-0.003949269554337831</v>
       </c>
     </row>
     <row r="17">
@@ -648,7 +648,7 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>0.05789553346650611</v>
+        <v>0.03546409807355522</v>
       </c>
     </row>
     <row r="18">
@@ -658,7 +658,7 @@
         </is>
       </c>
       <c r="B18" s="3" t="n">
-        <v>-0.06025186802839066</v>
+        <v>-0.03941336762789305</v>
       </c>
     </row>
     <row r="19">
@@ -692,7 +692,7 @@
     <col width="20" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
     <col width="19" customWidth="1" min="4" max="4"/>
-    <col width="24" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
     <col width="19" customWidth="1" min="6" max="6"/>
     <col width="19" customWidth="1" min="7" max="7"/>
     <col width="20" customWidth="1" min="8" max="8"/>
@@ -753,19 +753,19 @@
         <v>40</v>
       </c>
       <c r="D2" s="5" t="n">
-        <v>41.52000045776367</v>
+        <v>41.2599983215332</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>0.03800001144409171</v>
+        <v>0.03149995803833017</v>
       </c>
       <c r="F2" s="5" t="n">
         <v>33333.33333333333</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>34600.00038146972</v>
+        <v>34383.331934611</v>
       </c>
       <c r="H2" s="5" t="n">
-        <v>1266.667048136391</v>
+        <v>1049.998601277672</v>
       </c>
     </row>
     <row r="3">
@@ -781,19 +781,19 @@
         <v>45.5</v>
       </c>
       <c r="D3" s="5" t="n">
-        <v>43.47999954223633</v>
+        <v>43.15999984741211</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>-0.04439561445634443</v>
+        <v>-0.05142857478215146</v>
       </c>
       <c r="F3" s="5" t="n">
         <v>33333.33333333333</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>31853.47951812185</v>
+        <v>31619.04750726161</v>
       </c>
       <c r="H3" s="5" t="n">
-        <v>-1479.853815211482</v>
+        <v>-1714.285826071715</v>
       </c>
     </row>
     <row r="4">
@@ -809,19 +809,19 @@
         <v>371.25</v>
       </c>
       <c r="D4" s="5" t="n">
-        <v>371</v>
+        <v>374.25</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>-0.0006734006734007147</v>
+        <v>0.008080808080808133</v>
       </c>
       <c r="F4" s="5" t="n">
         <v>33333.33333333333</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>33310.88664421997</v>
+        <v>33602.6936026936</v>
       </c>
       <c r="H4" s="5" t="n">
-        <v>-22.44668911335611</v>
+        <v>269.3602693602734</v>
       </c>
     </row>
   </sheetData>
@@ -836,7 +836,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G28"/>
+  <dimension ref="A1:G29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -1488,13 +1488,13 @@
         <v>46210</v>
       </c>
       <c r="B28" s="5" t="n">
-        <v>99764.36654381154</v>
+        <v>99605.07304456622</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>0</v>
+        <v>-0.001596697345593534</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>-0.002356334561884554</v>
+        <v>-0.003949269554337831</v>
       </c>
       <c r="E28" s="5" t="n">
         <v>14497.400390625</v>
@@ -1503,11 +1503,34 @@
         <v>0.05789553346650611</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>-0.06025186802839066</v>
+        <v>-0.06184480302084394</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="6" t="n">
+        <v>46211</v>
+      </c>
+      <c r="B29" s="5" t="n">
+        <v>99605.07304456622</v>
+      </c>
+      <c r="C29" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D29" s="4" t="n">
+        <v>-0.003949269554337831</v>
+      </c>
+      <c r="E29" s="5" t="n">
+        <v>14190</v>
+      </c>
+      <c r="F29" s="4" t="n">
+        <v>0.03546409807355522</v>
+      </c>
+      <c r="G29" s="4" t="n">
+        <v>-0.03941336762789305</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G28"/>
+  <autoFilter ref="A1:G29"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/reports/latest_one_month_follow_up.xlsx
+++ b/reports/latest_one_month_follow_up.xlsx
@@ -15,7 +15,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'TAKIP_OZETI'!$A$1:$B$19</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'POZISYONLAR'!$A$1:$H$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'GUNLUK_TAKIP'!$A$1:$G$29</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'GUNLUK_TAKIP'!$A$1:$G$30</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'NOTLAR'!$A$1:$A$7</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -475,7 +475,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
     </row>
@@ -546,7 +546,7 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>14190</v>
+        <v>14105.400390625</v>
       </c>
     </row>
     <row r="9">
@@ -603,7 +603,7 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
     </row>
@@ -627,7 +627,7 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>-0.003949269554337831</v>
+        <v>-0.02488452365361637</v>
       </c>
     </row>
     <row r="17">
@@ -648,7 +648,7 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>0.03546409807355522</v>
+        <v>0.02929074654298014</v>
       </c>
     </row>
     <row r="18">
@@ -658,7 +658,7 @@
         </is>
       </c>
       <c r="B18" s="3" t="n">
-        <v>-0.03941336762789305</v>
+        <v>-0.05417527019659651</v>
       </c>
     </row>
     <row r="19">
@@ -692,7 +692,7 @@
     <col width="20" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
     <col width="19" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="23" customWidth="1" min="5" max="5"/>
     <col width="19" customWidth="1" min="6" max="6"/>
     <col width="19" customWidth="1" min="7" max="7"/>
     <col width="20" customWidth="1" min="8" max="8"/>
@@ -753,19 +753,19 @@
         <v>40</v>
       </c>
       <c r="D2" s="5" t="n">
-        <v>41.2599983215332</v>
+        <v>39.93999862670898</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>0.03149995803833017</v>
+        <v>-0.001500034332275413</v>
       </c>
       <c r="F2" s="5" t="n">
         <v>33333.33333333333</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>34383.331934611</v>
+        <v>33283.33218892415</v>
       </c>
       <c r="H2" s="5" t="n">
-        <v>1049.998601277672</v>
+        <v>-50.00114440917969</v>
       </c>
     </row>
     <row r="3">
@@ -781,19 +781,19 @@
         <v>45.5</v>
       </c>
       <c r="D3" s="5" t="n">
-        <v>43.15999984741211</v>
+        <v>41.61999893188477</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>-0.05142857478215146</v>
+        <v>-0.08527474874978536</v>
       </c>
       <c r="F3" s="5" t="n">
         <v>33333.33333333333</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>31619.04750726161</v>
+        <v>30490.84170834048</v>
       </c>
       <c r="H3" s="5" t="n">
-        <v>-1714.285826071715</v>
+        <v>-2842.491624992846</v>
       </c>
     </row>
     <row r="4">
@@ -809,19 +809,19 @@
         <v>371.25</v>
       </c>
       <c r="D4" s="5" t="n">
-        <v>374.25</v>
+        <v>375.75</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>0.008080808080808133</v>
+        <v>0.0121212121212122</v>
       </c>
       <c r="F4" s="5" t="n">
         <v>33333.33333333333</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>33602.6936026936</v>
+        <v>33737.37373737374</v>
       </c>
       <c r="H4" s="5" t="n">
-        <v>269.3602693602734</v>
+        <v>404.0404040404101</v>
       </c>
     </row>
   </sheetData>
@@ -836,7 +836,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G29"/>
+  <dimension ref="A1:G30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -1511,13 +1511,13 @@
         <v>46211</v>
       </c>
       <c r="B29" s="5" t="n">
-        <v>99605.07304456622</v>
+        <v>97511.54763463838</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>0</v>
+        <v>-0.02101826087704517</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>-0.003949269554337831</v>
+        <v>-0.02488452365361615</v>
       </c>
       <c r="E29" s="5" t="n">
         <v>14190</v>
@@ -1526,11 +1526,34 @@
         <v>0.03546409807355522</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>-0.03941336762789305</v>
+        <v>-0.06034862172717137</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="6" t="n">
+        <v>46212</v>
+      </c>
+      <c r="B30" s="5" t="n">
+        <v>97511.54763463838</v>
+      </c>
+      <c r="C30" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D30" s="4" t="n">
+        <v>-0.02488452365361615</v>
+      </c>
+      <c r="E30" s="5" t="n">
+        <v>14105.400390625</v>
+      </c>
+      <c r="F30" s="4" t="n">
+        <v>0.02929074654298014</v>
+      </c>
+      <c r="G30" s="4" t="n">
+        <v>-0.05417527019659629</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G29"/>
+  <autoFilter ref="A1:G30"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/reports/latest_one_month_follow_up.xlsx
+++ b/reports/latest_one_month_follow_up.xlsx
@@ -15,7 +15,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'TAKIP_OZETI'!$A$1:$B$19</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'POZISYONLAR'!$A$1:$H$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'GUNLUK_TAKIP'!$A$1:$G$30</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'GUNLUK_TAKIP'!$A$1:$G$31</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'NOTLAR'!$A$1:$A$7</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -475,7 +475,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
     </row>
@@ -546,7 +546,7 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>14105.400390625</v>
+        <v>14321.2001953125</v>
       </c>
     </row>
     <row r="9">
@@ -603,7 +603,7 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
     </row>
@@ -627,7 +627,7 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>-0.02488452365361637</v>
+        <v>-0.02914095592067123</v>
       </c>
     </row>
     <row r="17">
@@ -648,7 +648,7 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>0.02929074654298014</v>
+        <v>0.04503795937773636</v>
       </c>
     </row>
     <row r="18">
@@ -658,7 +658,7 @@
         </is>
       </c>
       <c r="B18" s="3" t="n">
-        <v>-0.05417527019659651</v>
+        <v>-0.07417891529840759</v>
       </c>
     </row>
     <row r="19">
@@ -692,7 +692,7 @@
     <col width="20" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
     <col width="19" customWidth="1" min="4" max="4"/>
-    <col width="23" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
     <col width="19" customWidth="1" min="6" max="6"/>
     <col width="19" customWidth="1" min="7" max="7"/>
     <col width="20" customWidth="1" min="8" max="8"/>
@@ -753,19 +753,19 @@
         <v>40</v>
       </c>
       <c r="D2" s="5" t="n">
-        <v>39.93999862670898</v>
+        <v>40.06000137329102</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>-0.001500034332275413</v>
+        <v>0.001500034332275302</v>
       </c>
       <c r="F2" s="5" t="n">
         <v>33333.33333333333</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>33283.33218892415</v>
+        <v>33383.33447774251</v>
       </c>
       <c r="H2" s="5" t="n">
-        <v>-50.00114440917969</v>
+        <v>50.00114440917969</v>
       </c>
     </row>
     <row r="3">
@@ -781,19 +781,19 @@
         <v>45.5</v>
       </c>
       <c r="D3" s="5" t="n">
-        <v>41.61999893188477</v>
+        <v>42.22000122070312</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>-0.08527474874978536</v>
+        <v>-0.07208788525927201</v>
       </c>
       <c r="F3" s="5" t="n">
         <v>33333.33333333333</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>30490.84170834048</v>
+        <v>30930.40382469093</v>
       </c>
       <c r="H3" s="5" t="n">
-        <v>-2842.491624992846</v>
+        <v>-2402.929508642399</v>
       </c>
     </row>
     <row r="4">
@@ -809,19 +809,19 @@
         <v>371.25</v>
       </c>
       <c r="D4" s="5" t="n">
-        <v>375.75</v>
+        <v>365</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>0.0121212121212122</v>
+        <v>-0.01683501683501687</v>
       </c>
       <c r="F4" s="5" t="n">
         <v>33333.33333333333</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>33737.37373737374</v>
+        <v>32772.16610549943</v>
       </c>
       <c r="H4" s="5" t="n">
-        <v>404.0404040404101</v>
+        <v>-561.1672278338956</v>
       </c>
     </row>
   </sheetData>
@@ -836,7 +836,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G30"/>
+  <dimension ref="A1:G31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -1534,13 +1534,13 @@
         <v>46212</v>
       </c>
       <c r="B30" s="5" t="n">
-        <v>97511.54763463838</v>
+        <v>97085.90440793287</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>0</v>
+        <v>-0.004365054570770743</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>-0.02488452365361615</v>
+        <v>-0.02914095592067123</v>
       </c>
       <c r="E30" s="5" t="n">
         <v>14105.400390625</v>
@@ -1549,11 +1549,34 @@
         <v>0.02929074654298014</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>-0.05417527019659629</v>
+        <v>-0.05843170246365137</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="6" t="n">
+        <v>46213</v>
+      </c>
+      <c r="B31" s="5" t="n">
+        <v>97085.90440793287</v>
+      </c>
+      <c r="C31" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D31" s="4" t="n">
+        <v>-0.02914095592067123</v>
+      </c>
+      <c r="E31" s="5" t="n">
+        <v>14321.2001953125</v>
+      </c>
+      <c r="F31" s="4" t="n">
+        <v>0.04503795937773636</v>
+      </c>
+      <c r="G31" s="4" t="n">
+        <v>-0.07417891529840759</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G30"/>
+  <autoFilter ref="A1:G31"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/reports/latest_one_month_follow_up.xlsx
+++ b/reports/latest_one_month_follow_up.xlsx
@@ -841,7 +841,7 @@
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
     <col width="19" customWidth="1" min="2" max="2"/>
-    <col width="23" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
     <col width="24" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
     <col width="24" customWidth="1" min="6" max="6"/>
@@ -1215,10 +1215,10 @@
         <v>101665.535802718</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>-0.01517965889001283</v>
+        <v>-0.0151796588900126</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>0.01665535802718021</v>
+        <v>0.01665535802718043</v>
       </c>
       <c r="E16" s="5" t="n">
         <v>14734.5</v>
@@ -1227,7 +1227,7 @@
         <v>0.07519702276707529</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>-0.05854166473989508</v>
+        <v>-0.05854166473989486</v>
       </c>
     </row>
     <row r="17">
@@ -1238,7 +1238,7 @@
         <v>101579.9132001645</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>-0.000842198901303659</v>
+        <v>-0.0008421989013038811</v>
       </c>
       <c r="D17" s="4" t="n">
         <v>0.01579913200164529</v>
@@ -1281,13 +1281,13 @@
         <v>46197</v>
       </c>
       <c r="B19" s="5" t="n">
-        <v>99903.87102493743</v>
+        <v>99903.87102493741</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>-0.007105427940044096</v>
+        <v>-0.007105427940044318</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>-0.0009612897506257045</v>
+        <v>-0.0009612897506259266</v>
       </c>
       <c r="E19" s="5" t="n">
         <v>14331.2001953125</v>
@@ -1296,7 +1296,7 @@
         <v>0.04576767332986709</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>-0.04672896308049279</v>
+        <v>-0.04672896308049301</v>
       </c>
     </row>
     <row r="20">
@@ -1307,7 +1307,7 @@
         <v>99725.18443384963</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>-0.001788585259556053</v>
+        <v>-0.00178858525955583</v>
       </c>
       <c r="D20" s="4" t="n">
         <v>-0.00274815566150366</v>
@@ -1353,10 +1353,10 @@
         <v>100567.2965303391</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>-0.01333614376284464</v>
+        <v>-0.01333614376284487</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>0.00567296530339112</v>
+        <v>0.005672965303390898</v>
       </c>
       <c r="E22" s="5" t="n">
         <v>14183.2001953125</v>
@@ -1365,7 +1365,7 @@
         <v>0.03496790683833195</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>-0.02929494153494083</v>
+        <v>-0.02929494153494105</v>
       </c>
     </row>
     <row r="23">
@@ -1376,7 +1376,7 @@
         <v>98982.15764175884</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>-0.01576197176685634</v>
+        <v>-0.01576197176685612</v>
       </c>
       <c r="D23" s="4" t="n">
         <v>-0.01017842358241161</v>
@@ -1402,7 +1402,7 @@
         <v>0.003127667249263499</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>-0.007082591055235898</v>
+        <v>-0.007082591055236009</v>
       </c>
       <c r="E24" s="5" t="n">
         <v>14350.599609375</v>
@@ -1411,7 +1411,7 @@
         <v>0.0471832756403241</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>-0.05426586669555999</v>
+        <v>-0.05426586669556011</v>
       </c>
     </row>
     <row r="25">
@@ -1422,7 +1422,7 @@
         <v>98699.49739704847</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>-0.005964680366087549</v>
+        <v>-0.005964680366087438</v>
       </c>
       <c r="D25" s="4" t="n">
         <v>-0.01300502602951525</v>
@@ -1511,13 +1511,13 @@
         <v>46211</v>
       </c>
       <c r="B29" s="5" t="n">
-        <v>97511.54763463838</v>
+        <v>97511.54763463837</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>-0.02101826087704517</v>
+        <v>-0.02101826087704539</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>-0.02488452365361615</v>
+        <v>-0.02488452365361637</v>
       </c>
       <c r="E29" s="5" t="n">
         <v>14190</v>
@@ -1526,7 +1526,7 @@
         <v>0.03546409807355522</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>-0.06034862172717137</v>
+        <v>-0.06034862172717159</v>
       </c>
     </row>
     <row r="30">
@@ -1537,7 +1537,7 @@
         <v>97085.90440793287</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>-0.004365054570770743</v>
+        <v>-0.004365054570770521</v>
       </c>
       <c r="D30" s="4" t="n">
         <v>-0.02914095592067123</v>

--- a/reports/latest_one_month_follow_up.xlsx
+++ b/reports/latest_one_month_follow_up.xlsx
@@ -15,7 +15,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'TAKIP_OZETI'!$A$1:$B$19</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'POZISYONLAR'!$A$1:$H$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'GUNLUK_TAKIP'!$A$1:$G$31</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'GUNLUK_TAKIP'!$A$1:$G$32</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'NOTLAR'!$A$1:$A$7</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -475,7 +475,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
     </row>
@@ -546,7 +546,7 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>14321.2001953125</v>
+        <v>14092</v>
       </c>
     </row>
     <row r="9">
@@ -603,7 +603,7 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
     </row>
@@ -627,7 +627,7 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>-0.02914095592067123</v>
+        <v>-0.0106359046476564</v>
       </c>
     </row>
     <row r="17">
@@ -648,7 +648,7 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>0.04503795937773636</v>
+        <v>0.02831290134267372</v>
       </c>
     </row>
     <row r="18">
@@ -658,7 +658,7 @@
         </is>
       </c>
       <c r="B18" s="3" t="n">
-        <v>-0.07417891529840759</v>
+        <v>-0.03894880599033013</v>
       </c>
     </row>
     <row r="19">
@@ -753,19 +753,19 @@
         <v>40</v>
       </c>
       <c r="D2" s="5" t="n">
-        <v>40.06000137329102</v>
+        <v>40.40000152587891</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>0.001500034332275302</v>
+        <v>0.0100000381469727</v>
       </c>
       <c r="F2" s="5" t="n">
         <v>33333.33333333333</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>33383.33447774251</v>
+        <v>33666.66793823242</v>
       </c>
       <c r="H2" s="5" t="n">
-        <v>50.00114440917969</v>
+        <v>333.3346048990934</v>
       </c>
     </row>
     <row r="3">
@@ -781,19 +781,19 @@
         <v>45.5</v>
       </c>
       <c r="D3" s="5" t="n">
-        <v>42.22000122070312</v>
+        <v>43.43999862670898</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>-0.07208788525927201</v>
+        <v>-0.04527475545694537</v>
       </c>
       <c r="F3" s="5" t="n">
         <v>33333.33333333333</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>30930.40382469093</v>
+        <v>31824.17481810182</v>
       </c>
       <c r="H3" s="5" t="n">
-        <v>-2402.929508642399</v>
+        <v>-1509.158515231513</v>
       </c>
     </row>
     <row r="4">
@@ -809,19 +809,19 @@
         <v>371.25</v>
       </c>
       <c r="D4" s="5" t="n">
-        <v>365</v>
+        <v>372.5</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>-0.01683501683501687</v>
+        <v>0.003367003367003463</v>
       </c>
       <c r="F4" s="5" t="n">
         <v>33333.33333333333</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>32772.16610549943</v>
+        <v>33445.56677890011</v>
       </c>
       <c r="H4" s="5" t="n">
-        <v>-561.1672278338956</v>
+        <v>112.2334455667806</v>
       </c>
     </row>
   </sheetData>
@@ -836,12 +836,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G31"/>
+  <dimension ref="A1:G32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
     <col width="19" customWidth="1" min="2" max="2"/>
-    <col width="24" customWidth="1" min="3" max="3"/>
+    <col width="23" customWidth="1" min="3" max="3"/>
     <col width="24" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
     <col width="24" customWidth="1" min="6" max="6"/>
@@ -1215,10 +1215,10 @@
         <v>101665.535802718</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>-0.0151796588900126</v>
+        <v>-0.01517965889001283</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>0.01665535802718043</v>
+        <v>0.01665535802718021</v>
       </c>
       <c r="E16" s="5" t="n">
         <v>14734.5</v>
@@ -1227,7 +1227,7 @@
         <v>0.07519702276707529</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>-0.05854166473989486</v>
+        <v>-0.05854166473989508</v>
       </c>
     </row>
     <row r="17">
@@ -1238,7 +1238,7 @@
         <v>101579.9132001645</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>-0.0008421989013038811</v>
+        <v>-0.000842198901303659</v>
       </c>
       <c r="D17" s="4" t="n">
         <v>0.01579913200164529</v>
@@ -1281,13 +1281,13 @@
         <v>46197</v>
       </c>
       <c r="B19" s="5" t="n">
-        <v>99903.87102493741</v>
+        <v>99903.87102493743</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>-0.007105427940044318</v>
+        <v>-0.007105427940044096</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>-0.0009612897506259266</v>
+        <v>-0.0009612897506257045</v>
       </c>
       <c r="E19" s="5" t="n">
         <v>14331.2001953125</v>
@@ -1296,7 +1296,7 @@
         <v>0.04576767332986709</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>-0.04672896308049301</v>
+        <v>-0.04672896308049279</v>
       </c>
     </row>
     <row r="20">
@@ -1307,7 +1307,7 @@
         <v>99725.18443384963</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>-0.00178858525955583</v>
+        <v>-0.001788585259556053</v>
       </c>
       <c r="D20" s="4" t="n">
         <v>-0.00274815566150366</v>
@@ -1353,10 +1353,10 @@
         <v>100567.2965303391</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>-0.01333614376284487</v>
+        <v>-0.01333614376284464</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>0.005672965303390898</v>
+        <v>0.00567296530339112</v>
       </c>
       <c r="E22" s="5" t="n">
         <v>14183.2001953125</v>
@@ -1365,7 +1365,7 @@
         <v>0.03496790683833195</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>-0.02929494153494105</v>
+        <v>-0.02929494153494083</v>
       </c>
     </row>
     <row r="23">
@@ -1376,7 +1376,7 @@
         <v>98982.15764175884</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>-0.01576197176685612</v>
+        <v>-0.01576197176685634</v>
       </c>
       <c r="D23" s="4" t="n">
         <v>-0.01017842358241161</v>
@@ -1402,7 +1402,7 @@
         <v>0.003127667249263499</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>-0.007082591055236009</v>
+        <v>-0.007082591055235898</v>
       </c>
       <c r="E24" s="5" t="n">
         <v>14350.599609375</v>
@@ -1411,7 +1411,7 @@
         <v>0.0471832756403241</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>-0.05426586669556011</v>
+        <v>-0.05426586669555999</v>
       </c>
     </row>
     <row r="25">
@@ -1422,7 +1422,7 @@
         <v>98699.49739704847</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>-0.005964680366087438</v>
+        <v>-0.005964680366087549</v>
       </c>
       <c r="D25" s="4" t="n">
         <v>-0.01300502602951525</v>
@@ -1511,13 +1511,13 @@
         <v>46211</v>
       </c>
       <c r="B29" s="5" t="n">
-        <v>97511.54763463837</v>
+        <v>97511.54763463838</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>-0.02101826087704539</v>
+        <v>-0.02101826087704517</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>-0.02488452365361637</v>
+        <v>-0.02488452365361615</v>
       </c>
       <c r="E29" s="5" t="n">
         <v>14190</v>
@@ -1526,7 +1526,7 @@
         <v>0.03546409807355522</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>-0.06034862172717159</v>
+        <v>-0.06034862172717137</v>
       </c>
     </row>
     <row r="30">
@@ -1537,7 +1537,7 @@
         <v>97085.90440793287</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>-0.004365054570770521</v>
+        <v>-0.004365054570770743</v>
       </c>
       <c r="D30" s="4" t="n">
         <v>-0.02914095592067123</v>
@@ -1557,13 +1557,13 @@
         <v>46213</v>
       </c>
       <c r="B31" s="5" t="n">
-        <v>97085.90440793287</v>
+        <v>98936.40953523434</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>0</v>
+        <v>0.01906049223712292</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>-0.02914095592067123</v>
+        <v>-0.01063590464765651</v>
       </c>
       <c r="E31" s="5" t="n">
         <v>14321.2001953125</v>
@@ -1572,11 +1572,34 @@
         <v>0.04503795937773636</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>-0.07417891529840759</v>
+        <v>-0.05567386402539287</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="6" t="n">
+        <v>46216</v>
+      </c>
+      <c r="B32" s="5" t="n">
+        <v>98936.40953523434</v>
+      </c>
+      <c r="C32" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D32" s="4" t="n">
+        <v>-0.01063590464765651</v>
+      </c>
+      <c r="E32" s="5" t="n">
+        <v>14092</v>
+      </c>
+      <c r="F32" s="4" t="n">
+        <v>0.02831290134267372</v>
+      </c>
+      <c r="G32" s="4" t="n">
+        <v>-0.03894880599033024</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G31"/>
+  <autoFilter ref="A1:G32"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/reports/latest_one_month_follow_up.xlsx
+++ b/reports/latest_one_month_follow_up.xlsx
@@ -475,7 +475,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -603,7 +603,7 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>-0.0106359046476564</v>
+        <v>-0.007429107314285033</v>
       </c>
     </row>
     <row r="17">
@@ -658,7 +658,7 @@
         </is>
       </c>
       <c r="B18" s="3" t="n">
-        <v>-0.03894880599033013</v>
+        <v>-0.03574200865695876</v>
       </c>
     </row>
     <row r="19">
@@ -694,8 +694,8 @@
     <col width="19" customWidth="1" min="4" max="4"/>
     <col width="22" customWidth="1" min="5" max="5"/>
     <col width="19" customWidth="1" min="6" max="6"/>
-    <col width="19" customWidth="1" min="7" max="7"/>
-    <col width="20" customWidth="1" min="8" max="8"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="19" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -753,19 +753,19 @@
         <v>40</v>
       </c>
       <c r="D2" s="5" t="n">
-        <v>40.40000152587891</v>
+        <v>40.86000061035156</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>0.0100000381469727</v>
+        <v>0.02150001525878897</v>
       </c>
       <c r="F2" s="5" t="n">
         <v>33333.33333333333</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>33666.66793823242</v>
+        <v>34050.0005086263</v>
       </c>
       <c r="H2" s="5" t="n">
-        <v>333.3346048990934</v>
+        <v>716.6671752929688</v>
       </c>
     </row>
     <row r="3">
@@ -781,19 +781,19 @@
         <v>45.5</v>
       </c>
       <c r="D3" s="5" t="n">
-        <v>43.43999862670898</v>
+        <v>43.13999938964844</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>-0.04527475545694537</v>
+        <v>-0.05186814528245187</v>
       </c>
       <c r="F3" s="5" t="n">
         <v>33333.33333333333</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>31824.17481810182</v>
+        <v>31604.3951572516</v>
       </c>
       <c r="H3" s="5" t="n">
-        <v>-1509.158515231513</v>
+        <v>-1728.93817608173</v>
       </c>
     </row>
     <row r="4">
@@ -809,19 +809,19 @@
         <v>371.25</v>
       </c>
       <c r="D4" s="5" t="n">
-        <v>372.5</v>
+        <v>374.25</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>0.003367003367003463</v>
+        <v>0.008080808080808133</v>
       </c>
       <c r="F4" s="5" t="n">
         <v>33333.33333333333</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>33445.56677890011</v>
+        <v>33602.6936026936</v>
       </c>
       <c r="H4" s="5" t="n">
-        <v>112.2334455667806</v>
+        <v>269.3602693602734</v>
       </c>
     </row>
   </sheetData>
@@ -1580,13 +1580,13 @@
         <v>46216</v>
       </c>
       <c r="B32" s="5" t="n">
-        <v>98936.40953523434</v>
+        <v>99257.08926857149</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>0</v>
+        <v>0.003241271184628358</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>-0.01063590464765651</v>
+        <v>-0.007429107314285033</v>
       </c>
       <c r="E32" s="5" t="n">
         <v>14092</v>
@@ -1595,7 +1595,7 @@
         <v>0.02831290134267372</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>-0.03894880599033024</v>
+        <v>-0.03574200865695876</v>
       </c>
     </row>
   </sheetData>

--- a/reports/latest_one_month_follow_up.xlsx
+++ b/reports/latest_one_month_follow_up.xlsx
@@ -15,7 +15,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'TAKIP_OZETI'!$A$1:$B$19</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'POZISYONLAR'!$A$1:$H$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'GUNLUK_TAKIP'!$A$1:$G$32</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'GUNLUK_TAKIP'!$A$1:$G$33</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'NOTLAR'!$A$1:$A$7</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -475,7 +475,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
     </row>
@@ -546,7 +546,7 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>14092</v>
+        <v>14080</v>
       </c>
     </row>
     <row r="9">
@@ -603,7 +603,7 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
     </row>
@@ -627,7 +627,7 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>-0.007429107314285033</v>
+        <v>0.01364399569969166</v>
       </c>
     </row>
     <row r="17">
@@ -648,7 +648,7 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>0.02831290134267372</v>
+        <v>0.02743724460011676</v>
       </c>
     </row>
     <row r="18">
@@ -658,7 +658,7 @@
         </is>
       </c>
       <c r="B18" s="3" t="n">
-        <v>-0.03574200865695876</v>
+        <v>-0.0137932489004251</v>
       </c>
     </row>
     <row r="19">
@@ -669,7 +669,7 @@
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>Zararda / BIST Altı</t>
+          <t>Karda / BIST Altı</t>
         </is>
       </c>
     </row>
@@ -694,8 +694,8 @@
     <col width="19" customWidth="1" min="4" max="4"/>
     <col width="22" customWidth="1" min="5" max="5"/>
     <col width="19" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
-    <col width="19" customWidth="1" min="8" max="8"/>
+    <col width="19" customWidth="1" min="7" max="7"/>
+    <col width="20" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -753,19 +753,19 @@
         <v>40</v>
       </c>
       <c r="D2" s="5" t="n">
-        <v>40.86000061035156</v>
+        <v>41.88000106811523</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>0.02150001525878897</v>
+        <v>0.04700002670288095</v>
       </c>
       <c r="F2" s="5" t="n">
         <v>33333.33333333333</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>34050.0005086263</v>
+        <v>34900.00089009602</v>
       </c>
       <c r="H2" s="5" t="n">
-        <v>716.6671752929688</v>
+        <v>1566.667556762695</v>
       </c>
     </row>
     <row r="3">
@@ -781,19 +781,19 @@
         <v>45.5</v>
       </c>
       <c r="D3" s="5" t="n">
-        <v>43.13999938964844</v>
+        <v>43.59999847412109</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>-0.05186814528245187</v>
+        <v>-0.04175827529404186</v>
       </c>
       <c r="F3" s="5" t="n">
         <v>33333.33333333333</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>31604.3951572516</v>
+        <v>31941.39082353193</v>
       </c>
       <c r="H3" s="5" t="n">
-        <v>-1728.93817608173</v>
+        <v>-1391.942509801396</v>
       </c>
     </row>
     <row r="4">
@@ -809,19 +809,19 @@
         <v>371.25</v>
       </c>
       <c r="D4" s="5" t="n">
-        <v>374.25</v>
+        <v>384.5</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>0.008080808080808133</v>
+        <v>0.03569023569023577</v>
       </c>
       <c r="F4" s="5" t="n">
         <v>33333.33333333333</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>33602.6936026936</v>
+        <v>34523.00785634119</v>
       </c>
       <c r="H4" s="5" t="n">
-        <v>269.3602693602734</v>
+        <v>1189.67452300786</v>
       </c>
     </row>
   </sheetData>
@@ -836,7 +836,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G32"/>
+  <dimension ref="A1:G33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -1598,8 +1598,31 @@
         <v>-0.03574200865695876</v>
       </c>
     </row>
+    <row r="33">
+      <c r="A33" s="6" t="n">
+        <v>46217</v>
+      </c>
+      <c r="B33" s="5" t="n">
+        <v>101364.3995699692</v>
+      </c>
+      <c r="C33" s="4" t="n">
+        <v>0.02123082912189456</v>
+      </c>
+      <c r="D33" s="4" t="n">
+        <v>0.01364399569969166</v>
+      </c>
+      <c r="E33" s="5" t="n">
+        <v>14080</v>
+      </c>
+      <c r="F33" s="4" t="n">
+        <v>0.02743724460011676</v>
+      </c>
+      <c r="G33" s="4" t="n">
+        <v>-0.0137932489004251</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G32"/>
+  <autoFilter ref="A1:G33"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/reports/latest_one_month_follow_up.xlsx
+++ b/reports/latest_one_month_follow_up.xlsx
@@ -15,7 +15,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'TAKIP_OZETI'!$A$1:$B$19</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'POZISYONLAR'!$A$1:$H$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'GUNLUK_TAKIP'!$A$1:$G$33</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'GUNLUK_TAKIP'!$A$1:$G$34</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'NOTLAR'!$A$1:$A$7</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -546,7 +546,7 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>14080</v>
+        <v>14251.2998046875</v>
       </c>
     </row>
     <row r="9">
@@ -627,7 +627,7 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-16</t>
         </is>
       </c>
     </row>
@@ -648,7 +648,7 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>0.02743724460011676</v>
+        <v>0.0399372303478911</v>
       </c>
     </row>
     <row r="18">
@@ -658,7 +658,7 @@
         </is>
       </c>
       <c r="B18" s="3" t="n">
-        <v>-0.0137932489004251</v>
+        <v>-0.02629323464819944</v>
       </c>
     </row>
     <row r="19">
@@ -836,7 +836,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G33"/>
+  <dimension ref="A1:G34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -1621,8 +1621,31 @@
         <v>-0.0137932489004251</v>
       </c>
     </row>
+    <row r="34">
+      <c r="A34" s="6" t="n">
+        <v>46219</v>
+      </c>
+      <c r="B34" s="5" t="n">
+        <v>101364.3995699692</v>
+      </c>
+      <c r="C34" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D34" s="4" t="n">
+        <v>0.01364399569969166</v>
+      </c>
+      <c r="E34" s="5" t="n">
+        <v>14251.2998046875</v>
+      </c>
+      <c r="F34" s="4" t="n">
+        <v>0.0399372303478911</v>
+      </c>
+      <c r="G34" s="4" t="n">
+        <v>-0.02629323464819944</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G33"/>
+  <autoFilter ref="A1:G34"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/reports/latest_one_month_follow_up.xlsx
+++ b/reports/latest_one_month_follow_up.xlsx
@@ -15,7 +15,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'TAKIP_OZETI'!$A$1:$B$19</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'POZISYONLAR'!$A$1:$H$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'GUNLUK_TAKIP'!$A$1:$G$34</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'GUNLUK_TAKIP'!$A$1:$G$35</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'NOTLAR'!$A$1:$A$7</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -475,7 +475,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-16</t>
         </is>
       </c>
     </row>
@@ -546,7 +546,7 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>14251.2998046875</v>
+        <v>13981.099609375</v>
       </c>
     </row>
     <row r="9">
@@ -603,7 +603,7 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-16</t>
         </is>
       </c>
     </row>
@@ -627,7 +627,7 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>0.01364399569969166</v>
+        <v>0.05261703022777708</v>
       </c>
     </row>
     <row r="17">
@@ -648,7 +648,7 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>0.0399372303478911</v>
+        <v>0.02022034510909232</v>
       </c>
     </row>
     <row r="18">
@@ -658,7 +658,7 @@
         </is>
       </c>
       <c r="B18" s="3" t="n">
-        <v>-0.02629323464819944</v>
+        <v>0.03239668511868476</v>
       </c>
     </row>
     <row r="19">
@@ -669,7 +669,7 @@
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>Karda / BIST Altı</t>
+          <t>Karda / BIST Üstü</t>
         </is>
       </c>
     </row>
@@ -753,19 +753,19 @@
         <v>40</v>
       </c>
       <c r="D2" s="5" t="n">
-        <v>41.88000106811523</v>
+        <v>44.06000137329102</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>0.04700002670288095</v>
+        <v>0.1015000343322754</v>
       </c>
       <c r="F2" s="5" t="n">
         <v>33333.33333333333</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>34900.00089009602</v>
+        <v>36716.66781107584</v>
       </c>
       <c r="H2" s="5" t="n">
-        <v>1566.667556762695</v>
+        <v>3383.334477742515</v>
       </c>
     </row>
     <row r="3">
@@ -781,19 +781,19 @@
         <v>45.5</v>
       </c>
       <c r="D3" s="5" t="n">
-        <v>43.59999847412109</v>
+        <v>45</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>-0.04175827529404186</v>
+        <v>-0.01098901098901095</v>
       </c>
       <c r="F3" s="5" t="n">
         <v>33333.33333333333</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>31941.39082353193</v>
+        <v>32967.03296703297</v>
       </c>
       <c r="H3" s="5" t="n">
-        <v>-1391.942509801396</v>
+        <v>-366.3003663003619</v>
       </c>
     </row>
     <row r="4">
@@ -809,19 +809,19 @@
         <v>371.25</v>
       </c>
       <c r="D4" s="5" t="n">
-        <v>384.5</v>
+        <v>396.25</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>0.03569023569023577</v>
+        <v>0.06734006734006726</v>
       </c>
       <c r="F4" s="5" t="n">
         <v>33333.33333333333</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>34523.00785634119</v>
+        <v>35578.0022446689</v>
       </c>
       <c r="H4" s="5" t="n">
-        <v>1189.67452300786</v>
+        <v>2244.668911335575</v>
       </c>
     </row>
   </sheetData>
@@ -836,7 +836,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G34"/>
+  <dimension ref="A1:G35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -1626,13 +1626,13 @@
         <v>46219</v>
       </c>
       <c r="B34" s="5" t="n">
-        <v>101364.3995699692</v>
+        <v>105261.7030227777</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>0</v>
+        <v>0.03844844412182757</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>0.01364399569969166</v>
+        <v>0.05261703022777731</v>
       </c>
       <c r="E34" s="5" t="n">
         <v>14251.2998046875</v>
@@ -1641,11 +1641,34 @@
         <v>0.0399372303478911</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>-0.02629323464819944</v>
+        <v>0.01267979987988621</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="6" t="n">
+        <v>46220</v>
+      </c>
+      <c r="B35" s="5" t="n">
+        <v>105261.7030227777</v>
+      </c>
+      <c r="C35" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D35" s="4" t="n">
+        <v>0.05261703022777731</v>
+      </c>
+      <c r="E35" s="5" t="n">
+        <v>13981.099609375</v>
+      </c>
+      <c r="F35" s="4" t="n">
+        <v>0.02022034510909232</v>
+      </c>
+      <c r="G35" s="4" t="n">
+        <v>0.03239668511868499</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G34"/>
+  <autoFilter ref="A1:G35"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/reports/latest_one_month_follow_up.xlsx
+++ b/reports/latest_one_month_follow_up.xlsx
@@ -841,7 +841,7 @@
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
     <col width="19" customWidth="1" min="2" max="2"/>
-    <col width="23" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
     <col width="24" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
     <col width="24" customWidth="1" min="6" max="6"/>
@@ -1215,10 +1215,10 @@
         <v>101665.535802718</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>-0.01517965889001283</v>
+        <v>-0.0151796588900126</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>0.01665535802718021</v>
+        <v>0.01665535802718043</v>
       </c>
       <c r="E16" s="5" t="n">
         <v>14734.5</v>
@@ -1227,7 +1227,7 @@
         <v>0.07519702276707529</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>-0.05854166473989508</v>
+        <v>-0.05854166473989486</v>
       </c>
     </row>
     <row r="17">
@@ -1238,7 +1238,7 @@
         <v>101579.9132001645</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>-0.000842198901303659</v>
+        <v>-0.0008421989013038811</v>
       </c>
       <c r="D17" s="4" t="n">
         <v>0.01579913200164529</v>
@@ -1281,13 +1281,13 @@
         <v>46197</v>
       </c>
       <c r="B19" s="5" t="n">
-        <v>99903.87102493743</v>
+        <v>99903.87102493741</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>-0.007105427940044096</v>
+        <v>-0.007105427940044318</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>-0.0009612897506257045</v>
+        <v>-0.0009612897506259266</v>
       </c>
       <c r="E19" s="5" t="n">
         <v>14331.2001953125</v>
@@ -1296,7 +1296,7 @@
         <v>0.04576767332986709</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>-0.04672896308049279</v>
+        <v>-0.04672896308049301</v>
       </c>
     </row>
     <row r="20">
@@ -1307,7 +1307,7 @@
         <v>99725.18443384963</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>-0.001788585259556053</v>
+        <v>-0.00178858525955583</v>
       </c>
       <c r="D20" s="4" t="n">
         <v>-0.00274815566150366</v>
@@ -1353,10 +1353,10 @@
         <v>100567.2965303391</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>-0.01333614376284464</v>
+        <v>-0.01333614376284487</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>0.00567296530339112</v>
+        <v>0.005672965303390898</v>
       </c>
       <c r="E22" s="5" t="n">
         <v>14183.2001953125</v>
@@ -1365,7 +1365,7 @@
         <v>0.03496790683833195</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>-0.02929494153494083</v>
+        <v>-0.02929494153494105</v>
       </c>
     </row>
     <row r="23">
@@ -1376,7 +1376,7 @@
         <v>98982.15764175884</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>-0.01576197176685634</v>
+        <v>-0.01576197176685612</v>
       </c>
       <c r="D23" s="4" t="n">
         <v>-0.01017842358241161</v>
@@ -1402,7 +1402,7 @@
         <v>0.003127667249263499</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>-0.007082591055235898</v>
+        <v>-0.007082591055236009</v>
       </c>
       <c r="E24" s="5" t="n">
         <v>14350.599609375</v>
@@ -1411,7 +1411,7 @@
         <v>0.0471832756403241</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>-0.05426586669555999</v>
+        <v>-0.05426586669556011</v>
       </c>
     </row>
     <row r="25">
@@ -1422,7 +1422,7 @@
         <v>98699.49739704847</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>-0.005964680366087549</v>
+        <v>-0.005964680366087438</v>
       </c>
       <c r="D25" s="4" t="n">
         <v>-0.01300502602951525</v>
@@ -1511,13 +1511,13 @@
         <v>46211</v>
       </c>
       <c r="B29" s="5" t="n">
-        <v>97511.54763463838</v>
+        <v>97511.54763463837</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>-0.02101826087704517</v>
+        <v>-0.02101826087704539</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>-0.02488452365361615</v>
+        <v>-0.02488452365361637</v>
       </c>
       <c r="E29" s="5" t="n">
         <v>14190</v>
@@ -1526,7 +1526,7 @@
         <v>0.03546409807355522</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>-0.06034862172717137</v>
+        <v>-0.06034862172717159</v>
       </c>
     </row>
     <row r="30">
@@ -1537,7 +1537,7 @@
         <v>97085.90440793287</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>-0.004365054570770743</v>
+        <v>-0.004365054570770521</v>
       </c>
       <c r="D30" s="4" t="n">
         <v>-0.02914095592067123</v>
@@ -1603,13 +1603,13 @@
         <v>46217</v>
       </c>
       <c r="B33" s="5" t="n">
-        <v>101364.3995699692</v>
+        <v>101364.3995699691</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>0.02123082912189456</v>
+        <v>0.02123082912189433</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>0.01364399569969166</v>
+        <v>0.01364399569969144</v>
       </c>
       <c r="E33" s="5" t="n">
         <v>14080</v>
@@ -1618,7 +1618,7 @@
         <v>0.02743724460011676</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>-0.0137932489004251</v>
+        <v>-0.01379324890042533</v>
       </c>
     </row>
     <row r="34">
@@ -1629,7 +1629,7 @@
         <v>105261.7030227777</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>0.03844844412182757</v>
+        <v>0.0384484441218278</v>
       </c>
       <c r="D34" s="4" t="n">
         <v>0.05261703022777731</v>

--- a/reports/latest_one_month_follow_up.xlsx
+++ b/reports/latest_one_month_follow_up.xlsx
@@ -15,7 +15,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'TAKIP_OZETI'!$A$1:$B$19</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'POZISYONLAR'!$A$1:$H$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'GUNLUK_TAKIP'!$A$1:$G$35</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'GUNLUK_TAKIP'!$A$1:$G$36</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'NOTLAR'!$A$1:$A$7</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -475,7 +475,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
     </row>
@@ -546,7 +546,7 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>13981.099609375</v>
+        <v>14071</v>
       </c>
     </row>
     <row r="9">
@@ -603,7 +603,7 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
     </row>
@@ -627,7 +627,7 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>0.05261703022777708</v>
+        <v>0.02321974391393589</v>
       </c>
     </row>
     <row r="17">
@@ -648,7 +648,7 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>0.02022034510909232</v>
+        <v>0.02678050204319904</v>
       </c>
     </row>
     <row r="18">
@@ -658,7 +658,7 @@
         </is>
       </c>
       <c r="B18" s="3" t="n">
-        <v>0.03239668511868476</v>
+        <v>-0.003560758129263153</v>
       </c>
     </row>
     <row r="19">
@@ -669,7 +669,7 @@
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>Karda / BIST Üstü</t>
+          <t>Karda / BIST Altı</t>
         </is>
       </c>
     </row>
@@ -753,19 +753,19 @@
         <v>40</v>
       </c>
       <c r="D2" s="5" t="n">
-        <v>44.06000137329102</v>
+        <v>42.34000015258789</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>0.1015000343322754</v>
+        <v>0.05850000381469722</v>
       </c>
       <c r="F2" s="5" t="n">
         <v>33333.33333333333</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>36716.66781107584</v>
+        <v>35283.3334604899</v>
       </c>
       <c r="H2" s="5" t="n">
-        <v>3383.334477742515</v>
+        <v>1950.000127156571</v>
       </c>
     </row>
     <row r="3">
@@ -781,19 +781,19 @@
         <v>45.5</v>
       </c>
       <c r="D3" s="5" t="n">
-        <v>45</v>
+        <v>44.20000076293945</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>-0.01098901098901095</v>
+        <v>-0.02857141180352851</v>
       </c>
       <c r="F3" s="5" t="n">
         <v>33333.33333333333</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>32967.03296703297</v>
+        <v>32380.95293988238</v>
       </c>
       <c r="H3" s="5" t="n">
-        <v>-366.3003663003619</v>
+        <v>-952.3803934509488</v>
       </c>
     </row>
     <row r="4">
@@ -809,19 +809,19 @@
         <v>371.25</v>
       </c>
       <c r="D4" s="5" t="n">
-        <v>396.25</v>
+        <v>386</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>0.06734006734006726</v>
+        <v>0.03973063973063984</v>
       </c>
       <c r="F4" s="5" t="n">
         <v>33333.33333333333</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>35578.0022446689</v>
+        <v>34657.68799102132</v>
       </c>
       <c r="H4" s="5" t="n">
-        <v>2244.668911335575</v>
+        <v>1324.354657687996</v>
       </c>
     </row>
   </sheetData>
@@ -836,16 +836,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G35"/>
+  <dimension ref="A1:G36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
     <col width="19" customWidth="1" min="2" max="2"/>
-    <col width="24" customWidth="1" min="3" max="3"/>
+    <col width="23" customWidth="1" min="3" max="3"/>
     <col width="24" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
     <col width="24" customWidth="1" min="6" max="6"/>
-    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="23" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1215,10 +1215,10 @@
         <v>101665.535802718</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>-0.0151796588900126</v>
+        <v>-0.01517965889001283</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>0.01665535802718043</v>
+        <v>0.01665535802718021</v>
       </c>
       <c r="E16" s="5" t="n">
         <v>14734.5</v>
@@ -1227,7 +1227,7 @@
         <v>0.07519702276707529</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>-0.05854166473989486</v>
+        <v>-0.05854166473989508</v>
       </c>
     </row>
     <row r="17">
@@ -1238,7 +1238,7 @@
         <v>101579.9132001645</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>-0.0008421989013038811</v>
+        <v>-0.000842198901303659</v>
       </c>
       <c r="D17" s="4" t="n">
         <v>0.01579913200164529</v>
@@ -1281,13 +1281,13 @@
         <v>46197</v>
       </c>
       <c r="B19" s="5" t="n">
-        <v>99903.87102493741</v>
+        <v>99903.87102493743</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>-0.007105427940044318</v>
+        <v>-0.007105427940044096</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>-0.0009612897506259266</v>
+        <v>-0.0009612897506257045</v>
       </c>
       <c r="E19" s="5" t="n">
         <v>14331.2001953125</v>
@@ -1296,7 +1296,7 @@
         <v>0.04576767332986709</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>-0.04672896308049301</v>
+        <v>-0.04672896308049279</v>
       </c>
     </row>
     <row r="20">
@@ -1307,7 +1307,7 @@
         <v>99725.18443384963</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>-0.00178858525955583</v>
+        <v>-0.001788585259556053</v>
       </c>
       <c r="D20" s="4" t="n">
         <v>-0.00274815566150366</v>
@@ -1353,10 +1353,10 @@
         <v>100567.2965303391</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>-0.01333614376284487</v>
+        <v>-0.01333614376284464</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>0.005672965303390898</v>
+        <v>0.00567296530339112</v>
       </c>
       <c r="E22" s="5" t="n">
         <v>14183.2001953125</v>
@@ -1365,7 +1365,7 @@
         <v>0.03496790683833195</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>-0.02929494153494105</v>
+        <v>-0.02929494153494083</v>
       </c>
     </row>
     <row r="23">
@@ -1376,7 +1376,7 @@
         <v>98982.15764175884</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>-0.01576197176685612</v>
+        <v>-0.01576197176685634</v>
       </c>
       <c r="D23" s="4" t="n">
         <v>-0.01017842358241161</v>
@@ -1402,7 +1402,7 @@
         <v>0.003127667249263499</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>-0.007082591055236009</v>
+        <v>-0.007082591055235898</v>
       </c>
       <c r="E24" s="5" t="n">
         <v>14350.599609375</v>
@@ -1411,7 +1411,7 @@
         <v>0.0471832756403241</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>-0.05426586669556011</v>
+        <v>-0.05426586669555999</v>
       </c>
     </row>
     <row r="25">
@@ -1422,7 +1422,7 @@
         <v>98699.49739704847</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>-0.005964680366087438</v>
+        <v>-0.005964680366087549</v>
       </c>
       <c r="D25" s="4" t="n">
         <v>-0.01300502602951525</v>
@@ -1511,13 +1511,13 @@
         <v>46211</v>
       </c>
       <c r="B29" s="5" t="n">
-        <v>97511.54763463837</v>
+        <v>97511.54763463838</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>-0.02101826087704539</v>
+        <v>-0.02101826087704517</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>-0.02488452365361637</v>
+        <v>-0.02488452365361615</v>
       </c>
       <c r="E29" s="5" t="n">
         <v>14190</v>
@@ -1526,7 +1526,7 @@
         <v>0.03546409807355522</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>-0.06034862172717159</v>
+        <v>-0.06034862172717137</v>
       </c>
     </row>
     <row r="30">
@@ -1537,7 +1537,7 @@
         <v>97085.90440793287</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>-0.004365054570770521</v>
+        <v>-0.004365054570770743</v>
       </c>
       <c r="D30" s="4" t="n">
         <v>-0.02914095592067123</v>
@@ -1603,13 +1603,13 @@
         <v>46217</v>
       </c>
       <c r="B33" s="5" t="n">
-        <v>101364.3995699691</v>
+        <v>101364.3995699692</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>0.02123082912189433</v>
+        <v>0.02123082912189456</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>0.01364399569969144</v>
+        <v>0.01364399569969166</v>
       </c>
       <c r="E33" s="5" t="n">
         <v>14080</v>
@@ -1618,7 +1618,7 @@
         <v>0.02743724460011676</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>-0.01379324890042533</v>
+        <v>-0.0137932489004251</v>
       </c>
     </row>
     <row r="34">
@@ -1629,7 +1629,7 @@
         <v>105261.7030227777</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>0.0384484441218278</v>
+        <v>0.03844844412182757</v>
       </c>
       <c r="D34" s="4" t="n">
         <v>0.05261703022777731</v>
@@ -1649,13 +1649,13 @@
         <v>46220</v>
       </c>
       <c r="B35" s="5" t="n">
-        <v>105261.7030227777</v>
+        <v>102321.9743913936</v>
       </c>
       <c r="C35" s="4" t="n">
-        <v>0</v>
+        <v>-0.02792780799630412</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>0.05261703022777731</v>
+        <v>0.02321974391393611</v>
       </c>
       <c r="E35" s="5" t="n">
         <v>13981.099609375</v>
@@ -1664,11 +1664,34 @@
         <v>0.02022034510909232</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>0.03239668511868499</v>
+        <v>0.002999398804843789</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="6" t="n">
+        <v>46223</v>
+      </c>
+      <c r="B36" s="5" t="n">
+        <v>102321.9743913936</v>
+      </c>
+      <c r="C36" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D36" s="4" t="n">
+        <v>0.02321974391393611</v>
+      </c>
+      <c r="E36" s="5" t="n">
+        <v>14071</v>
+      </c>
+      <c r="F36" s="4" t="n">
+        <v>0.02678050204319904</v>
+      </c>
+      <c r="G36" s="4" t="n">
+        <v>-0.003560758129262931</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G35"/>
+  <autoFilter ref="A1:G36"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/reports/latest_one_month_follow_up.xlsx
+++ b/reports/latest_one_month_follow_up.xlsx
@@ -15,7 +15,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'TAKIP_OZETI'!$A$1:$B$19</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'POZISYONLAR'!$A$1:$H$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'GUNLUK_TAKIP'!$A$1:$G$36</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'GUNLUK_TAKIP'!$A$1:$G$37</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'NOTLAR'!$A$1:$A$7</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -475,7 +475,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
     </row>
@@ -546,7 +546,7 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>14071</v>
+        <v>13974.099609375</v>
       </c>
     </row>
     <row r="9">
@@ -603,7 +603,7 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
     </row>
@@ -627,7 +627,7 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>0.02321974391393589</v>
+        <v>0.04848767243869423</v>
       </c>
     </row>
     <row r="17">
@@ -648,7 +648,7 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>0.02678050204319904</v>
+        <v>0.01970954534260061</v>
       </c>
     </row>
     <row r="18">
@@ -658,7 +658,7 @@
         </is>
       </c>
       <c r="B18" s="3" t="n">
-        <v>-0.003560758129263153</v>
+        <v>0.02877812709609362</v>
       </c>
     </row>
     <row r="19">
@@ -669,7 +669,7 @@
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>Karda / BIST Altı</t>
+          <t>Karda / BIST Üstü</t>
         </is>
       </c>
     </row>
@@ -753,19 +753,19 @@
         <v>40</v>
       </c>
       <c r="D2" s="5" t="n">
-        <v>42.34000015258789</v>
+        <v>43.59999847412109</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>0.05850000381469722</v>
+        <v>0.08999996185302739</v>
       </c>
       <c r="F2" s="5" t="n">
         <v>33333.33333333333</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>35283.3334604899</v>
+        <v>36333.33206176757</v>
       </c>
       <c r="H2" s="5" t="n">
-        <v>1950.000127156571</v>
+        <v>2999.998728434242</v>
       </c>
     </row>
     <row r="3">
@@ -781,19 +781,19 @@
         <v>45.5</v>
       </c>
       <c r="D3" s="5" t="n">
-        <v>44.20000076293945</v>
+        <v>44.5</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>-0.02857141180352851</v>
+        <v>-0.02197802197802201</v>
       </c>
       <c r="F3" s="5" t="n">
         <v>33333.33333333333</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>32380.95293988238</v>
+        <v>32600.73260073259</v>
       </c>
       <c r="H3" s="5" t="n">
-        <v>-952.3803934509488</v>
+        <v>-732.6007326007348</v>
       </c>
     </row>
     <row r="4">
@@ -809,19 +809,19 @@
         <v>371.25</v>
       </c>
       <c r="D4" s="5" t="n">
-        <v>386</v>
+        <v>400</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>0.03973063973063984</v>
+        <v>0.07744107744107742</v>
       </c>
       <c r="F4" s="5" t="n">
         <v>33333.33333333333</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>34657.68799102132</v>
+        <v>35914.70258136925</v>
       </c>
       <c r="H4" s="5" t="n">
-        <v>1324.354657687996</v>
+        <v>2581.369248035917</v>
       </c>
     </row>
   </sheetData>
@@ -836,7 +836,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G36"/>
+  <dimension ref="A1:G37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -845,7 +845,7 @@
     <col width="24" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
     <col width="24" customWidth="1" min="6" max="6"/>
-    <col width="23" customWidth="1" min="7" max="7"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1672,13 +1672,13 @@
         <v>46223</v>
       </c>
       <c r="B36" s="5" t="n">
-        <v>102321.9743913936</v>
+        <v>104848.7672438694</v>
       </c>
       <c r="C36" s="4" t="n">
-        <v>0</v>
+        <v>0.02469452791059856</v>
       </c>
       <c r="D36" s="4" t="n">
-        <v>0.02321974391393611</v>
+        <v>0.04848767243869423</v>
       </c>
       <c r="E36" s="5" t="n">
         <v>14071</v>
@@ -1687,11 +1687,34 @@
         <v>0.02678050204319904</v>
       </c>
       <c r="G36" s="4" t="n">
-        <v>-0.003560758129262931</v>
+        <v>0.02170717039549519</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="6" t="n">
+        <v>46224</v>
+      </c>
+      <c r="B37" s="5" t="n">
+        <v>104848.7672438694</v>
+      </c>
+      <c r="C37" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D37" s="4" t="n">
+        <v>0.04848767243869423</v>
+      </c>
+      <c r="E37" s="5" t="n">
+        <v>13974.099609375</v>
+      </c>
+      <c r="F37" s="4" t="n">
+        <v>0.01970954534260061</v>
+      </c>
+      <c r="G37" s="4" t="n">
+        <v>0.02877812709609362</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G36"/>
+  <autoFilter ref="A1:G37"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/reports/latest_one_month_follow_up.xlsx
+++ b/reports/latest_one_month_follow_up.xlsx
@@ -15,7 +15,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'TAKIP_OZETI'!$A$1:$B$19</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'POZISYONLAR'!$A$1:$H$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'GUNLUK_TAKIP'!$A$1:$G$37</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'GUNLUK_TAKIP'!$A$1:$G$38</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'NOTLAR'!$A$1:$A$7</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -475,7 +475,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -546,7 +546,7 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>13974.099609375</v>
+        <v>14138.900390625</v>
       </c>
     </row>
     <row r="9">
@@ -603,7 +603,7 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -627,7 +627,7 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>0.04848767243869423</v>
+        <v>0.02169894507684011</v>
       </c>
     </row>
     <row r="17">
@@ -648,7 +648,7 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>0.01970954534260061</v>
+        <v>0.03173528828261829</v>
       </c>
     </row>
     <row r="18">
@@ -658,7 +658,7 @@
         </is>
       </c>
       <c r="B18" s="3" t="n">
-        <v>0.02877812709609362</v>
+        <v>-0.01003634320577818</v>
       </c>
     </row>
     <row r="19">
@@ -669,7 +669,7 @@
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>Karda / BIST Üstü</t>
+          <t>Karda / BIST Altı</t>
         </is>
       </c>
     </row>
@@ -753,19 +753,19 @@
         <v>40</v>
       </c>
       <c r="D2" s="5" t="n">
-        <v>43.59999847412109</v>
+        <v>42.29999923706055</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>0.08999996185302739</v>
+        <v>0.05749998092651376</v>
       </c>
       <c r="F2" s="5" t="n">
         <v>33333.33333333333</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>36333.33206176757</v>
+        <v>35249.99936421712</v>
       </c>
       <c r="H2" s="5" t="n">
-        <v>2999.998728434242</v>
+        <v>1916.666030883789</v>
       </c>
     </row>
     <row r="3">
@@ -781,19 +781,19 @@
         <v>45.5</v>
       </c>
       <c r="D3" s="5" t="n">
-        <v>44.5</v>
+        <v>43.18000030517578</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>-0.02197802197802201</v>
+        <v>-0.05098900428185094</v>
       </c>
       <c r="F3" s="5" t="n">
         <v>33333.33333333333</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>32600.73260073259</v>
+        <v>31633.69985727163</v>
       </c>
       <c r="H3" s="5" t="n">
-        <v>-732.6007326007348</v>
+        <v>-1699.633476061699</v>
       </c>
     </row>
     <row r="4">
@@ -809,19 +809,19 @@
         <v>371.25</v>
       </c>
       <c r="D4" s="5" t="n">
-        <v>400</v>
+        <v>393</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>0.07744107744107742</v>
+        <v>0.05858585858585852</v>
       </c>
       <c r="F4" s="5" t="n">
         <v>33333.33333333333</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>35914.70258136925</v>
+        <v>35286.19528619528</v>
       </c>
       <c r="H4" s="5" t="n">
-        <v>2581.369248035917</v>
+        <v>1952.861952861953</v>
       </c>
     </row>
   </sheetData>
@@ -836,7 +836,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G37"/>
+  <dimension ref="A1:G38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -1695,13 +1695,13 @@
         <v>46224</v>
       </c>
       <c r="B37" s="5" t="n">
-        <v>104848.7672438694</v>
+        <v>102169.894507684</v>
       </c>
       <c r="C37" s="4" t="n">
-        <v>0</v>
+        <v>-0.02554987346636661</v>
       </c>
       <c r="D37" s="4" t="n">
-        <v>0.04848767243869423</v>
+        <v>0.02169894507684034</v>
       </c>
       <c r="E37" s="5" t="n">
         <v>13974.099609375</v>
@@ -1710,11 +1710,34 @@
         <v>0.01970954534260061</v>
       </c>
       <c r="G37" s="4" t="n">
-        <v>0.02877812709609362</v>
+        <v>0.001989399734239727</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="6" t="n">
+        <v>46225</v>
+      </c>
+      <c r="B38" s="5" t="n">
+        <v>102169.894507684</v>
+      </c>
+      <c r="C38" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D38" s="4" t="n">
+        <v>0.02169894507684034</v>
+      </c>
+      <c r="E38" s="5" t="n">
+        <v>14138.900390625</v>
+      </c>
+      <c r="F38" s="4" t="n">
+        <v>0.03173528828261829</v>
+      </c>
+      <c r="G38" s="4" t="n">
+        <v>-0.01003634320577795</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G37"/>
+  <autoFilter ref="A1:G38"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/reports/latest_one_month_follow_up.xlsx
+++ b/reports/latest_one_month_follow_up.xlsx
@@ -15,7 +15,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'TAKIP_OZETI'!$A$1:$B$19</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'POZISYONLAR'!$A$1:$H$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'GUNLUK_TAKIP'!$A$1:$G$38</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'GUNLUK_TAKIP'!$A$1:$G$39</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'NOTLAR'!$A$1:$A$7</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -475,7 +475,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -546,7 +546,7 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>14138.900390625</v>
+        <v>14077.7001953125</v>
       </c>
     </row>
     <row r="9">
@@ -603,7 +603,7 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -627,7 +627,7 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>0.02169894507684011</v>
+        <v>0.03048300464520182</v>
       </c>
     </row>
     <row r="17">
@@ -648,7 +648,7 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>0.03173528828261829</v>
+        <v>0.02726942464335225</v>
       </c>
     </row>
     <row r="18">
@@ -658,7 +658,7 @@
         </is>
       </c>
       <c r="B18" s="3" t="n">
-        <v>-0.01003634320577818</v>
+        <v>0.00321358000184957</v>
       </c>
     </row>
     <row r="19">
@@ -669,7 +669,7 @@
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>Karda / BIST Altı</t>
+          <t>Karda / BIST Üstü</t>
         </is>
       </c>
     </row>
@@ -753,19 +753,19 @@
         <v>40</v>
       </c>
       <c r="D2" s="5" t="n">
-        <v>42.29999923706055</v>
+        <v>42.2400016784668</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>0.05749998092651376</v>
+        <v>0.05600004196166997</v>
       </c>
       <c r="F2" s="5" t="n">
         <v>33333.33333333333</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>35249.99936421712</v>
+        <v>35200.00139872233</v>
       </c>
       <c r="H2" s="5" t="n">
-        <v>1916.666030883789</v>
+        <v>1866.668065389</v>
       </c>
     </row>
     <row r="3">
@@ -781,19 +781,19 @@
         <v>45.5</v>
       </c>
       <c r="D3" s="5" t="n">
-        <v>43.18000030517578</v>
+        <v>43.61999893188477</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>-0.05098900428185094</v>
+        <v>-0.04131870479374145</v>
       </c>
       <c r="F3" s="5" t="n">
         <v>33333.33333333333</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>31633.69985727163</v>
+        <v>31956.04317354195</v>
       </c>
       <c r="H3" s="5" t="n">
-        <v>-1699.633476061699</v>
+        <v>-1377.290159791381</v>
       </c>
     </row>
     <row r="4">
@@ -809,19 +809,19 @@
         <v>371.25</v>
       </c>
       <c r="D4" s="5" t="n">
-        <v>393</v>
+        <v>399.75</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>0.05858585858585852</v>
+        <v>0.07676767676767682</v>
       </c>
       <c r="F4" s="5" t="n">
         <v>33333.33333333333</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>35286.19528619528</v>
+        <v>35892.25589225589</v>
       </c>
       <c r="H4" s="5" t="n">
-        <v>1952.861952861953</v>
+        <v>2558.922558922561</v>
       </c>
     </row>
   </sheetData>
@@ -836,7 +836,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G38"/>
+  <dimension ref="A1:G39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -845,7 +845,7 @@
     <col width="24" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
     <col width="24" customWidth="1" min="6" max="6"/>
-    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="23" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1718,13 +1718,13 @@
         <v>46225</v>
       </c>
       <c r="B38" s="5" t="n">
-        <v>102169.894507684</v>
+        <v>103048.3004645202</v>
       </c>
       <c r="C38" s="4" t="n">
-        <v>0</v>
+        <v>0.008597502826726222</v>
       </c>
       <c r="D38" s="4" t="n">
-        <v>0.02169894507684034</v>
+        <v>0.03048300464520159</v>
       </c>
       <c r="E38" s="5" t="n">
         <v>14138.900390625</v>
@@ -1733,11 +1733,34 @@
         <v>0.03173528828261829</v>
       </c>
       <c r="G38" s="4" t="n">
-        <v>-0.01003634320577795</v>
+        <v>-0.001252283637416696</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="6" t="n">
+        <v>46226</v>
+      </c>
+      <c r="B39" s="5" t="n">
+        <v>103048.3004645202</v>
+      </c>
+      <c r="C39" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D39" s="4" t="n">
+        <v>0.03048300464520159</v>
+      </c>
+      <c r="E39" s="5" t="n">
+        <v>14077.7001953125</v>
+      </c>
+      <c r="F39" s="4" t="n">
+        <v>0.02726942464335225</v>
+      </c>
+      <c r="G39" s="4" t="n">
+        <v>0.003213580001849348</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G38"/>
+  <autoFilter ref="A1:G39"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/reports/latest_one_month_follow_up.xlsx
+++ b/reports/latest_one_month_follow_up.xlsx
@@ -15,7 +15,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'TAKIP_OZETI'!$A$1:$B$19</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'POZISYONLAR'!$A$1:$H$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'GUNLUK_TAKIP'!$A$1:$G$39</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'GUNLUK_TAKIP'!$A$1:$G$40</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'NOTLAR'!$A$1:$A$7</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -475,7 +475,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
     </row>
@@ -546,7 +546,7 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>14077.7001953125</v>
+        <v>13943.900390625</v>
       </c>
     </row>
     <row r="9">
@@ -603,7 +603,7 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
     </row>
@@ -627,7 +627,7 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>0.03048300464520182</v>
+        <v>0.0389506258774992</v>
       </c>
     </row>
     <row r="17">
@@ -648,7 +648,7 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>0.02726942464335225</v>
+        <v>0.01750586621606831</v>
       </c>
     </row>
     <row r="18">
@@ -658,7 +658,7 @@
         </is>
       </c>
       <c r="B18" s="3" t="n">
-        <v>0.00321358000184957</v>
+        <v>0.02144475966143089</v>
       </c>
     </row>
     <row r="19">
@@ -753,19 +753,19 @@
         <v>40</v>
       </c>
       <c r="D2" s="5" t="n">
-        <v>42.2400016784668</v>
+        <v>44.20000076293945</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>0.05600004196166997</v>
+        <v>0.1050000190734863</v>
       </c>
       <c r="F2" s="5" t="n">
         <v>33333.33333333333</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>35200.00139872233</v>
+        <v>36833.3339691162</v>
       </c>
       <c r="H2" s="5" t="n">
-        <v>1866.668065389</v>
+        <v>3500.000635782875</v>
       </c>
     </row>
     <row r="3">
@@ -781,19 +781,19 @@
         <v>45.5</v>
       </c>
       <c r="D3" s="5" t="n">
-        <v>43.61999893188477</v>
+        <v>43.68000030517578</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>-0.04131870479374145</v>
+        <v>-0.03999999329283999</v>
       </c>
       <c r="F3" s="5" t="n">
         <v>33333.33333333333</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>31956.04317354195</v>
+        <v>32000.00022357199</v>
       </c>
       <c r="H3" s="5" t="n">
-        <v>-1377.290159791381</v>
+        <v>-1333.333109761334</v>
       </c>
     </row>
     <row r="4">
@@ -809,19 +809,19 @@
         <v>371.25</v>
       </c>
       <c r="D4" s="5" t="n">
-        <v>399.75</v>
+        <v>390.5</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>0.07676767676767682</v>
+        <v>0.05185185185185182</v>
       </c>
       <c r="F4" s="5" t="n">
         <v>33333.33333333333</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>35892.25589225589</v>
+        <v>35061.72839506172</v>
       </c>
       <c r="H4" s="5" t="n">
-        <v>2558.922558922561</v>
+        <v>1728.395061728392</v>
       </c>
     </row>
   </sheetData>
@@ -836,7 +836,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G39"/>
+  <dimension ref="A1:G40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -1741,13 +1741,13 @@
         <v>46226</v>
       </c>
       <c r="B39" s="5" t="n">
-        <v>103048.3004645202</v>
+        <v>103895.0625877499</v>
       </c>
       <c r="C39" s="4" t="n">
-        <v>0</v>
+        <v>0.008217138171253247</v>
       </c>
       <c r="D39" s="4" t="n">
-        <v>0.03048300464520159</v>
+        <v>0.03895062587749942</v>
       </c>
       <c r="E39" s="5" t="n">
         <v>14077.7001953125</v>
@@ -1756,11 +1756,34 @@
         <v>0.02726942464335225</v>
       </c>
       <c r="G39" s="4" t="n">
-        <v>0.003213580001849348</v>
+        <v>0.01168120123414718</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="6" t="n">
+        <v>46227</v>
+      </c>
+      <c r="B40" s="5" t="n">
+        <v>103895.0625877499</v>
+      </c>
+      <c r="C40" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D40" s="4" t="n">
+        <v>0.03895062587749942</v>
+      </c>
+      <c r="E40" s="5" t="n">
+        <v>13943.900390625</v>
+      </c>
+      <c r="F40" s="4" t="n">
+        <v>0.01750586621606831</v>
+      </c>
+      <c r="G40" s="4" t="n">
+        <v>0.02144475966143111</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G39"/>
+  <autoFilter ref="A1:G40"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/reports/latest_one_month_follow_up.xlsx
+++ b/reports/latest_one_month_follow_up.xlsx
@@ -841,7 +841,7 @@
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
     <col width="19" customWidth="1" min="2" max="2"/>
-    <col width="23" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
     <col width="24" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
     <col width="24" customWidth="1" min="6" max="6"/>
@@ -1215,10 +1215,10 @@
         <v>101665.535802718</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>-0.01517965889001283</v>
+        <v>-0.0151796588900126</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>0.01665535802718021</v>
+        <v>0.01665535802718043</v>
       </c>
       <c r="E16" s="5" t="n">
         <v>14734.5</v>
@@ -1227,7 +1227,7 @@
         <v>0.07519702276707529</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>-0.05854166473989508</v>
+        <v>-0.05854166473989486</v>
       </c>
     </row>
     <row r="17">
@@ -1238,7 +1238,7 @@
         <v>101579.9132001645</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>-0.000842198901303659</v>
+        <v>-0.0008421989013038811</v>
       </c>
       <c r="D17" s="4" t="n">
         <v>0.01579913200164529</v>
@@ -1281,13 +1281,13 @@
         <v>46197</v>
       </c>
       <c r="B19" s="5" t="n">
-        <v>99903.87102493743</v>
+        <v>99903.87102493741</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>-0.007105427940044096</v>
+        <v>-0.007105427940044318</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>-0.0009612897506257045</v>
+        <v>-0.0009612897506259266</v>
       </c>
       <c r="E19" s="5" t="n">
         <v>14331.2001953125</v>
@@ -1296,7 +1296,7 @@
         <v>0.04576767332986709</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>-0.04672896308049279</v>
+        <v>-0.04672896308049301</v>
       </c>
     </row>
     <row r="20">
@@ -1307,7 +1307,7 @@
         <v>99725.18443384963</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>-0.001788585259556053</v>
+        <v>-0.00178858525955583</v>
       </c>
       <c r="D20" s="4" t="n">
         <v>-0.00274815566150366</v>
@@ -1353,10 +1353,10 @@
         <v>100567.2965303391</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>-0.01333614376284464</v>
+        <v>-0.01333614376284487</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>0.00567296530339112</v>
+        <v>0.005672965303390898</v>
       </c>
       <c r="E22" s="5" t="n">
         <v>14183.2001953125</v>
@@ -1365,7 +1365,7 @@
         <v>0.03496790683833195</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>-0.02929494153494083</v>
+        <v>-0.02929494153494105</v>
       </c>
     </row>
     <row r="23">
@@ -1376,7 +1376,7 @@
         <v>98982.15764175884</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>-0.01576197176685634</v>
+        <v>-0.01576197176685612</v>
       </c>
       <c r="D23" s="4" t="n">
         <v>-0.01017842358241161</v>
@@ -1402,7 +1402,7 @@
         <v>0.003127667249263499</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>-0.007082591055235898</v>
+        <v>-0.007082591055236009</v>
       </c>
       <c r="E24" s="5" t="n">
         <v>14350.599609375</v>
@@ -1411,7 +1411,7 @@
         <v>0.0471832756403241</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>-0.05426586669555999</v>
+        <v>-0.05426586669556011</v>
       </c>
     </row>
     <row r="25">
@@ -1422,7 +1422,7 @@
         <v>98699.49739704847</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>-0.005964680366087549</v>
+        <v>-0.005964680366087438</v>
       </c>
       <c r="D25" s="4" t="n">
         <v>-0.01300502602951525</v>
@@ -1511,13 +1511,13 @@
         <v>46211</v>
       </c>
       <c r="B29" s="5" t="n">
-        <v>97511.54763463838</v>
+        <v>97511.54763463837</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>-0.02101826087704517</v>
+        <v>-0.02101826087704539</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>-0.02488452365361615</v>
+        <v>-0.02488452365361637</v>
       </c>
       <c r="E29" s="5" t="n">
         <v>14190</v>
@@ -1526,7 +1526,7 @@
         <v>0.03546409807355522</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>-0.06034862172717137</v>
+        <v>-0.06034862172717159</v>
       </c>
     </row>
     <row r="30">
@@ -1537,7 +1537,7 @@
         <v>97085.90440793287</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>-0.004365054570770743</v>
+        <v>-0.004365054570770521</v>
       </c>
       <c r="D30" s="4" t="n">
         <v>-0.02914095592067123</v>
@@ -1603,13 +1603,13 @@
         <v>46217</v>
       </c>
       <c r="B33" s="5" t="n">
-        <v>101364.3995699692</v>
+        <v>101364.3995699691</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>0.02123082912189456</v>
+        <v>0.02123082912189433</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>0.01364399569969166</v>
+        <v>0.01364399569969144</v>
       </c>
       <c r="E33" s="5" t="n">
         <v>14080</v>
@@ -1618,7 +1618,7 @@
         <v>0.02743724460011676</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>-0.0137932489004251</v>
+        <v>-0.01379324890042533</v>
       </c>
     </row>
     <row r="34">
@@ -1629,7 +1629,7 @@
         <v>105261.7030227777</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>0.03844844412182757</v>
+        <v>0.0384484441218278</v>
       </c>
       <c r="D34" s="4" t="n">
         <v>0.05261703022777731</v>
@@ -1675,10 +1675,10 @@
         <v>104848.7672438694</v>
       </c>
       <c r="C36" s="4" t="n">
-        <v>0.02469452791059856</v>
+        <v>0.02469452791059834</v>
       </c>
       <c r="D36" s="4" t="n">
-        <v>0.04848767243869423</v>
+        <v>0.04848767243869401</v>
       </c>
       <c r="E36" s="5" t="n">
         <v>14071</v>
@@ -1687,7 +1687,7 @@
         <v>0.02678050204319904</v>
       </c>
       <c r="G36" s="4" t="n">
-        <v>0.02170717039549519</v>
+        <v>0.02170717039549497</v>
       </c>
     </row>
     <row r="37">
@@ -1698,7 +1698,7 @@
         <v>102169.894507684</v>
       </c>
       <c r="C37" s="4" t="n">
-        <v>-0.02554987346636661</v>
+        <v>-0.02554987346636639</v>
       </c>
       <c r="D37" s="4" t="n">
         <v>0.02169894507684034</v>

--- a/reports/latest_one_month_follow_up.xlsx
+++ b/reports/latest_one_month_follow_up.xlsx
@@ -15,7 +15,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'TAKIP_OZETI'!$A$1:$B$19</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'POZISYONLAR'!$A$1:$H$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'GUNLUK_TAKIP'!$A$1:$G$40</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'GUNLUK_TAKIP'!$A$1:$G$41</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'NOTLAR'!$A$1:$A$7</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -475,7 +475,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
     </row>
@@ -546,7 +546,7 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>13943.900390625</v>
+        <v>13774.7998046875</v>
       </c>
     </row>
     <row r="9">
@@ -603,7 +603,7 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
     </row>
@@ -627,7 +627,7 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>0.0389506258774992</v>
+        <v>0.02017602258919982</v>
       </c>
     </row>
     <row r="17">
@@ -648,7 +648,7 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>0.01750586621606831</v>
+        <v>0.005166360528860103</v>
       </c>
     </row>
     <row r="18">
@@ -658,7 +658,7 @@
         </is>
       </c>
       <c r="B18" s="3" t="n">
-        <v>0.02144475966143089</v>
+        <v>0.01500966206033971</v>
       </c>
     </row>
     <row r="19">
@@ -753,19 +753,19 @@
         <v>40</v>
       </c>
       <c r="D2" s="5" t="n">
-        <v>44.20000076293945</v>
+        <v>43.27999877929688</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>0.1050000190734863</v>
+        <v>0.08199996948242183</v>
       </c>
       <c r="F2" s="5" t="n">
         <v>33333.33333333333</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>36833.3339691162</v>
+        <v>36066.66564941406</v>
       </c>
       <c r="H2" s="5" t="n">
-        <v>3500.000635782875</v>
+        <v>2733.332316080727</v>
       </c>
     </row>
     <row r="3">
@@ -781,19 +781,19 @@
         <v>45.5</v>
       </c>
       <c r="D3" s="5" t="n">
-        <v>43.68000030517578</v>
+        <v>43.41999816894531</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>-0.03999999329283999</v>
+        <v>-0.04571432595724589</v>
       </c>
       <c r="F3" s="5" t="n">
         <v>33333.33333333333</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>32000.00022357199</v>
+        <v>31809.5224680918</v>
       </c>
       <c r="H3" s="5" t="n">
-        <v>-1333.333109761334</v>
+        <v>-1523.810865241529</v>
       </c>
     </row>
     <row r="4">
@@ -809,19 +809,19 @@
         <v>371.25</v>
       </c>
       <c r="D4" s="5" t="n">
-        <v>390.5</v>
+        <v>380.25</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>0.05185185185185182</v>
+        <v>0.02424242424242418</v>
       </c>
       <c r="F4" s="5" t="n">
         <v>33333.33333333333</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>35061.72839506172</v>
+        <v>34141.41414141413</v>
       </c>
       <c r="H4" s="5" t="n">
-        <v>1728.395061728392</v>
+        <v>808.0808080808056</v>
       </c>
     </row>
   </sheetData>
@@ -836,12 +836,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G40"/>
+  <dimension ref="A1:G41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
     <col width="19" customWidth="1" min="2" max="2"/>
-    <col width="24" customWidth="1" min="3" max="3"/>
+    <col width="23" customWidth="1" min="3" max="3"/>
     <col width="24" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
     <col width="24" customWidth="1" min="6" max="6"/>
@@ -1215,10 +1215,10 @@
         <v>101665.535802718</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>-0.0151796588900126</v>
+        <v>-0.01517965889001283</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>0.01665535802718043</v>
+        <v>0.01665535802718021</v>
       </c>
       <c r="E16" s="5" t="n">
         <v>14734.5</v>
@@ -1227,7 +1227,7 @@
         <v>0.07519702276707529</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>-0.05854166473989486</v>
+        <v>-0.05854166473989508</v>
       </c>
     </row>
     <row r="17">
@@ -1238,7 +1238,7 @@
         <v>101579.9132001645</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>-0.0008421989013038811</v>
+        <v>-0.000842198901303659</v>
       </c>
       <c r="D17" s="4" t="n">
         <v>0.01579913200164529</v>
@@ -1281,13 +1281,13 @@
         <v>46197</v>
       </c>
       <c r="B19" s="5" t="n">
-        <v>99903.87102493741</v>
+        <v>99903.87102493743</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>-0.007105427940044318</v>
+        <v>-0.007105427940044096</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>-0.0009612897506259266</v>
+        <v>-0.0009612897506257045</v>
       </c>
       <c r="E19" s="5" t="n">
         <v>14331.2001953125</v>
@@ -1296,7 +1296,7 @@
         <v>0.04576767332986709</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>-0.04672896308049301</v>
+        <v>-0.04672896308049279</v>
       </c>
     </row>
     <row r="20">
@@ -1307,7 +1307,7 @@
         <v>99725.18443384963</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>-0.00178858525955583</v>
+        <v>-0.001788585259556053</v>
       </c>
       <c r="D20" s="4" t="n">
         <v>-0.00274815566150366</v>
@@ -1353,10 +1353,10 @@
         <v>100567.2965303391</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>-0.01333614376284487</v>
+        <v>-0.01333614376284464</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>0.005672965303390898</v>
+        <v>0.00567296530339112</v>
       </c>
       <c r="E22" s="5" t="n">
         <v>14183.2001953125</v>
@@ -1365,7 +1365,7 @@
         <v>0.03496790683833195</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>-0.02929494153494105</v>
+        <v>-0.02929494153494083</v>
       </c>
     </row>
     <row r="23">
@@ -1376,7 +1376,7 @@
         <v>98982.15764175884</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>-0.01576197176685612</v>
+        <v>-0.01576197176685634</v>
       </c>
       <c r="D23" s="4" t="n">
         <v>-0.01017842358241161</v>
@@ -1402,7 +1402,7 @@
         <v>0.003127667249263499</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>-0.007082591055236009</v>
+        <v>-0.007082591055235898</v>
       </c>
       <c r="E24" s="5" t="n">
         <v>14350.599609375</v>
@@ -1411,7 +1411,7 @@
         <v>0.0471832756403241</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>-0.05426586669556011</v>
+        <v>-0.05426586669555999</v>
       </c>
     </row>
     <row r="25">
@@ -1422,7 +1422,7 @@
         <v>98699.49739704847</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>-0.005964680366087438</v>
+        <v>-0.005964680366087549</v>
       </c>
       <c r="D25" s="4" t="n">
         <v>-0.01300502602951525</v>
@@ -1511,13 +1511,13 @@
         <v>46211</v>
       </c>
       <c r="B29" s="5" t="n">
-        <v>97511.54763463837</v>
+        <v>97511.54763463838</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>-0.02101826087704539</v>
+        <v>-0.02101826087704517</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>-0.02488452365361637</v>
+        <v>-0.02488452365361615</v>
       </c>
       <c r="E29" s="5" t="n">
         <v>14190</v>
@@ -1526,7 +1526,7 @@
         <v>0.03546409807355522</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>-0.06034862172717159</v>
+        <v>-0.06034862172717137</v>
       </c>
     </row>
     <row r="30">
@@ -1537,7 +1537,7 @@
         <v>97085.90440793287</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>-0.004365054570770521</v>
+        <v>-0.004365054570770743</v>
       </c>
       <c r="D30" s="4" t="n">
         <v>-0.02914095592067123</v>
@@ -1603,13 +1603,13 @@
         <v>46217</v>
       </c>
       <c r="B33" s="5" t="n">
-        <v>101364.3995699691</v>
+        <v>101364.3995699692</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>0.02123082912189433</v>
+        <v>0.02123082912189456</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>0.01364399569969144</v>
+        <v>0.01364399569969166</v>
       </c>
       <c r="E33" s="5" t="n">
         <v>14080</v>
@@ -1618,7 +1618,7 @@
         <v>0.02743724460011676</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>-0.01379324890042533</v>
+        <v>-0.0137932489004251</v>
       </c>
     </row>
     <row r="34">
@@ -1629,7 +1629,7 @@
         <v>105261.7030227777</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>0.0384484441218278</v>
+        <v>0.03844844412182757</v>
       </c>
       <c r="D34" s="4" t="n">
         <v>0.05261703022777731</v>
@@ -1675,10 +1675,10 @@
         <v>104848.7672438694</v>
       </c>
       <c r="C36" s="4" t="n">
-        <v>0.02469452791059834</v>
+        <v>0.02469452791059856</v>
       </c>
       <c r="D36" s="4" t="n">
-        <v>0.04848767243869401</v>
+        <v>0.04848767243869423</v>
       </c>
       <c r="E36" s="5" t="n">
         <v>14071</v>
@@ -1687,7 +1687,7 @@
         <v>0.02678050204319904</v>
       </c>
       <c r="G36" s="4" t="n">
-        <v>0.02170717039549497</v>
+        <v>0.02170717039549519</v>
       </c>
     </row>
     <row r="37">
@@ -1698,7 +1698,7 @@
         <v>102169.894507684</v>
       </c>
       <c r="C37" s="4" t="n">
-        <v>-0.02554987346636639</v>
+        <v>-0.02554987346636661</v>
       </c>
       <c r="D37" s="4" t="n">
         <v>0.02169894507684034</v>
@@ -1764,26 +1764,49 @@
         <v>46227</v>
       </c>
       <c r="B40" s="5" t="n">
-        <v>103895.0625877499</v>
+        <v>102017.60225892</v>
       </c>
       <c r="C40" s="4" t="n">
+        <v>-0.01807073678062643</v>
+      </c>
+      <c r="D40" s="4" t="n">
+        <v>0.02017602258920004</v>
+      </c>
+      <c r="E40" s="5" t="n">
+        <v>14077.7001953125</v>
+      </c>
+      <c r="F40" s="4" t="n">
+        <v>0.02726942464335225</v>
+      </c>
+      <c r="G40" s="4" t="n">
+        <v>-0.007093402054152209</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="6" t="n">
+        <v>46230</v>
+      </c>
+      <c r="B41" s="5" t="n">
+        <v>102017.60225892</v>
+      </c>
+      <c r="C41" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="D40" s="4" t="n">
-        <v>0.03895062587749942</v>
-      </c>
-      <c r="E40" s="5" t="n">
-        <v>13943.900390625</v>
-      </c>
-      <c r="F40" s="4" t="n">
-        <v>0.01750586621606831</v>
-      </c>
-      <c r="G40" s="4" t="n">
-        <v>0.02144475966143111</v>
+      <c r="D41" s="4" t="n">
+        <v>0.02017602258920004</v>
+      </c>
+      <c r="E41" s="5" t="n">
+        <v>13774.7998046875</v>
+      </c>
+      <c r="F41" s="4" t="n">
+        <v>0.005166360528860103</v>
+      </c>
+      <c r="G41" s="4" t="n">
+        <v>0.01500966206033993</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G40"/>
+  <autoFilter ref="A1:G41"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/reports/latest_one_month_follow_up.xlsx
+++ b/reports/latest_one_month_follow_up.xlsx
@@ -15,7 +15,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'TAKIP_OZETI'!$A$1:$B$19</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'POZISYONLAR'!$A$1:$H$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'GUNLUK_TAKIP'!$A$1:$G$41</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'GUNLUK_TAKIP'!$A$1:$G$42</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'NOTLAR'!$A$1:$A$7</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -475,7 +475,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -546,7 +546,7 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>13774.7998046875</v>
+        <v>13687.900390625</v>
       </c>
     </row>
     <row r="9">
@@ -603,7 +603,7 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -627,7 +627,7 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>0.02017602258919982</v>
+        <v>0.0193329981386352</v>
       </c>
     </row>
     <row r="17">
@@ -648,7 +648,7 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>0.005166360528860103</v>
+        <v>-0.001174810958479267</v>
       </c>
     </row>
     <row r="18">
@@ -658,7 +658,7 @@
         </is>
       </c>
       <c r="B18" s="3" t="n">
-        <v>0.01500966206033971</v>
+        <v>0.02050780909711447</v>
       </c>
     </row>
     <row r="19">
@@ -753,19 +753,19 @@
         <v>40</v>
       </c>
       <c r="D2" s="5" t="n">
-        <v>43.27999877929688</v>
+        <v>43.2599983215332</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>0.08199996948242183</v>
+        <v>0.08149995803832999</v>
       </c>
       <c r="F2" s="5" t="n">
         <v>33333.33333333333</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>36066.66564941406</v>
+        <v>36049.99860127766</v>
       </c>
       <c r="H2" s="5" t="n">
-        <v>2733.332316080727</v>
+        <v>2716.665267944336</v>
       </c>
     </row>
     <row r="3">
@@ -781,19 +781,19 @@
         <v>45.5</v>
       </c>
       <c r="D3" s="5" t="n">
-        <v>43.41999816894531</v>
+        <v>42.95999908447266</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>-0.04571432595724589</v>
+        <v>-0.05582419594565591</v>
       </c>
       <c r="F3" s="5" t="n">
         <v>33333.33333333333</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>31809.5224680918</v>
+        <v>31472.52680181147</v>
       </c>
       <c r="H3" s="5" t="n">
-        <v>-1523.810865241529</v>
+        <v>-1860.806531521863</v>
       </c>
     </row>
     <row r="4">
@@ -809,19 +809,19 @@
         <v>371.25</v>
       </c>
       <c r="D4" s="5" t="n">
-        <v>380.25</v>
+        <v>383.25</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>0.02424242424242418</v>
+        <v>0.03232323232323231</v>
       </c>
       <c r="F4" s="5" t="n">
         <v>33333.33333333333</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>34141.41414141413</v>
+        <v>34410.77441077441</v>
       </c>
       <c r="H4" s="5" t="n">
-        <v>808.0808080808056</v>
+        <v>1077.441077441079</v>
       </c>
     </row>
   </sheetData>
@@ -836,12 +836,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G41"/>
+  <dimension ref="A1:G42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
     <col width="19" customWidth="1" min="2" max="2"/>
-    <col width="23" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
     <col width="24" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
     <col width="24" customWidth="1" min="6" max="6"/>
@@ -1773,13 +1773,13 @@
         <v>0.02017602258920004</v>
       </c>
       <c r="E40" s="5" t="n">
-        <v>14077.7001953125</v>
+        <v>13943.900390625</v>
       </c>
       <c r="F40" s="4" t="n">
-        <v>0.02726942464335225</v>
+        <v>0.01750586621606831</v>
       </c>
       <c r="G40" s="4" t="n">
-        <v>-0.007093402054152209</v>
+        <v>0.002670156373131727</v>
       </c>
     </row>
     <row r="41">
@@ -1787,13 +1787,13 @@
         <v>46230</v>
       </c>
       <c r="B41" s="5" t="n">
-        <v>102017.60225892</v>
+        <v>101933.2998138635</v>
       </c>
       <c r="C41" s="4" t="n">
-        <v>0</v>
+        <v>-0.0008263519548568077</v>
       </c>
       <c r="D41" s="4" t="n">
-        <v>0.02017602258920004</v>
+        <v>0.01933299813863543</v>
       </c>
       <c r="E41" s="5" t="n">
         <v>13774.7998046875</v>
@@ -1802,11 +1802,34 @@
         <v>0.005166360528860103</v>
       </c>
       <c r="G41" s="4" t="n">
-        <v>0.01500966206033993</v>
+        <v>0.01416663760977532</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="6" t="n">
+        <v>46231</v>
+      </c>
+      <c r="B42" s="5" t="n">
+        <v>101933.2998138635</v>
+      </c>
+      <c r="C42" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D42" s="4" t="n">
+        <v>0.01933299813863543</v>
+      </c>
+      <c r="E42" s="5" t="n">
+        <v>13687.900390625</v>
+      </c>
+      <c r="F42" s="4" t="n">
+        <v>-0.001174810958479267</v>
+      </c>
+      <c r="G42" s="4" t="n">
+        <v>0.02050780909711469</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G41"/>
+  <autoFilter ref="A1:G42"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/reports/latest_one_month_follow_up.xlsx
+++ b/reports/latest_one_month_follow_up.xlsx
@@ -15,7 +15,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'TAKIP_OZETI'!$A$1:$B$19</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'POZISYONLAR'!$A$1:$H$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'GUNLUK_TAKIP'!$A$1:$G$42</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'GUNLUK_TAKIP'!$A$1:$G$43</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'NOTLAR'!$A$1:$A$7</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -475,7 +475,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
     </row>
@@ -546,7 +546,7 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>13687.900390625</v>
+        <v>13501.599609375</v>
       </c>
     </row>
     <row r="9">
@@ -603,7 +603,7 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
     </row>
@@ -627,7 +627,7 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>0.0193329981386352</v>
+        <v>0.02672125632775746</v>
       </c>
     </row>
     <row r="17">
@@ -648,7 +648,7 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>-0.001174810958479267</v>
+        <v>-0.01476943889557791</v>
       </c>
     </row>
     <row r="18">
@@ -658,7 +658,7 @@
         </is>
       </c>
       <c r="B18" s="3" t="n">
-        <v>0.02050780909711447</v>
+        <v>0.04149069522333537</v>
       </c>
     </row>
     <row r="19">
@@ -692,7 +692,7 @@
     <col width="20" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
     <col width="19" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="21" customWidth="1" min="5" max="5"/>
     <col width="19" customWidth="1" min="6" max="6"/>
     <col width="19" customWidth="1" min="7" max="7"/>
     <col width="20" customWidth="1" min="8" max="8"/>
@@ -753,19 +753,19 @@
         <v>40</v>
       </c>
       <c r="D2" s="5" t="n">
-        <v>43.2599983215332</v>
+        <v>43.86000061035156</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>0.08149995803832999</v>
+        <v>0.09650001525878915</v>
       </c>
       <c r="F2" s="5" t="n">
         <v>33333.33333333333</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>36049.99860127766</v>
+        <v>36550.0005086263</v>
       </c>
       <c r="H2" s="5" t="n">
-        <v>2716.665267944336</v>
+        <v>3216.667175292969</v>
       </c>
     </row>
     <row r="3">
@@ -781,19 +781,19 @@
         <v>45.5</v>
       </c>
       <c r="D3" s="5" t="n">
-        <v>42.95999908447266</v>
+        <v>42.52000045776367</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>-0.05582419594565591</v>
+        <v>-0.0654944954337654</v>
       </c>
       <c r="F3" s="5" t="n">
         <v>33333.33333333333</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>31472.52680181147</v>
+        <v>31150.18348554115</v>
       </c>
       <c r="H3" s="5" t="n">
-        <v>-1860.806531521863</v>
+        <v>-2183.149847792181</v>
       </c>
     </row>
     <row r="4">
@@ -809,19 +809,19 @@
         <v>371.25</v>
       </c>
       <c r="D4" s="5" t="n">
-        <v>383.25</v>
+        <v>389.5</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>0.03232323232323231</v>
+        <v>0.04915824915824918</v>
       </c>
       <c r="F4" s="5" t="n">
         <v>33333.33333333333</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>34410.77441077441</v>
+        <v>34971.9416386083</v>
       </c>
       <c r="H4" s="5" t="n">
-        <v>1077.441077441079</v>
+        <v>1638.608305274975</v>
       </c>
     </row>
   </sheetData>
@@ -836,7 +836,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G42"/>
+  <dimension ref="A1:G43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -1810,13 +1810,13 @@
         <v>46231</v>
       </c>
       <c r="B42" s="5" t="n">
-        <v>101933.2998138635</v>
+        <v>102672.1256327757</v>
       </c>
       <c r="C42" s="4" t="n">
-        <v>0</v>
+        <v>0.007248130103325812</v>
       </c>
       <c r="D42" s="4" t="n">
-        <v>0.01933299813863543</v>
+        <v>0.02672125632775746</v>
       </c>
       <c r="E42" s="5" t="n">
         <v>13687.900390625</v>
@@ -1825,11 +1825,34 @@
         <v>-0.001174810958479267</v>
       </c>
       <c r="G42" s="4" t="n">
-        <v>0.02050780909711469</v>
+        <v>0.02789606728623673</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="6" t="n">
+        <v>46232</v>
+      </c>
+      <c r="B43" s="5" t="n">
+        <v>102672.1256327757</v>
+      </c>
+      <c r="C43" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D43" s="4" t="n">
+        <v>0.02672125632775746</v>
+      </c>
+      <c r="E43" s="5" t="n">
+        <v>13501.599609375</v>
+      </c>
+      <c r="F43" s="4" t="n">
+        <v>-0.01476943889557791</v>
+      </c>
+      <c r="G43" s="4" t="n">
+        <v>0.04149069522333537</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G42"/>
+  <autoFilter ref="A1:G43"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/reports/latest_one_month_follow_up.xlsx
+++ b/reports/latest_one_month_follow_up.xlsx
@@ -15,7 +15,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'TAKIP_OZETI'!$A$1:$B$19</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'POZISYONLAR'!$A$1:$H$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'GUNLUK_TAKIP'!$A$1:$G$43</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'GUNLUK_TAKIP'!$A$1:$G$44</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'NOTLAR'!$A$1:$A$7</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -475,7 +475,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -546,7 +546,7 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>13501.599609375</v>
+        <v>13292.900390625</v>
       </c>
     </row>
     <row r="9">
@@ -603,7 +603,7 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -627,7 +627,7 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>0.02672125632775746</v>
+        <v>0.01321262672558765</v>
       </c>
     </row>
     <row r="17">
@@ -648,7 +648,7 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>-0.01476943889557791</v>
+        <v>-0.02999851206764448</v>
       </c>
     </row>
     <row r="18">
@@ -658,7 +658,7 @@
         </is>
       </c>
       <c r="B18" s="3" t="n">
-        <v>0.04149069522333537</v>
+        <v>0.04321113879323213</v>
       </c>
     </row>
     <row r="19">
@@ -692,7 +692,7 @@
     <col width="20" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
     <col width="19" customWidth="1" min="4" max="4"/>
-    <col width="21" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
     <col width="19" customWidth="1" min="6" max="6"/>
     <col width="19" customWidth="1" min="7" max="7"/>
     <col width="20" customWidth="1" min="8" max="8"/>
@@ -753,19 +753,19 @@
         <v>40</v>
       </c>
       <c r="D2" s="5" t="n">
-        <v>43.86000061035156</v>
+        <v>43.15999984741211</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>0.09650001525878915</v>
+        <v>0.07899999618530273</v>
       </c>
       <c r="F2" s="5" t="n">
         <v>33333.33333333333</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>36550.0005086263</v>
+        <v>35966.66653951009</v>
       </c>
       <c r="H2" s="5" t="n">
-        <v>3216.667175292969</v>
+        <v>2633.333206176758</v>
       </c>
     </row>
     <row r="3">
@@ -781,19 +781,19 @@
         <v>45.5</v>
       </c>
       <c r="D3" s="5" t="n">
-        <v>42.52000045776367</v>
+        <v>41.84000015258789</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>-0.0654944954337654</v>
+        <v>-0.08043955708598038</v>
       </c>
       <c r="F3" s="5" t="n">
         <v>33333.33333333333</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>31150.18348554115</v>
+        <v>30652.01476380065</v>
       </c>
       <c r="H3" s="5" t="n">
-        <v>-2183.149847792181</v>
+        <v>-2681.318569532679</v>
       </c>
     </row>
     <row r="4">
@@ -809,19 +809,19 @@
         <v>371.25</v>
       </c>
       <c r="D4" s="5" t="n">
-        <v>389.5</v>
+        <v>386.5</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>0.04915824915824918</v>
+        <v>0.04107744107744105</v>
       </c>
       <c r="F4" s="5" t="n">
         <v>33333.33333333333</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>34971.9416386083</v>
+        <v>34702.58136924803</v>
       </c>
       <c r="H4" s="5" t="n">
-        <v>1638.608305274975</v>
+        <v>1369.248035914701</v>
       </c>
     </row>
   </sheetData>
@@ -836,7 +836,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G43"/>
+  <dimension ref="A1:G44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -1833,13 +1833,13 @@
         <v>46232</v>
       </c>
       <c r="B43" s="5" t="n">
-        <v>102672.1256327757</v>
+        <v>101321.2626725588</v>
       </c>
       <c r="C43" s="4" t="n">
-        <v>0</v>
+        <v>-0.01315705652231813</v>
       </c>
       <c r="D43" s="4" t="n">
-        <v>0.02672125632775746</v>
+        <v>0.01321262672558765</v>
       </c>
       <c r="E43" s="5" t="n">
         <v>13501.599609375</v>
@@ -1848,11 +1848,34 @@
         <v>-0.01476943889557791</v>
       </c>
       <c r="G43" s="4" t="n">
-        <v>0.04149069522333537</v>
+        <v>0.02798206562116556</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="6" t="n">
+        <v>46233</v>
+      </c>
+      <c r="B44" s="5" t="n">
+        <v>101321.2626725588</v>
+      </c>
+      <c r="C44" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D44" s="4" t="n">
+        <v>0.01321262672558765</v>
+      </c>
+      <c r="E44" s="5" t="n">
+        <v>13292.900390625</v>
+      </c>
+      <c r="F44" s="4" t="n">
+        <v>-0.02999851206764448</v>
+      </c>
+      <c r="G44" s="4" t="n">
+        <v>0.04321113879323213</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G43"/>
+  <autoFilter ref="A1:G44"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/reports/latest_one_month_follow_up.xlsx
+++ b/reports/latest_one_month_follow_up.xlsx
@@ -15,7 +15,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'TAKIP_OZETI'!$A$1:$B$19</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'POZISYONLAR'!$A$1:$H$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'GUNLUK_TAKIP'!$A$1:$G$44</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'GUNLUK_TAKIP'!$A$1:$G$45</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'NOTLAR'!$A$1:$A$7</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -475,7 +475,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -546,7 +546,7 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>13292.900390625</v>
+        <v>13458.099609375</v>
       </c>
     </row>
     <row r="9">
@@ -603,7 +603,7 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -627,7 +627,7 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>0.01321262672558765</v>
+        <v>7.376724060415008e-05</v>
       </c>
     </row>
     <row r="17">
@@ -648,7 +648,7 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>-0.02999851206764448</v>
+        <v>-0.01794369458734679</v>
       </c>
     </row>
     <row r="18">
@@ -658,7 +658,7 @@
         </is>
       </c>
       <c r="B18" s="3" t="n">
-        <v>0.04321113879323213</v>
+        <v>0.01801746182795094</v>
       </c>
     </row>
     <row r="19">
@@ -753,19 +753,19 @@
         <v>40</v>
       </c>
       <c r="D2" s="5" t="n">
-        <v>43.15999984741211</v>
+        <v>42.40000152587891</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>0.07899999618530273</v>
+        <v>0.06000003814697275</v>
       </c>
       <c r="F2" s="5" t="n">
         <v>33333.33333333333</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>35966.66653951009</v>
+        <v>35333.33460489909</v>
       </c>
       <c r="H2" s="5" t="n">
-        <v>2633.333206176758</v>
+        <v>2000.001271565758</v>
       </c>
     </row>
     <row r="3">
@@ -781,19 +781,19 @@
         <v>45.5</v>
       </c>
       <c r="D3" s="5" t="n">
-        <v>41.84000015258789</v>
+        <v>41.34000015258789</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>-0.08043955708598038</v>
+        <v>-0.09142856807499145</v>
       </c>
       <c r="F3" s="5" t="n">
         <v>33333.33333333333</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>30652.01476380065</v>
+        <v>30285.71439750028</v>
       </c>
       <c r="H3" s="5" t="n">
-        <v>-2681.318569532679</v>
+        <v>-3047.618935833048</v>
       </c>
     </row>
     <row r="4">
@@ -809,19 +809,19 @@
         <v>371.25</v>
       </c>
       <c r="D4" s="5" t="n">
-        <v>386.5</v>
+        <v>383</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>0.04107744107744105</v>
+        <v>0.03164983164983171</v>
       </c>
       <c r="F4" s="5" t="n">
         <v>33333.33333333333</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>34702.58136924803</v>
+        <v>34388.32772166105</v>
       </c>
       <c r="H4" s="5" t="n">
-        <v>1369.248035914701</v>
+        <v>1054.994388327723</v>
       </c>
     </row>
   </sheetData>
@@ -836,7 +836,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G44"/>
+  <dimension ref="A1:G45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -1856,13 +1856,13 @@
         <v>46233</v>
       </c>
       <c r="B44" s="5" t="n">
-        <v>101321.2626725588</v>
+        <v>100007.3767240604</v>
       </c>
       <c r="C44" s="4" t="n">
-        <v>0</v>
+        <v>-0.01296752442519822</v>
       </c>
       <c r="D44" s="4" t="n">
-        <v>0.01321262672558765</v>
+        <v>7.376724060437212e-05</v>
       </c>
       <c r="E44" s="5" t="n">
         <v>13292.900390625</v>
@@ -1871,11 +1871,34 @@
         <v>-0.02999851206764448</v>
       </c>
       <c r="G44" s="4" t="n">
-        <v>0.04321113879323213</v>
+        <v>0.03007227930824885</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="6" t="n">
+        <v>46234</v>
+      </c>
+      <c r="B45" s="5" t="n">
+        <v>100007.3767240604</v>
+      </c>
+      <c r="C45" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D45" s="4" t="n">
+        <v>7.376724060437212e-05</v>
+      </c>
+      <c r="E45" s="5" t="n">
+        <v>13458.099609375</v>
+      </c>
+      <c r="F45" s="4" t="n">
+        <v>-0.01794369458734679</v>
+      </c>
+      <c r="G45" s="4" t="n">
+        <v>0.01801746182795116</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G44"/>
+  <autoFilter ref="A1:G45"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/reports/latest_one_month_follow_up.xlsx
+++ b/reports/latest_one_month_follow_up.xlsx
@@ -1215,10 +1215,10 @@
         <v>101665.535802718</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>-0.01517965889001283</v>
+        <v>-0.0151796588900126</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>0.01665535802718021</v>
+        <v>0.01665535802718043</v>
       </c>
       <c r="E16" s="5" t="n">
         <v>14734.5</v>
@@ -1227,7 +1227,7 @@
         <v>0.07519702276707529</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>-0.05854166473989508</v>
+        <v>-0.05854166473989486</v>
       </c>
     </row>
     <row r="17">
@@ -1238,7 +1238,7 @@
         <v>101579.9132001645</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>-0.000842198901303659</v>
+        <v>-0.0008421989013038811</v>
       </c>
       <c r="D17" s="4" t="n">
         <v>0.01579913200164529</v>
@@ -1281,13 +1281,13 @@
         <v>46197</v>
       </c>
       <c r="B19" s="5" t="n">
-        <v>99903.87102493743</v>
+        <v>99903.87102493741</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>-0.007105427940044096</v>
+        <v>-0.007105427940044318</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>-0.0009612897506257045</v>
+        <v>-0.0009612897506259266</v>
       </c>
       <c r="E19" s="5" t="n">
         <v>14331.2001953125</v>
@@ -1296,7 +1296,7 @@
         <v>0.04576767332986709</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>-0.04672896308049279</v>
+        <v>-0.04672896308049301</v>
       </c>
     </row>
     <row r="20">
@@ -1307,7 +1307,7 @@
         <v>99725.18443384963</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>-0.001788585259556053</v>
+        <v>-0.00178858525955583</v>
       </c>
       <c r="D20" s="4" t="n">
         <v>-0.00274815566150366</v>
@@ -1353,10 +1353,10 @@
         <v>100567.2965303391</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>-0.01333614376284464</v>
+        <v>-0.01333614376284487</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>0.00567296530339112</v>
+        <v>0.005672965303390898</v>
       </c>
       <c r="E22" s="5" t="n">
         <v>14183.2001953125</v>
@@ -1365,7 +1365,7 @@
         <v>0.03496790683833195</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>-0.02929494153494083</v>
+        <v>-0.02929494153494105</v>
       </c>
     </row>
     <row r="23">
@@ -1376,7 +1376,7 @@
         <v>98982.15764175884</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>-0.01576197176685634</v>
+        <v>-0.01576197176685612</v>
       </c>
       <c r="D23" s="4" t="n">
         <v>-0.01017842358241161</v>
@@ -1402,7 +1402,7 @@
         <v>0.003127667249263499</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>-0.007082591055235898</v>
+        <v>-0.007082591055236009</v>
       </c>
       <c r="E24" s="5" t="n">
         <v>14350.599609375</v>
@@ -1411,7 +1411,7 @@
         <v>0.0471832756403241</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>-0.05426586669555999</v>
+        <v>-0.05426586669556011</v>
       </c>
     </row>
     <row r="25">
@@ -1422,7 +1422,7 @@
         <v>98699.49739704847</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>-0.005964680366087549</v>
+        <v>-0.005964680366087438</v>
       </c>
       <c r="D25" s="4" t="n">
         <v>-0.01300502602951525</v>
@@ -1511,13 +1511,13 @@
         <v>46211</v>
       </c>
       <c r="B29" s="5" t="n">
-        <v>97511.54763463838</v>
+        <v>97511.54763463837</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>-0.02101826087704517</v>
+        <v>-0.02101826087704539</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>-0.02488452365361615</v>
+        <v>-0.02488452365361637</v>
       </c>
       <c r="E29" s="5" t="n">
         <v>14190</v>
@@ -1526,7 +1526,7 @@
         <v>0.03546409807355522</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>-0.06034862172717137</v>
+        <v>-0.06034862172717159</v>
       </c>
     </row>
     <row r="30">
@@ -1537,7 +1537,7 @@
         <v>97085.90440793287</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>-0.004365054570770743</v>
+        <v>-0.004365054570770521</v>
       </c>
       <c r="D30" s="4" t="n">
         <v>-0.02914095592067123</v>
@@ -1603,13 +1603,13 @@
         <v>46217</v>
       </c>
       <c r="B33" s="5" t="n">
-        <v>101364.3995699692</v>
+        <v>101364.3995699691</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>0.02123082912189456</v>
+        <v>0.02123082912189433</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>0.01364399569969166</v>
+        <v>0.01364399569969144</v>
       </c>
       <c r="E33" s="5" t="n">
         <v>14080</v>
@@ -1618,7 +1618,7 @@
         <v>0.02743724460011676</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>-0.0137932489004251</v>
+        <v>-0.01379324890042533</v>
       </c>
     </row>
     <row r="34">
@@ -1629,7 +1629,7 @@
         <v>105261.7030227777</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>0.03844844412182757</v>
+        <v>0.0384484441218278</v>
       </c>
       <c r="D34" s="4" t="n">
         <v>0.05261703022777731</v>
@@ -1675,10 +1675,10 @@
         <v>104848.7672438694</v>
       </c>
       <c r="C36" s="4" t="n">
-        <v>0.02469452791059856</v>
+        <v>0.02469452791059834</v>
       </c>
       <c r="D36" s="4" t="n">
-        <v>0.04848767243869423</v>
+        <v>0.04848767243869401</v>
       </c>
       <c r="E36" s="5" t="n">
         <v>14071</v>
@@ -1687,7 +1687,7 @@
         <v>0.02678050204319904</v>
       </c>
       <c r="G36" s="4" t="n">
-        <v>0.02170717039549519</v>
+        <v>0.02170717039549497</v>
       </c>
     </row>
     <row r="37">
@@ -1698,7 +1698,7 @@
         <v>102169.894507684</v>
       </c>
       <c r="C37" s="4" t="n">
-        <v>-0.02554987346636661</v>
+        <v>-0.02554987346636639</v>
       </c>
       <c r="D37" s="4" t="n">
         <v>0.02169894507684034</v>

--- a/reports/latest_one_month_follow_up.xlsx
+++ b/reports/latest_one_month_follow_up.xlsx
@@ -1215,10 +1215,10 @@
         <v>101665.535802718</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>-0.0151796588900126</v>
+        <v>-0.01517965889001283</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>0.01665535802718043</v>
+        <v>0.01665535802718021</v>
       </c>
       <c r="E16" s="5" t="n">
         <v>14734.5</v>
@@ -1227,7 +1227,7 @@
         <v>0.07519702276707529</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>-0.05854166473989486</v>
+        <v>-0.05854166473989508</v>
       </c>
     </row>
     <row r="17">
@@ -1238,7 +1238,7 @@
         <v>101579.9132001645</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>-0.0008421989013038811</v>
+        <v>-0.000842198901303659</v>
       </c>
       <c r="D17" s="4" t="n">
         <v>0.01579913200164529</v>
@@ -1281,13 +1281,13 @@
         <v>46197</v>
       </c>
       <c r="B19" s="5" t="n">
-        <v>99903.87102493741</v>
+        <v>99903.87102493743</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>-0.007105427940044318</v>
+        <v>-0.007105427940044096</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>-0.0009612897506259266</v>
+        <v>-0.0009612897506257045</v>
       </c>
       <c r="E19" s="5" t="n">
         <v>14331.2001953125</v>
@@ -1296,7 +1296,7 @@
         <v>0.04576767332986709</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>-0.04672896308049301</v>
+        <v>-0.04672896308049279</v>
       </c>
     </row>
     <row r="20">
@@ -1307,7 +1307,7 @@
         <v>99725.18443384963</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>-0.00178858525955583</v>
+        <v>-0.001788585259556053</v>
       </c>
       <c r="D20" s="4" t="n">
         <v>-0.00274815566150366</v>
@@ -1353,10 +1353,10 @@
         <v>100567.2965303391</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>-0.01333614376284487</v>
+        <v>-0.01333614376284464</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>0.005672965303390898</v>
+        <v>0.00567296530339112</v>
       </c>
       <c r="E22" s="5" t="n">
         <v>14183.2001953125</v>
@@ -1365,7 +1365,7 @@
         <v>0.03496790683833195</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>-0.02929494153494105</v>
+        <v>-0.02929494153494083</v>
       </c>
     </row>
     <row r="23">
@@ -1376,7 +1376,7 @@
         <v>98982.15764175884</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>-0.01576197176685612</v>
+        <v>-0.01576197176685634</v>
       </c>
       <c r="D23" s="4" t="n">
         <v>-0.01017842358241161</v>
@@ -1402,7 +1402,7 @@
         <v>0.003127667249263499</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>-0.007082591055236009</v>
+        <v>-0.007082591055235898</v>
       </c>
       <c r="E24" s="5" t="n">
         <v>14350.599609375</v>
@@ -1411,7 +1411,7 @@
         <v>0.0471832756403241</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>-0.05426586669556011</v>
+        <v>-0.05426586669555999</v>
       </c>
     </row>
     <row r="25">
@@ -1422,7 +1422,7 @@
         <v>98699.49739704847</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>-0.005964680366087438</v>
+        <v>-0.005964680366087549</v>
       </c>
       <c r="D25" s="4" t="n">
         <v>-0.01300502602951525</v>
@@ -1511,13 +1511,13 @@
         <v>46211</v>
       </c>
       <c r="B29" s="5" t="n">
-        <v>97511.54763463837</v>
+        <v>97511.54763463838</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>-0.02101826087704539</v>
+        <v>-0.02101826087704517</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>-0.02488452365361637</v>
+        <v>-0.02488452365361615</v>
       </c>
       <c r="E29" s="5" t="n">
         <v>14190</v>
@@ -1526,7 +1526,7 @@
         <v>0.03546409807355522</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>-0.06034862172717159</v>
+        <v>-0.06034862172717137</v>
       </c>
     </row>
     <row r="30">
@@ -1537,7 +1537,7 @@
         <v>97085.90440793287</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>-0.004365054570770521</v>
+        <v>-0.004365054570770743</v>
       </c>
       <c r="D30" s="4" t="n">
         <v>-0.02914095592067123</v>
@@ -1603,13 +1603,13 @@
         <v>46217</v>
       </c>
       <c r="B33" s="5" t="n">
-        <v>101364.3995699691</v>
+        <v>101364.3995699692</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>0.02123082912189433</v>
+        <v>0.02123082912189456</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>0.01364399569969144</v>
+        <v>0.01364399569969166</v>
       </c>
       <c r="E33" s="5" t="n">
         <v>14080</v>
@@ -1618,7 +1618,7 @@
         <v>0.02743724460011676</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>-0.01379324890042533</v>
+        <v>-0.0137932489004251</v>
       </c>
     </row>
     <row r="34">
@@ -1629,7 +1629,7 @@
         <v>105261.7030227777</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>0.0384484441218278</v>
+        <v>0.03844844412182757</v>
       </c>
       <c r="D34" s="4" t="n">
         <v>0.05261703022777731</v>
@@ -1675,10 +1675,10 @@
         <v>104848.7672438694</v>
       </c>
       <c r="C36" s="4" t="n">
-        <v>0.02469452791059834</v>
+        <v>0.02469452791059856</v>
       </c>
       <c r="D36" s="4" t="n">
-        <v>0.04848767243869401</v>
+        <v>0.04848767243869423</v>
       </c>
       <c r="E36" s="5" t="n">
         <v>14071</v>
@@ -1687,7 +1687,7 @@
         <v>0.02678050204319904</v>
       </c>
       <c r="G36" s="4" t="n">
-        <v>0.02170717039549497</v>
+        <v>0.02170717039549519</v>
       </c>
     </row>
     <row r="37">
@@ -1698,7 +1698,7 @@
         <v>102169.894507684</v>
       </c>
       <c r="C37" s="4" t="n">
-        <v>-0.02554987346636639</v>
+        <v>-0.02554987346636661</v>
       </c>
       <c r="D37" s="4" t="n">
         <v>0.02169894507684034</v>

--- a/reports/latest_one_month_follow_up.xlsx
+++ b/reports/latest_one_month_follow_up.xlsx
@@ -15,7 +15,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'TAKIP_OZETI'!$A$1:$B$19</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'POZISYONLAR'!$A$1:$H$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'GUNLUK_TAKIP'!$A$1:$G$45</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'GUNLUK_TAKIP'!$A$1:$G$47</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'NOTLAR'!$A$1:$A$7</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -475,7 +475,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -546,7 +546,7 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>13458.099609375</v>
+        <v>13687.900390625</v>
       </c>
     </row>
     <row r="9">
@@ -603,7 +603,7 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -627,7 +627,7 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-04</t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>7.376724060415008e-05</v>
+        <v>-0.01182357577052229</v>
       </c>
     </row>
     <row r="17">
@@ -648,7 +648,7 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>-0.01794369458734679</v>
+        <v>-0.001174810958479267</v>
       </c>
     </row>
     <row r="18">
@@ -658,7 +658,7 @@
         </is>
       </c>
       <c r="B18" s="3" t="n">
-        <v>0.01801746182795094</v>
+        <v>-0.01064876481204302</v>
       </c>
     </row>
     <row r="19">
@@ -669,7 +669,7 @@
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>Karda / BIST Üstü</t>
+          <t>Zararda / BIST Altı</t>
         </is>
       </c>
     </row>
@@ -753,19 +753,19 @@
         <v>40</v>
       </c>
       <c r="D2" s="5" t="n">
-        <v>42.40000152587891</v>
+        <v>40.70000076293945</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>0.06000003814697275</v>
+        <v>0.01750001907348642</v>
       </c>
       <c r="F2" s="5" t="n">
         <v>33333.33333333333</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>35333.33460489909</v>
+        <v>33916.66730244954</v>
       </c>
       <c r="H2" s="5" t="n">
-        <v>2000.001271565758</v>
+        <v>583.3339691162109</v>
       </c>
     </row>
     <row r="3">
@@ -781,19 +781,19 @@
         <v>45.5</v>
       </c>
       <c r="D3" s="5" t="n">
-        <v>41.34000015258789</v>
+        <v>42.13999938964844</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>-0.09142856807499145</v>
+        <v>-0.07384616726047388</v>
       </c>
       <c r="F3" s="5" t="n">
         <v>33333.33333333333</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>30285.71439750028</v>
+        <v>30871.79442465087</v>
       </c>
       <c r="H3" s="5" t="n">
-        <v>-3047.618935833048</v>
+        <v>-2461.538908682462</v>
       </c>
     </row>
     <row r="4">
@@ -809,19 +809,19 @@
         <v>371.25</v>
       </c>
       <c r="D4" s="5" t="n">
-        <v>383</v>
+        <v>379</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>0.03164983164983171</v>
+        <v>0.02087542087542094</v>
       </c>
       <c r="F4" s="5" t="n">
         <v>33333.33333333333</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>34388.32772166105</v>
+        <v>34029.18069584736</v>
       </c>
       <c r="H4" s="5" t="n">
-        <v>1054.994388327723</v>
+        <v>695.8473625140323</v>
       </c>
     </row>
   </sheetData>
@@ -836,7 +836,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G45"/>
+  <dimension ref="A1:G47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -1879,13 +1879,13 @@
         <v>46234</v>
       </c>
       <c r="B45" s="5" t="n">
-        <v>100007.3767240604</v>
+        <v>101068.0382772884</v>
       </c>
       <c r="C45" s="4" t="n">
-        <v>0</v>
+        <v>0.01060583316923247</v>
       </c>
       <c r="D45" s="4" t="n">
-        <v>7.376724060437212e-05</v>
+        <v>0.01068038277288408</v>
       </c>
       <c r="E45" s="5" t="n">
         <v>13458.099609375</v>
@@ -1894,11 +1894,57 @@
         <v>-0.01794369458734679</v>
       </c>
       <c r="G45" s="4" t="n">
-        <v>0.01801746182795116</v>
+        <v>0.02862407736023087</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="6" t="n">
+        <v>46237</v>
+      </c>
+      <c r="B46" s="5" t="n">
+        <v>98817.64242294777</v>
+      </c>
+      <c r="C46" s="4" t="n">
+        <v>-0.0222661475645396</v>
+      </c>
+      <c r="D46" s="4" t="n">
+        <v>-0.01182357577052229</v>
+      </c>
+      <c r="E46" s="5" t="n">
+        <v>13410.5</v>
+      </c>
+      <c r="F46" s="4" t="n">
+        <v>-0.02141710449503798</v>
+      </c>
+      <c r="G46" s="4" t="n">
+        <v>0.009593528724515688</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="6" t="n">
+        <v>46238</v>
+      </c>
+      <c r="B47" s="5" t="n">
+        <v>98817.64242294777</v>
+      </c>
+      <c r="C47" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D47" s="4" t="n">
+        <v>-0.01182357577052229</v>
+      </c>
+      <c r="E47" s="5" t="n">
+        <v>13687.900390625</v>
+      </c>
+      <c r="F47" s="4" t="n">
+        <v>-0.001174810958479267</v>
+      </c>
+      <c r="G47" s="4" t="n">
+        <v>-0.01064876481204302</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G45"/>
+  <autoFilter ref="A1:G47"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/reports/latest_one_month_follow_up.xlsx
+++ b/reports/latest_one_month_follow_up.xlsx
@@ -15,7 +15,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'TAKIP_OZETI'!$A$1:$B$19</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'POZISYONLAR'!$A$1:$H$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'GUNLUK_TAKIP'!$A$1:$G$47</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'GUNLUK_TAKIP'!$A$1:$G$48</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'NOTLAR'!$A$1:$A$7</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -475,7 +475,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
     </row>
@@ -546,7 +546,7 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>13687.900390625</v>
+        <v>13703.099609375</v>
       </c>
     </row>
     <row r="9">
@@ -603,7 +603,7 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
     </row>
@@ -627,7 +627,7 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>-0.01182357577052229</v>
+        <v>0.005101501194646918</v>
       </c>
     </row>
     <row r="17">
@@ -648,7 +648,7 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>-0.001174810958479267</v>
+        <v>-6.570276014306042e-05</v>
       </c>
     </row>
     <row r="18">
@@ -658,7 +658,7 @@
         </is>
       </c>
       <c r="B18" s="3" t="n">
-        <v>-0.01064876481204302</v>
+        <v>0.005167203954789978</v>
       </c>
     </row>
     <row r="19">
@@ -669,7 +669,7 @@
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>Zararda / BIST Altı</t>
+          <t>Karda / BIST Üstü</t>
         </is>
       </c>
     </row>
@@ -753,19 +753,19 @@
         <v>40</v>
       </c>
       <c r="D2" s="5" t="n">
-        <v>40.70000076293945</v>
+        <v>41.7400016784668</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>0.01750001907348642</v>
+        <v>0.04350004196167001</v>
       </c>
       <c r="F2" s="5" t="n">
         <v>33333.33333333333</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>33916.66730244954</v>
+        <v>34783.33473205566</v>
       </c>
       <c r="H2" s="5" t="n">
-        <v>583.3339691162109</v>
+        <v>1450.001398722336</v>
       </c>
     </row>
     <row r="3">
@@ -781,19 +781,19 @@
         <v>45.5</v>
       </c>
       <c r="D3" s="5" t="n">
-        <v>42.13999938964844</v>
+        <v>42.43999862670898</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>-0.07384616726047388</v>
+        <v>-0.06725277743496738</v>
       </c>
       <c r="F3" s="5" t="n">
         <v>33333.33333333333</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>30871.79442465087</v>
+        <v>31091.57408550108</v>
       </c>
       <c r="H3" s="5" t="n">
-        <v>-2461.538908682462</v>
+        <v>-2241.759247832244</v>
       </c>
     </row>
     <row r="4">
@@ -809,19 +809,19 @@
         <v>371.25</v>
       </c>
       <c r="D4" s="5" t="n">
-        <v>379</v>
+        <v>385.75</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>0.02087542087542094</v>
+        <v>0.03905723905723901</v>
       </c>
       <c r="F4" s="5" t="n">
         <v>33333.33333333333</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>34029.18069584736</v>
+        <v>34635.24130190796</v>
       </c>
       <c r="H4" s="5" t="n">
-        <v>695.8473625140323</v>
+        <v>1301.907968574633</v>
       </c>
     </row>
   </sheetData>
@@ -836,7 +836,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G47"/>
+  <dimension ref="A1:G48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -1925,13 +1925,13 @@
         <v>46238</v>
       </c>
       <c r="B47" s="5" t="n">
-        <v>98817.64242294777</v>
+        <v>100510.1501194647</v>
       </c>
       <c r="C47" s="4" t="n">
-        <v>0</v>
+        <v>0.01712758627930899</v>
       </c>
       <c r="D47" s="4" t="n">
-        <v>-0.01182357577052229</v>
+        <v>0.00510150119464714</v>
       </c>
       <c r="E47" s="5" t="n">
         <v>13687.900390625</v>
@@ -1940,11 +1940,34 @@
         <v>-0.001174810958479267</v>
       </c>
       <c r="G47" s="4" t="n">
-        <v>-0.01064876481204302</v>
+        <v>0.006276312153126407</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="6" t="n">
+        <v>46239</v>
+      </c>
+      <c r="B48" s="5" t="n">
+        <v>100510.1501194647</v>
+      </c>
+      <c r="C48" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D48" s="4" t="n">
+        <v>0.00510150119464714</v>
+      </c>
+      <c r="E48" s="5" t="n">
+        <v>13703.099609375</v>
+      </c>
+      <c r="F48" s="4" t="n">
+        <v>-6.570276014306042e-05</v>
+      </c>
+      <c r="G48" s="4" t="n">
+        <v>0.0051672039547902</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G47"/>
+  <autoFilter ref="A1:G48"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/reports/latest_one_month_follow_up.xlsx
+++ b/reports/latest_one_month_follow_up.xlsx
@@ -15,7 +15,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'TAKIP_OZETI'!$A$1:$B$19</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'POZISYONLAR'!$A$1:$H$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'GUNLUK_TAKIP'!$A$1:$G$48</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'GUNLUK_TAKIP'!$A$1:$G$49</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'NOTLAR'!$A$1:$A$7</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -475,7 +475,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
     </row>
@@ -546,7 +546,7 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>13703.099609375</v>
+        <v>13798.7998046875</v>
       </c>
     </row>
     <row r="9">
@@ -603,7 +603,7 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
     </row>
@@ -627,7 +627,7 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>0.005101501194646918</v>
+        <v>0.003958946916856609</v>
       </c>
     </row>
     <row r="17">
@@ -648,7 +648,7 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>-6.570276014306042e-05</v>
+        <v>0.006917674013974029</v>
       </c>
     </row>
     <row r="18">
@@ -658,7 +658,7 @@
         </is>
       </c>
       <c r="B18" s="3" t="n">
-        <v>0.005167203954789978</v>
+        <v>-0.00295872709711742</v>
       </c>
     </row>
     <row r="19">
@@ -669,7 +669,7 @@
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>Karda / BIST Üstü</t>
+          <t>Karda / BIST Altı</t>
         </is>
       </c>
     </row>
@@ -753,19 +753,19 @@
         <v>40</v>
       </c>
       <c r="D2" s="5" t="n">
-        <v>41.7400016784668</v>
+        <v>41.97999954223633</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>0.04350004196167001</v>
+        <v>0.0494999885559082</v>
       </c>
       <c r="F2" s="5" t="n">
         <v>33333.33333333333</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>34783.33473205566</v>
+        <v>34983.3329518636</v>
       </c>
       <c r="H2" s="5" t="n">
-        <v>1450.001398722336</v>
+        <v>1649.999618530273</v>
       </c>
     </row>
     <row r="3">
@@ -809,19 +809,19 @@
         <v>371.25</v>
       </c>
       <c r="D4" s="5" t="n">
-        <v>385.75</v>
+        <v>382.25</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>0.03905723905723901</v>
+        <v>0.02962962962962967</v>
       </c>
       <c r="F4" s="5" t="n">
         <v>33333.33333333333</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>34635.24130190796</v>
+        <v>34320.98765432098</v>
       </c>
       <c r="H4" s="5" t="n">
-        <v>1301.907968574633</v>
+        <v>987.6543209876545</v>
       </c>
     </row>
   </sheetData>
@@ -836,7 +836,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G48"/>
+  <dimension ref="A1:G49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -1948,13 +1948,13 @@
         <v>46239</v>
       </c>
       <c r="B48" s="5" t="n">
-        <v>100510.1501194647</v>
+        <v>100395.8946916857</v>
       </c>
       <c r="C48" s="4" t="n">
-        <v>0</v>
+        <v>-0.001136755120186628</v>
       </c>
       <c r="D48" s="4" t="n">
-        <v>0.00510150119464714</v>
+        <v>0.003958946916856831</v>
       </c>
       <c r="E48" s="5" t="n">
         <v>13703.099609375</v>
@@ -1963,11 +1963,34 @@
         <v>-6.570276014306042e-05</v>
       </c>
       <c r="G48" s="4" t="n">
-        <v>0.0051672039547902</v>
+        <v>0.004024649676999892</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="6" t="n">
+        <v>46240</v>
+      </c>
+      <c r="B49" s="5" t="n">
+        <v>100395.8946916857</v>
+      </c>
+      <c r="C49" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D49" s="4" t="n">
+        <v>0.003958946916856831</v>
+      </c>
+      <c r="E49" s="5" t="n">
+        <v>13798.7998046875</v>
+      </c>
+      <c r="F49" s="4" t="n">
+        <v>0.006917674013974029</v>
+      </c>
+      <c r="G49" s="4" t="n">
+        <v>-0.002958727097117198</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G48"/>
+  <autoFilter ref="A1:G49"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/reports/latest_one_month_follow_up.xlsx
+++ b/reports/latest_one_month_follow_up.xlsx
@@ -15,7 +15,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'TAKIP_OZETI'!$A$1:$B$19</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'POZISYONLAR'!$A$1:$H$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'GUNLUK_TAKIP'!$A$1:$G$49</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'GUNLUK_TAKIP'!$A$1:$G$50</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'NOTLAR'!$A$1:$A$7</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -475,7 +475,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -546,7 +546,7 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>13798.7998046875</v>
+        <v>13779.400390625</v>
       </c>
     </row>
     <row r="9">
@@ -603,7 +603,7 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -627,7 +627,7 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>0.003958946916856609</v>
+        <v>-0.003643584041158276</v>
       </c>
     </row>
     <row r="17">
@@ -648,7 +648,7 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>0.006917674013974029</v>
+        <v>0.005502071703517242</v>
       </c>
     </row>
     <row r="18">
@@ -658,7 +658,7 @@
         </is>
       </c>
       <c r="B18" s="3" t="n">
-        <v>-0.00295872709711742</v>
+        <v>-0.009145655744675518</v>
       </c>
     </row>
     <row r="19">
@@ -669,7 +669,7 @@
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>Karda / BIST Altı</t>
+          <t>Zararda / BIST Altı</t>
         </is>
       </c>
     </row>
@@ -753,19 +753,19 @@
         <v>40</v>
       </c>
       <c r="D2" s="5" t="n">
-        <v>41.97999954223633</v>
+        <v>41.56000137329102</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>0.0494999885559082</v>
+        <v>0.03900003433227539</v>
       </c>
       <c r="F2" s="5" t="n">
         <v>33333.33333333333</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>34983.3329518636</v>
+        <v>34633.33447774251</v>
       </c>
       <c r="H2" s="5" t="n">
-        <v>1649.999618530273</v>
+        <v>1300.00114440918</v>
       </c>
     </row>
     <row r="3">
@@ -781,19 +781,19 @@
         <v>45.5</v>
       </c>
       <c r="D3" s="5" t="n">
-        <v>42.43999862670898</v>
+        <v>41.88000106811523</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>-0.06725277743496738</v>
+        <v>-0.07956041608537945</v>
       </c>
       <c r="F3" s="5" t="n">
         <v>33333.33333333333</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>31091.57408550108</v>
+        <v>30681.31946382068</v>
       </c>
       <c r="H3" s="5" t="n">
-        <v>-2241.759247832244</v>
+        <v>-2652.013869512648</v>
       </c>
     </row>
     <row r="4">
@@ -836,7 +836,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G49"/>
+  <dimension ref="A1:G50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -1971,13 +1971,13 @@
         <v>46240</v>
       </c>
       <c r="B49" s="5" t="n">
-        <v>100395.8946916857</v>
+        <v>99635.64159588418</v>
       </c>
       <c r="C49" s="4" t="n">
-        <v>0</v>
+        <v>-0.007572551628094226</v>
       </c>
       <c r="D49" s="4" t="n">
-        <v>0.003958946916856831</v>
+        <v>-0.003643584041158165</v>
       </c>
       <c r="E49" s="5" t="n">
         <v>13798.7998046875</v>
@@ -1986,11 +1986,34 @@
         <v>0.006917674013974029</v>
       </c>
       <c r="G49" s="4" t="n">
-        <v>-0.002958727097117198</v>
+        <v>-0.01056125805513219</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="6" t="n">
+        <v>46241</v>
+      </c>
+      <c r="B50" s="5" t="n">
+        <v>99635.64159588418</v>
+      </c>
+      <c r="C50" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D50" s="4" t="n">
+        <v>-0.003643584041158165</v>
+      </c>
+      <c r="E50" s="5" t="n">
+        <v>13779.400390625</v>
+      </c>
+      <c r="F50" s="4" t="n">
+        <v>0.005502071703517242</v>
+      </c>
+      <c r="G50" s="4" t="n">
+        <v>-0.009145655744675407</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G49"/>
+  <autoFilter ref="A1:G50"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/reports/latest_one_month_follow_up.xlsx
+++ b/reports/latest_one_month_follow_up.xlsx
@@ -15,7 +15,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'TAKIP_OZETI'!$A$1:$B$19</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'POZISYONLAR'!$A$1:$H$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'GUNLUK_TAKIP'!$A$1:$G$50</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'GUNLUK_TAKIP'!$A$1:$G$51</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'NOTLAR'!$A$1:$A$7</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -475,7 +475,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -546,7 +546,7 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>13779.400390625</v>
+        <v>13811.599609375</v>
       </c>
     </row>
     <row r="9">
@@ -603,7 +603,7 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -627,7 +627,7 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>-0.003643584041158276</v>
+        <v>-0.02845710712945282</v>
       </c>
     </row>
     <row r="17">
@@ -648,7 +648,7 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>0.005502071703517242</v>
+        <v>0.007851693620475775</v>
       </c>
     </row>
     <row r="18">
@@ -658,7 +658,7 @@
         </is>
       </c>
       <c r="B18" s="3" t="n">
-        <v>-0.009145655744675518</v>
+        <v>-0.03630880074992859</v>
       </c>
     </row>
     <row r="19">
@@ -753,19 +753,19 @@
         <v>40</v>
       </c>
       <c r="D2" s="5" t="n">
-        <v>41.56000137329102</v>
+        <v>38.68000030517578</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>0.03900003433227539</v>
+        <v>-0.03299999237060547</v>
       </c>
       <c r="F2" s="5" t="n">
         <v>33333.33333333333</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>34633.33447774251</v>
+        <v>32233.33358764648</v>
       </c>
       <c r="H2" s="5" t="n">
-        <v>1300.00114440918</v>
+        <v>-1099.999745686848</v>
       </c>
     </row>
     <row r="3">
@@ -781,19 +781,19 @@
         <v>45.5</v>
       </c>
       <c r="D3" s="5" t="n">
-        <v>41.88000106811523</v>
+        <v>41.34000015258789</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>-0.07956041608537945</v>
+        <v>-0.09142856807499145</v>
       </c>
       <c r="F3" s="5" t="n">
         <v>33333.33333333333</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>30681.31946382068</v>
+        <v>30285.71439750028</v>
       </c>
       <c r="H3" s="5" t="n">
-        <v>-2652.013869512648</v>
+        <v>-3047.618935833048</v>
       </c>
     </row>
     <row r="4">
@@ -809,19 +809,19 @@
         <v>371.25</v>
       </c>
       <c r="D4" s="5" t="n">
-        <v>382.25</v>
+        <v>385.75</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>0.02962962962962967</v>
+        <v>0.03905723905723901</v>
       </c>
       <c r="F4" s="5" t="n">
         <v>33333.33333333333</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>34320.98765432098</v>
+        <v>34635.24130190796</v>
       </c>
       <c r="H4" s="5" t="n">
-        <v>987.6543209876545</v>
+        <v>1301.907968574633</v>
       </c>
     </row>
   </sheetData>
@@ -836,7 +836,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G50"/>
+  <dimension ref="A1:G51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -1215,10 +1215,10 @@
         <v>101665.535802718</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>-0.0151796588900126</v>
+        <v>-0.01517965889001283</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>0.01665535802718043</v>
+        <v>0.01665535802718021</v>
       </c>
       <c r="E16" s="5" t="n">
         <v>14734.5</v>
@@ -1227,7 +1227,7 @@
         <v>0.07519702276707529</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>-0.05854166473989486</v>
+        <v>-0.05854166473989508</v>
       </c>
     </row>
     <row r="17">
@@ -1238,7 +1238,7 @@
         <v>101579.9132001645</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>-0.0008421989013038811</v>
+        <v>-0.000842198901303659</v>
       </c>
       <c r="D17" s="4" t="n">
         <v>0.01579913200164529</v>
@@ -1281,13 +1281,13 @@
         <v>46197</v>
       </c>
       <c r="B19" s="5" t="n">
-        <v>99903.87102493741</v>
+        <v>99903.87102493743</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>-0.007105427940044318</v>
+        <v>-0.007105427940044096</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>-0.0009612897506259266</v>
+        <v>-0.0009612897506257045</v>
       </c>
       <c r="E19" s="5" t="n">
         <v>14331.2001953125</v>
@@ -1296,7 +1296,7 @@
         <v>0.04576767332986709</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>-0.04672896308049301</v>
+        <v>-0.04672896308049279</v>
       </c>
     </row>
     <row r="20">
@@ -1307,7 +1307,7 @@
         <v>99725.18443384963</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>-0.00178858525955583</v>
+        <v>-0.001788585259556053</v>
       </c>
       <c r="D20" s="4" t="n">
         <v>-0.00274815566150366</v>
@@ -1353,10 +1353,10 @@
         <v>100567.2965303391</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>-0.01333614376284487</v>
+        <v>-0.01333614376284464</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>0.005672965303390898</v>
+        <v>0.00567296530339112</v>
       </c>
       <c r="E22" s="5" t="n">
         <v>14183.2001953125</v>
@@ -1365,7 +1365,7 @@
         <v>0.03496790683833195</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>-0.02929494153494105</v>
+        <v>-0.02929494153494083</v>
       </c>
     </row>
     <row r="23">
@@ -1376,7 +1376,7 @@
         <v>98982.15764175884</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>-0.01576197176685612</v>
+        <v>-0.01576197176685634</v>
       </c>
       <c r="D23" s="4" t="n">
         <v>-0.01017842358241161</v>
@@ -1402,7 +1402,7 @@
         <v>0.003127667249263499</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>-0.007082591055236009</v>
+        <v>-0.007082591055235898</v>
       </c>
       <c r="E24" s="5" t="n">
         <v>14350.599609375</v>
@@ -1411,7 +1411,7 @@
         <v>0.0471832756403241</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>-0.05426586669556011</v>
+        <v>-0.05426586669555999</v>
       </c>
     </row>
     <row r="25">
@@ -1422,7 +1422,7 @@
         <v>98699.49739704847</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>-0.005964680366087438</v>
+        <v>-0.005964680366087549</v>
       </c>
       <c r="D25" s="4" t="n">
         <v>-0.01300502602951525</v>
@@ -1511,13 +1511,13 @@
         <v>46211</v>
       </c>
       <c r="B29" s="5" t="n">
-        <v>97511.54763463837</v>
+        <v>97511.54763463838</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>-0.02101826087704539</v>
+        <v>-0.02101826087704517</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>-0.02488452365361637</v>
+        <v>-0.02488452365361615</v>
       </c>
       <c r="E29" s="5" t="n">
         <v>14190</v>
@@ -1526,7 +1526,7 @@
         <v>0.03546409807355522</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>-0.06034862172717159</v>
+        <v>-0.06034862172717137</v>
       </c>
     </row>
     <row r="30">
@@ -1537,7 +1537,7 @@
         <v>97085.90440793287</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>-0.004365054570770521</v>
+        <v>-0.004365054570770743</v>
       </c>
       <c r="D30" s="4" t="n">
         <v>-0.02914095592067123</v>
@@ -1603,13 +1603,13 @@
         <v>46217</v>
       </c>
       <c r="B33" s="5" t="n">
-        <v>101364.3995699691</v>
+        <v>101364.3995699692</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>0.02123082912189433</v>
+        <v>0.02123082912189456</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>0.01364399569969144</v>
+        <v>0.01364399569969166</v>
       </c>
       <c r="E33" s="5" t="n">
         <v>14080</v>
@@ -1618,7 +1618,7 @@
         <v>0.02743724460011676</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>-0.01379324890042533</v>
+        <v>-0.0137932489004251</v>
       </c>
     </row>
     <row r="34">
@@ -1629,7 +1629,7 @@
         <v>105261.7030227777</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>0.0384484441218278</v>
+        <v>0.03844844412182757</v>
       </c>
       <c r="D34" s="4" t="n">
         <v>0.05261703022777731</v>
@@ -1675,10 +1675,10 @@
         <v>104848.7672438694</v>
       </c>
       <c r="C36" s="4" t="n">
-        <v>0.02469452791059834</v>
+        <v>0.02469452791059856</v>
       </c>
       <c r="D36" s="4" t="n">
-        <v>0.04848767243869401</v>
+        <v>0.04848767243869423</v>
       </c>
       <c r="E36" s="5" t="n">
         <v>14071</v>
@@ -1687,7 +1687,7 @@
         <v>0.02678050204319904</v>
       </c>
       <c r="G36" s="4" t="n">
-        <v>0.02170717039549497</v>
+        <v>0.02170717039549519</v>
       </c>
     </row>
     <row r="37">
@@ -1698,7 +1698,7 @@
         <v>102169.894507684</v>
       </c>
       <c r="C37" s="4" t="n">
-        <v>-0.02554987346636639</v>
+        <v>-0.02554987346636661</v>
       </c>
       <c r="D37" s="4" t="n">
         <v>0.02169894507684034</v>
@@ -1879,13 +1879,13 @@
         <v>46234</v>
       </c>
       <c r="B45" s="5" t="n">
-        <v>101068.0382772884</v>
+        <v>100007.3767240604</v>
       </c>
       <c r="C45" s="4" t="n">
-        <v>0.01060583316923247</v>
+        <v>0</v>
       </c>
       <c r="D45" s="4" t="n">
-        <v>0.01068038277288408</v>
+        <v>7.376724060437212e-05</v>
       </c>
       <c r="E45" s="5" t="n">
         <v>13458.099609375</v>
@@ -1894,7 +1894,7 @@
         <v>-0.01794369458734679</v>
       </c>
       <c r="G45" s="4" t="n">
-        <v>0.02862407736023087</v>
+        <v>0.01801746182795116</v>
       </c>
     </row>
     <row r="46">
@@ -1905,7 +1905,7 @@
         <v>98817.64242294777</v>
       </c>
       <c r="C46" s="4" t="n">
-        <v>-0.0222661475645396</v>
+        <v>-0.01189646544169809</v>
       </c>
       <c r="D46" s="4" t="n">
         <v>-0.01182357577052229</v>
@@ -1994,13 +1994,13 @@
         <v>46241</v>
       </c>
       <c r="B50" s="5" t="n">
-        <v>99635.64159588418</v>
+        <v>97154.28928705474</v>
       </c>
       <c r="C50" s="4" t="n">
-        <v>0</v>
+        <v>-0.02490426386667588</v>
       </c>
       <c r="D50" s="4" t="n">
-        <v>-0.003643584041158165</v>
+        <v>-0.0284571071294526</v>
       </c>
       <c r="E50" s="5" t="n">
         <v>13779.400390625</v>
@@ -2009,11 +2009,34 @@
         <v>0.005502071703517242</v>
       </c>
       <c r="G50" s="4" t="n">
-        <v>-0.009145655744675407</v>
+        <v>-0.03395917883296984</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="6" t="n">
+        <v>46244</v>
+      </c>
+      <c r="B51" s="5" t="n">
+        <v>97154.28928705474</v>
+      </c>
+      <c r="C51" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D51" s="4" t="n">
+        <v>-0.0284571071294526</v>
+      </c>
+      <c r="E51" s="5" t="n">
+        <v>13811.599609375</v>
+      </c>
+      <c r="F51" s="4" t="n">
+        <v>0.007851693620475775</v>
+      </c>
+      <c r="G51" s="4" t="n">
+        <v>-0.03630880074992837</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G50"/>
+  <autoFilter ref="A1:G51"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/reports/latest_one_month_follow_up.xlsx
+++ b/reports/latest_one_month_follow_up.xlsx
@@ -15,7 +15,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'TAKIP_OZETI'!$A$1:$B$19</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'POZISYONLAR'!$A$1:$H$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'GUNLUK_TAKIP'!$A$1:$G$51</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'GUNLUK_TAKIP'!$A$1:$G$52</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'NOTLAR'!$A$1:$A$7</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -475,7 +475,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
     </row>
@@ -546,7 +546,7 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>13811.599609375</v>
+        <v>13704.5</v>
       </c>
     </row>
     <row r="9">
@@ -603,7 +603,7 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
     </row>
@@ -627,7 +627,7 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>-0.02845710712945282</v>
+        <v>-0.04377826556422426</v>
       </c>
     </row>
     <row r="17">
@@ -648,7 +648,7 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>0.007851693620475775</v>
+        <v>3.648569760650311e-05</v>
       </c>
     </row>
     <row r="18">
@@ -658,7 +658,7 @@
         </is>
       </c>
       <c r="B18" s="3" t="n">
-        <v>-0.03630880074992859</v>
+        <v>-0.04381475126183076</v>
       </c>
     </row>
     <row r="19">
@@ -753,19 +753,19 @@
         <v>40</v>
       </c>
       <c r="D2" s="5" t="n">
-        <v>38.68000030517578</v>
+        <v>36.88000106811523</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>-0.03299999237060547</v>
+        <v>-0.07799997329711916</v>
       </c>
       <c r="F2" s="5" t="n">
         <v>33333.33333333333</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>32233.33358764648</v>
+        <v>30733.33422342936</v>
       </c>
       <c r="H2" s="5" t="n">
-        <v>-1099.999745686848</v>
+        <v>-2599.999109903973</v>
       </c>
     </row>
     <row r="3">
@@ -781,19 +781,19 @@
         <v>45.5</v>
       </c>
       <c r="D3" s="5" t="n">
-        <v>41.34000015258789</v>
+        <v>41.47999954223633</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>-0.09142856807499145</v>
+        <v>-0.08835165841238835</v>
       </c>
       <c r="F3" s="5" t="n">
         <v>33333.33333333333</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>30285.71439750028</v>
+        <v>30388.27805292038</v>
       </c>
       <c r="H3" s="5" t="n">
-        <v>-3047.618935833048</v>
+        <v>-2945.055280412944</v>
       </c>
     </row>
     <row r="4">
@@ -809,19 +809,19 @@
         <v>371.25</v>
       </c>
       <c r="D4" s="5" t="n">
-        <v>385.75</v>
+        <v>384.25</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>0.03905723905723901</v>
+        <v>0.03501683501683495</v>
       </c>
       <c r="F4" s="5" t="n">
         <v>33333.33333333333</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>34635.24130190796</v>
+        <v>34500.56116722782</v>
       </c>
       <c r="H4" s="5" t="n">
-        <v>1301.907968574633</v>
+        <v>1167.227833894496</v>
       </c>
     </row>
   </sheetData>
@@ -836,7 +836,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G51"/>
+  <dimension ref="A1:G52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -1879,13 +1879,13 @@
         <v>46234</v>
       </c>
       <c r="B45" s="5" t="n">
-        <v>100007.3767240604</v>
+        <v>101068.0382772884</v>
       </c>
       <c r="C45" s="4" t="n">
-        <v>0</v>
+        <v>0.01060583316923247</v>
       </c>
       <c r="D45" s="4" t="n">
-        <v>7.376724060437212e-05</v>
+        <v>0.01068038277288408</v>
       </c>
       <c r="E45" s="5" t="n">
         <v>13458.099609375</v>
@@ -1894,7 +1894,7 @@
         <v>-0.01794369458734679</v>
       </c>
       <c r="G45" s="4" t="n">
-        <v>0.01801746182795116</v>
+        <v>0.02862407736023087</v>
       </c>
     </row>
     <row r="46">
@@ -1905,7 +1905,7 @@
         <v>98817.64242294777</v>
       </c>
       <c r="C46" s="4" t="n">
-        <v>-0.01189646544169809</v>
+        <v>-0.0222661475645396</v>
       </c>
       <c r="D46" s="4" t="n">
         <v>-0.01182357577052229</v>
@@ -2017,13 +2017,13 @@
         <v>46244</v>
       </c>
       <c r="B51" s="5" t="n">
-        <v>97154.28928705474</v>
+        <v>95622.17344357757</v>
       </c>
       <c r="C51" s="4" t="n">
-        <v>0</v>
+        <v>-0.01576992487640283</v>
       </c>
       <c r="D51" s="4" t="n">
-        <v>-0.0284571071294526</v>
+        <v>-0.04377826556422426</v>
       </c>
       <c r="E51" s="5" t="n">
         <v>13811.599609375</v>
@@ -2032,11 +2032,34 @@
         <v>0.007851693620475775</v>
       </c>
       <c r="G51" s="4" t="n">
-        <v>-0.03630880074992837</v>
+        <v>-0.05162995918470004</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="6" t="n">
+        <v>46245</v>
+      </c>
+      <c r="B52" s="5" t="n">
+        <v>95622.17344357757</v>
+      </c>
+      <c r="C52" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D52" s="4" t="n">
+        <v>-0.04377826556422426</v>
+      </c>
+      <c r="E52" s="5" t="n">
+        <v>13704.5</v>
+      </c>
+      <c r="F52" s="4" t="n">
+        <v>3.648569760650311e-05</v>
+      </c>
+      <c r="G52" s="4" t="n">
+        <v>-0.04381475126183076</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G51"/>
+  <autoFilter ref="A1:G52"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/reports/latest_one_month_follow_up.xlsx
+++ b/reports/latest_one_month_follow_up.xlsx
@@ -15,7 +15,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'TAKIP_OZETI'!$A$1:$B$19</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'POZISYONLAR'!$A$1:$H$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'GUNLUK_TAKIP'!$A$1:$G$52</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'GUNLUK_TAKIP'!$A$1:$G$53</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'NOTLAR'!$A$1:$A$7</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -475,7 +475,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -546,7 +546,7 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>13704.5</v>
+        <v>14110.099609375</v>
       </c>
     </row>
     <row r="9">
@@ -603,7 +603,7 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -627,7 +627,7 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>-0.04377826556422426</v>
+        <v>-0.0549186492145326</v>
       </c>
     </row>
     <row r="17">
@@ -648,7 +648,7 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>3.648569760650311e-05</v>
+        <v>0.029633655091579</v>
       </c>
     </row>
     <row r="18">
@@ -658,7 +658,7 @@
         </is>
       </c>
       <c r="B18" s="3" t="n">
-        <v>-0.04381475126183076</v>
+        <v>-0.0845523043061116</v>
       </c>
     </row>
     <row r="19">
@@ -692,7 +692,7 @@
     <col width="20" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
     <col width="19" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="21" customWidth="1" min="5" max="5"/>
     <col width="19" customWidth="1" min="6" max="6"/>
     <col width="19" customWidth="1" min="7" max="7"/>
     <col width="20" customWidth="1" min="8" max="8"/>
@@ -753,19 +753,19 @@
         <v>40</v>
       </c>
       <c r="D2" s="5" t="n">
-        <v>36.88000106811523</v>
+        <v>36.86000061035156</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>-0.07799997329711916</v>
+        <v>-0.07849998474121089</v>
       </c>
       <c r="F2" s="5" t="n">
         <v>33333.33333333333</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>30733.33422342936</v>
+        <v>30716.66717529297</v>
       </c>
       <c r="H2" s="5" t="n">
-        <v>-2599.999109903973</v>
+        <v>-2616.666158040363</v>
       </c>
     </row>
     <row r="3">
@@ -781,19 +781,19 @@
         <v>45.5</v>
       </c>
       <c r="D3" s="5" t="n">
-        <v>41.47999954223633</v>
+        <v>40.84000015258789</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>-0.08835165841238835</v>
+        <v>-0.1024175790640024</v>
       </c>
       <c r="F3" s="5" t="n">
         <v>33333.33333333333</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>30388.27805292038</v>
+        <v>29919.41403119991</v>
       </c>
       <c r="H3" s="5" t="n">
-        <v>-2945.055280412944</v>
+        <v>-3413.919302133414</v>
       </c>
     </row>
     <row r="4">
@@ -809,19 +809,19 @@
         <v>371.25</v>
       </c>
       <c r="D4" s="5" t="n">
-        <v>384.25</v>
+        <v>377.25</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>0.03501683501683495</v>
+        <v>0.01616161616161627</v>
       </c>
       <c r="F4" s="5" t="n">
         <v>33333.33333333333</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>34500.56116722782</v>
+        <v>33872.05387205387</v>
       </c>
       <c r="H4" s="5" t="n">
-        <v>1167.227833894496</v>
+        <v>538.7205387205395</v>
       </c>
     </row>
   </sheetData>
@@ -836,7 +836,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G52"/>
+  <dimension ref="A1:G53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -1672,13 +1672,13 @@
         <v>46223</v>
       </c>
       <c r="B36" s="5" t="n">
-        <v>104848.7672438694</v>
+        <v>102541.7540522438</v>
       </c>
       <c r="C36" s="4" t="n">
-        <v>0.02469452791059856</v>
+        <v>0.002147922400417501</v>
       </c>
       <c r="D36" s="4" t="n">
-        <v>0.04848767243869423</v>
+        <v>0.02541754052243839</v>
       </c>
       <c r="E36" s="5" t="n">
         <v>14071</v>
@@ -1687,7 +1687,7 @@
         <v>0.02678050204319904</v>
       </c>
       <c r="G36" s="4" t="n">
-        <v>0.02170717039549519</v>
+        <v>-0.001362961520760653</v>
       </c>
     </row>
     <row r="37">
@@ -1698,7 +1698,7 @@
         <v>102169.894507684</v>
       </c>
       <c r="C37" s="4" t="n">
-        <v>-0.02554987346636661</v>
+        <v>-0.003626420749252568</v>
       </c>
       <c r="D37" s="4" t="n">
         <v>0.02169894507684034</v>
@@ -1879,13 +1879,13 @@
         <v>46234</v>
       </c>
       <c r="B45" s="5" t="n">
-        <v>101068.0382772884</v>
+        <v>100300.4181349607</v>
       </c>
       <c r="C45" s="4" t="n">
-        <v>0.01060583316923247</v>
+        <v>0.002930197956385383</v>
       </c>
       <c r="D45" s="4" t="n">
-        <v>0.01068038277288408</v>
+        <v>0.003004181349607338</v>
       </c>
       <c r="E45" s="5" t="n">
         <v>13458.099609375</v>
@@ -1894,7 +1894,7 @@
         <v>-0.01794369458734679</v>
       </c>
       <c r="G45" s="4" t="n">
-        <v>0.02862407736023087</v>
+        <v>0.02094787593695413</v>
       </c>
     </row>
     <row r="46">
@@ -1905,7 +1905,7 @@
         <v>98817.64242294777</v>
       </c>
       <c r="C46" s="4" t="n">
-        <v>-0.0222661475645396</v>
+        <v>-0.0147833452699847</v>
       </c>
       <c r="D46" s="4" t="n">
         <v>-0.01182357577052229</v>
@@ -2040,13 +2040,13 @@
         <v>46245</v>
       </c>
       <c r="B52" s="5" t="n">
-        <v>95622.17344357757</v>
+        <v>94508.13507854677</v>
       </c>
       <c r="C52" s="4" t="n">
-        <v>0</v>
+        <v>-0.01165041877748318</v>
       </c>
       <c r="D52" s="4" t="n">
-        <v>-0.04377826556422426</v>
+        <v>-0.05491864921453238</v>
       </c>
       <c r="E52" s="5" t="n">
         <v>13704.5</v>
@@ -2055,11 +2055,34 @@
         <v>3.648569760650311e-05</v>
       </c>
       <c r="G52" s="4" t="n">
-        <v>-0.04381475126183076</v>
+        <v>-0.05495513491213888</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="6" t="n">
+        <v>46246</v>
+      </c>
+      <c r="B53" s="5" t="n">
+        <v>94508.13507854677</v>
+      </c>
+      <c r="C53" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D53" s="4" t="n">
+        <v>-0.05491864921453238</v>
+      </c>
+      <c r="E53" s="5" t="n">
+        <v>14110.099609375</v>
+      </c>
+      <c r="F53" s="4" t="n">
+        <v>0.029633655091579</v>
+      </c>
+      <c r="G53" s="4" t="n">
+        <v>-0.08455230430611138</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G52"/>
+  <autoFilter ref="A1:G53"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/reports/latest_one_month_follow_up.xlsx
+++ b/reports/latest_one_month_follow_up.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="TAKIP_OZETI" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="POZISYONLAR" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="GUNLUK_TAKIP" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="NOTLAR" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TAKIP_OZETI" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="POZISYONLAR" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GUNLUK_TAKIP" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NOTLAR" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'TAKIP_OZETI'!$A$1:$B$19</definedName>
@@ -475,7 +475,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
     </row>
@@ -546,7 +546,7 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>14110.099609375</v>
+        <v>14132.2001953125</v>
       </c>
     </row>
     <row r="9">
@@ -603,7 +603,7 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
     </row>
@@ -627,7 +627,7 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>-0.0549186492145326</v>
+        <v>-0.04531226597629046</v>
       </c>
     </row>
     <row r="17">
@@ -648,7 +648,7 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>0.029633655091579</v>
+        <v>0.03124636568246508</v>
       </c>
     </row>
     <row r="18">
@@ -658,7 +658,7 @@
         </is>
       </c>
       <c r="B18" s="3" t="n">
-        <v>-0.0845523043061116</v>
+        <v>-0.07655863165875554</v>
       </c>
     </row>
     <row r="19">
@@ -692,7 +692,7 @@
     <col width="20" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
     <col width="19" customWidth="1" min="4" max="4"/>
-    <col width="21" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
     <col width="19" customWidth="1" min="6" max="6"/>
     <col width="19" customWidth="1" min="7" max="7"/>
     <col width="20" customWidth="1" min="8" max="8"/>
@@ -753,19 +753,19 @@
         <v>40</v>
       </c>
       <c r="D2" s="5" t="n">
-        <v>36.86000061035156</v>
+        <v>37.18000030517578</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>-0.07849998474121089</v>
+        <v>-0.07049999237060545</v>
       </c>
       <c r="F2" s="5" t="n">
         <v>33333.33333333333</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>30716.66717529297</v>
+        <v>30983.33358764648</v>
       </c>
       <c r="H2" s="5" t="n">
-        <v>-2616.666158040363</v>
+        <v>-2349.999745686848</v>
       </c>
     </row>
     <row r="3">
@@ -781,19 +781,19 @@
         <v>45.5</v>
       </c>
       <c r="D3" s="5" t="n">
-        <v>40.84000015258789</v>
+        <v>40.95999908447266</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>-0.1024175790640024</v>
+        <v>-0.09978023990169982</v>
       </c>
       <c r="F3" s="5" t="n">
         <v>33333.33333333333</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>29919.41403119991</v>
+        <v>30007.32533661</v>
       </c>
       <c r="H3" s="5" t="n">
-        <v>-3413.919302133414</v>
+        <v>-3326.007996723325</v>
       </c>
     </row>
     <row r="4">
@@ -809,19 +809,19 @@
         <v>371.25</v>
       </c>
       <c r="D4" s="5" t="n">
-        <v>377.25</v>
+        <v>384</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>0.01616161616161627</v>
+        <v>0.03434343434343434</v>
       </c>
       <c r="F4" s="5" t="n">
         <v>33333.33333333333</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>33872.05387205387</v>
+        <v>34478.11447811448</v>
       </c>
       <c r="H4" s="5" t="n">
-        <v>538.7205387205395</v>
+        <v>1144.781144781147</v>
       </c>
     </row>
   </sheetData>
@@ -1672,13 +1672,13 @@
         <v>46223</v>
       </c>
       <c r="B36" s="5" t="n">
-        <v>102541.7540522438</v>
+        <v>102321.9743913936</v>
       </c>
       <c r="C36" s="4" t="n">
-        <v>0.002147922400417501</v>
+        <v>0</v>
       </c>
       <c r="D36" s="4" t="n">
-        <v>0.02541754052243839</v>
+        <v>0.02321974391393611</v>
       </c>
       <c r="E36" s="5" t="n">
         <v>14071</v>
@@ -1687,7 +1687,7 @@
         <v>0.02678050204319904</v>
       </c>
       <c r="G36" s="4" t="n">
-        <v>-0.001362961520760653</v>
+        <v>-0.003560758129262931</v>
       </c>
     </row>
     <row r="37">
@@ -1698,19 +1698,19 @@
         <v>102169.894507684</v>
       </c>
       <c r="C37" s="4" t="n">
-        <v>-0.003626420749252568</v>
+        <v>-0.001486287619195559</v>
       </c>
       <c r="D37" s="4" t="n">
         <v>0.02169894507684034</v>
       </c>
       <c r="E37" s="5" t="n">
-        <v>13974.099609375</v>
+        <v>14071</v>
       </c>
       <c r="F37" s="4" t="n">
-        <v>0.01970954534260061</v>
+        <v>0.02678050204319904</v>
       </c>
       <c r="G37" s="4" t="n">
-        <v>0.001989399734239727</v>
+        <v>-0.005081556966358702</v>
       </c>
     </row>
     <row r="38">
@@ -1727,13 +1727,13 @@
         <v>0.03048300464520159</v>
       </c>
       <c r="E38" s="5" t="n">
-        <v>14138.900390625</v>
+        <v>14071</v>
       </c>
       <c r="F38" s="4" t="n">
-        <v>0.03173528828261829</v>
+        <v>0.02678050204319904</v>
       </c>
       <c r="G38" s="4" t="n">
-        <v>-0.001252283637416696</v>
+        <v>0.003702502602002555</v>
       </c>
     </row>
     <row r="39">
@@ -1876,209 +1876,209 @@
     </row>
     <row r="45">
       <c r="A45" s="6" t="n">
-        <v>46234</v>
+        <v>46237</v>
       </c>
       <c r="B45" s="5" t="n">
-        <v>100300.4181349607</v>
+        <v>98817.64242294777</v>
       </c>
       <c r="C45" s="4" t="n">
-        <v>0.002930197956385383</v>
+        <v>-0.01189646544169809</v>
       </c>
       <c r="D45" s="4" t="n">
-        <v>0.003004181349607338</v>
+        <v>-0.01182357577052229</v>
       </c>
       <c r="E45" s="5" t="n">
-        <v>13458.099609375</v>
+        <v>13410.5</v>
       </c>
       <c r="F45" s="4" t="n">
-        <v>-0.01794369458734679</v>
+        <v>-0.02141710449503798</v>
       </c>
       <c r="G45" s="4" t="n">
-        <v>0.02094787593695413</v>
+        <v>0.009593528724515688</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="6" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="B46" s="5" t="n">
-        <v>98817.64242294777</v>
+        <v>100510.1501194647</v>
       </c>
       <c r="C46" s="4" t="n">
-        <v>-0.0147833452699847</v>
+        <v>0.01712758627930899</v>
       </c>
       <c r="D46" s="4" t="n">
-        <v>-0.01182357577052229</v>
+        <v>0.00510150119464714</v>
       </c>
       <c r="E46" s="5" t="n">
-        <v>13410.5</v>
+        <v>13687.900390625</v>
       </c>
       <c r="F46" s="4" t="n">
-        <v>-0.02141710449503798</v>
+        <v>-0.001174810958479267</v>
       </c>
       <c r="G46" s="4" t="n">
-        <v>0.009593528724515688</v>
+        <v>0.006276312153126407</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="6" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="B47" s="5" t="n">
-        <v>100510.1501194647</v>
+        <v>100395.8946916857</v>
       </c>
       <c r="C47" s="4" t="n">
-        <v>0.01712758627930899</v>
+        <v>-0.001136755120186628</v>
       </c>
       <c r="D47" s="4" t="n">
-        <v>0.00510150119464714</v>
+        <v>0.003958946916856831</v>
       </c>
       <c r="E47" s="5" t="n">
-        <v>13687.900390625</v>
+        <v>13703.099609375</v>
       </c>
       <c r="F47" s="4" t="n">
-        <v>-0.001174810958479267</v>
+        <v>-6.570276014306042e-05</v>
       </c>
       <c r="G47" s="4" t="n">
-        <v>0.006276312153126407</v>
+        <v>0.004024649676999892</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="6" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="B48" s="5" t="n">
-        <v>100395.8946916857</v>
+        <v>99635.64159588418</v>
       </c>
       <c r="C48" s="4" t="n">
-        <v>-0.001136755120186628</v>
+        <v>-0.007572551628094226</v>
       </c>
       <c r="D48" s="4" t="n">
-        <v>0.003958946916856831</v>
+        <v>-0.003643584041158165</v>
       </c>
       <c r="E48" s="5" t="n">
-        <v>13703.099609375</v>
+        <v>13798.7998046875</v>
       </c>
       <c r="F48" s="4" t="n">
-        <v>-6.570276014306042e-05</v>
+        <v>0.006917674013974029</v>
       </c>
       <c r="G48" s="4" t="n">
-        <v>0.004024649676999892</v>
+        <v>-0.01056125805513219</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="6" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="B49" s="5" t="n">
-        <v>99635.64159588418</v>
+        <v>97154.28928705474</v>
       </c>
       <c r="C49" s="4" t="n">
-        <v>-0.007572551628094226</v>
+        <v>-0.02490426386667588</v>
       </c>
       <c r="D49" s="4" t="n">
-        <v>-0.003643584041158165</v>
+        <v>-0.0284571071294526</v>
       </c>
       <c r="E49" s="5" t="n">
-        <v>13798.7998046875</v>
+        <v>13779.400390625</v>
       </c>
       <c r="F49" s="4" t="n">
-        <v>0.006917674013974029</v>
+        <v>0.005502071703517242</v>
       </c>
       <c r="G49" s="4" t="n">
-        <v>-0.01056125805513219</v>
+        <v>-0.03395917883296984</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="6" t="n">
-        <v>46241</v>
+        <v>46244</v>
       </c>
       <c r="B50" s="5" t="n">
-        <v>97154.28928705474</v>
+        <v>95622.17344357757</v>
       </c>
       <c r="C50" s="4" t="n">
-        <v>-0.02490426386667588</v>
+        <v>-0.01576992487640283</v>
       </c>
       <c r="D50" s="4" t="n">
-        <v>-0.0284571071294526</v>
+        <v>-0.04377826556422426</v>
       </c>
       <c r="E50" s="5" t="n">
-        <v>13779.400390625</v>
+        <v>13811.599609375</v>
       </c>
       <c r="F50" s="4" t="n">
-        <v>0.005502071703517242</v>
+        <v>0.007851693620475775</v>
       </c>
       <c r="G50" s="4" t="n">
-        <v>-0.03395917883296984</v>
+        <v>-0.05162995918470004</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="6" t="n">
-        <v>46244</v>
+        <v>46245</v>
       </c>
       <c r="B51" s="5" t="n">
-        <v>95622.17344357757</v>
+        <v>94508.13507854677</v>
       </c>
       <c r="C51" s="4" t="n">
-        <v>-0.01576992487640283</v>
+        <v>-0.01165041877748318</v>
       </c>
       <c r="D51" s="4" t="n">
-        <v>-0.04377826556422426</v>
+        <v>-0.05491864921453238</v>
       </c>
       <c r="E51" s="5" t="n">
-        <v>13811.599609375</v>
+        <v>13704.5</v>
       </c>
       <c r="F51" s="4" t="n">
-        <v>0.007851693620475775</v>
+        <v>3.648569760650311e-05</v>
       </c>
       <c r="G51" s="4" t="n">
-        <v>-0.05162995918470004</v>
+        <v>-0.05495513491213888</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="6" t="n">
-        <v>46245</v>
+        <v>46246</v>
       </c>
       <c r="B52" s="5" t="n">
-        <v>94508.13507854677</v>
+        <v>95468.77340237095</v>
       </c>
       <c r="C52" s="4" t="n">
-        <v>-0.01165041877748318</v>
+        <v>0.01016460988279788</v>
       </c>
       <c r="D52" s="4" t="n">
-        <v>-0.05491864921453238</v>
+        <v>-0.04531226597629046</v>
       </c>
       <c r="E52" s="5" t="n">
-        <v>13704.5</v>
+        <v>14110.099609375</v>
       </c>
       <c r="F52" s="4" t="n">
-        <v>3.648569760650311e-05</v>
+        <v>0.029633655091579</v>
       </c>
       <c r="G52" s="4" t="n">
-        <v>-0.05495513491213888</v>
+        <v>-0.07494592106786946</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="6" t="n">
-        <v>46246</v>
+        <v>46247</v>
       </c>
       <c r="B53" s="5" t="n">
-        <v>94508.13507854677</v>
+        <v>95468.77340237095</v>
       </c>
       <c r="C53" s="4" t="n">
         <v>0</v>
       </c>
       <c r="D53" s="4" t="n">
-        <v>-0.05491864921453238</v>
+        <v>-0.04531226597629046</v>
       </c>
       <c r="E53" s="5" t="n">
-        <v>14110.099609375</v>
+        <v>14132.2001953125</v>
       </c>
       <c r="F53" s="4" t="n">
-        <v>0.029633655091579</v>
+        <v>0.03124636568246508</v>
       </c>
       <c r="G53" s="4" t="n">
-        <v>-0.08455230430611138</v>
+        <v>-0.07655863165875554</v>
       </c>
     </row>
   </sheetData>

--- a/reports/latest_one_month_follow_up.xlsx
+++ b/reports/latest_one_month_follow_up.xlsx
@@ -15,7 +15,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'TAKIP_OZETI'!$A$1:$B$19</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'POZISYONLAR'!$A$1:$H$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'GUNLUK_TAKIP'!$A$1:$G$53</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'GUNLUK_TAKIP'!$A$1:$G$55</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'NOTLAR'!$A$1:$A$7</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -475,7 +475,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -546,7 +546,7 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>14132.2001953125</v>
+        <v>14172.2998046875</v>
       </c>
     </row>
     <row r="9">
@@ -603,7 +603,7 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -627,7 +627,7 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>-0.04531226597629046</v>
+        <v>-0.03823124071546713</v>
       </c>
     </row>
     <row r="17">
@@ -648,7 +648,7 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>0.03124636568246508</v>
+        <v>0.03417249012605805</v>
       </c>
     </row>
     <row r="18">
@@ -658,7 +658,7 @@
         </is>
       </c>
       <c r="B18" s="3" t="n">
-        <v>-0.07655863165875554</v>
+        <v>-0.07240373084152518</v>
       </c>
     </row>
     <row r="19">
@@ -753,19 +753,19 @@
         <v>40</v>
       </c>
       <c r="D2" s="5" t="n">
-        <v>37.18000030517578</v>
+        <v>38.2400016784668</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>-0.07049999237060545</v>
+        <v>-0.04399995803833012</v>
       </c>
       <c r="F2" s="5" t="n">
         <v>33333.33333333333</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>30983.33358764648</v>
+        <v>31866.66806538899</v>
       </c>
       <c r="H2" s="5" t="n">
-        <v>-2349.999745686848</v>
+        <v>-1466.665267944336</v>
       </c>
     </row>
     <row r="3">
@@ -781,19 +781,19 @@
         <v>45.5</v>
       </c>
       <c r="D3" s="5" t="n">
-        <v>40.95999908447266</v>
+        <v>41.63999938964844</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>-0.09978023990169982</v>
+        <v>-0.08483517824948494</v>
       </c>
       <c r="F3" s="5" t="n">
         <v>33333.33333333333</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>30007.32533661</v>
+        <v>30505.4940583505</v>
       </c>
       <c r="H3" s="5" t="n">
-        <v>-3326.007996723325</v>
+        <v>-2827.839274982831</v>
       </c>
     </row>
     <row r="4">
@@ -809,19 +809,19 @@
         <v>371.25</v>
       </c>
       <c r="D4" s="5" t="n">
-        <v>384</v>
+        <v>376.5</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>0.03434343434343434</v>
+        <v>0.01414141414141423</v>
       </c>
       <c r="F4" s="5" t="n">
         <v>33333.33333333333</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>34478.11447811448</v>
+        <v>33804.7138047138</v>
       </c>
       <c r="H4" s="5" t="n">
-        <v>1144.781144781147</v>
+        <v>471.3804713804711</v>
       </c>
     </row>
   </sheetData>
@@ -836,7 +836,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G53"/>
+  <dimension ref="A1:G55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -1672,13 +1672,13 @@
         <v>46223</v>
       </c>
       <c r="B36" s="5" t="n">
-        <v>102321.9743913936</v>
+        <v>102541.7540522438</v>
       </c>
       <c r="C36" s="4" t="n">
-        <v>0</v>
+        <v>0.002147922400417501</v>
       </c>
       <c r="D36" s="4" t="n">
-        <v>0.02321974391393611</v>
+        <v>0.02541754052243839</v>
       </c>
       <c r="E36" s="5" t="n">
         <v>14071</v>
@@ -1687,7 +1687,7 @@
         <v>0.02678050204319904</v>
       </c>
       <c r="G36" s="4" t="n">
-        <v>-0.003560758129262931</v>
+        <v>-0.001362961520760653</v>
       </c>
     </row>
     <row r="37">
@@ -1698,7 +1698,7 @@
         <v>102169.894507684</v>
       </c>
       <c r="C37" s="4" t="n">
-        <v>-0.001486287619195559</v>
+        <v>-0.003626420749252568</v>
       </c>
       <c r="D37" s="4" t="n">
         <v>0.02169894507684034</v>
@@ -1876,213 +1876,259 @@
     </row>
     <row r="45">
       <c r="A45" s="6" t="n">
-        <v>46237</v>
+        <v>46234</v>
       </c>
       <c r="B45" s="5" t="n">
-        <v>98817.64242294777</v>
+        <v>100300.4181349607</v>
       </c>
       <c r="C45" s="4" t="n">
-        <v>-0.01189646544169809</v>
+        <v>0.002930197956385383</v>
       </c>
       <c r="D45" s="4" t="n">
-        <v>-0.01182357577052229</v>
+        <v>0.003004181349607338</v>
       </c>
       <c r="E45" s="5" t="n">
-        <v>13410.5</v>
+        <v>13292.900390625</v>
       </c>
       <c r="F45" s="4" t="n">
-        <v>-0.02141710449503798</v>
+        <v>-0.02999851206764448</v>
       </c>
       <c r="G45" s="4" t="n">
-        <v>0.009593528724515688</v>
+        <v>0.03300269341725182</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="6" t="n">
-        <v>46238</v>
+        <v>46237</v>
       </c>
       <c r="B46" s="5" t="n">
-        <v>100510.1501194647</v>
+        <v>98817.64242294777</v>
       </c>
       <c r="C46" s="4" t="n">
-        <v>0.01712758627930899</v>
+        <v>-0.0147833452699847</v>
       </c>
       <c r="D46" s="4" t="n">
-        <v>0.00510150119464714</v>
+        <v>-0.01182357577052229</v>
       </c>
       <c r="E46" s="5" t="n">
-        <v>13687.900390625</v>
+        <v>13410.5</v>
       </c>
       <c r="F46" s="4" t="n">
-        <v>-0.001174810958479267</v>
+        <v>-0.02141710449503798</v>
       </c>
       <c r="G46" s="4" t="n">
-        <v>0.006276312153126407</v>
+        <v>0.009593528724515688</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="6" t="n">
-        <v>46239</v>
+        <v>46238</v>
       </c>
       <c r="B47" s="5" t="n">
-        <v>100395.8946916857</v>
+        <v>100510.1501194647</v>
       </c>
       <c r="C47" s="4" t="n">
-        <v>-0.001136755120186628</v>
+        <v>0.01712758627930899</v>
       </c>
       <c r="D47" s="4" t="n">
-        <v>0.003958946916856831</v>
+        <v>0.00510150119464714</v>
       </c>
       <c r="E47" s="5" t="n">
-        <v>13703.099609375</v>
+        <v>13687.900390625</v>
       </c>
       <c r="F47" s="4" t="n">
-        <v>-6.570276014306042e-05</v>
+        <v>-0.001174810958479267</v>
       </c>
       <c r="G47" s="4" t="n">
-        <v>0.004024649676999892</v>
+        <v>0.006276312153126407</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="6" t="n">
-        <v>46240</v>
+        <v>46239</v>
       </c>
       <c r="B48" s="5" t="n">
-        <v>99635.64159588418</v>
+        <v>100395.8946916857</v>
       </c>
       <c r="C48" s="4" t="n">
-        <v>-0.007572551628094226</v>
+        <v>-0.001136755120186628</v>
       </c>
       <c r="D48" s="4" t="n">
-        <v>-0.003643584041158165</v>
+        <v>0.003958946916856831</v>
       </c>
       <c r="E48" s="5" t="n">
-        <v>13798.7998046875</v>
+        <v>13703.099609375</v>
       </c>
       <c r="F48" s="4" t="n">
-        <v>0.006917674013974029</v>
+        <v>-6.570276014306042e-05</v>
       </c>
       <c r="G48" s="4" t="n">
-        <v>-0.01056125805513219</v>
+        <v>0.004024649676999892</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="6" t="n">
-        <v>46241</v>
+        <v>46240</v>
       </c>
       <c r="B49" s="5" t="n">
-        <v>97154.28928705474</v>
+        <v>99635.64159588418</v>
       </c>
       <c r="C49" s="4" t="n">
-        <v>-0.02490426386667588</v>
+        <v>-0.007572551628094226</v>
       </c>
       <c r="D49" s="4" t="n">
-        <v>-0.0284571071294526</v>
+        <v>-0.003643584041158165</v>
       </c>
       <c r="E49" s="5" t="n">
-        <v>13779.400390625</v>
+        <v>13798.7998046875</v>
       </c>
       <c r="F49" s="4" t="n">
-        <v>0.005502071703517242</v>
+        <v>0.006917674013974029</v>
       </c>
       <c r="G49" s="4" t="n">
-        <v>-0.03395917883296984</v>
+        <v>-0.01056125805513219</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="6" t="n">
-        <v>46244</v>
+        <v>46241</v>
       </c>
       <c r="B50" s="5" t="n">
-        <v>95622.17344357757</v>
+        <v>97154.28928705474</v>
       </c>
       <c r="C50" s="4" t="n">
-        <v>-0.01576992487640283</v>
+        <v>-0.02490426386667588</v>
       </c>
       <c r="D50" s="4" t="n">
-        <v>-0.04377826556422426</v>
+        <v>-0.0284571071294526</v>
       </c>
       <c r="E50" s="5" t="n">
-        <v>13811.599609375</v>
+        <v>13779.400390625</v>
       </c>
       <c r="F50" s="4" t="n">
-        <v>0.007851693620475775</v>
+        <v>0.005502071703517242</v>
       </c>
       <c r="G50" s="4" t="n">
-        <v>-0.05162995918470004</v>
+        <v>-0.03395917883296984</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="6" t="n">
-        <v>46245</v>
+        <v>46244</v>
       </c>
       <c r="B51" s="5" t="n">
-        <v>94508.13507854677</v>
+        <v>95622.17344357757</v>
       </c>
       <c r="C51" s="4" t="n">
-        <v>-0.01165041877748318</v>
+        <v>-0.01576992487640283</v>
       </c>
       <c r="D51" s="4" t="n">
-        <v>-0.05491864921453238</v>
+        <v>-0.04377826556422426</v>
       </c>
       <c r="E51" s="5" t="n">
-        <v>13704.5</v>
+        <v>13811.599609375</v>
       </c>
       <c r="F51" s="4" t="n">
-        <v>3.648569760650311e-05</v>
+        <v>0.007851693620475775</v>
       </c>
       <c r="G51" s="4" t="n">
-        <v>-0.05495513491213888</v>
+        <v>-0.05162995918470004</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="6" t="n">
-        <v>46246</v>
+        <v>46245</v>
       </c>
       <c r="B52" s="5" t="n">
-        <v>95468.77340237095</v>
+        <v>94508.13507854677</v>
       </c>
       <c r="C52" s="4" t="n">
-        <v>0.01016460988279788</v>
+        <v>-0.01165041877748318</v>
       </c>
       <c r="D52" s="4" t="n">
-        <v>-0.04531226597629046</v>
+        <v>-0.05491864921453238</v>
       </c>
       <c r="E52" s="5" t="n">
-        <v>14110.099609375</v>
+        <v>13704.5</v>
       </c>
       <c r="F52" s="4" t="n">
-        <v>0.029633655091579</v>
+        <v>3.648569760650311e-05</v>
       </c>
       <c r="G52" s="4" t="n">
-        <v>-0.07494592106786946</v>
+        <v>-0.05495513491213888</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="6" t="n">
-        <v>46247</v>
+        <v>46246</v>
       </c>
       <c r="B53" s="5" t="n">
         <v>95468.77340237095</v>
       </c>
       <c r="C53" s="4" t="n">
-        <v>0</v>
+        <v>0.01016460988279788</v>
       </c>
       <c r="D53" s="4" t="n">
         <v>-0.04531226597629046</v>
       </c>
       <c r="E53" s="5" t="n">
+        <v>14110.099609375</v>
+      </c>
+      <c r="F53" s="4" t="n">
+        <v>0.029633655091579</v>
+      </c>
+      <c r="G53" s="4" t="n">
+        <v>-0.07494592106786946</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="6" t="n">
+        <v>46247</v>
+      </c>
+      <c r="B54" s="5" t="n">
+        <v>96176.8759284533</v>
+      </c>
+      <c r="C54" s="4" t="n">
+        <v>0.007417111384661057</v>
+      </c>
+      <c r="D54" s="4" t="n">
+        <v>-0.03823124071546702</v>
+      </c>
+      <c r="E54" s="5" t="n">
         <v>14132.2001953125</v>
       </c>
-      <c r="F53" s="4" t="n">
+      <c r="F54" s="4" t="n">
         <v>0.03124636568246508</v>
       </c>
-      <c r="G53" s="4" t="n">
-        <v>-0.07655863165875554</v>
+      <c r="G54" s="4" t="n">
+        <v>-0.0694776063979321</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="6" t="n">
+        <v>46248</v>
+      </c>
+      <c r="B55" s="5" t="n">
+        <v>96176.8759284533</v>
+      </c>
+      <c r="C55" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D55" s="4" t="n">
+        <v>-0.03823124071546702</v>
+      </c>
+      <c r="E55" s="5" t="n">
+        <v>14172.2998046875</v>
+      </c>
+      <c r="F55" s="4" t="n">
+        <v>0.03417249012605805</v>
+      </c>
+      <c r="G55" s="4" t="n">
+        <v>-0.07240373084152507</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G53"/>
+  <autoFilter ref="A1:G55"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/reports/latest_one_month_follow_up.xlsx
+++ b/reports/latest_one_month_follow_up.xlsx
@@ -1215,10 +1215,10 @@
         <v>101665.535802718</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>-0.01517965889001283</v>
+        <v>-0.0151796588900126</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>0.01665535802718021</v>
+        <v>0.01665535802718043</v>
       </c>
       <c r="E16" s="5" t="n">
         <v>14734.5</v>
@@ -1227,7 +1227,7 @@
         <v>0.07519702276707529</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>-0.05854166473989508</v>
+        <v>-0.05854166473989486</v>
       </c>
     </row>
     <row r="17">
@@ -1238,7 +1238,7 @@
         <v>101579.9132001645</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>-0.000842198901303659</v>
+        <v>-0.0008421989013038811</v>
       </c>
       <c r="D17" s="4" t="n">
         <v>0.01579913200164529</v>
@@ -1281,13 +1281,13 @@
         <v>46197</v>
       </c>
       <c r="B19" s="5" t="n">
-        <v>99903.87102493743</v>
+        <v>99903.87102493741</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>-0.007105427940044096</v>
+        <v>-0.007105427940044318</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>-0.0009612897506257045</v>
+        <v>-0.0009612897506259266</v>
       </c>
       <c r="E19" s="5" t="n">
         <v>14331.2001953125</v>
@@ -1296,7 +1296,7 @@
         <v>0.04576767332986709</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>-0.04672896308049279</v>
+        <v>-0.04672896308049301</v>
       </c>
     </row>
     <row r="20">
@@ -1307,7 +1307,7 @@
         <v>99725.18443384963</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>-0.001788585259556053</v>
+        <v>-0.00178858525955583</v>
       </c>
       <c r="D20" s="4" t="n">
         <v>-0.00274815566150366</v>
@@ -1353,10 +1353,10 @@
         <v>100567.2965303391</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>-0.01333614376284464</v>
+        <v>-0.01333614376284487</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>0.00567296530339112</v>
+        <v>0.005672965303390898</v>
       </c>
       <c r="E22" s="5" t="n">
         <v>14183.2001953125</v>
@@ -1365,7 +1365,7 @@
         <v>0.03496790683833195</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>-0.02929494153494083</v>
+        <v>-0.02929494153494105</v>
       </c>
     </row>
     <row r="23">
@@ -1376,7 +1376,7 @@
         <v>98982.15764175884</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>-0.01576197176685634</v>
+        <v>-0.01576197176685612</v>
       </c>
       <c r="D23" s="4" t="n">
         <v>-0.01017842358241161</v>
@@ -1402,7 +1402,7 @@
         <v>0.003127667249263499</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>-0.007082591055235898</v>
+        <v>-0.007082591055236009</v>
       </c>
       <c r="E24" s="5" t="n">
         <v>14350.599609375</v>
@@ -1411,7 +1411,7 @@
         <v>0.0471832756403241</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>-0.05426586669555999</v>
+        <v>-0.05426586669556011</v>
       </c>
     </row>
     <row r="25">
@@ -1422,7 +1422,7 @@
         <v>98699.49739704847</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>-0.005964680366087549</v>
+        <v>-0.005964680366087438</v>
       </c>
       <c r="D25" s="4" t="n">
         <v>-0.01300502602951525</v>
@@ -1511,13 +1511,13 @@
         <v>46211</v>
       </c>
       <c r="B29" s="5" t="n">
-        <v>97511.54763463838</v>
+        <v>97511.54763463837</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>-0.02101826087704517</v>
+        <v>-0.02101826087704539</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>-0.02488452365361615</v>
+        <v>-0.02488452365361637</v>
       </c>
       <c r="E29" s="5" t="n">
         <v>14190</v>
@@ -1526,7 +1526,7 @@
         <v>0.03546409807355522</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>-0.06034862172717137</v>
+        <v>-0.06034862172717159</v>
       </c>
     </row>
     <row r="30">
@@ -1537,7 +1537,7 @@
         <v>97085.90440793287</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>-0.004365054570770743</v>
+        <v>-0.004365054570770521</v>
       </c>
       <c r="D30" s="4" t="n">
         <v>-0.02914095592067123</v>
@@ -1603,13 +1603,13 @@
         <v>46217</v>
       </c>
       <c r="B33" s="5" t="n">
-        <v>101364.3995699692</v>
+        <v>101364.3995699691</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>0.02123082912189456</v>
+        <v>0.02123082912189433</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>0.01364399569969166</v>
+        <v>0.01364399569969144</v>
       </c>
       <c r="E33" s="5" t="n">
         <v>14080</v>
@@ -1618,7 +1618,7 @@
         <v>0.02743724460011676</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>-0.0137932489004251</v>
+        <v>-0.01379324890042533</v>
       </c>
     </row>
     <row r="34">
@@ -1629,7 +1629,7 @@
         <v>105261.7030227777</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>0.03844844412182757</v>
+        <v>0.0384484441218278</v>
       </c>
       <c r="D34" s="4" t="n">
         <v>0.05261703022777731</v>

--- a/reports/latest_one_month_follow_up.xlsx
+++ b/reports/latest_one_month_follow_up.xlsx
@@ -475,7 +475,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
     </row>
@@ -603,7 +603,7 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>-0.03823124071546713</v>
+        <v>-0.04872740681453347</v>
       </c>
     </row>
     <row r="17">
@@ -658,7 +658,7 @@
         </is>
       </c>
       <c r="B18" s="3" t="n">
-        <v>-0.07240373084152518</v>
+        <v>-0.08289989694059152</v>
       </c>
     </row>
     <row r="19">
@@ -753,19 +753,19 @@
         <v>40</v>
       </c>
       <c r="D2" s="5" t="n">
-        <v>38.2400016784668</v>
+        <v>37.38000106811523</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>-0.04399995803833012</v>
+        <v>-0.0654999732971191</v>
       </c>
       <c r="F2" s="5" t="n">
         <v>33333.33333333333</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>31866.66806538899</v>
+        <v>31150.00089009602</v>
       </c>
       <c r="H2" s="5" t="n">
-        <v>-1466.665267944336</v>
+        <v>-2183.332443237305</v>
       </c>
     </row>
     <row r="3">
@@ -781,19 +781,19 @@
         <v>45.5</v>
       </c>
       <c r="D3" s="5" t="n">
-        <v>41.63999938964844</v>
+        <v>41.40000152587891</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>-0.08483517824948494</v>
+        <v>-0.09010985657408999</v>
       </c>
       <c r="F3" s="5" t="n">
         <v>33333.33333333333</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>30505.4940583505</v>
+        <v>30329.67144753033</v>
       </c>
       <c r="H3" s="5" t="n">
-        <v>-2827.839274982831</v>
+        <v>-3003.661885802998</v>
       </c>
     </row>
     <row r="4">
@@ -809,19 +809,19 @@
         <v>371.25</v>
       </c>
       <c r="D4" s="5" t="n">
-        <v>376.5</v>
+        <v>374.75</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>0.01414141414141423</v>
+        <v>0.00942760942760934</v>
       </c>
       <c r="F4" s="5" t="n">
         <v>33333.33333333333</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>33804.7138047138</v>
+        <v>33647.58698092031</v>
       </c>
       <c r="H4" s="5" t="n">
-        <v>471.3804713804711</v>
+        <v>314.2536475869783</v>
       </c>
     </row>
   </sheetData>
@@ -1215,10 +1215,10 @@
         <v>101665.535802718</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>-0.0151796588900126</v>
+        <v>-0.01517965889001283</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>0.01665535802718043</v>
+        <v>0.01665535802718021</v>
       </c>
       <c r="E16" s="5" t="n">
         <v>14734.5</v>
@@ -1227,7 +1227,7 @@
         <v>0.07519702276707529</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>-0.05854166473989486</v>
+        <v>-0.05854166473989508</v>
       </c>
     </row>
     <row r="17">
@@ -1238,7 +1238,7 @@
         <v>101579.9132001645</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>-0.0008421989013038811</v>
+        <v>-0.000842198901303659</v>
       </c>
       <c r="D17" s="4" t="n">
         <v>0.01579913200164529</v>
@@ -1281,13 +1281,13 @@
         <v>46197</v>
       </c>
       <c r="B19" s="5" t="n">
-        <v>99903.87102493741</v>
+        <v>99903.87102493743</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>-0.007105427940044318</v>
+        <v>-0.007105427940044096</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>-0.0009612897506259266</v>
+        <v>-0.0009612897506257045</v>
       </c>
       <c r="E19" s="5" t="n">
         <v>14331.2001953125</v>
@@ -1296,7 +1296,7 @@
         <v>0.04576767332986709</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>-0.04672896308049301</v>
+        <v>-0.04672896308049279</v>
       </c>
     </row>
     <row r="20">
@@ -1307,7 +1307,7 @@
         <v>99725.18443384963</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>-0.00178858525955583</v>
+        <v>-0.001788585259556053</v>
       </c>
       <c r="D20" s="4" t="n">
         <v>-0.00274815566150366</v>
@@ -1353,10 +1353,10 @@
         <v>100567.2965303391</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>-0.01333614376284487</v>
+        <v>-0.01333614376284464</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>0.005672965303390898</v>
+        <v>0.00567296530339112</v>
       </c>
       <c r="E22" s="5" t="n">
         <v>14183.2001953125</v>
@@ -1365,7 +1365,7 @@
         <v>0.03496790683833195</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>-0.02929494153494105</v>
+        <v>-0.02929494153494083</v>
       </c>
     </row>
     <row r="23">
@@ -1376,7 +1376,7 @@
         <v>98982.15764175884</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>-0.01576197176685612</v>
+        <v>-0.01576197176685634</v>
       </c>
       <c r="D23" s="4" t="n">
         <v>-0.01017842358241161</v>
@@ -1402,7 +1402,7 @@
         <v>0.003127667249263499</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>-0.007082591055236009</v>
+        <v>-0.007082591055235898</v>
       </c>
       <c r="E24" s="5" t="n">
         <v>14350.599609375</v>
@@ -1411,7 +1411,7 @@
         <v>0.0471832756403241</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>-0.05426586669556011</v>
+        <v>-0.05426586669555999</v>
       </c>
     </row>
     <row r="25">
@@ -1422,7 +1422,7 @@
         <v>98699.49739704847</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>-0.005964680366087438</v>
+        <v>-0.005964680366087549</v>
       </c>
       <c r="D25" s="4" t="n">
         <v>-0.01300502602951525</v>
@@ -1511,13 +1511,13 @@
         <v>46211</v>
       </c>
       <c r="B29" s="5" t="n">
-        <v>97511.54763463837</v>
+        <v>97511.54763463838</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>-0.02101826087704539</v>
+        <v>-0.02101826087704517</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>-0.02488452365361637</v>
+        <v>-0.02488452365361615</v>
       </c>
       <c r="E29" s="5" t="n">
         <v>14190</v>
@@ -1526,7 +1526,7 @@
         <v>0.03546409807355522</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>-0.06034862172717159</v>
+        <v>-0.06034862172717137</v>
       </c>
     </row>
     <row r="30">
@@ -1537,7 +1537,7 @@
         <v>97085.90440793287</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>-0.004365054570770521</v>
+        <v>-0.004365054570770743</v>
       </c>
       <c r="D30" s="4" t="n">
         <v>-0.02914095592067123</v>
@@ -1603,13 +1603,13 @@
         <v>46217</v>
       </c>
       <c r="B33" s="5" t="n">
-        <v>101364.3995699691</v>
+        <v>101364.3995699692</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>0.02123082912189433</v>
+        <v>0.02123082912189456</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>0.01364399569969144</v>
+        <v>0.01364399569969166</v>
       </c>
       <c r="E33" s="5" t="n">
         <v>14080</v>
@@ -1618,7 +1618,7 @@
         <v>0.02743724460011676</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>-0.01379324890042533</v>
+        <v>-0.0137932489004251</v>
       </c>
     </row>
     <row r="34">
@@ -1629,7 +1629,7 @@
         <v>105261.7030227777</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>0.0384484441218278</v>
+        <v>0.03844844412182757</v>
       </c>
       <c r="D34" s="4" t="n">
         <v>0.05261703022777731</v>
@@ -1672,13 +1672,13 @@
         <v>46223</v>
       </c>
       <c r="B36" s="5" t="n">
-        <v>102541.7540522438</v>
+        <v>104848.7672438694</v>
       </c>
       <c r="C36" s="4" t="n">
-        <v>0.002147922400417501</v>
+        <v>0.02469452791059856</v>
       </c>
       <c r="D36" s="4" t="n">
-        <v>0.02541754052243839</v>
+        <v>0.04848767243869423</v>
       </c>
       <c r="E36" s="5" t="n">
         <v>14071</v>
@@ -1687,7 +1687,7 @@
         <v>0.02678050204319904</v>
       </c>
       <c r="G36" s="4" t="n">
-        <v>-0.001362961520760653</v>
+        <v>0.02170717039549519</v>
       </c>
     </row>
     <row r="37">
@@ -1698,19 +1698,19 @@
         <v>102169.894507684</v>
       </c>
       <c r="C37" s="4" t="n">
-        <v>-0.003626420749252568</v>
+        <v>-0.02554987346636661</v>
       </c>
       <c r="D37" s="4" t="n">
         <v>0.02169894507684034</v>
       </c>
       <c r="E37" s="5" t="n">
-        <v>14071</v>
+        <v>13974.099609375</v>
       </c>
       <c r="F37" s="4" t="n">
-        <v>0.02678050204319904</v>
+        <v>0.01970954534260061</v>
       </c>
       <c r="G37" s="4" t="n">
-        <v>-0.005081556966358702</v>
+        <v>0.001989399734239727</v>
       </c>
     </row>
     <row r="38">
@@ -1727,13 +1727,13 @@
         <v>0.03048300464520159</v>
       </c>
       <c r="E38" s="5" t="n">
-        <v>14071</v>
+        <v>14138.900390625</v>
       </c>
       <c r="F38" s="4" t="n">
-        <v>0.02678050204319904</v>
+        <v>0.03173528828261829</v>
       </c>
       <c r="G38" s="4" t="n">
-        <v>0.003702502602002555</v>
+        <v>-0.001252283637416696</v>
       </c>
     </row>
     <row r="39">
@@ -1879,22 +1879,22 @@
         <v>46234</v>
       </c>
       <c r="B45" s="5" t="n">
-        <v>100300.4181349607</v>
+        <v>100007.3767240604</v>
       </c>
       <c r="C45" s="4" t="n">
-        <v>0.002930197956385383</v>
+        <v>0</v>
       </c>
       <c r="D45" s="4" t="n">
-        <v>0.003004181349607338</v>
+        <v>7.376724060437212e-05</v>
       </c>
       <c r="E45" s="5" t="n">
-        <v>13292.900390625</v>
+        <v>13458.099609375</v>
       </c>
       <c r="F45" s="4" t="n">
-        <v>-0.02999851206764448</v>
+        <v>-0.01794369458734679</v>
       </c>
       <c r="G45" s="4" t="n">
-        <v>0.03300269341725182</v>
+        <v>0.01801746182795116</v>
       </c>
     </row>
     <row r="46">
@@ -1905,7 +1905,7 @@
         <v>98817.64242294777</v>
       </c>
       <c r="C46" s="4" t="n">
-        <v>-0.0147833452699847</v>
+        <v>-0.01189646544169809</v>
       </c>
       <c r="D46" s="4" t="n">
         <v>-0.01182357577052229</v>
@@ -2109,13 +2109,13 @@
         <v>46248</v>
       </c>
       <c r="B55" s="5" t="n">
-        <v>96176.8759284533</v>
+        <v>95127.25931854667</v>
       </c>
       <c r="C55" s="4" t="n">
-        <v>0</v>
+        <v>-0.01091339887861864</v>
       </c>
       <c r="D55" s="4" t="n">
-        <v>-0.03823124071546702</v>
+        <v>-0.04872740681453325</v>
       </c>
       <c r="E55" s="5" t="n">
         <v>14172.2998046875</v>
@@ -2124,7 +2124,7 @@
         <v>0.03417249012605805</v>
       </c>
       <c r="G55" s="4" t="n">
-        <v>-0.07240373084152507</v>
+        <v>-0.0828998969405913</v>
       </c>
     </row>
   </sheetData>

--- a/reports/latest_one_month_follow_up.xlsx
+++ b/reports/latest_one_month_follow_up.xlsx
@@ -15,7 +15,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'TAKIP_OZETI'!$A$1:$B$19</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'POZISYONLAR'!$A$1:$H$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'GUNLUK_TAKIP'!$A$1:$G$55</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'GUNLUK_TAKIP'!$A$1:$G$57</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'NOTLAR'!$A$1:$A$7</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -475,7 +475,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
@@ -546,7 +546,7 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>14172.2998046875</v>
+        <v>14128</v>
       </c>
     </row>
     <row r="9">
@@ -603,7 +603,7 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
@@ -627,7 +627,7 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-18</t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>-0.04872740681453347</v>
+        <v>-0.05777101651986594</v>
       </c>
     </row>
     <row r="17">
@@ -648,7 +648,7 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>0.03417249012605805</v>
+        <v>0.03093987157034439</v>
       </c>
     </row>
     <row r="18">
@@ -658,7 +658,7 @@
         </is>
       </c>
       <c r="B18" s="3" t="n">
-        <v>-0.08289989694059152</v>
+        <v>-0.08871088809021033</v>
       </c>
     </row>
     <row r="19">
@@ -753,19 +753,19 @@
         <v>40</v>
       </c>
       <c r="D2" s="5" t="n">
-        <v>37.38000106811523</v>
+        <v>37.93999862670898</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>-0.0654999732971191</v>
+        <v>-0.05150003433227535</v>
       </c>
       <c r="F2" s="5" t="n">
         <v>33333.33333333333</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>31150.00089009602</v>
+        <v>31616.66552225748</v>
       </c>
       <c r="H2" s="5" t="n">
-        <v>-2183.332443237305</v>
+        <v>-1716.667811075844</v>
       </c>
     </row>
     <row r="3">
@@ -781,19 +781,19 @@
         <v>45.5</v>
       </c>
       <c r="D3" s="5" t="n">
-        <v>41.40000152587891</v>
+        <v>38.63999938964844</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>-0.09010985657408999</v>
+        <v>-0.1507692441835509</v>
       </c>
       <c r="F3" s="5" t="n">
         <v>33333.33333333333</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>30329.67144753033</v>
+        <v>28307.6918605483</v>
       </c>
       <c r="H3" s="5" t="n">
-        <v>-3003.661885802998</v>
+        <v>-5025.641472785028</v>
       </c>
     </row>
     <row r="4">
@@ -809,19 +809,19 @@
         <v>371.25</v>
       </c>
       <c r="D4" s="5" t="n">
-        <v>374.75</v>
+        <v>382</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>0.00942760942760934</v>
+        <v>0.02895622895622885</v>
       </c>
       <c r="F4" s="5" t="n">
         <v>33333.33333333333</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>33647.58698092031</v>
+        <v>34298.54096520762</v>
       </c>
       <c r="H4" s="5" t="n">
-        <v>314.2536475869783</v>
+        <v>965.2076318742911</v>
       </c>
     </row>
   </sheetData>
@@ -836,7 +836,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G55"/>
+  <dimension ref="A1:G57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -1672,13 +1672,13 @@
         <v>46223</v>
       </c>
       <c r="B36" s="5" t="n">
-        <v>104848.7672438694</v>
+        <v>102321.9743913936</v>
       </c>
       <c r="C36" s="4" t="n">
-        <v>0.02469452791059856</v>
+        <v>0</v>
       </c>
       <c r="D36" s="4" t="n">
-        <v>0.04848767243869423</v>
+        <v>0.02321974391393611</v>
       </c>
       <c r="E36" s="5" t="n">
         <v>14071</v>
@@ -1687,7 +1687,7 @@
         <v>0.02678050204319904</v>
       </c>
       <c r="G36" s="4" t="n">
-        <v>0.02170717039549519</v>
+        <v>-0.003560758129262931</v>
       </c>
     </row>
     <row r="37">
@@ -1698,7 +1698,7 @@
         <v>102169.894507684</v>
       </c>
       <c r="C37" s="4" t="n">
-        <v>-0.02554987346636661</v>
+        <v>-0.001486287619195559</v>
       </c>
       <c r="D37" s="4" t="n">
         <v>0.02169894507684034</v>
@@ -2127,8 +2127,54 @@
         <v>-0.0828998969405913</v>
       </c>
     </row>
+    <row r="56">
+      <c r="A56" s="6" t="n">
+        <v>46251</v>
+      </c>
+      <c r="B56" s="5" t="n">
+        <v>94222.89834801342</v>
+      </c>
+      <c r="C56" s="4" t="n">
+        <v>-0.009506854050161162</v>
+      </c>
+      <c r="D56" s="4" t="n">
+        <v>-0.05777101651986583</v>
+      </c>
+      <c r="E56" s="5" t="n">
+        <v>14132.099609375</v>
+      </c>
+      <c r="F56" s="4" t="n">
+        <v>0.03123902578626669</v>
+      </c>
+      <c r="G56" s="4" t="n">
+        <v>-0.08901004230613252</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="6" t="n">
+        <v>46252</v>
+      </c>
+      <c r="B57" s="5" t="n">
+        <v>94222.89834801342</v>
+      </c>
+      <c r="C57" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D57" s="4" t="n">
+        <v>-0.05777101651986583</v>
+      </c>
+      <c r="E57" s="5" t="n">
+        <v>14128</v>
+      </c>
+      <c r="F57" s="4" t="n">
+        <v>0.03093987157034439</v>
+      </c>
+      <c r="G57" s="4" t="n">
+        <v>-0.08871088809021022</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G55"/>
+  <autoFilter ref="A1:G57"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/reports/latest_one_month_follow_up.xlsx
+++ b/reports/latest_one_month_follow_up.xlsx
@@ -475,7 +475,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
     </row>
@@ -546,7 +546,7 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>14128</v>
+        <v>14459</v>
       </c>
     </row>
     <row r="9">
@@ -603,7 +603,7 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
     </row>
@@ -627,7 +627,7 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>-0.05777101651986594</v>
+        <v>-0.04292957189676194</v>
       </c>
     </row>
     <row r="17">
@@ -648,7 +648,7 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>0.03093987157034439</v>
+        <v>0.05509340338587276</v>
       </c>
     </row>
     <row r="18">
@@ -658,7 +658,7 @@
         </is>
       </c>
       <c r="B18" s="3" t="n">
-        <v>-0.08871088809021033</v>
+        <v>-0.09802297528263471</v>
       </c>
     </row>
     <row r="19">
@@ -753,19 +753,19 @@
         <v>40</v>
       </c>
       <c r="D2" s="5" t="n">
-        <v>37.93999862670898</v>
+        <v>37.70000076293945</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>-0.05150003433227535</v>
+        <v>-0.05749998092651365</v>
       </c>
       <c r="F2" s="5" t="n">
         <v>33333.33333333333</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>31616.66552225748</v>
+        <v>31416.66730244954</v>
       </c>
       <c r="H2" s="5" t="n">
-        <v>-1716.667811075844</v>
+        <v>-1916.666030883789</v>
       </c>
     </row>
     <row r="3">
@@ -781,19 +781,19 @@
         <v>45.5</v>
       </c>
       <c r="D3" s="5" t="n">
-        <v>38.63999938964844</v>
+        <v>38.11999893188477</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>-0.1507692441835509</v>
+        <v>-0.1621978256728623</v>
       </c>
       <c r="F3" s="5" t="n">
         <v>33333.33333333333</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>28307.6918605483</v>
+        <v>27926.73914423792</v>
       </c>
       <c r="H3" s="5" t="n">
-        <v>-5025.641472785028</v>
+        <v>-5406.594189095409</v>
       </c>
     </row>
     <row r="4">
@@ -809,19 +809,19 @@
         <v>371.25</v>
       </c>
       <c r="D4" s="5" t="n">
-        <v>382</v>
+        <v>405</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>0.02895622895622885</v>
+        <v>0.09090909090909083</v>
       </c>
       <c r="F4" s="5" t="n">
         <v>33333.33333333333</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>34298.54096520762</v>
+        <v>36363.63636363635</v>
       </c>
       <c r="H4" s="5" t="n">
-        <v>965.2076318742911</v>
+        <v>3030.303030303025</v>
       </c>
     </row>
   </sheetData>
@@ -1704,13 +1704,13 @@
         <v>0.02169894507684034</v>
       </c>
       <c r="E37" s="5" t="n">
-        <v>13974.099609375</v>
+        <v>14071</v>
       </c>
       <c r="F37" s="4" t="n">
-        <v>0.01970954534260061</v>
+        <v>0.02678050204319904</v>
       </c>
       <c r="G37" s="4" t="n">
-        <v>0.001989399734239727</v>
+        <v>-0.005081556966358702</v>
       </c>
     </row>
     <row r="38">
@@ -1727,13 +1727,13 @@
         <v>0.03048300464520159</v>
       </c>
       <c r="E38" s="5" t="n">
-        <v>14138.900390625</v>
+        <v>14071</v>
       </c>
       <c r="F38" s="4" t="n">
-        <v>0.03173528828261829</v>
+        <v>0.02678050204319904</v>
       </c>
       <c r="G38" s="4" t="n">
-        <v>-0.001252283637416696</v>
+        <v>0.003702502602002555</v>
       </c>
     </row>
     <row r="39">
@@ -1876,301 +1876,301 @@
     </row>
     <row r="45">
       <c r="A45" s="6" t="n">
-        <v>46234</v>
+        <v>46237</v>
       </c>
       <c r="B45" s="5" t="n">
-        <v>100007.3767240604</v>
+        <v>98817.64242294777</v>
       </c>
       <c r="C45" s="4" t="n">
-        <v>0</v>
+        <v>-0.01189646544169809</v>
       </c>
       <c r="D45" s="4" t="n">
-        <v>7.376724060437212e-05</v>
+        <v>-0.01182357577052229</v>
       </c>
       <c r="E45" s="5" t="n">
-        <v>13458.099609375</v>
+        <v>13410.5</v>
       </c>
       <c r="F45" s="4" t="n">
-        <v>-0.01794369458734679</v>
+        <v>-0.02141710449503798</v>
       </c>
       <c r="G45" s="4" t="n">
-        <v>0.01801746182795116</v>
+        <v>0.009593528724515688</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="6" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="B46" s="5" t="n">
-        <v>98817.64242294777</v>
+        <v>100510.1501194647</v>
       </c>
       <c r="C46" s="4" t="n">
-        <v>-0.01189646544169809</v>
+        <v>0.01712758627930899</v>
       </c>
       <c r="D46" s="4" t="n">
-        <v>-0.01182357577052229</v>
+        <v>0.00510150119464714</v>
       </c>
       <c r="E46" s="5" t="n">
-        <v>13410.5</v>
+        <v>13687.900390625</v>
       </c>
       <c r="F46" s="4" t="n">
-        <v>-0.02141710449503798</v>
+        <v>-0.001174810958479267</v>
       </c>
       <c r="G46" s="4" t="n">
-        <v>0.009593528724515688</v>
+        <v>0.006276312153126407</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="6" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="B47" s="5" t="n">
-        <v>100510.1501194647</v>
+        <v>100395.8946916857</v>
       </c>
       <c r="C47" s="4" t="n">
-        <v>0.01712758627930899</v>
+        <v>-0.001136755120186628</v>
       </c>
       <c r="D47" s="4" t="n">
-        <v>0.00510150119464714</v>
+        <v>0.003958946916856831</v>
       </c>
       <c r="E47" s="5" t="n">
-        <v>13687.900390625</v>
+        <v>13703.099609375</v>
       </c>
       <c r="F47" s="4" t="n">
-        <v>-0.001174810958479267</v>
+        <v>-6.570276014306042e-05</v>
       </c>
       <c r="G47" s="4" t="n">
-        <v>0.006276312153126407</v>
+        <v>0.004024649676999892</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="6" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="B48" s="5" t="n">
-        <v>100395.8946916857</v>
+        <v>99635.64159588418</v>
       </c>
       <c r="C48" s="4" t="n">
-        <v>-0.001136755120186628</v>
+        <v>-0.007572551628094226</v>
       </c>
       <c r="D48" s="4" t="n">
-        <v>0.003958946916856831</v>
+        <v>-0.003643584041158165</v>
       </c>
       <c r="E48" s="5" t="n">
-        <v>13703.099609375</v>
+        <v>13798.7998046875</v>
       </c>
       <c r="F48" s="4" t="n">
-        <v>-6.570276014306042e-05</v>
+        <v>0.006917674013974029</v>
       </c>
       <c r="G48" s="4" t="n">
-        <v>0.004024649676999892</v>
+        <v>-0.01056125805513219</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="6" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="B49" s="5" t="n">
-        <v>99635.64159588418</v>
+        <v>97154.28928705474</v>
       </c>
       <c r="C49" s="4" t="n">
-        <v>-0.007572551628094226</v>
+        <v>-0.02490426386667588</v>
       </c>
       <c r="D49" s="4" t="n">
-        <v>-0.003643584041158165</v>
+        <v>-0.0284571071294526</v>
       </c>
       <c r="E49" s="5" t="n">
-        <v>13798.7998046875</v>
+        <v>13779.400390625</v>
       </c>
       <c r="F49" s="4" t="n">
-        <v>0.006917674013974029</v>
+        <v>0.005502071703517242</v>
       </c>
       <c r="G49" s="4" t="n">
-        <v>-0.01056125805513219</v>
+        <v>-0.03395917883296984</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="6" t="n">
-        <v>46241</v>
+        <v>46244</v>
       </c>
       <c r="B50" s="5" t="n">
-        <v>97154.28928705474</v>
+        <v>95622.17344357757</v>
       </c>
       <c r="C50" s="4" t="n">
-        <v>-0.02490426386667588</v>
+        <v>-0.01576992487640283</v>
       </c>
       <c r="D50" s="4" t="n">
-        <v>-0.0284571071294526</v>
+        <v>-0.04377826556422426</v>
       </c>
       <c r="E50" s="5" t="n">
-        <v>13779.400390625</v>
+        <v>13811.599609375</v>
       </c>
       <c r="F50" s="4" t="n">
-        <v>0.005502071703517242</v>
+        <v>0.007851693620475775</v>
       </c>
       <c r="G50" s="4" t="n">
-        <v>-0.03395917883296984</v>
+        <v>-0.05162995918470004</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="6" t="n">
-        <v>46244</v>
+        <v>46245</v>
       </c>
       <c r="B51" s="5" t="n">
-        <v>95622.17344357757</v>
+        <v>94508.13507854677</v>
       </c>
       <c r="C51" s="4" t="n">
-        <v>-0.01576992487640283</v>
+        <v>-0.01165041877748318</v>
       </c>
       <c r="D51" s="4" t="n">
-        <v>-0.04377826556422426</v>
+        <v>-0.05491864921453238</v>
       </c>
       <c r="E51" s="5" t="n">
-        <v>13811.599609375</v>
+        <v>13704.5</v>
       </c>
       <c r="F51" s="4" t="n">
-        <v>0.007851693620475775</v>
+        <v>3.648569760650311e-05</v>
       </c>
       <c r="G51" s="4" t="n">
-        <v>-0.05162995918470004</v>
+        <v>-0.05495513491213888</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="6" t="n">
-        <v>46245</v>
+        <v>46246</v>
       </c>
       <c r="B52" s="5" t="n">
-        <v>94508.13507854677</v>
+        <v>95468.77340237095</v>
       </c>
       <c r="C52" s="4" t="n">
-        <v>-0.01165041877748318</v>
+        <v>0.01016460988279788</v>
       </c>
       <c r="D52" s="4" t="n">
-        <v>-0.05491864921453238</v>
+        <v>-0.04531226597629046</v>
       </c>
       <c r="E52" s="5" t="n">
-        <v>13704.5</v>
+        <v>14110.099609375</v>
       </c>
       <c r="F52" s="4" t="n">
-        <v>3.648569760650311e-05</v>
+        <v>0.029633655091579</v>
       </c>
       <c r="G52" s="4" t="n">
-        <v>-0.05495513491213888</v>
+        <v>-0.07494592106786946</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="6" t="n">
-        <v>46246</v>
+        <v>46247</v>
       </c>
       <c r="B53" s="5" t="n">
-        <v>95468.77340237095</v>
+        <v>96176.8759284533</v>
       </c>
       <c r="C53" s="4" t="n">
-        <v>0.01016460988279788</v>
+        <v>0.007417111384661057</v>
       </c>
       <c r="D53" s="4" t="n">
-        <v>-0.04531226597629046</v>
+        <v>-0.03823124071546702</v>
       </c>
       <c r="E53" s="5" t="n">
-        <v>14110.099609375</v>
+        <v>14132.2001953125</v>
       </c>
       <c r="F53" s="4" t="n">
-        <v>0.029633655091579</v>
+        <v>0.03124636568246508</v>
       </c>
       <c r="G53" s="4" t="n">
-        <v>-0.07494592106786946</v>
+        <v>-0.0694776063979321</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="6" t="n">
-        <v>46247</v>
+        <v>46248</v>
       </c>
       <c r="B54" s="5" t="n">
-        <v>96176.8759284533</v>
+        <v>95127.25931854667</v>
       </c>
       <c r="C54" s="4" t="n">
-        <v>0.007417111384661057</v>
+        <v>-0.01091339887861864</v>
       </c>
       <c r="D54" s="4" t="n">
-        <v>-0.03823124071546702</v>
+        <v>-0.04872740681453325</v>
       </c>
       <c r="E54" s="5" t="n">
-        <v>14132.2001953125</v>
+        <v>14172.2998046875</v>
       </c>
       <c r="F54" s="4" t="n">
-        <v>0.03124636568246508</v>
+        <v>0.03417249012605805</v>
       </c>
       <c r="G54" s="4" t="n">
-        <v>-0.0694776063979321</v>
+        <v>-0.0828998969405913</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="6" t="n">
-        <v>46248</v>
+        <v>46251</v>
       </c>
       <c r="B55" s="5" t="n">
-        <v>95127.25931854667</v>
+        <v>94222.89834801342</v>
       </c>
       <c r="C55" s="4" t="n">
-        <v>-0.01091339887861864</v>
+        <v>-0.009506854050161162</v>
       </c>
       <c r="D55" s="4" t="n">
-        <v>-0.04872740681453325</v>
+        <v>-0.05777101651986583</v>
       </c>
       <c r="E55" s="5" t="n">
-        <v>14172.2998046875</v>
+        <v>14132.099609375</v>
       </c>
       <c r="F55" s="4" t="n">
-        <v>0.03417249012605805</v>
+        <v>0.03123902578626669</v>
       </c>
       <c r="G55" s="4" t="n">
-        <v>-0.0828998969405913</v>
+        <v>-0.08901004230613252</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="6" t="n">
-        <v>46251</v>
+        <v>46252</v>
       </c>
       <c r="B56" s="5" t="n">
-        <v>94222.89834801342</v>
+        <v>95707.04281032382</v>
       </c>
       <c r="C56" s="4" t="n">
-        <v>-0.009506854050161162</v>
+        <v>0.01575142017844433</v>
       </c>
       <c r="D56" s="4" t="n">
-        <v>-0.05777101651986583</v>
+        <v>-0.04292957189676172</v>
       </c>
       <c r="E56" s="5" t="n">
-        <v>14132.099609375</v>
+        <v>14128</v>
       </c>
       <c r="F56" s="4" t="n">
-        <v>0.03123902578626669</v>
+        <v>0.03093987157034439</v>
       </c>
       <c r="G56" s="4" t="n">
-        <v>-0.08901004230613252</v>
+        <v>-0.07386944346710611</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="6" t="n">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="B57" s="5" t="n">
-        <v>94222.89834801342</v>
+        <v>95707.04281032382</v>
       </c>
       <c r="C57" s="4" t="n">
         <v>0</v>
       </c>
       <c r="D57" s="4" t="n">
-        <v>-0.05777101651986583</v>
+        <v>-0.04292957189676172</v>
       </c>
       <c r="E57" s="5" t="n">
-        <v>14128</v>
+        <v>14459</v>
       </c>
       <c r="F57" s="4" t="n">
-        <v>0.03093987157034439</v>
+        <v>0.05509340338587276</v>
       </c>
       <c r="G57" s="4" t="n">
-        <v>-0.08871088809021022</v>
+        <v>-0.09802297528263448</v>
       </c>
     </row>
   </sheetData>

--- a/reports/latest_one_month_follow_up.xlsx
+++ b/reports/latest_one_month_follow_up.xlsx
@@ -15,7 +15,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'TAKIP_OZETI'!$A$1:$B$19</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'POZISYONLAR'!$A$1:$H$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'GUNLUK_TAKIP'!$A$1:$G$57</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'GUNLUK_TAKIP'!$A$1:$G$59</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'NOTLAR'!$A$1:$A$7</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -475,7 +475,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
     </row>
@@ -546,7 +546,7 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>14459</v>
+        <v>14396.5</v>
       </c>
     </row>
     <row r="9">
@@ -603,7 +603,7 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
     </row>
@@ -627,7 +627,7 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>-0.04292957189676194</v>
+        <v>-0.02682938103206489</v>
       </c>
     </row>
     <row r="17">
@@ -648,7 +648,7 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>0.05509340338587276</v>
+        <v>0.05053269118505543</v>
       </c>
     </row>
     <row r="18">
@@ -658,7 +658,7 @@
         </is>
       </c>
       <c r="B18" s="3" t="n">
-        <v>-0.09802297528263471</v>
+        <v>-0.07736207221712033</v>
       </c>
     </row>
     <row r="19">
@@ -753,19 +753,19 @@
         <v>40</v>
       </c>
       <c r="D2" s="5" t="n">
-        <v>37.70000076293945</v>
+        <v>37.7599983215332</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>-0.05749998092651365</v>
+        <v>-0.05600004196166997</v>
       </c>
       <c r="F2" s="5" t="n">
         <v>33333.33333333333</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>31416.66730244954</v>
+        <v>31466.66526794433</v>
       </c>
       <c r="H2" s="5" t="n">
-        <v>-1916.666030883789</v>
+        <v>-1866.668065389</v>
       </c>
     </row>
     <row r="3">
@@ -781,19 +781,19 @@
         <v>45.5</v>
       </c>
       <c r="D3" s="5" t="n">
-        <v>38.11999893188477</v>
+        <v>38.84000015258789</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>-0.1621978256728623</v>
+        <v>-0.1463736230200463</v>
       </c>
       <c r="F3" s="5" t="n">
         <v>33333.33333333333</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>27926.73914423792</v>
+        <v>28454.21256599845</v>
       </c>
       <c r="H3" s="5" t="n">
-        <v>-5406.594189095409</v>
+        <v>-4879.120767334876</v>
       </c>
     </row>
     <row r="4">
@@ -809,19 +809,19 @@
         <v>371.25</v>
       </c>
       <c r="D4" s="5" t="n">
-        <v>405</v>
+        <v>416.5</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>0.09090909090909083</v>
+        <v>0.1218855218855219</v>
       </c>
       <c r="F4" s="5" t="n">
         <v>33333.33333333333</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>36363.63636363635</v>
+        <v>37396.18406285073</v>
       </c>
       <c r="H4" s="5" t="n">
-        <v>3030.303030303025</v>
+        <v>4062.850729517399</v>
       </c>
     </row>
   </sheetData>
@@ -836,7 +836,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G57"/>
+  <dimension ref="A1:G59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -1672,13 +1672,13 @@
         <v>46223</v>
       </c>
       <c r="B36" s="5" t="n">
-        <v>102321.9743913936</v>
+        <v>104848.7672438694</v>
       </c>
       <c r="C36" s="4" t="n">
-        <v>0</v>
+        <v>0.02469452791059856</v>
       </c>
       <c r="D36" s="4" t="n">
-        <v>0.02321974391393611</v>
+        <v>0.04848767243869423</v>
       </c>
       <c r="E36" s="5" t="n">
         <v>14071</v>
@@ -1687,7 +1687,7 @@
         <v>0.02678050204319904</v>
       </c>
       <c r="G36" s="4" t="n">
-        <v>-0.003560758129262931</v>
+        <v>0.02170717039549519</v>
       </c>
     </row>
     <row r="37">
@@ -1698,19 +1698,19 @@
         <v>102169.894507684</v>
       </c>
       <c r="C37" s="4" t="n">
-        <v>-0.001486287619195559</v>
+        <v>-0.02554987346636661</v>
       </c>
       <c r="D37" s="4" t="n">
         <v>0.02169894507684034</v>
       </c>
       <c r="E37" s="5" t="n">
-        <v>14071</v>
+        <v>13974.099609375</v>
       </c>
       <c r="F37" s="4" t="n">
-        <v>0.02678050204319904</v>
+        <v>0.01970954534260061</v>
       </c>
       <c r="G37" s="4" t="n">
-        <v>-0.005081556966358702</v>
+        <v>0.001989399734239727</v>
       </c>
     </row>
     <row r="38">
@@ -1727,13 +1727,13 @@
         <v>0.03048300464520159</v>
       </c>
       <c r="E38" s="5" t="n">
-        <v>14071</v>
+        <v>14138.900390625</v>
       </c>
       <c r="F38" s="4" t="n">
-        <v>0.02678050204319904</v>
+        <v>0.03173528828261829</v>
       </c>
       <c r="G38" s="4" t="n">
-        <v>0.003702502602002555</v>
+        <v>-0.001252283637416696</v>
       </c>
     </row>
     <row r="39">
@@ -1876,305 +1876,351 @@
     </row>
     <row r="45">
       <c r="A45" s="6" t="n">
-        <v>46237</v>
+        <v>46234</v>
       </c>
       <c r="B45" s="5" t="n">
-        <v>98817.64242294777</v>
+        <v>100007.3767240604</v>
       </c>
       <c r="C45" s="4" t="n">
-        <v>-0.01189646544169809</v>
+        <v>0</v>
       </c>
       <c r="D45" s="4" t="n">
-        <v>-0.01182357577052229</v>
+        <v>7.376724060437212e-05</v>
       </c>
       <c r="E45" s="5" t="n">
-        <v>13410.5</v>
+        <v>13458.099609375</v>
       </c>
       <c r="F45" s="4" t="n">
-        <v>-0.02141710449503798</v>
+        <v>-0.01794369458734679</v>
       </c>
       <c r="G45" s="4" t="n">
-        <v>0.009593528724515688</v>
+        <v>0.01801746182795116</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="6" t="n">
-        <v>46238</v>
+        <v>46237</v>
       </c>
       <c r="B46" s="5" t="n">
-        <v>100510.1501194647</v>
+        <v>98817.64242294777</v>
       </c>
       <c r="C46" s="4" t="n">
-        <v>0.01712758627930899</v>
+        <v>-0.01189646544169809</v>
       </c>
       <c r="D46" s="4" t="n">
-        <v>0.00510150119464714</v>
+        <v>-0.01182357577052229</v>
       </c>
       <c r="E46" s="5" t="n">
-        <v>13687.900390625</v>
+        <v>13410.5</v>
       </c>
       <c r="F46" s="4" t="n">
-        <v>-0.001174810958479267</v>
+        <v>-0.02141710449503798</v>
       </c>
       <c r="G46" s="4" t="n">
-        <v>0.006276312153126407</v>
+        <v>0.009593528724515688</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="6" t="n">
-        <v>46239</v>
+        <v>46238</v>
       </c>
       <c r="B47" s="5" t="n">
-        <v>100395.8946916857</v>
+        <v>100510.1501194647</v>
       </c>
       <c r="C47" s="4" t="n">
-        <v>-0.001136755120186628</v>
+        <v>0.01712758627930899</v>
       </c>
       <c r="D47" s="4" t="n">
-        <v>0.003958946916856831</v>
+        <v>0.00510150119464714</v>
       </c>
       <c r="E47" s="5" t="n">
-        <v>13703.099609375</v>
+        <v>13687.900390625</v>
       </c>
       <c r="F47" s="4" t="n">
-        <v>-6.570276014306042e-05</v>
+        <v>-0.001174810958479267</v>
       </c>
       <c r="G47" s="4" t="n">
-        <v>0.004024649676999892</v>
+        <v>0.006276312153126407</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="6" t="n">
-        <v>46240</v>
+        <v>46239</v>
       </c>
       <c r="B48" s="5" t="n">
-        <v>99635.64159588418</v>
+        <v>100395.8946916857</v>
       </c>
       <c r="C48" s="4" t="n">
-        <v>-0.007572551628094226</v>
+        <v>-0.001136755120186628</v>
       </c>
       <c r="D48" s="4" t="n">
-        <v>-0.003643584041158165</v>
+        <v>0.003958946916856831</v>
       </c>
       <c r="E48" s="5" t="n">
-        <v>13798.7998046875</v>
+        <v>13703.099609375</v>
       </c>
       <c r="F48" s="4" t="n">
-        <v>0.006917674013974029</v>
+        <v>-6.570276014306042e-05</v>
       </c>
       <c r="G48" s="4" t="n">
-        <v>-0.01056125805513219</v>
+        <v>0.004024649676999892</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="6" t="n">
-        <v>46241</v>
+        <v>46240</v>
       </c>
       <c r="B49" s="5" t="n">
-        <v>97154.28928705474</v>
+        <v>99635.64159588418</v>
       </c>
       <c r="C49" s="4" t="n">
-        <v>-0.02490426386667588</v>
+        <v>-0.007572551628094226</v>
       </c>
       <c r="D49" s="4" t="n">
-        <v>-0.0284571071294526</v>
+        <v>-0.003643584041158165</v>
       </c>
       <c r="E49" s="5" t="n">
-        <v>13779.400390625</v>
+        <v>13798.7998046875</v>
       </c>
       <c r="F49" s="4" t="n">
-        <v>0.005502071703517242</v>
+        <v>0.006917674013974029</v>
       </c>
       <c r="G49" s="4" t="n">
-        <v>-0.03395917883296984</v>
+        <v>-0.01056125805513219</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="6" t="n">
-        <v>46244</v>
+        <v>46241</v>
       </c>
       <c r="B50" s="5" t="n">
-        <v>95622.17344357757</v>
+        <v>97154.28928705474</v>
       </c>
       <c r="C50" s="4" t="n">
-        <v>-0.01576992487640283</v>
+        <v>-0.02490426386667588</v>
       </c>
       <c r="D50" s="4" t="n">
-        <v>-0.04377826556422426</v>
+        <v>-0.0284571071294526</v>
       </c>
       <c r="E50" s="5" t="n">
-        <v>13811.599609375</v>
+        <v>13779.400390625</v>
       </c>
       <c r="F50" s="4" t="n">
-        <v>0.007851693620475775</v>
+        <v>0.005502071703517242</v>
       </c>
       <c r="G50" s="4" t="n">
-        <v>-0.05162995918470004</v>
+        <v>-0.03395917883296984</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="6" t="n">
-        <v>46245</v>
+        <v>46244</v>
       </c>
       <c r="B51" s="5" t="n">
-        <v>94508.13507854677</v>
+        <v>95622.17344357757</v>
       </c>
       <c r="C51" s="4" t="n">
-        <v>-0.01165041877748318</v>
+        <v>-0.01576992487640283</v>
       </c>
       <c r="D51" s="4" t="n">
-        <v>-0.05491864921453238</v>
+        <v>-0.04377826556422426</v>
       </c>
       <c r="E51" s="5" t="n">
-        <v>13704.5</v>
+        <v>13811.599609375</v>
       </c>
       <c r="F51" s="4" t="n">
-        <v>3.648569760650311e-05</v>
+        <v>0.007851693620475775</v>
       </c>
       <c r="G51" s="4" t="n">
-        <v>-0.05495513491213888</v>
+        <v>-0.05162995918470004</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="6" t="n">
-        <v>46246</v>
+        <v>46245</v>
       </c>
       <c r="B52" s="5" t="n">
-        <v>95468.77340237095</v>
+        <v>94508.13507854677</v>
       </c>
       <c r="C52" s="4" t="n">
-        <v>0.01016460988279788</v>
+        <v>-0.01165041877748318</v>
       </c>
       <c r="D52" s="4" t="n">
-        <v>-0.04531226597629046</v>
+        <v>-0.05491864921453238</v>
       </c>
       <c r="E52" s="5" t="n">
-        <v>14110.099609375</v>
+        <v>13704.5</v>
       </c>
       <c r="F52" s="4" t="n">
-        <v>0.029633655091579</v>
+        <v>3.648569760650311e-05</v>
       </c>
       <c r="G52" s="4" t="n">
-        <v>-0.07494592106786946</v>
+        <v>-0.05495513491213888</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="6" t="n">
-        <v>46247</v>
+        <v>46246</v>
       </c>
       <c r="B53" s="5" t="n">
-        <v>96176.8759284533</v>
+        <v>95468.77340237095</v>
       </c>
       <c r="C53" s="4" t="n">
-        <v>0.007417111384661057</v>
+        <v>0.01016460988279788</v>
       </c>
       <c r="D53" s="4" t="n">
-        <v>-0.03823124071546702</v>
+        <v>-0.04531226597629046</v>
       </c>
       <c r="E53" s="5" t="n">
-        <v>14132.2001953125</v>
+        <v>14110.099609375</v>
       </c>
       <c r="F53" s="4" t="n">
-        <v>0.03124636568246508</v>
+        <v>0.029633655091579</v>
       </c>
       <c r="G53" s="4" t="n">
-        <v>-0.0694776063979321</v>
+        <v>-0.07494592106786946</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="6" t="n">
-        <v>46248</v>
+        <v>46247</v>
       </c>
       <c r="B54" s="5" t="n">
-        <v>95127.25931854667</v>
+        <v>96176.8759284533</v>
       </c>
       <c r="C54" s="4" t="n">
-        <v>-0.01091339887861864</v>
+        <v>0.007417111384661057</v>
       </c>
       <c r="D54" s="4" t="n">
-        <v>-0.04872740681453325</v>
+        <v>-0.03823124071546702</v>
       </c>
       <c r="E54" s="5" t="n">
-        <v>14172.2998046875</v>
+        <v>14132.2001953125</v>
       </c>
       <c r="F54" s="4" t="n">
-        <v>0.03417249012605805</v>
+        <v>0.03124636568246508</v>
       </c>
       <c r="G54" s="4" t="n">
-        <v>-0.0828998969405913</v>
+        <v>-0.0694776063979321</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="6" t="n">
-        <v>46251</v>
+        <v>46248</v>
       </c>
       <c r="B55" s="5" t="n">
-        <v>94222.89834801342</v>
+        <v>95127.25931854667</v>
       </c>
       <c r="C55" s="4" t="n">
-        <v>-0.009506854050161162</v>
+        <v>-0.01091339887861864</v>
       </c>
       <c r="D55" s="4" t="n">
-        <v>-0.05777101651986583</v>
+        <v>-0.04872740681453325</v>
       </c>
       <c r="E55" s="5" t="n">
-        <v>14132.099609375</v>
+        <v>14172.2998046875</v>
       </c>
       <c r="F55" s="4" t="n">
-        <v>0.03123902578626669</v>
+        <v>0.03417249012605805</v>
       </c>
       <c r="G55" s="4" t="n">
-        <v>-0.08901004230613252</v>
+        <v>-0.0828998969405913</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="6" t="n">
-        <v>46252</v>
+        <v>46251</v>
       </c>
       <c r="B56" s="5" t="n">
-        <v>95707.04281032382</v>
+        <v>94222.89834801342</v>
       </c>
       <c r="C56" s="4" t="n">
-        <v>0.01575142017844433</v>
+        <v>-0.009506854050161162</v>
       </c>
       <c r="D56" s="4" t="n">
-        <v>-0.04292957189676172</v>
+        <v>-0.05777101651986583</v>
       </c>
       <c r="E56" s="5" t="n">
-        <v>14128</v>
+        <v>14132.099609375</v>
       </c>
       <c r="F56" s="4" t="n">
-        <v>0.03093987157034439</v>
+        <v>0.03123902578626669</v>
       </c>
       <c r="G56" s="4" t="n">
-        <v>-0.07386944346710611</v>
+        <v>-0.08901004230613252</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="6" t="n">
-        <v>46253</v>
+        <v>46252</v>
       </c>
       <c r="B57" s="5" t="n">
         <v>95707.04281032382</v>
       </c>
       <c r="C57" s="4" t="n">
-        <v>0</v>
+        <v>0.01575142017844433</v>
       </c>
       <c r="D57" s="4" t="n">
         <v>-0.04292957189676172</v>
       </c>
       <c r="E57" s="5" t="n">
+        <v>14128</v>
+      </c>
+      <c r="F57" s="4" t="n">
+        <v>0.03093987157034439</v>
+      </c>
+      <c r="G57" s="4" t="n">
+        <v>-0.07386944346710611</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="6" t="n">
+        <v>46253</v>
+      </c>
+      <c r="B58" s="5" t="n">
+        <v>97317.06189679352</v>
+      </c>
+      <c r="C58" s="4" t="n">
+        <v>0.01682236791769331</v>
+      </c>
+      <c r="D58" s="4" t="n">
+        <v>-0.02682938103206478</v>
+      </c>
+      <c r="E58" s="5" t="n">
         <v>14459</v>
       </c>
-      <c r="F57" s="4" t="n">
+      <c r="F58" s="4" t="n">
         <v>0.05509340338587276</v>
       </c>
-      <c r="G57" s="4" t="n">
-        <v>-0.09802297528263448</v>
+      <c r="G58" s="4" t="n">
+        <v>-0.08192278441793754</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="6" t="n">
+        <v>46254</v>
+      </c>
+      <c r="B59" s="5" t="n">
+        <v>97317.06189679352</v>
+      </c>
+      <c r="C59" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D59" s="4" t="n">
+        <v>-0.02682938103206478</v>
+      </c>
+      <c r="E59" s="5" t="n">
+        <v>14396.5</v>
+      </c>
+      <c r="F59" s="4" t="n">
+        <v>0.05053269118505543</v>
+      </c>
+      <c r="G59" s="4" t="n">
+        <v>-0.07736207221712021</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G57"/>
+  <autoFilter ref="A1:G59"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/reports/latest_one_month_follow_up.xlsx
+++ b/reports/latest_one_month_follow_up.xlsx
@@ -15,7 +15,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'TAKIP_OZETI'!$A$1:$B$19</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'POZISYONLAR'!$A$1:$H$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'GUNLUK_TAKIP'!$A$1:$G$59</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'GUNLUK_TAKIP'!$A$1:$G$60</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'NOTLAR'!$A$1:$A$7</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -475,7 +475,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
     </row>
@@ -546,7 +546,7 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>14396.5</v>
+        <v>14514.7998046875</v>
       </c>
     </row>
     <row r="9">
@@ -603,7 +603,7 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
     </row>
@@ -627,7 +627,7 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>-0.02682938103206489</v>
+        <v>-0.0204361506517956</v>
       </c>
     </row>
     <row r="17">
@@ -648,7 +648,7 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>0.05053269118505543</v>
+        <v>0.05916519298653689</v>
       </c>
     </row>
     <row r="18">
@@ -658,7 +658,7 @@
         </is>
       </c>
       <c r="B18" s="3" t="n">
-        <v>-0.07736207221712033</v>
+        <v>-0.07960134363833249</v>
       </c>
     </row>
     <row r="19">
@@ -753,19 +753,19 @@
         <v>40</v>
       </c>
       <c r="D2" s="5" t="n">
-        <v>37.7599983215332</v>
+        <v>38.09999847412109</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>-0.05600004196166997</v>
+        <v>-0.04750003814697268</v>
       </c>
       <c r="F2" s="5" t="n">
         <v>33333.33333333333</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>31466.66526794433</v>
+        <v>31749.99872843424</v>
       </c>
       <c r="H2" s="5" t="n">
-        <v>-1866.668065389</v>
+        <v>-1583.33460489909</v>
       </c>
     </row>
     <row r="3">
@@ -781,19 +781,19 @@
         <v>45.5</v>
       </c>
       <c r="D3" s="5" t="n">
-        <v>38.84000015258789</v>
+        <v>40</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>-0.1463736230200463</v>
+        <v>-0.1208791208791209</v>
       </c>
       <c r="F3" s="5" t="n">
         <v>33333.33333333333</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>28454.21256599845</v>
+        <v>29304.0293040293</v>
       </c>
       <c r="H3" s="5" t="n">
-        <v>-4879.120767334876</v>
+        <v>-4029.304029304029</v>
       </c>
     </row>
     <row r="4">
@@ -809,19 +809,19 @@
         <v>371.25</v>
       </c>
       <c r="D4" s="5" t="n">
-        <v>416.5</v>
+        <v>411</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>0.1218855218855219</v>
+        <v>0.1070707070707071</v>
       </c>
       <c r="F4" s="5" t="n">
         <v>33333.33333333333</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>37396.18406285073</v>
+        <v>36902.3569023569</v>
       </c>
       <c r="H4" s="5" t="n">
-        <v>4062.850729517399</v>
+        <v>3569.023569023571</v>
       </c>
     </row>
   </sheetData>
@@ -836,7 +836,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G59"/>
+  <dimension ref="A1:G60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -1879,13 +1879,13 @@
         <v>46234</v>
       </c>
       <c r="B45" s="5" t="n">
-        <v>100007.3767240604</v>
+        <v>101068.0382772884</v>
       </c>
       <c r="C45" s="4" t="n">
-        <v>0</v>
+        <v>0.01060583316923247</v>
       </c>
       <c r="D45" s="4" t="n">
-        <v>7.376724060437212e-05</v>
+        <v>0.01068038277288408</v>
       </c>
       <c r="E45" s="5" t="n">
         <v>13458.099609375</v>
@@ -1894,7 +1894,7 @@
         <v>-0.01794369458734679</v>
       </c>
       <c r="G45" s="4" t="n">
-        <v>0.01801746182795116</v>
+        <v>0.02862407736023087</v>
       </c>
     </row>
     <row r="46">
@@ -1905,7 +1905,7 @@
         <v>98817.64242294777</v>
       </c>
       <c r="C46" s="4" t="n">
-        <v>-0.01189646544169809</v>
+        <v>-0.0222661475645396</v>
       </c>
       <c r="D46" s="4" t="n">
         <v>-0.01182357577052229</v>
@@ -2201,13 +2201,13 @@
         <v>46254</v>
       </c>
       <c r="B59" s="5" t="n">
-        <v>97317.06189679352</v>
+        <v>97956.38493482044</v>
       </c>
       <c r="C59" s="4" t="n">
-        <v>0</v>
+        <v>0.00656948561296411</v>
       </c>
       <c r="D59" s="4" t="n">
-        <v>-0.02682938103206478</v>
+        <v>-0.0204361506517956</v>
       </c>
       <c r="E59" s="5" t="n">
         <v>14396.5</v>
@@ -2216,11 +2216,34 @@
         <v>0.05053269118505543</v>
       </c>
       <c r="G59" s="4" t="n">
-        <v>-0.07736207221712021</v>
+        <v>-0.07096884183685104</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="6" t="n">
+        <v>46255</v>
+      </c>
+      <c r="B60" s="5" t="n">
+        <v>97956.38493482044</v>
+      </c>
+      <c r="C60" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D60" s="4" t="n">
+        <v>-0.0204361506517956</v>
+      </c>
+      <c r="E60" s="5" t="n">
+        <v>14514.7998046875</v>
+      </c>
+      <c r="F60" s="4" t="n">
+        <v>0.05916519298653689</v>
+      </c>
+      <c r="G60" s="4" t="n">
+        <v>-0.07960134363833249</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G59"/>
+  <autoFilter ref="A1:G60"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/reports/latest_one_month_follow_up.xlsx
+++ b/reports/latest_one_month_follow_up.xlsx
@@ -756,7 +756,7 @@
         <v>38.09999847412109</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>-0.04750003814697268</v>
+        <v>-0.04750003814697279</v>
       </c>
       <c r="F2" s="5" t="n">
         <v>33333.33333333333</v>
@@ -765,7 +765,7 @@
         <v>31749.99872843424</v>
       </c>
       <c r="H2" s="5" t="n">
-        <v>-1583.33460489909</v>
+        <v>-1583.334604899093</v>
       </c>
     </row>
     <row r="3">
@@ -1215,10 +1215,10 @@
         <v>101665.535802718</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>-0.01517965889001283</v>
+        <v>-0.0151796588900126</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>0.01665535802718021</v>
+        <v>0.01665535802718043</v>
       </c>
       <c r="E16" s="5" t="n">
         <v>14734.5</v>
@@ -1227,7 +1227,7 @@
         <v>0.07519702276707529</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>-0.05854166473989508</v>
+        <v>-0.05854166473989486</v>
       </c>
     </row>
     <row r="17">
@@ -1238,7 +1238,7 @@
         <v>101579.9132001645</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>-0.000842198901303659</v>
+        <v>-0.0008421989013038811</v>
       </c>
       <c r="D17" s="4" t="n">
         <v>0.01579913200164529</v>
@@ -1281,13 +1281,13 @@
         <v>46197</v>
       </c>
       <c r="B19" s="5" t="n">
-        <v>99903.87102493743</v>
+        <v>99903.87102493741</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>-0.007105427940044096</v>
+        <v>-0.007105427940044318</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>-0.0009612897506257045</v>
+        <v>-0.0009612897506259266</v>
       </c>
       <c r="E19" s="5" t="n">
         <v>14331.2001953125</v>
@@ -1296,7 +1296,7 @@
         <v>0.04576767332986709</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>-0.04672896308049279</v>
+        <v>-0.04672896308049301</v>
       </c>
     </row>
     <row r="20">
@@ -1307,7 +1307,7 @@
         <v>99725.18443384963</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>-0.001788585259556053</v>
+        <v>-0.00178858525955583</v>
       </c>
       <c r="D20" s="4" t="n">
         <v>-0.00274815566150366</v>
@@ -1353,10 +1353,10 @@
         <v>100567.2965303391</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>-0.01333614376284464</v>
+        <v>-0.01333614376284487</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>0.00567296530339112</v>
+        <v>0.005672965303390898</v>
       </c>
       <c r="E22" s="5" t="n">
         <v>14183.2001953125</v>
@@ -1365,7 +1365,7 @@
         <v>0.03496790683833195</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>-0.02929494153494083</v>
+        <v>-0.02929494153494105</v>
       </c>
     </row>
     <row r="23">
@@ -1376,7 +1376,7 @@
         <v>98982.15764175884</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>-0.01576197176685634</v>
+        <v>-0.01576197176685612</v>
       </c>
       <c r="D23" s="4" t="n">
         <v>-0.01017842358241161</v>
@@ -1402,7 +1402,7 @@
         <v>0.003127667249263499</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>-0.007082591055235898</v>
+        <v>-0.007082591055236009</v>
       </c>
       <c r="E24" s="5" t="n">
         <v>14350.599609375</v>
@@ -1411,7 +1411,7 @@
         <v>0.0471832756403241</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>-0.05426586669555999</v>
+        <v>-0.05426586669556011</v>
       </c>
     </row>
     <row r="25">
@@ -1422,7 +1422,7 @@
         <v>98699.49739704847</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>-0.005964680366087549</v>
+        <v>-0.005964680366087438</v>
       </c>
       <c r="D25" s="4" t="n">
         <v>-0.01300502602951525</v>
@@ -1511,13 +1511,13 @@
         <v>46211</v>
       </c>
       <c r="B29" s="5" t="n">
-        <v>97511.54763463838</v>
+        <v>97511.54763463837</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>-0.02101826087704517</v>
+        <v>-0.02101826087704539</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>-0.02488452365361615</v>
+        <v>-0.02488452365361637</v>
       </c>
       <c r="E29" s="5" t="n">
         <v>14190</v>
@@ -1526,7 +1526,7 @@
         <v>0.03546409807355522</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>-0.06034862172717137</v>
+        <v>-0.06034862172717159</v>
       </c>
     </row>
     <row r="30">
@@ -1537,7 +1537,7 @@
         <v>97085.90440793287</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>-0.004365054570770743</v>
+        <v>-0.004365054570770521</v>
       </c>
       <c r="D30" s="4" t="n">
         <v>-0.02914095592067123</v>
@@ -1603,13 +1603,13 @@
         <v>46217</v>
       </c>
       <c r="B33" s="5" t="n">
-        <v>101364.3995699692</v>
+        <v>101364.3995699691</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>0.02123082912189456</v>
+        <v>0.02123082912189433</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>0.01364399569969166</v>
+        <v>0.01364399569969144</v>
       </c>
       <c r="E33" s="5" t="n">
         <v>14080</v>
@@ -1618,7 +1618,7 @@
         <v>0.02743724460011676</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>-0.0137932489004251</v>
+        <v>-0.01379324890042533</v>
       </c>
     </row>
     <row r="34">
@@ -1629,7 +1629,7 @@
         <v>105261.7030227777</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>0.03844844412182757</v>
+        <v>0.0384484441218278</v>
       </c>
       <c r="D34" s="4" t="n">
         <v>0.05261703022777731</v>
@@ -1675,10 +1675,10 @@
         <v>104848.7672438694</v>
       </c>
       <c r="C36" s="4" t="n">
-        <v>0.02469452791059856</v>
+        <v>0.02469452791059834</v>
       </c>
       <c r="D36" s="4" t="n">
-        <v>0.04848767243869423</v>
+        <v>0.04848767243869401</v>
       </c>
       <c r="E36" s="5" t="n">
         <v>14071</v>
@@ -1687,7 +1687,7 @@
         <v>0.02678050204319904</v>
       </c>
       <c r="G36" s="4" t="n">
-        <v>0.02170717039549519</v>
+        <v>0.02170717039549497</v>
       </c>
     </row>
     <row r="37">
@@ -1698,7 +1698,7 @@
         <v>102169.894507684</v>
       </c>
       <c r="C37" s="4" t="n">
-        <v>-0.02554987346636661</v>
+        <v>-0.02554987346636639</v>
       </c>
       <c r="D37" s="4" t="n">
         <v>0.02169894507684034</v>
@@ -2132,13 +2132,13 @@
         <v>46251</v>
       </c>
       <c r="B56" s="5" t="n">
-        <v>94222.89834801342</v>
+        <v>94222.8983480134</v>
       </c>
       <c r="C56" s="4" t="n">
-        <v>-0.009506854050161162</v>
+        <v>-0.009506854050161273</v>
       </c>
       <c r="D56" s="4" t="n">
-        <v>-0.05777101651986583</v>
+        <v>-0.05777101651986594</v>
       </c>
       <c r="E56" s="5" t="n">
         <v>14132.099609375</v>
@@ -2147,7 +2147,7 @@
         <v>0.03123902578626669</v>
       </c>
       <c r="G56" s="4" t="n">
-        <v>-0.08901004230613252</v>
+        <v>-0.08901004230613263</v>
       </c>
     </row>
     <row r="57">
@@ -2158,7 +2158,7 @@
         <v>95707.04281032382</v>
       </c>
       <c r="C57" s="4" t="n">
-        <v>0.01575142017844433</v>
+        <v>0.01575142017844455</v>
       </c>
       <c r="D57" s="4" t="n">
         <v>-0.04292957189676172</v>

--- a/reports/latest_one_month_follow_up.xlsx
+++ b/reports/latest_one_month_follow_up.xlsx
@@ -15,7 +15,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'TAKIP_OZETI'!$A$1:$B$19</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'POZISYONLAR'!$A$1:$H$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'GUNLUK_TAKIP'!$A$1:$G$60</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'GUNLUK_TAKIP'!$A$1:$G$61</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'NOTLAR'!$A$1:$A$7</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -475,7 +475,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
     </row>
@@ -546,7 +546,7 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>14514.7998046875</v>
+        <v>14501.5</v>
       </c>
     </row>
     <row r="9">
@@ -603,7 +603,7 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
     </row>
@@ -627,7 +627,7 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>-0.0204361506517956</v>
+        <v>-0.01589712763813023</v>
       </c>
     </row>
     <row r="17">
@@ -648,7 +648,7 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>0.05916519298653689</v>
+        <v>0.05819468768242841</v>
       </c>
     </row>
     <row r="18">
@@ -658,7 +658,7 @@
         </is>
       </c>
       <c r="B18" s="3" t="n">
-        <v>-0.07960134363833249</v>
+        <v>-0.07409181532055864</v>
       </c>
     </row>
     <row r="19">
@@ -753,19 +753,19 @@
         <v>40</v>
       </c>
       <c r="D2" s="5" t="n">
-        <v>38.09999847412109</v>
+        <v>38.13999938964844</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>-0.04750003814697279</v>
+        <v>-0.04650001525878911</v>
       </c>
       <c r="F2" s="5" t="n">
         <v>33333.33333333333</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>31749.99872843424</v>
+        <v>31783.33282470702</v>
       </c>
       <c r="H2" s="5" t="n">
-        <v>-1583.334604899093</v>
+        <v>-1550.000508626305</v>
       </c>
     </row>
     <row r="3">
@@ -781,19 +781,19 @@
         <v>45.5</v>
       </c>
       <c r="D3" s="5" t="n">
-        <v>40</v>
+        <v>39.90000152587891</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>-0.1208791208791209</v>
+        <v>-0.1230768895411229</v>
       </c>
       <c r="F3" s="5" t="n">
         <v>33333.33333333333</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>29304.0293040293</v>
+        <v>29230.77034862923</v>
       </c>
       <c r="H3" s="5" t="n">
-        <v>-4029.304029304029</v>
+        <v>-4102.562984704098</v>
       </c>
     </row>
     <row r="4">
@@ -809,19 +809,19 @@
         <v>371.25</v>
       </c>
       <c r="D4" s="5" t="n">
-        <v>411</v>
+        <v>416.5</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>0.1070707070707071</v>
+        <v>0.1218855218855219</v>
       </c>
       <c r="F4" s="5" t="n">
         <v>33333.33333333333</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>36902.3569023569</v>
+        <v>37396.18406285073</v>
       </c>
       <c r="H4" s="5" t="n">
-        <v>3569.023569023571</v>
+        <v>4062.850729517399</v>
       </c>
     </row>
   </sheetData>
@@ -836,7 +836,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G60"/>
+  <dimension ref="A1:G61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -1215,10 +1215,10 @@
         <v>101665.535802718</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>-0.0151796588900126</v>
+        <v>-0.01517965889001283</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>0.01665535802718043</v>
+        <v>0.01665535802718021</v>
       </c>
       <c r="E16" s="5" t="n">
         <v>14734.5</v>
@@ -1227,7 +1227,7 @@
         <v>0.07519702276707529</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>-0.05854166473989486</v>
+        <v>-0.05854166473989508</v>
       </c>
     </row>
     <row r="17">
@@ -1238,7 +1238,7 @@
         <v>101579.9132001645</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>-0.0008421989013038811</v>
+        <v>-0.000842198901303659</v>
       </c>
       <c r="D17" s="4" t="n">
         <v>0.01579913200164529</v>
@@ -1281,13 +1281,13 @@
         <v>46197</v>
       </c>
       <c r="B19" s="5" t="n">
-        <v>99903.87102493741</v>
+        <v>99903.87102493743</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>-0.007105427940044318</v>
+        <v>-0.007105427940044096</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>-0.0009612897506259266</v>
+        <v>-0.0009612897506257045</v>
       </c>
       <c r="E19" s="5" t="n">
         <v>14331.2001953125</v>
@@ -1296,7 +1296,7 @@
         <v>0.04576767332986709</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>-0.04672896308049301</v>
+        <v>-0.04672896308049279</v>
       </c>
     </row>
     <row r="20">
@@ -1307,7 +1307,7 @@
         <v>99725.18443384963</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>-0.00178858525955583</v>
+        <v>-0.001788585259556053</v>
       </c>
       <c r="D20" s="4" t="n">
         <v>-0.00274815566150366</v>
@@ -1353,10 +1353,10 @@
         <v>100567.2965303391</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>-0.01333614376284487</v>
+        <v>-0.01333614376284464</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>0.005672965303390898</v>
+        <v>0.00567296530339112</v>
       </c>
       <c r="E22" s="5" t="n">
         <v>14183.2001953125</v>
@@ -1365,7 +1365,7 @@
         <v>0.03496790683833195</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>-0.02929494153494105</v>
+        <v>-0.02929494153494083</v>
       </c>
     </row>
     <row r="23">
@@ -1376,7 +1376,7 @@
         <v>98982.15764175884</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>-0.01576197176685612</v>
+        <v>-0.01576197176685634</v>
       </c>
       <c r="D23" s="4" t="n">
         <v>-0.01017842358241161</v>
@@ -1402,7 +1402,7 @@
         <v>0.003127667249263499</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>-0.007082591055236009</v>
+        <v>-0.007082591055235898</v>
       </c>
       <c r="E24" s="5" t="n">
         <v>14350.599609375</v>
@@ -1411,7 +1411,7 @@
         <v>0.0471832756403241</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>-0.05426586669556011</v>
+        <v>-0.05426586669555999</v>
       </c>
     </row>
     <row r="25">
@@ -1422,7 +1422,7 @@
         <v>98699.49739704847</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>-0.005964680366087438</v>
+        <v>-0.005964680366087549</v>
       </c>
       <c r="D25" s="4" t="n">
         <v>-0.01300502602951525</v>
@@ -1511,13 +1511,13 @@
         <v>46211</v>
       </c>
       <c r="B29" s="5" t="n">
-        <v>97511.54763463837</v>
+        <v>97511.54763463838</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>-0.02101826087704539</v>
+        <v>-0.02101826087704517</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>-0.02488452365361637</v>
+        <v>-0.02488452365361615</v>
       </c>
       <c r="E29" s="5" t="n">
         <v>14190</v>
@@ -1526,7 +1526,7 @@
         <v>0.03546409807355522</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>-0.06034862172717159</v>
+        <v>-0.06034862172717137</v>
       </c>
     </row>
     <row r="30">
@@ -1537,7 +1537,7 @@
         <v>97085.90440793287</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>-0.004365054570770521</v>
+        <v>-0.004365054570770743</v>
       </c>
       <c r="D30" s="4" t="n">
         <v>-0.02914095592067123</v>
@@ -1603,13 +1603,13 @@
         <v>46217</v>
       </c>
       <c r="B33" s="5" t="n">
-        <v>101364.3995699691</v>
+        <v>101364.3995699692</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>0.02123082912189433</v>
+        <v>0.02123082912189456</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>0.01364399569969144</v>
+        <v>0.01364399569969166</v>
       </c>
       <c r="E33" s="5" t="n">
         <v>14080</v>
@@ -1618,7 +1618,7 @@
         <v>0.02743724460011676</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>-0.01379324890042533</v>
+        <v>-0.0137932489004251</v>
       </c>
     </row>
     <row r="34">
@@ -1629,7 +1629,7 @@
         <v>105261.7030227777</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>0.0384484441218278</v>
+        <v>0.03844844412182757</v>
       </c>
       <c r="D34" s="4" t="n">
         <v>0.05261703022777731</v>
@@ -1675,10 +1675,10 @@
         <v>104848.7672438694</v>
       </c>
       <c r="C36" s="4" t="n">
-        <v>0.02469452791059834</v>
+        <v>0.02469452791059856</v>
       </c>
       <c r="D36" s="4" t="n">
-        <v>0.04848767243869401</v>
+        <v>0.04848767243869423</v>
       </c>
       <c r="E36" s="5" t="n">
         <v>14071</v>
@@ -1687,7 +1687,7 @@
         <v>0.02678050204319904</v>
       </c>
       <c r="G36" s="4" t="n">
-        <v>0.02170717039549497</v>
+        <v>0.02170717039549519</v>
       </c>
     </row>
     <row r="37">
@@ -1698,7 +1698,7 @@
         <v>102169.894507684</v>
       </c>
       <c r="C37" s="4" t="n">
-        <v>-0.02554987346636639</v>
+        <v>-0.02554987346636661</v>
       </c>
       <c r="D37" s="4" t="n">
         <v>0.02169894507684034</v>
@@ -2132,13 +2132,13 @@
         <v>46251</v>
       </c>
       <c r="B56" s="5" t="n">
-        <v>94222.8983480134</v>
+        <v>94222.89834801342</v>
       </c>
       <c r="C56" s="4" t="n">
-        <v>-0.009506854050161273</v>
+        <v>-0.009506854050161162</v>
       </c>
       <c r="D56" s="4" t="n">
-        <v>-0.05777101651986594</v>
+        <v>-0.05777101651986583</v>
       </c>
       <c r="E56" s="5" t="n">
         <v>14132.099609375</v>
@@ -2147,7 +2147,7 @@
         <v>0.03123902578626669</v>
       </c>
       <c r="G56" s="4" t="n">
-        <v>-0.08901004230613263</v>
+        <v>-0.08901004230613252</v>
       </c>
     </row>
     <row r="57">
@@ -2158,7 +2158,7 @@
         <v>95707.04281032382</v>
       </c>
       <c r="C57" s="4" t="n">
-        <v>0.01575142017844455</v>
+        <v>0.01575142017844433</v>
       </c>
       <c r="D57" s="4" t="n">
         <v>-0.04292957189676172</v>
@@ -2224,13 +2224,13 @@
         <v>46255</v>
       </c>
       <c r="B60" s="5" t="n">
-        <v>97956.38493482044</v>
+        <v>98410.28723618698</v>
       </c>
       <c r="C60" s="4" t="n">
-        <v>0</v>
+        <v>0.004633718380568697</v>
       </c>
       <c r="D60" s="4" t="n">
-        <v>-0.0204361506517956</v>
+        <v>-0.01589712763813012</v>
       </c>
       <c r="E60" s="5" t="n">
         <v>14514.7998046875</v>
@@ -2239,11 +2239,34 @@
         <v>0.05916519298653689</v>
       </c>
       <c r="G60" s="4" t="n">
-        <v>-0.07960134363833249</v>
+        <v>-0.075062320624667</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="6" t="n">
+        <v>46258</v>
+      </c>
+      <c r="B61" s="5" t="n">
+        <v>98410.28723618698</v>
+      </c>
+      <c r="C61" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D61" s="4" t="n">
+        <v>-0.01589712763813012</v>
+      </c>
+      <c r="E61" s="5" t="n">
+        <v>14501.5</v>
+      </c>
+      <c r="F61" s="4" t="n">
+        <v>0.05819468768242841</v>
+      </c>
+      <c r="G61" s="4" t="n">
+        <v>-0.07409181532055853</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G60"/>
+  <autoFilter ref="A1:G61"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/reports/latest_one_month_follow_up.xlsx
+++ b/reports/latest_one_month_follow_up.xlsx
@@ -15,7 +15,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'TAKIP_OZETI'!$A$1:$B$19</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'POZISYONLAR'!$A$1:$H$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'GUNLUK_TAKIP'!$A$1:$G$61</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'GUNLUK_TAKIP'!$A$1:$G$62</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'NOTLAR'!$A$1:$A$7</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -475,7 +475,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
@@ -546,7 +546,7 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>14501.5</v>
+        <v>14473.400390625</v>
       </c>
     </row>
     <row r="9">
@@ -603,7 +603,7 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
@@ -627,7 +627,7 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>-0.01589712763813023</v>
+        <v>-0.020551883878974</v>
       </c>
     </row>
     <row r="17">
@@ -648,7 +648,7 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>0.05819468768242841</v>
+        <v>0.05614421998139218</v>
       </c>
     </row>
     <row r="18">
@@ -658,7 +658,7 @@
         </is>
       </c>
       <c r="B18" s="3" t="n">
-        <v>-0.07409181532055864</v>
+        <v>-0.07669610386036618</v>
       </c>
     </row>
     <row r="19">
@@ -753,19 +753,19 @@
         <v>40</v>
       </c>
       <c r="D2" s="5" t="n">
-        <v>38.13999938964844</v>
+        <v>38.18000030517578</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>-0.04650001525878911</v>
+        <v>-0.04549999237060542</v>
       </c>
       <c r="F2" s="5" t="n">
         <v>33333.33333333333</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>31783.33282470702</v>
+        <v>31816.66692097981</v>
       </c>
       <c r="H2" s="5" t="n">
-        <v>-1550.000508626305</v>
+        <v>-1516.666412353516</v>
       </c>
     </row>
     <row r="3">
@@ -781,19 +781,19 @@
         <v>45.5</v>
       </c>
       <c r="D3" s="5" t="n">
-        <v>39.90000152587891</v>
+        <v>39.7400016784668</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>-0.1230768895411229</v>
+        <v>-0.1265933697040265</v>
       </c>
       <c r="F3" s="5" t="n">
         <v>33333.33333333333</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>29230.77034862923</v>
+        <v>29113.55434319911</v>
       </c>
       <c r="H3" s="5" t="n">
-        <v>-4102.562984704098</v>
+        <v>-4219.778990134215</v>
       </c>
     </row>
     <row r="4">
@@ -809,19 +809,19 @@
         <v>371.25</v>
       </c>
       <c r="D4" s="5" t="n">
-        <v>416.5</v>
+        <v>412.25</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>0.1218855218855219</v>
+        <v>0.1104377104377103</v>
       </c>
       <c r="F4" s="5" t="n">
         <v>33333.33333333333</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>37396.18406285073</v>
+        <v>37014.59034792367</v>
       </c>
       <c r="H4" s="5" t="n">
-        <v>4062.850729517399</v>
+        <v>3681.257014590345</v>
       </c>
     </row>
   </sheetData>
@@ -836,7 +836,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G61"/>
+  <dimension ref="A1:G62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -2247,13 +2247,13 @@
         <v>46258</v>
       </c>
       <c r="B61" s="5" t="n">
-        <v>98410.28723618698</v>
+        <v>97944.8116121026</v>
       </c>
       <c r="C61" s="4" t="n">
-        <v>0</v>
+        <v>-0.004729948841295739</v>
       </c>
       <c r="D61" s="4" t="n">
-        <v>-0.01589712763813012</v>
+        <v>-0.020551883878974</v>
       </c>
       <c r="E61" s="5" t="n">
         <v>14501.5</v>
@@ -2262,11 +2262,34 @@
         <v>0.05819468768242841</v>
       </c>
       <c r="G61" s="4" t="n">
-        <v>-0.07409181532055853</v>
+        <v>-0.07874657156140241</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="6" t="n">
+        <v>46259</v>
+      </c>
+      <c r="B62" s="5" t="n">
+        <v>97944.8116121026</v>
+      </c>
+      <c r="C62" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D62" s="4" t="n">
+        <v>-0.020551883878974</v>
+      </c>
+      <c r="E62" s="5" t="n">
+        <v>14473.400390625</v>
+      </c>
+      <c r="F62" s="4" t="n">
+        <v>0.05614421998139218</v>
+      </c>
+      <c r="G62" s="4" t="n">
+        <v>-0.07669610386036618</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G61"/>
+  <autoFilter ref="A1:G62"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/reports/latest_one_month_follow_up.xlsx
+++ b/reports/latest_one_month_follow_up.xlsx
@@ -15,7 +15,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'TAKIP_OZETI'!$A$1:$B$19</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'POZISYONLAR'!$A$1:$H$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'GUNLUK_TAKIP'!$A$1:$G$62</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'GUNLUK_TAKIP'!$A$1:$G$63</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'NOTLAR'!$A$1:$A$7</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -475,7 +475,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-26</t>
         </is>
       </c>
     </row>
@@ -546,7 +546,7 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>14473.400390625</v>
+        <v>14610.900390625</v>
       </c>
     </row>
     <row r="9">
@@ -603,7 +603,7 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-26</t>
         </is>
       </c>
     </row>
@@ -627,7 +627,7 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>-0.020551883878974</v>
+        <v>-0.007168337680734438</v>
       </c>
     </row>
     <row r="17">
@@ -648,7 +648,7 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>0.05614421998139218</v>
+        <v>0.06617778682319031</v>
       </c>
     </row>
     <row r="18">
@@ -658,7 +658,7 @@
         </is>
       </c>
       <c r="B18" s="3" t="n">
-        <v>-0.07669610386036618</v>
+        <v>-0.07334612450392475</v>
       </c>
     </row>
     <row r="19">
@@ -753,19 +753,19 @@
         <v>40</v>
       </c>
       <c r="D2" s="5" t="n">
-        <v>38.18000030517578</v>
+        <v>38.70000076293945</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>-0.04549999237060542</v>
+        <v>-0.03249998092651363</v>
       </c>
       <c r="F2" s="5" t="n">
         <v>33333.33333333333</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>31816.66692097981</v>
+        <v>32250.00063578288</v>
       </c>
       <c r="H2" s="5" t="n">
-        <v>-1516.666412353516</v>
+        <v>-1083.332697550453</v>
       </c>
     </row>
     <row r="3">
@@ -781,19 +781,19 @@
         <v>45.5</v>
       </c>
       <c r="D3" s="5" t="n">
-        <v>39.7400016784668</v>
+        <v>40.2400016784668</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>-0.1265933697040265</v>
+        <v>-0.1156043587150154</v>
       </c>
       <c r="F3" s="5" t="n">
         <v>33333.33333333333</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>29113.55434319911</v>
+        <v>29479.85470949948</v>
       </c>
       <c r="H3" s="5" t="n">
-        <v>-4219.778990134215</v>
+        <v>-3853.478623833846</v>
       </c>
     </row>
     <row r="4">
@@ -809,19 +809,19 @@
         <v>371.25</v>
       </c>
       <c r="D4" s="5" t="n">
-        <v>412.25</v>
+        <v>418.25</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>0.1104377104377103</v>
+        <v>0.1265993265993266</v>
       </c>
       <c r="F4" s="5" t="n">
         <v>33333.33333333333</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>37014.59034792367</v>
+        <v>37553.31088664421</v>
       </c>
       <c r="H4" s="5" t="n">
-        <v>3681.257014590345</v>
+        <v>4219.977553310884</v>
       </c>
     </row>
   </sheetData>
@@ -836,7 +836,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G62"/>
+  <dimension ref="A1:G63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -2270,13 +2270,13 @@
         <v>46259</v>
       </c>
       <c r="B62" s="5" t="n">
-        <v>97944.8116121026</v>
+        <v>98436.88852787223</v>
       </c>
       <c r="C62" s="4" t="n">
-        <v>0</v>
+        <v>0.005024022280204266</v>
       </c>
       <c r="D62" s="4" t="n">
-        <v>-0.020551883878974</v>
+        <v>-0.01563111472127776</v>
       </c>
       <c r="E62" s="5" t="n">
         <v>14473.400390625</v>
@@ -2285,11 +2285,34 @@
         <v>0.05614421998139218</v>
       </c>
       <c r="G62" s="4" t="n">
-        <v>-0.07669610386036618</v>
+        <v>-0.07177533470266995</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="6" t="n">
+        <v>46260</v>
+      </c>
+      <c r="B63" s="5" t="n">
+        <v>99283.16623192659</v>
+      </c>
+      <c r="C63" s="4" t="n">
+        <v>0.008597160238509094</v>
+      </c>
+      <c r="D63" s="4" t="n">
+        <v>-0.007168337680734105</v>
+      </c>
+      <c r="E63" s="5" t="n">
+        <v>14610.900390625</v>
+      </c>
+      <c r="F63" s="4" t="n">
+        <v>0.06617778682319031</v>
+      </c>
+      <c r="G63" s="4" t="n">
+        <v>-0.07334612450392441</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G62"/>
+  <autoFilter ref="A1:G63"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/reports/latest_one_month_follow_up.xlsx
+++ b/reports/latest_one_month_follow_up.xlsx
@@ -15,7 +15,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'TAKIP_OZETI'!$A$1:$B$19</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'POZISYONLAR'!$A$1:$H$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'GUNLUK_TAKIP'!$A$1:$G$63</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'GUNLUK_TAKIP'!$A$1:$G$64</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'NOTLAR'!$A$1:$A$7</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -475,7 +475,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
@@ -546,7 +546,7 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>14610.900390625</v>
+        <v>14575.5</v>
       </c>
     </row>
     <row r="9">
@@ -603,7 +603,7 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
@@ -627,7 +627,7 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>-0.007168337680734438</v>
+        <v>-0.01350730118245946</v>
       </c>
     </row>
     <row r="17">
@@ -648,7 +648,7 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>0.06617778682319031</v>
+        <v>0.0635945709281962</v>
       </c>
     </row>
     <row r="18">
@@ -658,7 +658,7 @@
         </is>
       </c>
       <c r="B18" s="3" t="n">
-        <v>-0.07334612450392475</v>
+        <v>-0.07710187211065567</v>
       </c>
     </row>
     <row r="19">
@@ -753,19 +753,19 @@
         <v>40</v>
       </c>
       <c r="D2" s="5" t="n">
-        <v>38.70000076293945</v>
+        <v>38.59999847412109</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>-0.03249998092651363</v>
+        <v>-0.03500003814697261</v>
       </c>
       <c r="F2" s="5" t="n">
         <v>33333.33333333333</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>32250.00063578288</v>
+        <v>32166.66539510091</v>
       </c>
       <c r="H2" s="5" t="n">
-        <v>-1083.332697550453</v>
+        <v>-1166.667938232422</v>
       </c>
     </row>
     <row r="3">
@@ -781,19 +781,19 @@
         <v>45.5</v>
       </c>
       <c r="D3" s="5" t="n">
-        <v>40.2400016784668</v>
+        <v>40.04000091552734</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>-0.1156043587150154</v>
+        <v>-0.11999997987852</v>
       </c>
       <c r="F3" s="5" t="n">
         <v>33333.33333333333</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>29479.85470949948</v>
+        <v>29333.33400404933</v>
       </c>
       <c r="H3" s="5" t="n">
-        <v>-3853.478623833846</v>
+        <v>-3999.999329283997</v>
       </c>
     </row>
     <row r="4">
@@ -809,19 +809,19 @@
         <v>371.25</v>
       </c>
       <c r="D4" s="5" t="n">
-        <v>418.25</v>
+        <v>413.75</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>0.1265993265993266</v>
+        <v>0.1144781144781144</v>
       </c>
       <c r="F4" s="5" t="n">
         <v>33333.33333333333</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>37553.31088664421</v>
+        <v>37149.27048260381</v>
       </c>
       <c r="H4" s="5" t="n">
-        <v>4219.977553310884</v>
+        <v>3815.937149270481</v>
       </c>
     </row>
   </sheetData>
@@ -836,7 +836,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G63"/>
+  <dimension ref="A1:G64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -2311,8 +2311,31 @@
         <v>-0.07334612450392441</v>
       </c>
     </row>
+    <row r="64">
+      <c r="A64" s="6" t="n">
+        <v>46261</v>
+      </c>
+      <c r="B64" s="5" t="n">
+        <v>98649.26988175407</v>
+      </c>
+      <c r="C64" s="4" t="n">
+        <v>-0.006384731412490741</v>
+      </c>
+      <c r="D64" s="4" t="n">
+        <v>-0.01350730118245935</v>
+      </c>
+      <c r="E64" s="5" t="n">
+        <v>14575.5</v>
+      </c>
+      <c r="F64" s="4" t="n">
+        <v>0.0635945709281962</v>
+      </c>
+      <c r="G64" s="4" t="n">
+        <v>-0.07710187211065556</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G63"/>
+  <autoFilter ref="A1:G64"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/reports/latest_one_month_follow_up.xlsx
+++ b/reports/latest_one_month_follow_up.xlsx
@@ -15,7 +15,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'TAKIP_OZETI'!$A$1:$B$19</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'POZISYONLAR'!$A$1:$H$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'GUNLUK_TAKIP'!$A$1:$G$64</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'GUNLUK_TAKIP'!$A$1:$G$65</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'NOTLAR'!$A$1:$A$7</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -546,7 +546,7 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>14575.5</v>
+        <v>14641.599609375</v>
       </c>
     </row>
     <row r="9">
@@ -627,7 +627,7 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>-0.01350730118245946</v>
+        <v>-0.01350730118245969</v>
       </c>
     </row>
     <row r="17">
@@ -648,7 +648,7 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>0.0635945709281962</v>
+        <v>0.06841795164732933</v>
       </c>
     </row>
     <row r="18">
@@ -658,7 +658,7 @@
         </is>
       </c>
       <c r="B18" s="3" t="n">
-        <v>-0.07710187211065567</v>
+        <v>-0.08192525282978902</v>
       </c>
     </row>
     <row r="19">
@@ -756,16 +756,16 @@
         <v>38.59999847412109</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>-0.03500003814697261</v>
+        <v>-0.03500003814697283</v>
       </c>
       <c r="F2" s="5" t="n">
         <v>33333.33333333333</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>32166.66539510091</v>
+        <v>32166.6653951009</v>
       </c>
       <c r="H2" s="5" t="n">
-        <v>-1166.667938232422</v>
+        <v>-1166.667938232429</v>
       </c>
     </row>
     <row r="3">
@@ -836,7 +836,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G64"/>
+  <dimension ref="A1:G65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -1215,10 +1215,10 @@
         <v>101665.535802718</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>-0.01517965889001283</v>
+        <v>-0.0151796588900126</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>0.01665535802718021</v>
+        <v>0.01665535802718043</v>
       </c>
       <c r="E16" s="5" t="n">
         <v>14734.5</v>
@@ -1227,7 +1227,7 @@
         <v>0.07519702276707529</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>-0.05854166473989508</v>
+        <v>-0.05854166473989486</v>
       </c>
     </row>
     <row r="17">
@@ -1238,7 +1238,7 @@
         <v>101579.9132001645</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>-0.000842198901303659</v>
+        <v>-0.0008421989013038811</v>
       </c>
       <c r="D17" s="4" t="n">
         <v>0.01579913200164529</v>
@@ -1281,13 +1281,13 @@
         <v>46197</v>
       </c>
       <c r="B19" s="5" t="n">
-        <v>99903.87102493743</v>
+        <v>99903.87102493741</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>-0.007105427940044096</v>
+        <v>-0.007105427940044318</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>-0.0009612897506257045</v>
+        <v>-0.0009612897506259266</v>
       </c>
       <c r="E19" s="5" t="n">
         <v>14331.2001953125</v>
@@ -1296,7 +1296,7 @@
         <v>0.04576767332986709</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>-0.04672896308049279</v>
+        <v>-0.04672896308049301</v>
       </c>
     </row>
     <row r="20">
@@ -1307,7 +1307,7 @@
         <v>99725.18443384963</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>-0.001788585259556053</v>
+        <v>-0.00178858525955583</v>
       </c>
       <c r="D20" s="4" t="n">
         <v>-0.00274815566150366</v>
@@ -1353,10 +1353,10 @@
         <v>100567.2965303391</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>-0.01333614376284464</v>
+        <v>-0.01333614376284487</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>0.00567296530339112</v>
+        <v>0.005672965303390898</v>
       </c>
       <c r="E22" s="5" t="n">
         <v>14183.2001953125</v>
@@ -1365,7 +1365,7 @@
         <v>0.03496790683833195</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>-0.02929494153494083</v>
+        <v>-0.02929494153494105</v>
       </c>
     </row>
     <row r="23">
@@ -1376,7 +1376,7 @@
         <v>98982.15764175884</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>-0.01576197176685634</v>
+        <v>-0.01576197176685612</v>
       </c>
       <c r="D23" s="4" t="n">
         <v>-0.01017842358241161</v>
@@ -1402,7 +1402,7 @@
         <v>0.003127667249263499</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>-0.007082591055235898</v>
+        <v>-0.007082591055236009</v>
       </c>
       <c r="E24" s="5" t="n">
         <v>14350.599609375</v>
@@ -1411,7 +1411,7 @@
         <v>0.0471832756403241</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>-0.05426586669555999</v>
+        <v>-0.05426586669556011</v>
       </c>
     </row>
     <row r="25">
@@ -1422,7 +1422,7 @@
         <v>98699.49739704847</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>-0.005964680366087549</v>
+        <v>-0.005964680366087438</v>
       </c>
       <c r="D25" s="4" t="n">
         <v>-0.01300502602951525</v>
@@ -1511,13 +1511,13 @@
         <v>46211</v>
       </c>
       <c r="B29" s="5" t="n">
-        <v>97511.54763463838</v>
+        <v>97511.54763463837</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>-0.02101826087704517</v>
+        <v>-0.02101826087704539</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>-0.02488452365361615</v>
+        <v>-0.02488452365361637</v>
       </c>
       <c r="E29" s="5" t="n">
         <v>14190</v>
@@ -1526,7 +1526,7 @@
         <v>0.03546409807355522</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>-0.06034862172717137</v>
+        <v>-0.06034862172717159</v>
       </c>
     </row>
     <row r="30">
@@ -1537,7 +1537,7 @@
         <v>97085.90440793287</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>-0.004365054570770743</v>
+        <v>-0.004365054570770521</v>
       </c>
       <c r="D30" s="4" t="n">
         <v>-0.02914095592067123</v>
@@ -1603,13 +1603,13 @@
         <v>46217</v>
       </c>
       <c r="B33" s="5" t="n">
-        <v>101364.3995699692</v>
+        <v>101364.3995699691</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>0.02123082912189456</v>
+        <v>0.02123082912189433</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>0.01364399569969166</v>
+        <v>0.01364399569969144</v>
       </c>
       <c r="E33" s="5" t="n">
         <v>14080</v>
@@ -1618,7 +1618,7 @@
         <v>0.02743724460011676</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>-0.0137932489004251</v>
+        <v>-0.01379324890042533</v>
       </c>
     </row>
     <row r="34">
@@ -1629,7 +1629,7 @@
         <v>105261.7030227777</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>0.03844844412182757</v>
+        <v>0.0384484441218278</v>
       </c>
       <c r="D34" s="4" t="n">
         <v>0.05261703022777731</v>
@@ -1675,10 +1675,10 @@
         <v>104848.7672438694</v>
       </c>
       <c r="C36" s="4" t="n">
-        <v>0.02469452791059856</v>
+        <v>0.02469452791059834</v>
       </c>
       <c r="D36" s="4" t="n">
-        <v>0.04848767243869423</v>
+        <v>0.04848767243869401</v>
       </c>
       <c r="E36" s="5" t="n">
         <v>14071</v>
@@ -1687,7 +1687,7 @@
         <v>0.02678050204319904</v>
       </c>
       <c r="G36" s="4" t="n">
-        <v>0.02170717039549519</v>
+        <v>0.02170717039549497</v>
       </c>
     </row>
     <row r="37">
@@ -1698,7 +1698,7 @@
         <v>102169.894507684</v>
       </c>
       <c r="C37" s="4" t="n">
-        <v>-0.02554987346636661</v>
+        <v>-0.02554987346636639</v>
       </c>
       <c r="D37" s="4" t="n">
         <v>0.02169894507684034</v>
@@ -2132,13 +2132,13 @@
         <v>46251</v>
       </c>
       <c r="B56" s="5" t="n">
-        <v>94222.89834801342</v>
+        <v>94222.8983480134</v>
       </c>
       <c r="C56" s="4" t="n">
-        <v>-0.009506854050161162</v>
+        <v>-0.009506854050161273</v>
       </c>
       <c r="D56" s="4" t="n">
-        <v>-0.05777101651986583</v>
+        <v>-0.05777101651986594</v>
       </c>
       <c r="E56" s="5" t="n">
         <v>14132.099609375</v>
@@ -2147,7 +2147,7 @@
         <v>0.03123902578626669</v>
       </c>
       <c r="G56" s="4" t="n">
-        <v>-0.08901004230613252</v>
+        <v>-0.08901004230613263</v>
       </c>
     </row>
     <row r="57">
@@ -2158,7 +2158,7 @@
         <v>95707.04281032382</v>
       </c>
       <c r="C57" s="4" t="n">
-        <v>0.01575142017844433</v>
+        <v>0.01575142017844455</v>
       </c>
       <c r="D57" s="4" t="n">
         <v>-0.04292957189676172</v>
@@ -2316,13 +2316,13 @@
         <v>46261</v>
       </c>
       <c r="B64" s="5" t="n">
-        <v>98649.26988175407</v>
+        <v>98649.26988175404</v>
       </c>
       <c r="C64" s="4" t="n">
-        <v>-0.006384731412490741</v>
+        <v>-0.006384731412490963</v>
       </c>
       <c r="D64" s="4" t="n">
-        <v>-0.01350730118245935</v>
+        <v>-0.01350730118245957</v>
       </c>
       <c r="E64" s="5" t="n">
         <v>14575.5</v>
@@ -2331,11 +2331,34 @@
         <v>0.0635945709281962</v>
       </c>
       <c r="G64" s="4" t="n">
-        <v>-0.07710187211065556</v>
+        <v>-0.07710187211065578</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="6" t="n">
+        <v>46262</v>
+      </c>
+      <c r="B65" s="5" t="n">
+        <v>98649.26988175404</v>
+      </c>
+      <c r="C65" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D65" s="4" t="n">
+        <v>-0.01350730118245957</v>
+      </c>
+      <c r="E65" s="5" t="n">
+        <v>14641.599609375</v>
+      </c>
+      <c r="F65" s="4" t="n">
+        <v>0.06841795164732933</v>
+      </c>
+      <c r="G65" s="4" t="n">
+        <v>-0.08192525282978891</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G64"/>
+  <autoFilter ref="A1:G65"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/reports/latest_one_month_follow_up.xlsx
+++ b/reports/latest_one_month_follow_up.xlsx
@@ -15,7 +15,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'TAKIP_OZETI'!$A$1:$B$19</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'POZISYONLAR'!$A$1:$H$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'GUNLUK_TAKIP'!$A$1:$G$65</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'GUNLUK_TAKIP'!$A$1:$G$66</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'NOTLAR'!$A$1:$A$7</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -475,7 +475,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
     </row>
@@ -546,7 +546,7 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>14641.599609375</v>
+        <v>14334.099609375</v>
       </c>
     </row>
     <row r="9">
@@ -603,7 +603,7 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
     </row>
@@ -627,7 +627,7 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>-0.01350730118245969</v>
+        <v>-0.006536765279765544</v>
       </c>
     </row>
     <row r="17">
@@ -648,7 +648,7 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>0.06841795164732933</v>
+        <v>0.04597924761930816</v>
       </c>
     </row>
     <row r="18">
@@ -658,7 +658,7 @@
         </is>
       </c>
       <c r="B18" s="3" t="n">
-        <v>-0.08192525282978902</v>
+        <v>-0.05251601289907371</v>
       </c>
     </row>
     <row r="19">
@@ -753,19 +753,19 @@
         <v>40</v>
       </c>
       <c r="D2" s="5" t="n">
-        <v>38.59999847412109</v>
+        <v>39.15999984741211</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>-0.03500003814697283</v>
+        <v>-0.02100000381469724</v>
       </c>
       <c r="F2" s="5" t="n">
         <v>33333.33333333333</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>32166.6653951009</v>
+        <v>32633.33320617675</v>
       </c>
       <c r="H2" s="5" t="n">
-        <v>-1166.667938232429</v>
+        <v>-700.0001271565743</v>
       </c>
     </row>
     <row r="3">
@@ -781,19 +781,19 @@
         <v>45.5</v>
       </c>
       <c r="D3" s="5" t="n">
-        <v>40.04000091552734</v>
+        <v>40.13999938964844</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>-0.11999997987852</v>
+        <v>-0.1178022112165179</v>
       </c>
       <c r="F3" s="5" t="n">
         <v>33333.33333333333</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>29333.33400404933</v>
+        <v>29406.5929594494</v>
       </c>
       <c r="H3" s="5" t="n">
-        <v>-3999.999329283997</v>
+        <v>-3926.740373883931</v>
       </c>
     </row>
     <row r="4">
@@ -809,19 +809,19 @@
         <v>371.25</v>
       </c>
       <c r="D4" s="5" t="n">
-        <v>413.75</v>
+        <v>415.5</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>0.1144781144781144</v>
+        <v>0.1191919191919193</v>
       </c>
       <c r="F4" s="5" t="n">
         <v>33333.33333333333</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>37149.27048260381</v>
+        <v>37306.3973063973</v>
       </c>
       <c r="H4" s="5" t="n">
-        <v>3815.937149270481</v>
+        <v>3973.063973063974</v>
       </c>
     </row>
   </sheetData>
@@ -836,7 +836,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G65"/>
+  <dimension ref="A1:G66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -1215,10 +1215,10 @@
         <v>101665.535802718</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>-0.0151796588900126</v>
+        <v>-0.01517965889001283</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>0.01665535802718043</v>
+        <v>0.01665535802718021</v>
       </c>
       <c r="E16" s="5" t="n">
         <v>14734.5</v>
@@ -1227,7 +1227,7 @@
         <v>0.07519702276707529</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>-0.05854166473989486</v>
+        <v>-0.05854166473989508</v>
       </c>
     </row>
     <row r="17">
@@ -1238,7 +1238,7 @@
         <v>101579.9132001645</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>-0.0008421989013038811</v>
+        <v>-0.000842198901303659</v>
       </c>
       <c r="D17" s="4" t="n">
         <v>0.01579913200164529</v>
@@ -1281,13 +1281,13 @@
         <v>46197</v>
       </c>
       <c r="B19" s="5" t="n">
-        <v>99903.87102493741</v>
+        <v>99903.87102493743</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>-0.007105427940044318</v>
+        <v>-0.007105427940044096</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>-0.0009612897506259266</v>
+        <v>-0.0009612897506257045</v>
       </c>
       <c r="E19" s="5" t="n">
         <v>14331.2001953125</v>
@@ -1296,7 +1296,7 @@
         <v>0.04576767332986709</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>-0.04672896308049301</v>
+        <v>-0.04672896308049279</v>
       </c>
     </row>
     <row r="20">
@@ -1307,7 +1307,7 @@
         <v>99725.18443384963</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>-0.00178858525955583</v>
+        <v>-0.001788585259556053</v>
       </c>
       <c r="D20" s="4" t="n">
         <v>-0.00274815566150366</v>
@@ -1353,10 +1353,10 @@
         <v>100567.2965303391</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>-0.01333614376284487</v>
+        <v>-0.01333614376284464</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>0.005672965303390898</v>
+        <v>0.00567296530339112</v>
       </c>
       <c r="E22" s="5" t="n">
         <v>14183.2001953125</v>
@@ -1365,7 +1365,7 @@
         <v>0.03496790683833195</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>-0.02929494153494105</v>
+        <v>-0.02929494153494083</v>
       </c>
     </row>
     <row r="23">
@@ -1376,7 +1376,7 @@
         <v>98982.15764175884</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>-0.01576197176685612</v>
+        <v>-0.01576197176685634</v>
       </c>
       <c r="D23" s="4" t="n">
         <v>-0.01017842358241161</v>
@@ -1402,7 +1402,7 @@
         <v>0.003127667249263499</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>-0.007082591055236009</v>
+        <v>-0.007082591055235898</v>
       </c>
       <c r="E24" s="5" t="n">
         <v>14350.599609375</v>
@@ -1411,7 +1411,7 @@
         <v>0.0471832756403241</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>-0.05426586669556011</v>
+        <v>-0.05426586669555999</v>
       </c>
     </row>
     <row r="25">
@@ -1422,7 +1422,7 @@
         <v>98699.49739704847</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>-0.005964680366087438</v>
+        <v>-0.005964680366087549</v>
       </c>
       <c r="D25" s="4" t="n">
         <v>-0.01300502602951525</v>
@@ -1511,13 +1511,13 @@
         <v>46211</v>
       </c>
       <c r="B29" s="5" t="n">
-        <v>97511.54763463837</v>
+        <v>97511.54763463838</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>-0.02101826087704539</v>
+        <v>-0.02101826087704517</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>-0.02488452365361637</v>
+        <v>-0.02488452365361615</v>
       </c>
       <c r="E29" s="5" t="n">
         <v>14190</v>
@@ -1526,7 +1526,7 @@
         <v>0.03546409807355522</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>-0.06034862172717159</v>
+        <v>-0.06034862172717137</v>
       </c>
     </row>
     <row r="30">
@@ -1537,7 +1537,7 @@
         <v>97085.90440793287</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>-0.004365054570770521</v>
+        <v>-0.004365054570770743</v>
       </c>
       <c r="D30" s="4" t="n">
         <v>-0.02914095592067123</v>
@@ -1603,13 +1603,13 @@
         <v>46217</v>
       </c>
       <c r="B33" s="5" t="n">
-        <v>101364.3995699691</v>
+        <v>101364.3995699692</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>0.02123082912189433</v>
+        <v>0.02123082912189456</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>0.01364399569969144</v>
+        <v>0.01364399569969166</v>
       </c>
       <c r="E33" s="5" t="n">
         <v>14080</v>
@@ -1618,7 +1618,7 @@
         <v>0.02743724460011676</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>-0.01379324890042533</v>
+        <v>-0.0137932489004251</v>
       </c>
     </row>
     <row r="34">
@@ -1629,7 +1629,7 @@
         <v>105261.7030227777</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>0.0384484441218278</v>
+        <v>0.03844844412182757</v>
       </c>
       <c r="D34" s="4" t="n">
         <v>0.05261703022777731</v>
@@ -1675,10 +1675,10 @@
         <v>104848.7672438694</v>
       </c>
       <c r="C36" s="4" t="n">
-        <v>0.02469452791059834</v>
+        <v>0.02469452791059856</v>
       </c>
       <c r="D36" s="4" t="n">
-        <v>0.04848767243869401</v>
+        <v>0.04848767243869423</v>
       </c>
       <c r="E36" s="5" t="n">
         <v>14071</v>
@@ -1687,7 +1687,7 @@
         <v>0.02678050204319904</v>
       </c>
       <c r="G36" s="4" t="n">
-        <v>0.02170717039549497</v>
+        <v>0.02170717039549519</v>
       </c>
     </row>
     <row r="37">
@@ -1698,7 +1698,7 @@
         <v>102169.894507684</v>
       </c>
       <c r="C37" s="4" t="n">
-        <v>-0.02554987346636639</v>
+        <v>-0.02554987346636661</v>
       </c>
       <c r="D37" s="4" t="n">
         <v>0.02169894507684034</v>
@@ -2132,13 +2132,13 @@
         <v>46251</v>
       </c>
       <c r="B56" s="5" t="n">
-        <v>94222.8983480134</v>
+        <v>94222.89834801342</v>
       </c>
       <c r="C56" s="4" t="n">
-        <v>-0.009506854050161273</v>
+        <v>-0.009506854050161162</v>
       </c>
       <c r="D56" s="4" t="n">
-        <v>-0.05777101651986594</v>
+        <v>-0.05777101651986583</v>
       </c>
       <c r="E56" s="5" t="n">
         <v>14132.099609375</v>
@@ -2147,7 +2147,7 @@
         <v>0.03123902578626669</v>
       </c>
       <c r="G56" s="4" t="n">
-        <v>-0.08901004230613263</v>
+        <v>-0.08901004230613252</v>
       </c>
     </row>
     <row r="57">
@@ -2158,7 +2158,7 @@
         <v>95707.04281032382</v>
       </c>
       <c r="C57" s="4" t="n">
-        <v>0.01575142017844455</v>
+        <v>0.01575142017844433</v>
       </c>
       <c r="D57" s="4" t="n">
         <v>-0.04292957189676172</v>
@@ -2316,13 +2316,13 @@
         <v>46261</v>
       </c>
       <c r="B64" s="5" t="n">
-        <v>98649.26988175404</v>
+        <v>98649.26988175407</v>
       </c>
       <c r="C64" s="4" t="n">
-        <v>-0.006384731412490963</v>
+        <v>-0.006384731412490741</v>
       </c>
       <c r="D64" s="4" t="n">
-        <v>-0.01350730118245957</v>
+        <v>-0.01350730118245935</v>
       </c>
       <c r="E64" s="5" t="n">
         <v>14575.5</v>
@@ -2331,7 +2331,7 @@
         <v>0.0635945709281962</v>
       </c>
       <c r="G64" s="4" t="n">
-        <v>-0.07710187211065578</v>
+        <v>-0.07710187211065556</v>
       </c>
     </row>
     <row r="65">
@@ -2339,13 +2339,13 @@
         <v>46262</v>
       </c>
       <c r="B65" s="5" t="n">
-        <v>98649.26988175404</v>
+        <v>99346.32347202346</v>
       </c>
       <c r="C65" s="4" t="n">
-        <v>0</v>
+        <v>0.007065978198368184</v>
       </c>
       <c r="D65" s="4" t="n">
-        <v>-0.01350730118245957</v>
+        <v>-0.006536765279765322</v>
       </c>
       <c r="E65" s="5" t="n">
         <v>14641.599609375</v>
@@ -2354,11 +2354,34 @@
         <v>0.06841795164732933</v>
       </c>
       <c r="G65" s="4" t="n">
-        <v>-0.08192525282978891</v>
+        <v>-0.07495471692709466</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="6" t="n">
+        <v>46265</v>
+      </c>
+      <c r="B66" s="5" t="n">
+        <v>99346.32347202346</v>
+      </c>
+      <c r="C66" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D66" s="4" t="n">
+        <v>-0.006536765279765322</v>
+      </c>
+      <c r="E66" s="5" t="n">
+        <v>14334.099609375</v>
+      </c>
+      <c r="F66" s="4" t="n">
+        <v>0.04597924761930816</v>
+      </c>
+      <c r="G66" s="4" t="n">
+        <v>-0.05251601289907348</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G65"/>
+  <autoFilter ref="A1:G66"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/reports/latest_one_month_follow_up.xlsx
+++ b/reports/latest_one_month_follow_up.xlsx
@@ -15,7 +15,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'TAKIP_OZETI'!$A$1:$B$19</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'POZISYONLAR'!$A$1:$H$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'GUNLUK_TAKIP'!$A$1:$G$66</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'GUNLUK_TAKIP'!$A$1:$G$67</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'NOTLAR'!$A$1:$A$7</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -475,7 +475,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
     </row>
@@ -546,7 +546,7 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>14334.099609375</v>
+        <v>14229</v>
       </c>
     </row>
     <row r="9">
@@ -603,7 +603,7 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
     </row>
@@ -627,7 +627,7 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>-0.006536765279765544</v>
+        <v>-0.02249164365583856</v>
       </c>
     </row>
     <row r="17">
@@ -648,7 +648,7 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>0.04597924761930816</v>
+        <v>0.03830998248686512</v>
       </c>
     </row>
     <row r="18">
@@ -658,7 +658,7 @@
         </is>
       </c>
       <c r="B18" s="3" t="n">
-        <v>-0.05251601289907371</v>
+        <v>-0.06080162614270368</v>
       </c>
     </row>
     <row r="19">
@@ -692,7 +692,7 @@
     <col width="20" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
     <col width="19" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="21" customWidth="1" min="5" max="5"/>
     <col width="19" customWidth="1" min="6" max="6"/>
     <col width="19" customWidth="1" min="7" max="7"/>
     <col width="20" customWidth="1" min="8" max="8"/>
@@ -753,19 +753,19 @@
         <v>40</v>
       </c>
       <c r="D2" s="5" t="n">
-        <v>39.15999984741211</v>
+        <v>38.77999877929688</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>-0.02100000381469724</v>
+        <v>-0.0305000305175781</v>
       </c>
       <c r="F2" s="5" t="n">
         <v>33333.33333333333</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>32633.33320617675</v>
+        <v>32316.66564941406</v>
       </c>
       <c r="H2" s="5" t="n">
-        <v>-700.0001271565743</v>
+        <v>-1016.66768391927</v>
       </c>
     </row>
     <row r="3">
@@ -781,19 +781,19 @@
         <v>45.5</v>
       </c>
       <c r="D3" s="5" t="n">
-        <v>40.13999938964844</v>
+        <v>39.61999893188477</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>-0.1178022112165179</v>
+        <v>-0.1292307927058294</v>
       </c>
       <c r="F3" s="5" t="n">
         <v>33333.33333333333</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>29406.5929594494</v>
+        <v>29025.64024313902</v>
       </c>
       <c r="H3" s="5" t="n">
-        <v>-3926.740373883931</v>
+        <v>-4307.693090194312</v>
       </c>
     </row>
     <row r="4">
@@ -809,19 +809,19 @@
         <v>371.25</v>
       </c>
       <c r="D4" s="5" t="n">
-        <v>415.5</v>
+        <v>405.5</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>0.1191919191919193</v>
+        <v>0.09225589225589226</v>
       </c>
       <c r="F4" s="5" t="n">
         <v>33333.33333333333</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>37306.3973063973</v>
+        <v>36408.52974186307</v>
       </c>
       <c r="H4" s="5" t="n">
-        <v>3973.063973063974</v>
+        <v>3075.196408529744</v>
       </c>
     </row>
   </sheetData>
@@ -836,7 +836,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G66"/>
+  <dimension ref="A1:G67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -2348,13 +2348,13 @@
         <v>-0.006536765279765322</v>
       </c>
       <c r="E65" s="5" t="n">
-        <v>14641.599609375</v>
+        <v>14575.5</v>
       </c>
       <c r="F65" s="4" t="n">
-        <v>0.06841795164732933</v>
+        <v>0.0635945709281962</v>
       </c>
       <c r="G65" s="4" t="n">
-        <v>-0.07495471692709466</v>
+        <v>-0.07013133620796153</v>
       </c>
     </row>
     <row r="66">
@@ -2362,13 +2362,13 @@
         <v>46265</v>
       </c>
       <c r="B66" s="5" t="n">
-        <v>99346.32347202346</v>
+        <v>97750.83563441614</v>
       </c>
       <c r="C66" s="4" t="n">
-        <v>0</v>
+        <v>-0.01605985789757602</v>
       </c>
       <c r="D66" s="4" t="n">
-        <v>-0.006536765279765322</v>
+        <v>-0.02249164365583856</v>
       </c>
       <c r="E66" s="5" t="n">
         <v>14334.099609375</v>
@@ -2377,11 +2377,34 @@
         <v>0.04597924761930816</v>
       </c>
       <c r="G66" s="4" t="n">
-        <v>-0.05251601289907348</v>
+        <v>-0.06847089127514672</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="6" t="n">
+        <v>46266</v>
+      </c>
+      <c r="B67" s="5" t="n">
+        <v>97750.83563441614</v>
+      </c>
+      <c r="C67" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D67" s="4" t="n">
+        <v>-0.02249164365583856</v>
+      </c>
+      <c r="E67" s="5" t="n">
+        <v>14229</v>
+      </c>
+      <c r="F67" s="4" t="n">
+        <v>0.03830998248686512</v>
+      </c>
+      <c r="G67" s="4" t="n">
+        <v>-0.06080162614270368</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G66"/>
+  <autoFilter ref="A1:G67"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/reports/latest_one_month_follow_up.xlsx
+++ b/reports/latest_one_month_follow_up.xlsx
@@ -15,7 +15,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'TAKIP_OZETI'!$A$1:$B$19</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'POZISYONLAR'!$A$1:$H$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'GUNLUK_TAKIP'!$A$1:$G$67</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'GUNLUK_TAKIP'!$A$1:$G$68</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'NOTLAR'!$A$1:$A$7</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -475,7 +475,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
     </row>
@@ -546,7 +546,7 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>14229</v>
+        <v>14050.599609375</v>
       </c>
     </row>
     <row r="9">
@@ -603,7 +603,7 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
     </row>
@@ -627,7 +627,7 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>-0.02249164365583856</v>
+        <v>-0.02879538374050317</v>
       </c>
     </row>
     <row r="17">
@@ -648,7 +648,7 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>0.03830998248686512</v>
+        <v>0.02529185707640114</v>
       </c>
     </row>
     <row r="18">
@@ -658,7 +658,7 @@
         </is>
       </c>
       <c r="B18" s="3" t="n">
-        <v>-0.06080162614270368</v>
+        <v>-0.0540872408169043</v>
       </c>
     </row>
     <row r="19">
@@ -692,7 +692,7 @@
     <col width="20" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
     <col width="19" customWidth="1" min="4" max="4"/>
-    <col width="21" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
     <col width="19" customWidth="1" min="6" max="6"/>
     <col width="19" customWidth="1" min="7" max="7"/>
     <col width="20" customWidth="1" min="8" max="8"/>
@@ -753,19 +753,19 @@
         <v>40</v>
       </c>
       <c r="D2" s="5" t="n">
-        <v>38.77999877929688</v>
+        <v>37.77999877929688</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>-0.0305000305175781</v>
+        <v>-0.05550003051757812</v>
       </c>
       <c r="F2" s="5" t="n">
         <v>33333.33333333333</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>32316.66564941406</v>
+        <v>31483.33231608072</v>
       </c>
       <c r="H2" s="5" t="n">
-        <v>-1016.66768391927</v>
+        <v>-1850.001017252605</v>
       </c>
     </row>
     <row r="3">
@@ -781,19 +781,19 @@
         <v>45.5</v>
       </c>
       <c r="D3" s="5" t="n">
-        <v>39.61999893188477</v>
+        <v>39.56000137329102</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>-0.1292307927058294</v>
+        <v>-0.1305494203672304</v>
       </c>
       <c r="F3" s="5" t="n">
         <v>33333.33333333333</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>29025.64024313902</v>
+        <v>28981.68598775898</v>
       </c>
       <c r="H3" s="5" t="n">
-        <v>-4307.693090194312</v>
+        <v>-4351.647345574347</v>
       </c>
     </row>
     <row r="4">
@@ -809,19 +809,19 @@
         <v>371.25</v>
       </c>
       <c r="D4" s="5" t="n">
-        <v>405.5</v>
+        <v>408.25</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>0.09225589225589226</v>
+        <v>0.09966329966329956</v>
       </c>
       <c r="F4" s="5" t="n">
         <v>33333.33333333333</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>36408.52974186307</v>
+        <v>36655.44332210998</v>
       </c>
       <c r="H4" s="5" t="n">
-        <v>3075.196408529744</v>
+        <v>3322.109988776654</v>
       </c>
     </row>
   </sheetData>
@@ -836,7 +836,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G67"/>
+  <dimension ref="A1:G68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -2348,13 +2348,13 @@
         <v>-0.006536765279765322</v>
       </c>
       <c r="E65" s="5" t="n">
-        <v>14575.5</v>
+        <v>14641.599609375</v>
       </c>
       <c r="F65" s="4" t="n">
-        <v>0.0635945709281962</v>
+        <v>0.06841795164732933</v>
       </c>
       <c r="G65" s="4" t="n">
-        <v>-0.07013133620796153</v>
+        <v>-0.07495471692709466</v>
       </c>
     </row>
     <row r="66">
@@ -2385,13 +2385,13 @@
         <v>46266</v>
       </c>
       <c r="B67" s="5" t="n">
-        <v>97750.83563441614</v>
+        <v>97120.4616259497</v>
       </c>
       <c r="C67" s="4" t="n">
-        <v>0</v>
+        <v>-0.006448783832641802</v>
       </c>
       <c r="D67" s="4" t="n">
-        <v>-0.02249164365583856</v>
+        <v>-0.02879538374050306</v>
       </c>
       <c r="E67" s="5" t="n">
         <v>14229</v>
@@ -2400,11 +2400,34 @@
         <v>0.03830998248686512</v>
       </c>
       <c r="G67" s="4" t="n">
-        <v>-0.06080162614270368</v>
+        <v>-0.06710536622736818</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="6" t="n">
+        <v>46267</v>
+      </c>
+      <c r="B68" s="5" t="n">
+        <v>97120.4616259497</v>
+      </c>
+      <c r="C68" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D68" s="4" t="n">
+        <v>-0.02879538374050306</v>
+      </c>
+      <c r="E68" s="5" t="n">
+        <v>14050.599609375</v>
+      </c>
+      <c r="F68" s="4" t="n">
+        <v>0.02529185707640114</v>
+      </c>
+      <c r="G68" s="4" t="n">
+        <v>-0.05408724081690419</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G67"/>
+  <autoFilter ref="A1:G68"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/reports/latest_one_month_follow_up.xlsx
+++ b/reports/latest_one_month_follow_up.xlsx
@@ -15,7 +15,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'TAKIP_OZETI'!$A$1:$B$19</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'POZISYONLAR'!$A$1:$H$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'GUNLUK_TAKIP'!$A$1:$G$68</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'GUNLUK_TAKIP'!$A$1:$G$69</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'NOTLAR'!$A$1:$A$7</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -475,7 +475,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
     </row>
@@ -546,7 +546,7 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>14050.599609375</v>
+        <v>13932.5</v>
       </c>
     </row>
     <row r="9">
@@ -603,7 +603,7 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
     </row>
@@ -627,7 +627,7 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>-0.02879538374050317</v>
+        <v>-0.03546110602200647</v>
       </c>
     </row>
     <row r="17">
@@ -648,7 +648,7 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>0.02529185707640114</v>
+        <v>0.01667396380618791</v>
       </c>
     </row>
     <row r="18">
@@ -658,7 +658,7 @@
         </is>
       </c>
       <c r="B18" s="3" t="n">
-        <v>-0.0540872408169043</v>
+        <v>-0.05213506982819438</v>
       </c>
     </row>
     <row r="19">
@@ -753,19 +753,19 @@
         <v>40</v>
       </c>
       <c r="D2" s="5" t="n">
-        <v>37.77999877929688</v>
+        <v>37.59999847412109</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>-0.05550003051757812</v>
+        <v>-0.06000003814697263</v>
       </c>
       <c r="F2" s="5" t="n">
         <v>33333.33333333333</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>31483.33231608072</v>
+        <v>31333.33206176757</v>
       </c>
       <c r="H2" s="5" t="n">
-        <v>-1850.001017252605</v>
+        <v>-2000.001271565754</v>
       </c>
     </row>
     <row r="3">
@@ -781,19 +781,19 @@
         <v>45.5</v>
       </c>
       <c r="D3" s="5" t="n">
-        <v>39.56000137329102</v>
+        <v>39.09999847412109</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>-0.1305494203672304</v>
+        <v>-0.1406593741951409</v>
       </c>
       <c r="F3" s="5" t="n">
         <v>33333.33333333333</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>28981.68598775898</v>
+        <v>28644.68752682863</v>
       </c>
       <c r="H3" s="5" t="n">
-        <v>-4351.647345574347</v>
+        <v>-4688.645806504694</v>
       </c>
     </row>
     <row r="4">
@@ -809,19 +809,19 @@
         <v>371.25</v>
       </c>
       <c r="D4" s="5" t="n">
-        <v>408.25</v>
+        <v>406.25</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>0.09966329966329956</v>
+        <v>0.09427609427609429</v>
       </c>
       <c r="F4" s="5" t="n">
         <v>33333.33333333333</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>36655.44332210998</v>
+        <v>36475.86980920314</v>
       </c>
       <c r="H4" s="5" t="n">
-        <v>3322.109988776654</v>
+        <v>3142.536475869812</v>
       </c>
     </row>
   </sheetData>
@@ -836,7 +836,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G68"/>
+  <dimension ref="A1:G69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -2408,13 +2408,13 @@
         <v>46267</v>
       </c>
       <c r="B68" s="5" t="n">
-        <v>97120.4616259497</v>
+        <v>96453.88939779936</v>
       </c>
       <c r="C68" s="4" t="n">
-        <v>0</v>
+        <v>-0.006863355229071888</v>
       </c>
       <c r="D68" s="4" t="n">
-        <v>-0.02879538374050306</v>
+        <v>-0.03546110602200647</v>
       </c>
       <c r="E68" s="5" t="n">
         <v>14050.599609375</v>
@@ -2423,11 +2423,34 @@
         <v>0.02529185707640114</v>
       </c>
       <c r="G68" s="4" t="n">
-        <v>-0.05408724081690419</v>
+        <v>-0.06075296309840761</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="6" t="n">
+        <v>46268</v>
+      </c>
+      <c r="B69" s="5" t="n">
+        <v>96453.88939779936</v>
+      </c>
+      <c r="C69" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D69" s="4" t="n">
+        <v>-0.03546110602200647</v>
+      </c>
+      <c r="E69" s="5" t="n">
+        <v>13932.5</v>
+      </c>
+      <c r="F69" s="4" t="n">
+        <v>0.01667396380618791</v>
+      </c>
+      <c r="G69" s="4" t="n">
+        <v>-0.05213506982819438</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G68"/>
+  <autoFilter ref="A1:G69"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/reports/latest_one_month_follow_up.xlsx
+++ b/reports/latest_one_month_follow_up.xlsx
@@ -15,7 +15,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'TAKIP_OZETI'!$A$1:$B$19</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'POZISYONLAR'!$A$1:$H$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'GUNLUK_TAKIP'!$A$1:$G$69</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'GUNLUK_TAKIP'!$A$1:$G$70</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'NOTLAR'!$A$1:$A$7</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -475,7 +475,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
     </row>
@@ -546,7 +546,7 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>13932.5</v>
+        <v>14012.400390625</v>
       </c>
     </row>
     <row r="9">
@@ -603,7 +603,7 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
     </row>
@@ -627,7 +627,7 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>-0.03546110602200647</v>
+        <v>-0.04120184854069042</v>
       </c>
     </row>
     <row r="17">
@@ -648,7 +648,7 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>0.01667396380618791</v>
+        <v>0.02250440678816412</v>
       </c>
     </row>
     <row r="18">
@@ -658,7 +658,7 @@
         </is>
       </c>
       <c r="B18" s="3" t="n">
-        <v>-0.05213506982819438</v>
+        <v>-0.06370625532885454</v>
       </c>
     </row>
     <row r="19">
@@ -753,19 +753,19 @@
         <v>40</v>
       </c>
       <c r="D2" s="5" t="n">
-        <v>37.59999847412109</v>
+        <v>36.58000183105469</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>-0.06000003814697263</v>
+        <v>-0.08549995422363277</v>
       </c>
       <c r="F2" s="5" t="n">
         <v>33333.33333333333</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>31333.33206176757</v>
+        <v>30483.33485921224</v>
       </c>
       <c r="H2" s="5" t="n">
-        <v>-2000.001271565754</v>
+        <v>-2849.99847412109</v>
       </c>
     </row>
     <row r="3">
@@ -781,19 +781,19 @@
         <v>45.5</v>
       </c>
       <c r="D3" s="5" t="n">
-        <v>39.09999847412109</v>
+        <v>38.68000030517578</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>-0.1406593741951409</v>
+        <v>-0.1498901031829498</v>
       </c>
       <c r="F3" s="5" t="n">
         <v>33333.33333333333</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>28644.68752682863</v>
+        <v>28336.99656056834</v>
       </c>
       <c r="H3" s="5" t="n">
-        <v>-4688.645806504694</v>
+        <v>-4996.336772764993</v>
       </c>
     </row>
     <row r="4">
@@ -809,19 +809,19 @@
         <v>371.25</v>
       </c>
       <c r="D4" s="5" t="n">
-        <v>406.25</v>
+        <v>412.75</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>0.09427609427609429</v>
+        <v>0.1117845117845118</v>
       </c>
       <c r="F4" s="5" t="n">
         <v>33333.33333333333</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>36475.86980920314</v>
+        <v>37059.48372615039</v>
       </c>
       <c r="H4" s="5" t="n">
-        <v>3142.536475869812</v>
+        <v>3726.150392817057</v>
       </c>
     </row>
   </sheetData>
@@ -836,7 +836,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G69"/>
+  <dimension ref="A1:G70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -2431,13 +2431,13 @@
         <v>46268</v>
       </c>
       <c r="B69" s="5" t="n">
-        <v>96453.88939779936</v>
+        <v>95879.81514593097</v>
       </c>
       <c r="C69" s="4" t="n">
-        <v>0</v>
+        <v>-0.005951799926913859</v>
       </c>
       <c r="D69" s="4" t="n">
-        <v>-0.03546110602200647</v>
+        <v>-0.04120184854069031</v>
       </c>
       <c r="E69" s="5" t="n">
         <v>13932.5</v>
@@ -2446,11 +2446,34 @@
         <v>0.01667396380618791</v>
       </c>
       <c r="G69" s="4" t="n">
-        <v>-0.05213506982819438</v>
+        <v>-0.05787581234687822</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="6" t="n">
+        <v>46269</v>
+      </c>
+      <c r="B70" s="5" t="n">
+        <v>95879.81514593097</v>
+      </c>
+      <c r="C70" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D70" s="4" t="n">
+        <v>-0.04120184854069031</v>
+      </c>
+      <c r="E70" s="5" t="n">
+        <v>14012.400390625</v>
+      </c>
+      <c r="F70" s="4" t="n">
+        <v>0.02250440678816412</v>
+      </c>
+      <c r="G70" s="4" t="n">
+        <v>-0.06370625532885443</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G69"/>
+  <autoFilter ref="A1:G70"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/reports/latest_one_month_follow_up.xlsx
+++ b/reports/latest_one_month_follow_up.xlsx
@@ -1215,10 +1215,10 @@
         <v>101665.535802718</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>-0.01517965889001283</v>
+        <v>-0.0151796588900126</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>0.01665535802718021</v>
+        <v>0.01665535802718043</v>
       </c>
       <c r="E16" s="5" t="n">
         <v>14734.5</v>
@@ -1227,7 +1227,7 @@
         <v>0.07519702276707529</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>-0.05854166473989508</v>
+        <v>-0.05854166473989486</v>
       </c>
     </row>
     <row r="17">
@@ -1238,7 +1238,7 @@
         <v>101579.9132001645</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>-0.000842198901303659</v>
+        <v>-0.0008421989013038811</v>
       </c>
       <c r="D17" s="4" t="n">
         <v>0.01579913200164529</v>
@@ -1281,13 +1281,13 @@
         <v>46197</v>
       </c>
       <c r="B19" s="5" t="n">
-        <v>99903.87102493743</v>
+        <v>99903.87102493741</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>-0.007105427940044096</v>
+        <v>-0.007105427940044318</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>-0.0009612897506257045</v>
+        <v>-0.0009612897506259266</v>
       </c>
       <c r="E19" s="5" t="n">
         <v>14331.2001953125</v>
@@ -1296,7 +1296,7 @@
         <v>0.04576767332986709</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>-0.04672896308049279</v>
+        <v>-0.04672896308049301</v>
       </c>
     </row>
     <row r="20">
@@ -1307,7 +1307,7 @@
         <v>99725.18443384963</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>-0.001788585259556053</v>
+        <v>-0.00178858525955583</v>
       </c>
       <c r="D20" s="4" t="n">
         <v>-0.00274815566150366</v>
@@ -1353,10 +1353,10 @@
         <v>100567.2965303391</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>-0.01333614376284464</v>
+        <v>-0.01333614376284487</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>0.00567296530339112</v>
+        <v>0.005672965303390898</v>
       </c>
       <c r="E22" s="5" t="n">
         <v>14183.2001953125</v>
@@ -1365,7 +1365,7 @@
         <v>0.03496790683833195</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>-0.02929494153494083</v>
+        <v>-0.02929494153494105</v>
       </c>
     </row>
     <row r="23">
@@ -1376,7 +1376,7 @@
         <v>98982.15764175884</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>-0.01576197176685634</v>
+        <v>-0.01576197176685612</v>
       </c>
       <c r="D23" s="4" t="n">
         <v>-0.01017842358241161</v>
@@ -1402,7 +1402,7 @@
         <v>0.003127667249263499</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>-0.007082591055235898</v>
+        <v>-0.007082591055236009</v>
       </c>
       <c r="E24" s="5" t="n">
         <v>14350.599609375</v>
@@ -1411,7 +1411,7 @@
         <v>0.0471832756403241</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>-0.05426586669555999</v>
+        <v>-0.05426586669556011</v>
       </c>
     </row>
     <row r="25">
@@ -1422,7 +1422,7 @@
         <v>98699.49739704847</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>-0.005964680366087549</v>
+        <v>-0.005964680366087438</v>
       </c>
       <c r="D25" s="4" t="n">
         <v>-0.01300502602951525</v>
@@ -1511,13 +1511,13 @@
         <v>46211</v>
       </c>
       <c r="B29" s="5" t="n">
-        <v>97511.54763463838</v>
+        <v>97511.54763463837</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>-0.02101826087704517</v>
+        <v>-0.02101826087704539</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>-0.02488452365361615</v>
+        <v>-0.02488452365361637</v>
       </c>
       <c r="E29" s="5" t="n">
         <v>14190</v>
@@ -1526,7 +1526,7 @@
         <v>0.03546409807355522</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>-0.06034862172717137</v>
+        <v>-0.06034862172717159</v>
       </c>
     </row>
     <row r="30">
@@ -1537,7 +1537,7 @@
         <v>97085.90440793287</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>-0.004365054570770743</v>
+        <v>-0.004365054570770521</v>
       </c>
       <c r="D30" s="4" t="n">
         <v>-0.02914095592067123</v>
@@ -1603,13 +1603,13 @@
         <v>46217</v>
       </c>
       <c r="B33" s="5" t="n">
-        <v>101364.3995699692</v>
+        <v>101364.3995699691</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>0.02123082912189456</v>
+        <v>0.02123082912189433</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>0.01364399569969166</v>
+        <v>0.01364399569969144</v>
       </c>
       <c r="E33" s="5" t="n">
         <v>14080</v>
@@ -1618,7 +1618,7 @@
         <v>0.02743724460011676</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>-0.0137932489004251</v>
+        <v>-0.01379324890042533</v>
       </c>
     </row>
     <row r="34">
@@ -1629,7 +1629,7 @@
         <v>105261.7030227777</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>0.03844844412182757</v>
+        <v>0.0384484441218278</v>
       </c>
       <c r="D34" s="4" t="n">
         <v>0.05261703022777731</v>
@@ -1675,10 +1675,10 @@
         <v>104848.7672438694</v>
       </c>
       <c r="C36" s="4" t="n">
-        <v>0.02469452791059856</v>
+        <v>0.02469452791059834</v>
       </c>
       <c r="D36" s="4" t="n">
-        <v>0.04848767243869423</v>
+        <v>0.04848767243869401</v>
       </c>
       <c r="E36" s="5" t="n">
         <v>14071</v>
@@ -1687,7 +1687,7 @@
         <v>0.02678050204319904</v>
       </c>
       <c r="G36" s="4" t="n">
-        <v>0.02170717039549519</v>
+        <v>0.02170717039549497</v>
       </c>
     </row>
     <row r="37">
@@ -1698,7 +1698,7 @@
         <v>102169.894507684</v>
       </c>
       <c r="C37" s="4" t="n">
-        <v>-0.02554987346636661</v>
+        <v>-0.02554987346636639</v>
       </c>
       <c r="D37" s="4" t="n">
         <v>0.02169894507684034</v>
@@ -2132,13 +2132,13 @@
         <v>46251</v>
       </c>
       <c r="B56" s="5" t="n">
-        <v>94222.89834801342</v>
+        <v>94222.8983480134</v>
       </c>
       <c r="C56" s="4" t="n">
-        <v>-0.009506854050161162</v>
+        <v>-0.009506854050161273</v>
       </c>
       <c r="D56" s="4" t="n">
-        <v>-0.05777101651986583</v>
+        <v>-0.05777101651986594</v>
       </c>
       <c r="E56" s="5" t="n">
         <v>14132.099609375</v>
@@ -2147,7 +2147,7 @@
         <v>0.03123902578626669</v>
       </c>
       <c r="G56" s="4" t="n">
-        <v>-0.08901004230613252</v>
+        <v>-0.08901004230613263</v>
       </c>
     </row>
     <row r="57">
@@ -2158,7 +2158,7 @@
         <v>95707.04281032382</v>
       </c>
       <c r="C57" s="4" t="n">
-        <v>0.01575142017844433</v>
+        <v>0.01575142017844455</v>
       </c>
       <c r="D57" s="4" t="n">
         <v>-0.04292957189676172</v>
@@ -2316,13 +2316,13 @@
         <v>46261</v>
       </c>
       <c r="B64" s="5" t="n">
-        <v>98649.26988175407</v>
+        <v>98649.26988175404</v>
       </c>
       <c r="C64" s="4" t="n">
-        <v>-0.006384731412490741</v>
+        <v>-0.006384731412490963</v>
       </c>
       <c r="D64" s="4" t="n">
-        <v>-0.01350730118245935</v>
+        <v>-0.01350730118245957</v>
       </c>
       <c r="E64" s="5" t="n">
         <v>14575.5</v>
@@ -2331,7 +2331,7 @@
         <v>0.0635945709281962</v>
       </c>
       <c r="G64" s="4" t="n">
-        <v>-0.07710187211065556</v>
+        <v>-0.07710187211065578</v>
       </c>
     </row>
     <row r="65">
@@ -2342,7 +2342,7 @@
         <v>99346.32347202346</v>
       </c>
       <c r="C65" s="4" t="n">
-        <v>0.007065978198368184</v>
+        <v>0.007065978198368406</v>
       </c>
       <c r="D65" s="4" t="n">
         <v>-0.006536765279765322</v>
@@ -2362,13 +2362,13 @@
         <v>46265</v>
       </c>
       <c r="B66" s="5" t="n">
-        <v>97750.83563441614</v>
+        <v>97750.83563441616</v>
       </c>
       <c r="C66" s="4" t="n">
-        <v>-0.01605985789757602</v>
+        <v>-0.01605985789757591</v>
       </c>
       <c r="D66" s="4" t="n">
-        <v>-0.02249164365583856</v>
+        <v>-0.02249164365583844</v>
       </c>
       <c r="E66" s="5" t="n">
         <v>14334.099609375</v>
@@ -2377,7 +2377,7 @@
         <v>0.04597924761930816</v>
       </c>
       <c r="G66" s="4" t="n">
-        <v>-0.06847089127514672</v>
+        <v>-0.06847089127514661</v>
       </c>
     </row>
     <row r="67">
@@ -2385,13 +2385,13 @@
         <v>46266</v>
       </c>
       <c r="B67" s="5" t="n">
-        <v>97120.4616259497</v>
+        <v>97120.46162594971</v>
       </c>
       <c r="C67" s="4" t="n">
         <v>-0.006448783832641802</v>
       </c>
       <c r="D67" s="4" t="n">
-        <v>-0.02879538374050306</v>
+        <v>-0.02879538374050294</v>
       </c>
       <c r="E67" s="5" t="n">
         <v>14229</v>
@@ -2400,7 +2400,7 @@
         <v>0.03830998248686512</v>
       </c>
       <c r="G67" s="4" t="n">
-        <v>-0.06710536622736818</v>
+        <v>-0.06710536622736807</v>
       </c>
     </row>
     <row r="68">
@@ -2411,7 +2411,7 @@
         <v>96453.88939779936</v>
       </c>
       <c r="C68" s="4" t="n">
-        <v>-0.006863355229071888</v>
+        <v>-0.006863355229071999</v>
       </c>
       <c r="D68" s="4" t="n">
         <v>-0.03546110602200647</v>

--- a/reports/latest_one_month_follow_up.xlsx
+++ b/reports/latest_one_month_follow_up.xlsx
@@ -15,7 +15,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'TAKIP_OZETI'!$A$1:$B$19</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'POZISYONLAR'!$A$1:$H$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'GUNLUK_TAKIP'!$A$1:$G$70</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'GUNLUK_TAKIP'!$A$1:$G$71</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'NOTLAR'!$A$1:$A$7</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -475,7 +475,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
     </row>
@@ -546,7 +546,7 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>14012.400390625</v>
+        <v>14151.599609375</v>
       </c>
     </row>
     <row r="9">
@@ -603,7 +603,7 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
     </row>
@@ -627,7 +627,7 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>-0.04120184854069042</v>
+        <v>-0.03041117397237836</v>
       </c>
     </row>
     <row r="17">
@@ -648,7 +648,7 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>0.02250440678816412</v>
+        <v>0.03266196799292187</v>
       </c>
     </row>
     <row r="18">
@@ -658,7 +658,7 @@
         </is>
       </c>
       <c r="B18" s="3" t="n">
-        <v>-0.06370625532885454</v>
+        <v>-0.06307314196530023</v>
       </c>
     </row>
     <row r="19">
@@ -753,19 +753,19 @@
         <v>40</v>
       </c>
       <c r="D2" s="5" t="n">
-        <v>36.58000183105469</v>
+        <v>37.20000076293945</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>-0.08549995422363277</v>
+        <v>-0.06999998092651372</v>
       </c>
       <c r="F2" s="5" t="n">
         <v>33333.33333333333</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>30483.33485921224</v>
+        <v>31000.00063578287</v>
       </c>
       <c r="H2" s="5" t="n">
-        <v>-2849.99847412109</v>
+        <v>-2333.332697550457</v>
       </c>
     </row>
     <row r="3">
@@ -781,19 +781,19 @@
         <v>45.5</v>
       </c>
       <c r="D3" s="5" t="n">
-        <v>38.68000030517578</v>
+        <v>39.08000183105469</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>-0.1498901031829498</v>
+        <v>-0.1410988608559409</v>
       </c>
       <c r="F3" s="5" t="n">
         <v>33333.33333333333</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>28336.99656056834</v>
+        <v>28630.03797146863</v>
       </c>
       <c r="H3" s="5" t="n">
-        <v>-4996.336772764993</v>
+        <v>-4703.295361864697</v>
       </c>
     </row>
     <row r="4">
@@ -809,19 +809,19 @@
         <v>371.25</v>
       </c>
       <c r="D4" s="5" t="n">
-        <v>412.75</v>
+        <v>415.75</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>0.1117845117845118</v>
+        <v>0.1198653198653199</v>
       </c>
       <c r="F4" s="5" t="n">
         <v>33333.33333333333</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>37059.48372615039</v>
+        <v>37328.84399551066</v>
       </c>
       <c r="H4" s="5" t="n">
-        <v>3726.150392817057</v>
+        <v>3995.51066217733</v>
       </c>
     </row>
   </sheetData>
@@ -836,7 +836,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G70"/>
+  <dimension ref="A1:G71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -1215,10 +1215,10 @@
         <v>101665.535802718</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>-0.0151796588900126</v>
+        <v>-0.01517965889001283</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>0.01665535802718043</v>
+        <v>0.01665535802718021</v>
       </c>
       <c r="E16" s="5" t="n">
         <v>14734.5</v>
@@ -1227,7 +1227,7 @@
         <v>0.07519702276707529</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>-0.05854166473989486</v>
+        <v>-0.05854166473989508</v>
       </c>
     </row>
     <row r="17">
@@ -1238,7 +1238,7 @@
         <v>101579.9132001645</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>-0.0008421989013038811</v>
+        <v>-0.000842198901303659</v>
       </c>
       <c r="D17" s="4" t="n">
         <v>0.01579913200164529</v>
@@ -1281,13 +1281,13 @@
         <v>46197</v>
       </c>
       <c r="B19" s="5" t="n">
-        <v>99903.87102493741</v>
+        <v>99903.87102493743</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>-0.007105427940044318</v>
+        <v>-0.007105427940044096</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>-0.0009612897506259266</v>
+        <v>-0.0009612897506257045</v>
       </c>
       <c r="E19" s="5" t="n">
         <v>14331.2001953125</v>
@@ -1296,7 +1296,7 @@
         <v>0.04576767332986709</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>-0.04672896308049301</v>
+        <v>-0.04672896308049279</v>
       </c>
     </row>
     <row r="20">
@@ -1307,7 +1307,7 @@
         <v>99725.18443384963</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>-0.00178858525955583</v>
+        <v>-0.001788585259556053</v>
       </c>
       <c r="D20" s="4" t="n">
         <v>-0.00274815566150366</v>
@@ -1353,10 +1353,10 @@
         <v>100567.2965303391</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>-0.01333614376284487</v>
+        <v>-0.01333614376284464</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>0.005672965303390898</v>
+        <v>0.00567296530339112</v>
       </c>
       <c r="E22" s="5" t="n">
         <v>14183.2001953125</v>
@@ -1365,7 +1365,7 @@
         <v>0.03496790683833195</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>-0.02929494153494105</v>
+        <v>-0.02929494153494083</v>
       </c>
     </row>
     <row r="23">
@@ -1376,7 +1376,7 @@
         <v>98982.15764175884</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>-0.01576197176685612</v>
+        <v>-0.01576197176685634</v>
       </c>
       <c r="D23" s="4" t="n">
         <v>-0.01017842358241161</v>
@@ -1402,7 +1402,7 @@
         <v>0.003127667249263499</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>-0.007082591055236009</v>
+        <v>-0.007082591055235898</v>
       </c>
       <c r="E24" s="5" t="n">
         <v>14350.599609375</v>
@@ -1411,7 +1411,7 @@
         <v>0.0471832756403241</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>-0.05426586669556011</v>
+        <v>-0.05426586669555999</v>
       </c>
     </row>
     <row r="25">
@@ -1422,7 +1422,7 @@
         <v>98699.49739704847</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>-0.005964680366087438</v>
+        <v>-0.005964680366087549</v>
       </c>
       <c r="D25" s="4" t="n">
         <v>-0.01300502602951525</v>
@@ -1511,13 +1511,13 @@
         <v>46211</v>
       </c>
       <c r="B29" s="5" t="n">
-        <v>97511.54763463837</v>
+        <v>97511.54763463838</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>-0.02101826087704539</v>
+        <v>-0.02101826087704517</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>-0.02488452365361637</v>
+        <v>-0.02488452365361615</v>
       </c>
       <c r="E29" s="5" t="n">
         <v>14190</v>
@@ -1526,7 +1526,7 @@
         <v>0.03546409807355522</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>-0.06034862172717159</v>
+        <v>-0.06034862172717137</v>
       </c>
     </row>
     <row r="30">
@@ -1537,7 +1537,7 @@
         <v>97085.90440793287</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>-0.004365054570770521</v>
+        <v>-0.004365054570770743</v>
       </c>
       <c r="D30" s="4" t="n">
         <v>-0.02914095592067123</v>
@@ -1603,13 +1603,13 @@
         <v>46217</v>
       </c>
       <c r="B33" s="5" t="n">
-        <v>101364.3995699691</v>
+        <v>101364.3995699692</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>0.02123082912189433</v>
+        <v>0.02123082912189456</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>0.01364399569969144</v>
+        <v>0.01364399569969166</v>
       </c>
       <c r="E33" s="5" t="n">
         <v>14080</v>
@@ -1618,7 +1618,7 @@
         <v>0.02743724460011676</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>-0.01379324890042533</v>
+        <v>-0.0137932489004251</v>
       </c>
     </row>
     <row r="34">
@@ -1629,7 +1629,7 @@
         <v>105261.7030227777</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>0.0384484441218278</v>
+        <v>0.03844844412182757</v>
       </c>
       <c r="D34" s="4" t="n">
         <v>0.05261703022777731</v>
@@ -1675,10 +1675,10 @@
         <v>104848.7672438694</v>
       </c>
       <c r="C36" s="4" t="n">
-        <v>0.02469452791059834</v>
+        <v>0.02469452791059856</v>
       </c>
       <c r="D36" s="4" t="n">
-        <v>0.04848767243869401</v>
+        <v>0.04848767243869423</v>
       </c>
       <c r="E36" s="5" t="n">
         <v>14071</v>
@@ -1687,7 +1687,7 @@
         <v>0.02678050204319904</v>
       </c>
       <c r="G36" s="4" t="n">
-        <v>0.02170717039549497</v>
+        <v>0.02170717039549519</v>
       </c>
     </row>
     <row r="37">
@@ -1698,7 +1698,7 @@
         <v>102169.894507684</v>
       </c>
       <c r="C37" s="4" t="n">
-        <v>-0.02554987346636639</v>
+        <v>-0.02554987346636661</v>
       </c>
       <c r="D37" s="4" t="n">
         <v>0.02169894507684034</v>
@@ -2132,13 +2132,13 @@
         <v>46251</v>
       </c>
       <c r="B56" s="5" t="n">
-        <v>94222.8983480134</v>
+        <v>94222.89834801342</v>
       </c>
       <c r="C56" s="4" t="n">
-        <v>-0.009506854050161273</v>
+        <v>-0.009506854050161162</v>
       </c>
       <c r="D56" s="4" t="n">
-        <v>-0.05777101651986594</v>
+        <v>-0.05777101651986583</v>
       </c>
       <c r="E56" s="5" t="n">
         <v>14132.099609375</v>
@@ -2147,7 +2147,7 @@
         <v>0.03123902578626669</v>
       </c>
       <c r="G56" s="4" t="n">
-        <v>-0.08901004230613263</v>
+        <v>-0.08901004230613252</v>
       </c>
     </row>
     <row r="57">
@@ -2158,7 +2158,7 @@
         <v>95707.04281032382</v>
       </c>
       <c r="C57" s="4" t="n">
-        <v>0.01575142017844455</v>
+        <v>0.01575142017844433</v>
       </c>
       <c r="D57" s="4" t="n">
         <v>-0.04292957189676172</v>
@@ -2316,13 +2316,13 @@
         <v>46261</v>
       </c>
       <c r="B64" s="5" t="n">
-        <v>98649.26988175404</v>
+        <v>98649.26988175407</v>
       </c>
       <c r="C64" s="4" t="n">
-        <v>-0.006384731412490963</v>
+        <v>-0.006384731412490741</v>
       </c>
       <c r="D64" s="4" t="n">
-        <v>-0.01350730118245957</v>
+        <v>-0.01350730118245935</v>
       </c>
       <c r="E64" s="5" t="n">
         <v>14575.5</v>
@@ -2331,7 +2331,7 @@
         <v>0.0635945709281962</v>
       </c>
       <c r="G64" s="4" t="n">
-        <v>-0.07710187211065578</v>
+        <v>-0.07710187211065556</v>
       </c>
     </row>
     <row r="65">
@@ -2342,7 +2342,7 @@
         <v>99346.32347202346</v>
       </c>
       <c r="C65" s="4" t="n">
-        <v>0.007065978198368406</v>
+        <v>0.007065978198368184</v>
       </c>
       <c r="D65" s="4" t="n">
         <v>-0.006536765279765322</v>
@@ -2362,13 +2362,13 @@
         <v>46265</v>
       </c>
       <c r="B66" s="5" t="n">
-        <v>97750.83563441616</v>
+        <v>97750.83563441614</v>
       </c>
       <c r="C66" s="4" t="n">
-        <v>-0.01605985789757591</v>
+        <v>-0.01605985789757602</v>
       </c>
       <c r="D66" s="4" t="n">
-        <v>-0.02249164365583844</v>
+        <v>-0.02249164365583856</v>
       </c>
       <c r="E66" s="5" t="n">
         <v>14334.099609375</v>
@@ -2377,7 +2377,7 @@
         <v>0.04597924761930816</v>
       </c>
       <c r="G66" s="4" t="n">
-        <v>-0.06847089127514661</v>
+        <v>-0.06847089127514672</v>
       </c>
     </row>
     <row r="67">
@@ -2385,13 +2385,13 @@
         <v>46266</v>
       </c>
       <c r="B67" s="5" t="n">
-        <v>97120.46162594971</v>
+        <v>97120.4616259497</v>
       </c>
       <c r="C67" s="4" t="n">
         <v>-0.006448783832641802</v>
       </c>
       <c r="D67" s="4" t="n">
-        <v>-0.02879538374050294</v>
+        <v>-0.02879538374050306</v>
       </c>
       <c r="E67" s="5" t="n">
         <v>14229</v>
@@ -2400,7 +2400,7 @@
         <v>0.03830998248686512</v>
       </c>
       <c r="G67" s="4" t="n">
-        <v>-0.06710536622736807</v>
+        <v>-0.06710536622736818</v>
       </c>
     </row>
     <row r="68">
@@ -2411,7 +2411,7 @@
         <v>96453.88939779936</v>
       </c>
       <c r="C68" s="4" t="n">
-        <v>-0.006863355229071999</v>
+        <v>-0.006863355229071888</v>
       </c>
       <c r="D68" s="4" t="n">
         <v>-0.03546110602200647</v>
@@ -2454,13 +2454,13 @@
         <v>46269</v>
       </c>
       <c r="B70" s="5" t="n">
-        <v>95879.81514593097</v>
+        <v>96958.88260276217</v>
       </c>
       <c r="C70" s="4" t="n">
-        <v>0</v>
+        <v>0.01125437564923182</v>
       </c>
       <c r="D70" s="4" t="n">
-        <v>-0.04120184854069031</v>
+        <v>-0.03041117397237825</v>
       </c>
       <c r="E70" s="5" t="n">
         <v>14012.400390625</v>
@@ -2469,11 +2469,34 @@
         <v>0.02250440678816412</v>
       </c>
       <c r="G70" s="4" t="n">
-        <v>-0.06370625532885443</v>
+        <v>-0.05291558076054237</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="6" t="n">
+        <v>46272</v>
+      </c>
+      <c r="B71" s="5" t="n">
+        <v>96958.88260276217</v>
+      </c>
+      <c r="C71" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D71" s="4" t="n">
+        <v>-0.03041117397237825</v>
+      </c>
+      <c r="E71" s="5" t="n">
+        <v>14151.599609375</v>
+      </c>
+      <c r="F71" s="4" t="n">
+        <v>0.03266196799292187</v>
+      </c>
+      <c r="G71" s="4" t="n">
+        <v>-0.06307314196530012</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G70"/>
+  <autoFilter ref="A1:G71"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/reports/latest_one_month_follow_up.xlsx
+++ b/reports/latest_one_month_follow_up.xlsx
@@ -15,7 +15,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'TAKIP_OZETI'!$A$1:$B$19</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'POZISYONLAR'!$A$1:$H$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'GUNLUK_TAKIP'!$A$1:$G$71</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'GUNLUK_TAKIP'!$A$1:$G$72</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'NOTLAR'!$A$1:$A$7</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -546,7 +546,7 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>14151.599609375</v>
+        <v>14405.2998046875</v>
       </c>
     </row>
     <row r="9">
@@ -627,7 +627,7 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
     </row>
@@ -648,7 +648,7 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>0.03266196799292187</v>
+        <v>0.05117482521070493</v>
       </c>
     </row>
     <row r="18">
@@ -658,7 +658,7 @@
         </is>
       </c>
       <c r="B18" s="3" t="n">
-        <v>-0.06307314196530023</v>
+        <v>-0.08158599918308329</v>
       </c>
     </row>
     <row r="19">
@@ -836,7 +836,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G71"/>
+  <dimension ref="A1:G72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -2495,8 +2495,31 @@
         <v>-0.06307314196530012</v>
       </c>
     </row>
+    <row r="72">
+      <c r="A72" s="6" t="n">
+        <v>46273</v>
+      </c>
+      <c r="B72" s="5" t="n">
+        <v>96958.88260276217</v>
+      </c>
+      <c r="C72" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D72" s="4" t="n">
+        <v>-0.03041117397237825</v>
+      </c>
+      <c r="E72" s="5" t="n">
+        <v>14405.2998046875</v>
+      </c>
+      <c r="F72" s="4" t="n">
+        <v>0.05117482521070493</v>
+      </c>
+      <c r="G72" s="4" t="n">
+        <v>-0.08158599918308318</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G71"/>
+  <autoFilter ref="A1:G72"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/reports/latest_one_month_follow_up.xlsx
+++ b/reports/latest_one_month_follow_up.xlsx
@@ -15,7 +15,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'TAKIP_OZETI'!$A$1:$B$19</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'POZISYONLAR'!$A$1:$H$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'GUNLUK_TAKIP'!$A$1:$G$72</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'GUNLUK_TAKIP'!$A$1:$G$73</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'NOTLAR'!$A$1:$A$7</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -475,7 +475,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-08</t>
         </is>
       </c>
     </row>
@@ -546,7 +546,7 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>14405.2998046875</v>
+        <v>14505.5</v>
       </c>
     </row>
     <row r="9">
@@ -603,7 +603,7 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-08</t>
         </is>
       </c>
     </row>
@@ -627,7 +627,7 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>-0.03041117397237836</v>
+        <v>0.04589761573645745</v>
       </c>
     </row>
     <row r="17">
@@ -648,7 +648,7 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>0.05117482521070493</v>
+        <v>0.05848657326328088</v>
       </c>
     </row>
     <row r="18">
@@ -658,7 +658,7 @@
         </is>
       </c>
       <c r="B18" s="3" t="n">
-        <v>-0.08158599918308329</v>
+        <v>-0.01258895752682343</v>
       </c>
     </row>
     <row r="19">
@@ -669,7 +669,7 @@
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>Zararda / BIST Altı</t>
+          <t>Karda / BIST Altı</t>
         </is>
       </c>
     </row>
@@ -692,7 +692,7 @@
     <col width="20" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
     <col width="19" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="23" customWidth="1" min="5" max="5"/>
     <col width="19" customWidth="1" min="6" max="6"/>
     <col width="19" customWidth="1" min="7" max="7"/>
     <col width="20" customWidth="1" min="8" max="8"/>
@@ -753,19 +753,19 @@
         <v>40</v>
       </c>
       <c r="D2" s="5" t="n">
-        <v>37.20000076293945</v>
+        <v>39.91999816894531</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>-0.06999998092651372</v>
+        <v>-0.002000045776367143</v>
       </c>
       <c r="F2" s="5" t="n">
         <v>33333.33333333333</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>31000.00063578287</v>
+        <v>33266.66514078776</v>
       </c>
       <c r="H2" s="5" t="n">
-        <v>-2333.332697550457</v>
+        <v>-66.66819254557049</v>
       </c>
     </row>
     <row r="3">
@@ -781,19 +781,19 @@
         <v>45.5</v>
       </c>
       <c r="D3" s="5" t="n">
-        <v>39.08000183105469</v>
+        <v>45.81999969482422</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>-0.1410988608559409</v>
+        <v>0.007032960325807025</v>
       </c>
       <c r="F3" s="5" t="n">
         <v>33333.33333333333</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>28630.03797146863</v>
+        <v>33567.76534419356</v>
       </c>
       <c r="H3" s="5" t="n">
-        <v>-4703.295361864697</v>
+        <v>234.4320108602333</v>
       </c>
     </row>
     <row r="4">
@@ -809,19 +809,19 @@
         <v>371.25</v>
       </c>
       <c r="D4" s="5" t="n">
-        <v>415.75</v>
+        <v>420.5</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>0.1198653198653199</v>
+        <v>0.1326599326599327</v>
       </c>
       <c r="F4" s="5" t="n">
         <v>33333.33333333333</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>37328.84399551066</v>
+        <v>37755.33108866442</v>
       </c>
       <c r="H4" s="5" t="n">
-        <v>3995.51066217733</v>
+        <v>4421.997755331089</v>
       </c>
     </row>
   </sheetData>
@@ -836,7 +836,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G72"/>
+  <dimension ref="A1:G73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -2500,13 +2500,13 @@
         <v>46273</v>
       </c>
       <c r="B72" s="5" t="n">
-        <v>96958.88260276217</v>
+        <v>104589.7615736458</v>
       </c>
       <c r="C72" s="4" t="n">
-        <v>0</v>
+        <v>0.07870221650704323</v>
       </c>
       <c r="D72" s="4" t="n">
-        <v>-0.03041117397237825</v>
+        <v>0.04589761573645745</v>
       </c>
       <c r="E72" s="5" t="n">
         <v>14405.2998046875</v>
@@ -2515,11 +2515,34 @@
         <v>0.05117482521070493</v>
       </c>
       <c r="G72" s="4" t="n">
-        <v>-0.08158599918308318</v>
+        <v>-0.00527720947424748</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="6" t="n">
+        <v>46274</v>
+      </c>
+      <c r="B73" s="5" t="n">
+        <v>104589.7615736458</v>
+      </c>
+      <c r="C73" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D73" s="4" t="n">
+        <v>0.04589761573645745</v>
+      </c>
+      <c r="E73" s="5" t="n">
+        <v>14505.5</v>
+      </c>
+      <c r="F73" s="4" t="n">
+        <v>0.05848657326328088</v>
+      </c>
+      <c r="G73" s="4" t="n">
+        <v>-0.01258895752682343</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G72"/>
+  <autoFilter ref="A1:G73"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/reports/latest_one_month_follow_up.xlsx
+++ b/reports/latest_one_month_follow_up.xlsx
@@ -15,7 +15,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'TAKIP_OZETI'!$A$1:$B$19</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'POZISYONLAR'!$A$1:$H$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'GUNLUK_TAKIP'!$A$1:$G$73</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'GUNLUK_TAKIP'!$A$1:$G$74</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'NOTLAR'!$A$1:$A$7</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -475,7 +475,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
     </row>
@@ -546,7 +546,7 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>14505.5</v>
+        <v>14393.900390625</v>
       </c>
     </row>
     <row r="9">
@@ -603,7 +603,7 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
     </row>
@@ -627,7 +627,7 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>0.04589761573645745</v>
+        <v>0.03814975887996819</v>
       </c>
     </row>
     <row r="17">
@@ -648,7 +648,7 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>0.05848657326328088</v>
+        <v>0.05034299406195264</v>
       </c>
     </row>
     <row r="18">
@@ -658,7 +658,7 @@
         </is>
       </c>
       <c r="B18" s="3" t="n">
-        <v>-0.01258895752682343</v>
+        <v>-0.01219323518198445</v>
       </c>
     </row>
     <row r="19">
@@ -692,7 +692,7 @@
     <col width="20" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
     <col width="19" customWidth="1" min="4" max="4"/>
-    <col width="23" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
     <col width="19" customWidth="1" min="6" max="6"/>
     <col width="19" customWidth="1" min="7" max="7"/>
     <col width="20" customWidth="1" min="8" max="8"/>
@@ -753,19 +753,19 @@
         <v>40</v>
       </c>
       <c r="D2" s="5" t="n">
-        <v>39.91999816894531</v>
+        <v>39.08000183105469</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>-0.002000045776367143</v>
+        <v>-0.02299995422363277</v>
       </c>
       <c r="F2" s="5" t="n">
         <v>33333.33333333333</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>33266.66514078776</v>
+        <v>32566.66819254557</v>
       </c>
       <c r="H2" s="5" t="n">
-        <v>-66.66819254557049</v>
+        <v>-766.665140787758</v>
       </c>
     </row>
     <row r="3">
@@ -781,19 +781,19 @@
         <v>45.5</v>
       </c>
       <c r="D3" s="5" t="n">
-        <v>45.81999969482422</v>
+        <v>44.86000061035156</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>0.007032960325807025</v>
+        <v>-0.01406592065161405</v>
       </c>
       <c r="F3" s="5" t="n">
         <v>33333.33333333333</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>33567.76534419356</v>
+        <v>32864.46931161286</v>
       </c>
       <c r="H3" s="5" t="n">
-        <v>234.4320108602333</v>
+        <v>-468.8640217204666</v>
       </c>
     </row>
     <row r="4">
@@ -809,19 +809,19 @@
         <v>371.25</v>
       </c>
       <c r="D4" s="5" t="n">
-        <v>420.5</v>
+        <v>427.5</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>0.1326599326599327</v>
+        <v>0.1515151515151516</v>
       </c>
       <c r="F4" s="5" t="n">
         <v>33333.33333333333</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>37755.33108866442</v>
+        <v>38383.83838383838</v>
       </c>
       <c r="H4" s="5" t="n">
-        <v>4421.997755331089</v>
+        <v>5050.505050505053</v>
       </c>
     </row>
   </sheetData>
@@ -836,7 +836,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G73"/>
+  <dimension ref="A1:G74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -2523,13 +2523,13 @@
         <v>46274</v>
       </c>
       <c r="B73" s="5" t="n">
-        <v>104589.7615736458</v>
+        <v>103814.9758879968</v>
       </c>
       <c r="C73" s="4" t="n">
-        <v>0</v>
+        <v>-0.007407854019280569</v>
       </c>
       <c r="D73" s="4" t="n">
-        <v>0.04589761573645745</v>
+        <v>0.03814975887996819</v>
       </c>
       <c r="E73" s="5" t="n">
         <v>14505.5</v>
@@ -2538,11 +2538,34 @@
         <v>0.05848657326328088</v>
       </c>
       <c r="G73" s="4" t="n">
-        <v>-0.01258895752682343</v>
+        <v>-0.0203368143833127</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="6" t="n">
+        <v>46275</v>
+      </c>
+      <c r="B74" s="5" t="n">
+        <v>103814.9758879968</v>
+      </c>
+      <c r="C74" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D74" s="4" t="n">
+        <v>0.03814975887996819</v>
+      </c>
+      <c r="E74" s="5" t="n">
+        <v>14393.900390625</v>
+      </c>
+      <c r="F74" s="4" t="n">
+        <v>0.05034299406195264</v>
+      </c>
+      <c r="G74" s="4" t="n">
+        <v>-0.01219323518198445</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G73"/>
+  <autoFilter ref="A1:G74"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/reports/latest_one_month_follow_up.xlsx
+++ b/reports/latest_one_month_follow_up.xlsx
@@ -15,7 +15,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'TAKIP_OZETI'!$A$1:$B$19</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'POZISYONLAR'!$A$1:$H$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'GUNLUK_TAKIP'!$A$1:$G$74</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'GUNLUK_TAKIP'!$A$1:$G$75</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'NOTLAR'!$A$1:$A$7</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -475,7 +475,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
     </row>
@@ -546,7 +546,7 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>14393.900390625</v>
+        <v>14467.2998046875</v>
       </c>
     </row>
     <row r="9">
@@ -603,7 +603,7 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
     </row>
@@ -627,7 +627,7 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>0.03814975887996819</v>
+        <v>0.03370027511297802</v>
       </c>
     </row>
     <row r="17">
@@ -648,7 +648,7 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>0.05034299406195264</v>
+        <v>0.05569905171391554</v>
       </c>
     </row>
     <row r="18">
@@ -658,7 +658,7 @@
         </is>
       </c>
       <c r="B18" s="3" t="n">
-        <v>-0.01219323518198445</v>
+        <v>-0.02199877660093752</v>
       </c>
     </row>
     <row r="19">
@@ -753,19 +753,19 @@
         <v>40</v>
       </c>
       <c r="D2" s="5" t="n">
-        <v>39.08000183105469</v>
+        <v>38.97999954223633</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>-0.02299995422363277</v>
+        <v>-0.02550001144409175</v>
       </c>
       <c r="F2" s="5" t="n">
         <v>33333.33333333333</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>32566.66819254557</v>
+        <v>32483.3329518636</v>
       </c>
       <c r="H2" s="5" t="n">
-        <v>-766.665140787758</v>
+        <v>-850.0003814697266</v>
       </c>
     </row>
     <row r="3">
@@ -781,19 +781,19 @@
         <v>45.5</v>
       </c>
       <c r="D3" s="5" t="n">
-        <v>44.86000061035156</v>
+        <v>44.06000137329102</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>-0.01406592065161405</v>
+        <v>-0.0316483214661315</v>
       </c>
       <c r="F3" s="5" t="n">
         <v>33333.33333333333</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>32864.46931161286</v>
+        <v>32278.38928446228</v>
       </c>
       <c r="H3" s="5" t="n">
-        <v>-468.8640217204666</v>
+        <v>-1054.94404887105</v>
       </c>
     </row>
     <row r="4">
@@ -809,19 +809,19 @@
         <v>371.25</v>
       </c>
       <c r="D4" s="5" t="n">
-        <v>427.5</v>
+        <v>430</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>0.1515151515151516</v>
+        <v>0.1582491582491583</v>
       </c>
       <c r="F4" s="5" t="n">
         <v>33333.33333333333</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>38383.83838383838</v>
+        <v>38608.30527497194</v>
       </c>
       <c r="H4" s="5" t="n">
-        <v>5050.505050505053</v>
+        <v>5274.971941638607</v>
       </c>
     </row>
   </sheetData>
@@ -836,7 +836,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G74"/>
+  <dimension ref="A1:G75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -2546,13 +2546,13 @@
         <v>46275</v>
       </c>
       <c r="B74" s="5" t="n">
-        <v>103814.9758879968</v>
+        <v>103370.0275112978</v>
       </c>
       <c r="C74" s="4" t="n">
-        <v>0</v>
+        <v>-0.004285974859533193</v>
       </c>
       <c r="D74" s="4" t="n">
-        <v>0.03814975887996819</v>
+        <v>0.03370027511297824</v>
       </c>
       <c r="E74" s="5" t="n">
         <v>14393.900390625</v>
@@ -2561,11 +2561,34 @@
         <v>0.05034299406195264</v>
       </c>
       <c r="G74" s="4" t="n">
-        <v>-0.01219323518198445</v>
+        <v>-0.0166427189489744</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="6" t="n">
+        <v>46276</v>
+      </c>
+      <c r="B75" s="5" t="n">
+        <v>103370.0275112978</v>
+      </c>
+      <c r="C75" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D75" s="4" t="n">
+        <v>0.03370027511297824</v>
+      </c>
+      <c r="E75" s="5" t="n">
+        <v>14467.2998046875</v>
+      </c>
+      <c r="F75" s="4" t="n">
+        <v>0.05569905171391554</v>
+      </c>
+      <c r="G75" s="4" t="n">
+        <v>-0.0219987766009373</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G74"/>
+  <autoFilter ref="A1:G75"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
